--- a/DC-Colos.xlsx
+++ b/DC-Colos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F332"/>
+  <dimension ref="A1:F333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9095,44 +9095,44 @@
     <row r="274">
       <c r="A274" s="1" t="inlineStr">
         <is>
-          <t>ABQ</t>
+          <t>ACX</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, United States</t>
+          <t>Xingyi, China</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Albuquerque, NM</t>
+          <t>Xingyi</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="1" t="inlineStr">
         <is>
-          <t>ANC</t>
+          <t>ABQ</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Anchorage, AK, United States</t>
+          <t>Albuquerque, NM, United States</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Anchorage, AK</t>
+          <t>Albuquerque, NM</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -9159,12 +9159,12 @@
     <row r="276">
       <c r="A276" s="1" t="inlineStr">
         <is>
-          <t>IAD</t>
+          <t>ANC</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Ashburn, VA, United States</t>
+          <t>Anchorage, AK, United States</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Ashburn, VA</t>
+          <t>Anchorage, AK</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -9191,12 +9191,12 @@
     <row r="277">
       <c r="A277" s="1" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>IAD</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Atlanta, GA, United States</t>
+          <t>Ashburn, VA, United States</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Ashburn, VA</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -9223,12 +9223,12 @@
     <row r="278">
       <c r="A278" s="1" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Austin, TX, United States</t>
+          <t>Atlanta, GA, United States</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -9255,12 +9255,12 @@
     <row r="279">
       <c r="A279" s="1" t="inlineStr">
         <is>
-          <t>BGR</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Bangor, ME, United States</t>
+          <t>Austin, TX, United States</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Bangor, ME</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -9287,12 +9287,12 @@
     <row r="280">
       <c r="A280" s="1" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BGR</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Boston, MA, United States</t>
+          <t>Bangor, ME, United States</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -9302,7 +9302,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Bangor, ME</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -9319,12 +9319,12 @@
     <row r="281">
       <c r="A281" s="1" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Buffalo, NY, United States</t>
+          <t>Boston, MA, United States</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Buffalo, NY</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -9351,12 +9351,12 @@
     <row r="282">
       <c r="A282" s="1" t="inlineStr">
         <is>
-          <t>YYC</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Calgary, AB, Canada</t>
+          <t>Buffalo, NY, United States</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -9366,29 +9366,29 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Calgary, AB</t>
+          <t>Buffalo, NY</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="1" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>YYC</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Charlotte, NC, United States</t>
+          <t>Calgary, AB, Canada</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -9398,29 +9398,29 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Charlotte, NC</t>
+          <t>Calgary, AB</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="1" t="inlineStr">
         <is>
-          <t>ORD</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Chicago, IL, United States</t>
+          <t>Charlotte, NC, United States</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -9430,7 +9430,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Charlotte, NC</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -9447,12 +9447,12 @@
     <row r="285">
       <c r="A285" s="1" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ORD</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Cleveland, OH, United States</t>
+          <t>Chicago, IL, United States</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -9462,7 +9462,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Cleveland, OH</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -9479,12 +9479,12 @@
     <row r="286">
       <c r="A286" s="1" t="inlineStr">
         <is>
-          <t>CMH</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Columbus, OH, United States</t>
+          <t>Cleveland, OH, United States</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -9494,7 +9494,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Columbus, OH</t>
+          <t>Cleveland, OH</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -9511,12 +9511,12 @@
     <row r="287">
       <c r="A287" s="1" t="inlineStr">
         <is>
-          <t>DFW</t>
+          <t>CMH</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Dallas, TX, United States</t>
+          <t>Columbus, OH, United States</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Dallas, TX</t>
+          <t>Columbus, OH</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -9543,12 +9543,12 @@
     <row r="288">
       <c r="A288" s="1" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DFW</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Denver, CO, United States</t>
+          <t>Dallas, TX, United States</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -9558,7 +9558,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>Dallas, TX</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -9575,12 +9575,12 @@
     <row r="289">
       <c r="A289" s="1" t="inlineStr">
         <is>
-          <t>DTW</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Detroit, MI, United States</t>
+          <t>Denver, CO, United States</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Detroit, MI</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -9607,12 +9607,12 @@
     <row r="290">
       <c r="A290" s="1" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DTW</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Durham, NC, United States</t>
+          <t>Detroit, MI, United States</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Durham, NC</t>
+          <t>Detroit, MI</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -9639,12 +9639,12 @@
     <row r="291">
       <c r="A291" s="1" t="inlineStr">
         <is>
-          <t>GDL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Guadalajara, Mexico</t>
+          <t>Durham, NC, United States</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -9654,29 +9654,29 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Durham, NC</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="1" t="inlineStr">
         <is>
-          <t>YHZ</t>
+          <t>GDL</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Halifax, Canada</t>
+          <t>Guadalajara, Mexico</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -9686,29 +9686,29 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Halifax</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>MX</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="1" t="inlineStr">
         <is>
-          <t>HNL</t>
+          <t>YHZ</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Honolulu, HI, United States</t>
+          <t>Halifax, Canada</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -9718,29 +9718,29 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Honolulu, HI</t>
+          <t>Halifax</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="inlineStr">
         <is>
-          <t>IAH</t>
+          <t>HNL</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Houston, TX, United States</t>
+          <t>Honolulu, HI, United States</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -9750,7 +9750,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Houston, TX</t>
+          <t>Honolulu, HI</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -9767,12 +9767,12 @@
     <row r="295">
       <c r="A295" s="1" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>IAH</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, United States</t>
+          <t>Houston, TX, United States</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -9782,7 +9782,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Indianapolis, IN</t>
+          <t>Houston, TX</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -9799,12 +9799,12 @@
     <row r="296">
       <c r="A296" s="1" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, United States</t>
+          <t>Indianapolis, IN, United States</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Jacksonville, FL</t>
+          <t>Indianapolis, IN</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -9831,12 +9831,12 @@
     <row r="297">
       <c r="A297" s="1" t="inlineStr">
         <is>
-          <t>MCI</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Kansas City, MO, United States</t>
+          <t>Jacksonville, FL, United States</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -9846,7 +9846,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Kansas City, MO</t>
+          <t>Jacksonville, FL</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -9863,12 +9863,12 @@
     <row r="298">
       <c r="A298" s="1" t="inlineStr">
         <is>
-          <t>KIN</t>
+          <t>MCI</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Kingston, Jamaica</t>
+          <t>Kansas City, MO, United States</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -9878,29 +9878,29 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Kingston</t>
+          <t>Kansas City, MO</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Jamaica</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>JM</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="1" t="inlineStr">
         <is>
-          <t>LAS</t>
+          <t>KIN</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, United States</t>
+          <t>Kingston, Jamaica</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -9910,29 +9910,29 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Las Vegas, NV</t>
+          <t>Kingston</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Jamaica</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JM</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="1" t="inlineStr">
         <is>
-          <t>LAX</t>
+          <t>LAS</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, United States</t>
+          <t>Las Vegas, NV, United States</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
+          <t>Las Vegas, NV</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -9959,12 +9959,12 @@
     <row r="301">
       <c r="A301" s="1" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>LAX</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Memphis, TN, United States</t>
+          <t>Los Angeles, CA, United States</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Memphis, TN</t>
+          <t>Los Angeles, CA</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -9991,12 +9991,12 @@
     <row r="302">
       <c r="A302" s="1" t="inlineStr">
         <is>
-          <t>MEX</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Mexico City, Mexico</t>
+          <t>Memphis, TN, United States</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -10006,29 +10006,29 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Mexico City</t>
+          <t>Memphis, TN</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MEX</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Miami, FL, United States</t>
+          <t>Mexico City, Mexico</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -10038,29 +10038,29 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Miami, FL</t>
+          <t>Mexico City</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="inlineStr">
         <is>
-          <t>MSP</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, United States</t>
+          <t>Miami, FL, United States</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -10070,7 +10070,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Minneapolis, MN</t>
+          <t>Miami, FL</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -10087,12 +10087,12 @@
     <row r="305">
       <c r="A305" s="1" t="inlineStr">
         <is>
-          <t>YUL</t>
+          <t>MSP</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Montréal, QC, Canada</t>
+          <t>Minneapolis, MN, United States</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -10102,29 +10102,29 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Montréal, QC</t>
+          <t>Minneapolis, MN</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="1" t="inlineStr">
         <is>
-          <t>BNA</t>
+          <t>YUL</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Nashville, United States</t>
+          <t>Montréal, QC, Canada</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -10134,29 +10134,29 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Nashville</t>
+          <t>Montréal, QC</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="inlineStr">
         <is>
-          <t>EWR</t>
+          <t>BNA</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Newark, NJ, United States</t>
+          <t>Nashville, United States</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Newark, NJ</t>
+          <t>Nashville</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -10183,12 +10183,12 @@
     <row r="308">
       <c r="A308" s="1" t="inlineStr">
         <is>
-          <t>ORF</t>
+          <t>EWR</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Norfolk, VA, United States</t>
+          <t>Newark, NJ, United States</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -10198,7 +10198,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Norfolk, VA</t>
+          <t>Newark, NJ</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -10215,12 +10215,12 @@
     <row r="309">
       <c r="A309" s="1" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>ORF</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, United States</t>
+          <t>Norfolk, VA, United States</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK</t>
+          <t>Norfolk, VA</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -10247,12 +10247,12 @@
     <row r="310">
       <c r="A310" s="1" t="inlineStr">
         <is>
-          <t>OMA</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Omaha, NE, United States</t>
+          <t>Oklahoma City, OK, United States</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Omaha, NE</t>
+          <t>Oklahoma City, OK</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -10279,12 +10279,12 @@
     <row r="311">
       <c r="A311" s="1" t="inlineStr">
         <is>
-          <t>YOW</t>
+          <t>OMA</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Ottawa, Canada</t>
+          <t>Omaha, NE, United States</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -10294,29 +10294,29 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Ottawa</t>
+          <t>Omaha, NE</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="1" t="inlineStr">
         <is>
-          <t>PHL</t>
+          <t>YOW</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Philadelphia, United States</t>
+          <t>Ottawa, Canada</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -10326,29 +10326,29 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Ottawa</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="1" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>PHL</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, United States</t>
+          <t>Philadelphia, United States</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Phoenix, AZ</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -10375,12 +10375,12 @@
     <row r="314">
       <c r="A314" s="1" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, United States</t>
+          <t>Phoenix, AZ, United States</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -10390,7 +10390,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA</t>
+          <t>Phoenix, AZ</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -10407,12 +10407,12 @@
     <row r="315">
       <c r="A315" s="1" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Portland, OR, United States</t>
+          <t>Pittsburgh, PA, United States</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Portland, OR</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -10439,12 +10439,12 @@
     <row r="316">
       <c r="A316" s="1" t="inlineStr">
         <is>
-          <t>QRO</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Queretaro, MX, Mexico</t>
+          <t>Portland, OR, United States</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -10454,29 +10454,29 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Queretaro, MX</t>
+          <t>Portland, OR</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="1" t="inlineStr">
         <is>
-          <t>RIC</t>
+          <t>QRO</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Richmond, VA, United States</t>
+          <t>Queretaro, MX, Mexico</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -10486,29 +10486,29 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Richmond, VA</t>
+          <t>Queretaro, MX</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="1" t="inlineStr">
         <is>
-          <t>SMF</t>
+          <t>RIC</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Sacramento, CA, United States</t>
+          <t>Richmond, VA, United States</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -10518,7 +10518,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Sacramento, CA</t>
+          <t>Richmond, VA</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -10535,12 +10535,12 @@
     <row r="319">
       <c r="A319" s="1" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>SMF</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, United States</t>
+          <t>Sacramento, CA, United States</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -10550,7 +10550,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT</t>
+          <t>Sacramento, CA</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -10567,12 +10567,12 @@
     <row r="320">
       <c r="A320" s="1" t="inlineStr">
         <is>
-          <t>SAT</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>San Antonio, TX, United States</t>
+          <t>Salt Lake City, UT, United States</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -10582,7 +10582,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>San Antonio, TX</t>
+          <t>Salt Lake City, UT</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -10599,12 +10599,12 @@
     <row r="321">
       <c r="A321" s="1" t="inlineStr">
         <is>
-          <t>SAN</t>
+          <t>SAT</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>San Diego, CA, United States</t>
+          <t>San Antonio, TX, United States</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>San Diego, CA</t>
+          <t>San Antonio, TX</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -10631,12 +10631,12 @@
     <row r="322">
       <c r="A322" s="1" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>SAN</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>San Francisco, CA, United States</t>
+          <t>San Diego, CA, United States</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -10646,7 +10646,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>San Diego, CA</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -10663,12 +10663,12 @@
     <row r="323">
       <c r="A323" s="1" t="inlineStr">
         <is>
-          <t>SJC</t>
+          <t>SFO</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>San Jose, CA, United States</t>
+          <t>San Francisco, CA, United States</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -10678,7 +10678,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -10695,12 +10695,12 @@
     <row r="324">
       <c r="A324" s="1" t="inlineStr">
         <is>
-          <t>YXE</t>
+          <t>SJC</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Saskatoon, SK, Canada</t>
+          <t>San Jose, CA, United States</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -10710,29 +10710,29 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Saskatoon, SK</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>YXE</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Seattle, WA, United States</t>
+          <t>Saskatoon, SK, Canada</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -10742,29 +10742,29 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Saskatoon, SK</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="1" t="inlineStr">
         <is>
-          <t>FSD</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, United States</t>
+          <t>Seattle, WA, United States</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -10774,7 +10774,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -10791,12 +10791,12 @@
     <row r="327">
       <c r="A327" s="1" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>FSD</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>St. Louis, MO, United States</t>
+          <t>Sioux Falls, SD, United States</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -10806,7 +10806,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>St. Louis, MO</t>
+          <t>Sioux Falls, SD</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -10823,12 +10823,12 @@
     <row r="328">
       <c r="A328" s="1" t="inlineStr">
         <is>
-          <t>TLH</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, United States</t>
+          <t>St. Louis, MO, United States</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Tallahassee, FL</t>
+          <t>St. Louis, MO</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -10855,12 +10855,12 @@
     <row r="329">
       <c r="A329" s="1" t="inlineStr">
         <is>
-          <t>TPA</t>
+          <t>TLH</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Tampa, FL, United States</t>
+          <t>Tallahassee, FL, United States</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -10870,7 +10870,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Tampa, FL</t>
+          <t>Tallahassee, FL</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -10887,12 +10887,12 @@
     <row r="330">
       <c r="A330" s="1" t="inlineStr">
         <is>
-          <t>YYZ</t>
+          <t>TPA</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Toronto, ON, Canada</t>
+          <t>Tampa, FL, United States</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -10902,29 +10902,29 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Toronto, ON</t>
+          <t>Tampa, FL</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="1" t="inlineStr">
         <is>
-          <t>YVR</t>
+          <t>YYZ</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Vancouver, BC, Canada</t>
+          <t>Toronto, ON, Canada</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Vancouver, BC</t>
+          <t>Toronto, ON</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -10951,30 +10951,62 @@
     <row r="332">
       <c r="A332" s="1" t="inlineStr">
         <is>
+          <t>YVR</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Vancouver, BC, Canada</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Vancouver, BC</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="1" t="inlineStr">
+        <is>
           <t>YWG</t>
         </is>
       </c>
-      <c r="B332" t="inlineStr">
+      <c r="B333" t="inlineStr">
         <is>
           <t>Winnipeg, MB, Canada</t>
         </is>
       </c>
-      <c r="C332" t="inlineStr">
+      <c r="C333" t="inlineStr">
         <is>
           <t>North America</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr">
+      <c r="D333" t="inlineStr">
         <is>
           <t>Winnipeg, MB</t>
         </is>
       </c>
-      <c r="E332" t="inlineStr">
+      <c r="E333" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="F332" t="inlineStr">
+      <c r="F333" t="inlineStr">
         <is>
           <t>CA</t>
         </is>

--- a/DC-Colos.xlsx
+++ b/DC-Colos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F333"/>
+  <dimension ref="A1:F334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3359,44 +3359,44 @@
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>QWJ</t>
+          <t>WLG</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Americana, Brazil</t>
+          <t>Wellington, New Zealand</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Latin America &amp; the Caribbean</t>
+          <t>Oceania</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Americana</t>
+          <t>Wellington</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>NZ</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>QWJ</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Arica, Chile</t>
+          <t>Americana, Brazil</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3406,29 +3406,29 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Arica</t>
+          <t>Americana</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>ASU</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Asunción, Paraguay</t>
+          <t>Arica, Chile</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3438,29 +3438,29 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Asunción</t>
+          <t>Arica</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>PY</t>
+          <t>CL</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>ASU</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Belém, Brazil</t>
+          <t>Asunción, Paraguay</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3470,29 +3470,29 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Belém</t>
+          <t>Asunción</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>PY</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>CNF</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Belo Horizonte, Brazil</t>
+          <t>Belém, Brazil</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Belo Horizonte</t>
+          <t>Belém</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3519,12 +3519,12 @@
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>BNU</t>
+          <t>CNF</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Blumenau, Brazil</t>
+          <t>Belo Horizonte, Brazil</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Blumenau</t>
+          <t>Belo Horizonte</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -3551,12 +3551,12 @@
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>BOG</t>
+          <t>BNU</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Bogota, Colombia</t>
+          <t>Blumenau, Brazil</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3566,29 +3566,29 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Bogota</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>BSB</t>
+          <t>BOG</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Brasilia, Brazil</t>
+          <t>Bogota, Colombia</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3598,29 +3598,29 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Brasilia</t>
+          <t>Bogota</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CO</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>EZE</t>
+          <t>BSB</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Buenos Aires, Argentina</t>
+          <t>Brasilia, Brazil</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3630,29 +3630,29 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Brasilia</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>CFC</t>
+          <t>EZE</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Cacador, Brazil</t>
+          <t>Buenos Aires, Argentina</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3662,29 +3662,29 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Cacador</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>AR</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>VCP</t>
+          <t>CFC</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Campinas, Brazil</t>
+          <t>Cacador, Brazil</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Campinas</t>
+          <t>Cacador</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -3711,12 +3711,12 @@
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>VCP</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Córdoba, Argentina</t>
+          <t>Campinas, Brazil</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3726,29 +3726,29 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Campinas</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>CWB</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Curitiba, Brazil</t>
+          <t>Córdoba, Argentina</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3758,29 +3758,29 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Curitiba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>AR</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>FLN</t>
+          <t>CWB</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Florianopolis, Brazil</t>
+          <t>Curitiba, Brazil</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Florianopolis</t>
+          <t>Curitiba</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -3807,12 +3807,12 @@
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>FOR</t>
+          <t>FLN</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Fortaleza, Brazil</t>
+          <t>Florianopolis, Brazil</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Florianopolis</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -3839,12 +3839,12 @@
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>GEO</t>
+          <t>FOR</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Georgetown, Guyana</t>
+          <t>Fortaleza, Brazil</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3854,29 +3854,29 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Georgetown</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>GY</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>GYN</t>
+          <t>GEO</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Goiania, Brazil</t>
+          <t>Georgetown, Guyana</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3886,29 +3886,29 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Goiania</t>
+          <t>Georgetown</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>GY</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>GUA</t>
+          <t>GYN</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Guatemala City, Guatemala</t>
+          <t>Goiania, Brazil</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3918,29 +3918,29 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Guatemala City</t>
+          <t>Goiania</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Guatemala</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>GYE</t>
+          <t>GUA</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Guayaquil, Ecuador</t>
+          <t>Guatemala City, Guatemala</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3950,29 +3950,29 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Guayaquil</t>
+          <t>Guatemala City</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Guatemala</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>GT</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>JOI</t>
+          <t>GYE</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Joinville, Brazil</t>
+          <t>Guayaquil, Ecuador</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3982,29 +3982,29 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Joinville</t>
+          <t>Guayaquil</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>EC</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>JDO</t>
+          <t>JOI</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Juazeiro do Norte, Brazil</t>
+          <t>Joinville, Brazil</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Juazeiro do Norte</t>
+          <t>Joinville</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -4031,12 +4031,12 @@
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>JDO</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Lima, Peru</t>
+          <t>Juazeiro do Norte, Brazil</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4046,29 +4046,29 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Lima</t>
+          <t>Juazeiro do Norte</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>MAO</t>
+          <t>LIM</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Manaus, Brazil</t>
+          <t>Lima, Peru</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4078,29 +4078,29 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Manaus</t>
+          <t>Lima</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>PE</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>MDE</t>
+          <t>MAO</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Medellín, Colombia</t>
+          <t>Manaus, Brazil</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4110,29 +4110,29 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Manaus</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>NQN</t>
+          <t>MDE</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Neuquen, Argentina</t>
+          <t>Medellín, Colombia</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4142,29 +4142,29 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Neuquen</t>
+          <t>Medellín</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CO</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>PTY</t>
+          <t>NQN</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Panama City, Panama</t>
+          <t>Neuquen, Argentina</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4174,29 +4174,29 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Panama City</t>
+          <t>Neuquen</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>AR</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>PBM</t>
+          <t>PTY</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Paramaribo, Suriname</t>
+          <t>Panama City, Panama</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4206,29 +4206,29 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Paramaribo</t>
+          <t>Panama City</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Suriname</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>PA</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>PBM</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Porto Alegre, Brazil</t>
+          <t>Paramaribo, Suriname</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4238,29 +4238,29 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Porto Alegre</t>
+          <t>Paramaribo</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Suriname</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>SR</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>UIO</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Quito, Ecuador</t>
+          <t>Porto Alegre, Brazil</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4270,29 +4270,29 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Quito</t>
+          <t>Porto Alegre</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>REC</t>
+          <t>UIO</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Recife, Brazil</t>
+          <t>Quito, Ecuador</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4302,29 +4302,29 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Recife</t>
+          <t>Quito</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>EC</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>RAO</t>
+          <t>REC</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Ribeirao Preto, Brazil</t>
+          <t>Recife, Brazil</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Ribeirao Preto</t>
+          <t>Recife</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -4351,12 +4351,12 @@
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>GIG</t>
+          <t>RAO</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Rio de Janeiro, Brazil</t>
+          <t>Ribeirao Preto, Brazil</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Rio de Janeiro</t>
+          <t>Ribeirao Preto</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -4383,12 +4383,12 @@
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>SJO</t>
+          <t>GIG</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>San José, Costa Rica</t>
+          <t>Rio de Janeiro, Brazil</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4398,29 +4398,29 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>San José</t>
+          <t>Rio de Janeiro</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Costa Rica</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>SCL</t>
+          <t>SJO</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Santiago, Chile</t>
+          <t>San José, Costa Rica</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4430,29 +4430,29 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>San José</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Costa Rica</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>CR</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>SDQ</t>
+          <t>SCL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Santo Domingo, Dominican Republic</t>
+          <t>Santiago, Chile</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4462,29 +4462,29 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Santo Domingo</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>CL</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>SJP</t>
+          <t>SDQ</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>São José do Rio Preto, Brazil</t>
+          <t>Santo Domingo, Dominican Republic</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4494,29 +4494,29 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>São José do Rio Preto</t>
+          <t>Santo Domingo</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>DO</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>SJP</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>São José dos Campos, Brazil</t>
+          <t>São José do Rio Preto, Brazil</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>São José dos Campos</t>
+          <t>São José do Rio Preto</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -4543,12 +4543,12 @@
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>GRU</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>São Paulo, Brazil</t>
+          <t>São José dos Campos, Brazil</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>São José dos Campos</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -4575,12 +4575,12 @@
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>SOD</t>
+          <t>GRU</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Sorocaba, Brazil</t>
+          <t>São Paulo, Brazil</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Sorocaba</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -4607,12 +4607,12 @@
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>TGU</t>
+          <t>SOD</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Tegucigalpa, Honduras</t>
+          <t>Sorocaba, Brazil</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4622,29 +4622,29 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Tegucigalpa</t>
+          <t>Sorocaba</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Honduras</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>HN</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>TGU</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Timbo, Brazil</t>
+          <t>Tegucigalpa, Honduras</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4654,29 +4654,29 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Timbo</t>
+          <t>Tegucigalpa</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Honduras</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>HN</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>UDI</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Uberlandia, Brazil</t>
+          <t>Timbo, Brazil</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Uberlandia</t>
+          <t>Timbo</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -4703,12 +4703,12 @@
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>VIX</t>
+          <t>UDI</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Vitoria, Brazil</t>
+          <t>Uberlandia, Brazil</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Vitoria</t>
+          <t>Uberlandia</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -4735,12 +4735,12 @@
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>CAW</t>
+          <t>VIX</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Campos dos Goytacazes, Brazil</t>
+          <t>Vitoria, Brazil</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Campos dos Goytacazes</t>
+          <t>Vitoria</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -4767,12 +4767,12 @@
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>XAP</t>
+          <t>CAW</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Chapeco, Brazil</t>
+          <t>Campos dos Goytacazes, Brazil</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Chapeco</t>
+          <t>Campos dos Goytacazes</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -4799,12 +4799,12 @@
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>BGI</t>
+          <t>XAP</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Bridgetown, Barbados</t>
+          <t>Chapeco, Brazil</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4814,29 +4814,29 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Bridgetown</t>
+          <t>Chapeco</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Barbados</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>GND</t>
+          <t>BGI</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>St. George's, Grenada</t>
+          <t>Bridgetown, Barbados</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4846,29 +4846,29 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>St. George's</t>
+          <t>Bridgetown</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Grenada</t>
+          <t>Barbados</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>BB</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>STI</t>
+          <t>GND</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Santiago de los Caballeros, Dominican Republic</t>
+          <t>St. George's, Grenada</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4878,29 +4878,29 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Santiago de los Caballeros</t>
+          <t>St. George's</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Grenada</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>GD</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>LPB</t>
+          <t>STI</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>La Paz, Bolivia</t>
+          <t>Santiago de los Caballeros, Dominican Republic</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4910,29 +4910,29 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Santiago de los Caballeros</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>DO</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>SJU</t>
+          <t>LPB</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>San Juan, Puerto Rico</t>
+          <t>La Paz, Bolivia</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4942,29 +4942,29 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>San Juan</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Puerto Rico</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>BO</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>BAQ</t>
+          <t>SJU</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Barranquilla, Colombia</t>
+          <t>San Juan, Puerto Rico</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4974,29 +4974,29 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>San Juan</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Puerto Rico</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>PR</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>PMW</t>
+          <t>BAQ</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Palmas, Brazil</t>
+          <t>Barranquilla, Colombia</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5006,29 +5006,29 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Palmas</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CO</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>ARU</t>
+          <t>PMW</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Aracatuba, Brazil</t>
+          <t>Palmas, Brazil</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Aracatuba</t>
+          <t>Palmas</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -5055,12 +5055,12 @@
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>POS</t>
+          <t>ARU</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Port of Spain, Trinidad and Tobago</t>
+          <t>Aracatuba, Brazil</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5070,25 +5070,29 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Port of Spain</t>
+          <t>Aracatuba</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Trinidad and Tobago</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr"/>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>POS</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Salvador, Brazil</t>
+          <t>Port of Spain, Trinidad and Tobago</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5098,29 +5102,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Salvador</t>
+          <t>Port of Spain</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>BR</t>
-        </is>
-      </c>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Cuiaba, Brazil</t>
+          <t>Salvador, Brazil</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Cuiaba</t>
+          <t>Salvador</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -5147,12 +5147,12 @@
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>CLO</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Cali, Colombia</t>
+          <t>Cuiaba, Brazil</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5162,29 +5162,29 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Cuiaba</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>CLO</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>San Pedro Sula, Honduras</t>
+          <t>Cali, Colombia</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5194,29 +5194,29 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>San Pedro Sula</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Honduras</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>HN</t>
+          <t>CO</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>CCP</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Concepción, Chile</t>
+          <t>San Pedro Sula, Honduras</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5226,61 +5226,61 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>San Pedro Sula</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Honduras</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>HN</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>CCP</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Accra, Ghana</t>
+          <t>Concepción, Chile</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Latin America &amp; the Caribbean</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Accra</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>GH</t>
+          <t>CL</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>ALG</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Algiers, Algeria</t>
+          <t>Accra, Ghana</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5290,29 +5290,29 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Algiers</t>
+          <t>Accra</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>DZ</t>
+          <t>GH</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>AAE</t>
+          <t>ALG</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Annaba, Algeria</t>
+          <t>Algiers, Algeria</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Annaba</t>
+          <t>Algiers</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -5339,12 +5339,12 @@
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>TNR</t>
+          <t>AAE</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Antananarivo, Madagascar</t>
+          <t>Annaba, Algeria</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5354,29 +5354,29 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Antananarivo</t>
+          <t>Annaba</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>DZ</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>CPT</t>
+          <t>TNR</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Cape Town, South Africa</t>
+          <t>Antananarivo, Madagascar</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5386,29 +5386,29 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Cape Town</t>
+          <t>Antananarivo</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>MG</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>DKR</t>
+          <t>CPT</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Dakar, Senegal</t>
+          <t>Cape Town, South Africa</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5418,29 +5418,29 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Dakar</t>
+          <t>Cape Town</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>SN</t>
+          <t>ZA</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>DKR</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Dar es Salaam, Tanzania</t>
+          <t>Dakar, Senegal</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5450,29 +5450,29 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Dar es Salaam</t>
+          <t>Dakar</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>TZ</t>
+          <t>SN</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>JIB</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Djibouti, Djibouti</t>
+          <t>Dar es Salaam, Tanzania</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5482,29 +5482,29 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Djibouti</t>
+          <t>Dar es Salaam</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Djibouti</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>DJ</t>
+          <t>TZ</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>DUR</t>
+          <t>JIB</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Durban, South Africa</t>
+          <t>Djibouti, Djibouti</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5514,29 +5514,29 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Durban</t>
+          <t>Djibouti</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Djibouti</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>DJ</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>GBE</t>
+          <t>DUR</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Gaborone, Botswana</t>
+          <t>Durban, South Africa</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5546,29 +5546,29 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Gaborone</t>
+          <t>Durban</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>BW</t>
+          <t>ZA</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>HRE</t>
+          <t>GBE</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Harare, Zimbabwe</t>
+          <t>Gaborone, Botswana</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5578,29 +5578,29 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Harare</t>
+          <t>Gaborone</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>ZW</t>
+          <t>BW</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Johannesburg, South Africa</t>
+          <t>Harare, Zimbabwe</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5610,29 +5610,29 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Johannesburg</t>
+          <t>Harare</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>ZW</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>KGL</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Kigali, Rwanda</t>
+          <t>Johannesburg, South Africa</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5642,29 +5642,29 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Kigali</t>
+          <t>Johannesburg</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>ZA</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>LOS</t>
+          <t>KGL</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Lagos, Nigeria</t>
+          <t>Kigali, Rwanda</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -5674,29 +5674,29 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Lagos</t>
+          <t>Kigali</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>NG</t>
+          <t>RW</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>LOS</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Luanda, Angola</t>
+          <t>Lagos, Nigeria</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -5706,29 +5706,29 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Luanda</t>
+          <t>Lagos</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>AO</t>
+          <t>NG</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>MPM</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Maputo, Mozambique</t>
+          <t>Luanda, Angola</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -5738,29 +5738,29 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Maputo</t>
+          <t>Luanda</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>MZ</t>
+          <t>AO</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>MPM</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Mombasa, Kenya</t>
+          <t>Maputo, Mozambique</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5770,29 +5770,29 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Mombasa</t>
+          <t>Maputo</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>KE</t>
+          <t>MZ</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Nairobi, Kenya</t>
+          <t>Mombasa, Kenya</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Nairobi</t>
+          <t>Mombasa</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -5819,12 +5819,12 @@
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>ORN</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Oran, Algeria</t>
+          <t>Nairobi, Kenya</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5834,29 +5834,29 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Oran</t>
+          <t>Nairobi</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>DZ</t>
+          <t>KE</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>OUA</t>
+          <t>ORN</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Ouagadougou, Burkina Faso</t>
+          <t>Oran, Algeria</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5866,29 +5866,29 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Ouagadougou</t>
+          <t>Oran</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Burkina Faso</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>BF</t>
+          <t>DZ</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>MRU</t>
+          <t>OUA</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Port Louis, Mauritius</t>
+          <t>Ouagadougou, Burkina Faso</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5898,29 +5898,29 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Port Louis</t>
+          <t>Ouagadougou</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Mauritius</t>
+          <t>Burkina Faso</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>BF</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>TUN</t>
+          <t>MRU</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Tunis, Tunisia</t>
+          <t>Port Louis, Mauritius</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5930,29 +5930,29 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Tunis</t>
+          <t>Port Louis</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Mauritius</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>MU</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>FIH</t>
+          <t>TUN</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Kinshasa, DR Congo</t>
+          <t>Tunis, Tunisia</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5962,25 +5962,29 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Kinshasa</t>
+          <t>Tunis</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>DR Congo</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr"/>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>CAI</t>
+          <t>FIH</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Cairo, Egypt</t>
+          <t>Kinshasa, DR Congo</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5990,29 +5994,25 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Cairo</t>
+          <t>Kinshasa</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
+          <t>DR Congo</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t>WDH</t>
+          <t>CAI</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Windhoek, Namibia</t>
+          <t>Cairo, Egypt</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6022,29 +6022,29 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Windhoek</t>
+          <t>Cairo</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>EG</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t>ASK</t>
+          <t>WDH</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Yamoussoukro, Ivory Coast</t>
+          <t>Windhoek, Namibia</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6054,25 +6054,29 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Yamoussoukro</t>
+          <t>Windhoek</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr"/>
+          <t>Namibia</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t>ABJ</t>
+          <t>ASK</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Abidjan, Ivory Coast</t>
+          <t>Yamoussoukro, Ivory Coast</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6082,7 +6086,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Abidjan</t>
+          <t>Yamoussoukro</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -6095,12 +6099,12 @@
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>ABJ</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Kampala, Uganda</t>
+          <t>Abidjan, Ivory Coast</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6110,29 +6114,25 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Kampala</t>
+          <t>Abidjan</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Uganda</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
+          <t>Ivory Coast</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t>RUN</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Saint-Denis, Réunion</t>
+          <t>Kampala, Uganda</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6142,25 +6142,29 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Saint-Denis</t>
+          <t>Kampala</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Réunion</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr"/>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>LUN</t>
+          <t>RUN</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Lusaka, Zambia</t>
+          <t>Saint-Denis, Réunion</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6170,29 +6174,25 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Lusaka</t>
+          <t>Saint-Denis</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Zambia</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>ZM</t>
-        </is>
-      </c>
+          <t>Réunion</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t>ADD</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Addis Ababa, Ethiopia</t>
+          <t>Lusaka, Zambia</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6202,29 +6202,29 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Addis Ababa</t>
+          <t>Lusaka</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>ET</t>
+          <t>ZM</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t>LLW</t>
+          <t>ADD</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Lilongwe, Malawi</t>
+          <t>Addis Ababa, Ethiopia</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6234,29 +6234,29 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Lilongwe</t>
+          <t>Addis Ababa</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Malawi</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>MW</t>
+          <t>ET</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t>CZL</t>
+          <t>LLW</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Constantine, Algeria</t>
+          <t>Lilongwe, Malawi</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6266,61 +6266,61 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Constantine</t>
+          <t>Lilongwe</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>DZ</t>
+          <t>MW</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>CZL</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Ahmedabad, India</t>
+          <t>Constantine, Algeria</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>Constantine</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>DZ</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Almaty, Kazakhstan</t>
+          <t>Ahmedabad, India</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6330,29 +6330,29 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Almaty</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t>BLR</t>
+          <t>ALA</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Bangalore, India</t>
+          <t>Almaty, Kazakhstan</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6362,29 +6362,29 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Almaty</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>KZ</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>BKK</t>
+          <t>BLR</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Bangkok, Thailand</t>
+          <t>Bangalore, India</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6394,29 +6394,29 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>BWN</t>
+          <t>BKK</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Bandar Seri Begawan, Brunei</t>
+          <t>Bangkok, Thailand</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6426,29 +6426,29 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Bandar Seri Begawan</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Brunei</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>BN</t>
+          <t>TH</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>BWN</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Cebu, Philippines</t>
+          <t>Bandar Seri Begawan, Brunei</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6458,29 +6458,29 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Cebu</t>
+          <t>Bandar Seri Begawan</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Brunei</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>BN</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>IXC</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Chandigarh, India</t>
+          <t>Cebu, Philippines</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6490,29 +6490,29 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Chandigarh</t>
+          <t>Cebu</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>PH</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>CGD</t>
+          <t>IXC</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Changde, China</t>
+          <t>Chandigarh, India</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6522,29 +6522,29 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Changde</t>
+          <t>Chandigarh</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>CGD</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Chennai, India</t>
+          <t>Changde, China</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6554,29 +6554,29 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Changde</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>CGP</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Chittagong, Bangladesh</t>
+          <t>Chennai, India</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -6586,29 +6586,29 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Chittagong</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>BD</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t>CMB</t>
+          <t>CGP</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Colombo, Sri Lanka</t>
+          <t>Chittagong, Bangladesh</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -6618,29 +6618,29 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Colombo</t>
+          <t>Chittagong</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>LK</t>
+          <t>BD</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>CMB</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Dhaka, Bangladesh</t>
+          <t>Colombo, Sri Lanka</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -6650,29 +6650,29 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>Colombo</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>Sri Lanka</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>BD</t>
+          <t>LK</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>FUO</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Foshan, China</t>
+          <t>Dhaka, Bangladesh</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -6682,29 +6682,29 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Foshan</t>
+          <t>Dhaka</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>BD</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>FUK</t>
+          <t>FUO</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Fukuoka, Japan</t>
+          <t>Foshan, China</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -6714,29 +6714,29 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Fukuoka</t>
+          <t>Foshan</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>FOC</t>
+          <t>FUK</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Fuzhou, China</t>
+          <t>Fukuoka, Japan</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -6746,29 +6746,29 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Fuzhou</t>
+          <t>Fukuoka</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>JP</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>FOC</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Guangzhou, China</t>
+          <t>Fuzhou, China</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Guangzhou</t>
+          <t>Fuzhou</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -6795,12 +6795,12 @@
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t>HAK</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Chengmai, China</t>
+          <t>Guangzhou, China</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Chengmai</t>
+          <t>Guangzhou</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -6827,12 +6827,12 @@
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t>HAN</t>
+          <t>HAK</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Hanoi, Vietnam</t>
+          <t>Chengmai, China</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -6842,29 +6842,29 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Hanoi</t>
+          <t>Chengmai</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>VN</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
         <is>
-          <t>SJW</t>
+          <t>HAN</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Shijiazhuang, China</t>
+          <t>Hanoi, Vietnam</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -6874,29 +6874,29 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Shijiazhuang</t>
+          <t>Hanoi</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>VN</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
         <is>
-          <t>SGN</t>
+          <t>SJW</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City, Vietnam</t>
+          <t>Shijiazhuang, China</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -6906,29 +6906,29 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Shijiazhuang</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>VN</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t>HKG</t>
+          <t>SGN</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Ho Chi Minh City, Vietnam</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6936,19 +6936,31 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
-      <c r="E205" t="inlineStr"/>
-      <c r="F205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Ho Chi Minh City</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>VN</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="inlineStr">
         <is>
-          <t>HYD</t>
+          <t>HKG</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Hyderabad, India</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6956,31 +6968,19 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>Hyderabad</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
         <is>
-          <t>ISB</t>
+          <t>HYD</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Islamabad, Pakistan</t>
+          <t>Hyderabad, India</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -6990,29 +6990,29 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Islamabad</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="inlineStr">
         <is>
-          <t>CGK</t>
+          <t>ISB</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Jakarta, Indonesia</t>
+          <t>Islamabad, Pakistan</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7022,29 +7022,29 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Jakarta</t>
+          <t>Islamabad</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>PK</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="inlineStr">
         <is>
-          <t>TNA</t>
+          <t>CGK</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Zibo, China</t>
+          <t>Jakarta, Indonesia</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7054,29 +7054,29 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Zibo</t>
+          <t>Jakarta</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="inlineStr">
         <is>
-          <t>JHB</t>
+          <t>TNA</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Johor Bahru, Malaysia</t>
+          <t>Zibo, China</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7086,29 +7086,29 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Johor Bahru</t>
+          <t>Zibo</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
         <is>
-          <t>KNU</t>
+          <t>JHB</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Kanpur, India</t>
+          <t>Johor Bahru, Malaysia</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -7118,29 +7118,29 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Kanpur</t>
+          <t>Johor Bahru</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>MY</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
         <is>
-          <t>KHH</t>
+          <t>KNU</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Kaohsiung City, Taiwan</t>
+          <t>Kanpur, India</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -7150,29 +7150,29 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Kaohsiung City</t>
+          <t>Kanpur</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="inlineStr">
         <is>
-          <t>KHI</t>
+          <t>KHH</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Karachi, Pakistan</t>
+          <t>Kaohsiung City, Taiwan</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -7182,29 +7182,29 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Karachi</t>
+          <t>Kaohsiung City</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>TW</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="inlineStr">
         <is>
-          <t>KTM</t>
+          <t>KHI</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Kathmandu, Nepal</t>
+          <t>Karachi, Pakistan</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -7214,29 +7214,29 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Kathmandu</t>
+          <t>Karachi</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>PK</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="inlineStr">
         <is>
-          <t>CCU</t>
+          <t>KTM</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Kolkata, India</t>
+          <t>Kathmandu, Nepal</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -7246,29 +7246,29 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Kathmandu</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NP</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="inlineStr">
         <is>
-          <t>KJA</t>
+          <t>CCU</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Krasnoyarsk, Russia</t>
+          <t>Kolkata, India</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -7278,29 +7278,29 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Krasnoyarsk</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>RU</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
         <is>
-          <t>KUL</t>
+          <t>KJA</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Kuala Lumpur, Malaysia</t>
+          <t>Krasnoyarsk, Russia</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -7310,29 +7310,29 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Krasnoyarsk</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>RU</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="inlineStr">
         <is>
-          <t>PKX</t>
+          <t>KUL</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Langfang, China</t>
+          <t>Kuala Lumpur, Malaysia</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -7342,29 +7342,29 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Langfang</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MY</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="inlineStr">
         <is>
-          <t>MFM</t>
+          <t>PKX</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Macau</t>
+          <t>Langfang, China</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -7372,19 +7372,31 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
-      <c r="E219" t="inlineStr"/>
-      <c r="F219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Langfang</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
         <is>
-          <t>MLE</t>
+          <t>MFM</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Male, Maldives</t>
+          <t>Macau</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -7392,31 +7404,19 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>Maldives</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>MV</t>
-        </is>
-      </c>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="1" t="inlineStr">
         <is>
-          <t>MNL</t>
+          <t>MLE</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Manila, Philippines</t>
+          <t>Male, Maldives</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -7426,29 +7426,29 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Manila</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Maldives</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>MV</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="inlineStr">
         <is>
-          <t>BOM</t>
+          <t>MNL</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Mumbai, India</t>
+          <t>Manila, Philippines</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -7458,29 +7458,29 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Manila</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>PH</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="inlineStr">
         <is>
-          <t>NAG</t>
+          <t>BOM</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Nagpur, India</t>
+          <t>Mumbai, India</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Nagpur</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -7507,12 +7507,12 @@
     <row r="224">
       <c r="A224" s="1" t="inlineStr">
         <is>
-          <t>OKA</t>
+          <t>NAG</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Naha, Japan</t>
+          <t>Nagpur, India</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -7522,29 +7522,29 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Naha</t>
+          <t>Nagpur</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="inlineStr">
         <is>
-          <t>DEL</t>
+          <t>OKA</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>New Delhi, India</t>
+          <t>Naha, Japan</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -7554,29 +7554,29 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>Naha</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>JP</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="inlineStr">
         <is>
-          <t>KIX</t>
+          <t>DEL</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Osaka, Japan</t>
+          <t>New Delhi, India</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -7586,29 +7586,29 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Osaka</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="inlineStr">
         <is>
-          <t>PAT</t>
+          <t>KIX</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Patna, India</t>
+          <t>Osaka, Japan</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -7618,29 +7618,29 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Patna</t>
+          <t>Osaka</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>JP</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="inlineStr">
         <is>
-          <t>PNH</t>
+          <t>PAT</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Phnom Penh, Cambodia</t>
+          <t>Patna, India</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -7650,29 +7650,29 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Phnom Penh</t>
+          <t>Patna</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Cambodia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>KH</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="inlineStr">
         <is>
-          <t>TAO</t>
+          <t>PNH</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Qingdao, China</t>
+          <t>Phnom Penh, Cambodia</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -7682,29 +7682,29 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Qingdao</t>
+          <t>Phnom Penh</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>KH</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="inlineStr">
         <is>
-          <t>ICN</t>
+          <t>TAO</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Seoul, South Korea</t>
+          <t>Qingdao, China</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -7714,29 +7714,29 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Seoul</t>
+          <t>Qingdao</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="inlineStr">
         <is>
-          <t>SHA</t>
+          <t>ICN</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Seoul, South Korea</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -7746,29 +7746,29 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Shanghai</t>
+          <t>Seoul</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>KR</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="inlineStr">
         <is>
-          <t>SIN</t>
+          <t>SHA</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Singapore, Singapore</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -7778,29 +7778,29 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="inlineStr">
         <is>
-          <t>URT</t>
+          <t>SIN</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Surat Thani, Thailand</t>
+          <t>Singapore, Singapore</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -7810,29 +7810,29 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Surat Thani</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>SG</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="inlineStr">
         <is>
-          <t>TPE</t>
+          <t>URT</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Taipei</t>
+          <t>Surat Thani, Thailand</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -7840,19 +7840,31 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
-      <c r="E234" t="inlineStr"/>
-      <c r="F234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Surat Thani</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="inlineStr">
         <is>
-          <t>NRT</t>
+          <t>TPE</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Tokyo, Japan</t>
+          <t>Taipei</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -7860,31 +7872,19 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>Tokyo</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="1" t="inlineStr">
         <is>
-          <t>ULN</t>
+          <t>NRT</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Ulaanbaatar, Mongolia</t>
+          <t>Tokyo, Japan</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -7894,29 +7894,29 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Ulaanbaatar</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Mongolia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>MN</t>
+          <t>JP</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="inlineStr">
         <is>
-          <t>VTE</t>
+          <t>ULN</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Vientiane, Laos</t>
+          <t>Ulaanbaatar, Mongolia</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -7926,29 +7926,29 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Vientiane</t>
+          <t>Ulaanbaatar</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Laos</t>
+          <t>Mongolia</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>MN</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="inlineStr">
         <is>
-          <t>KHN</t>
+          <t>VTE</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Nanchang, China</t>
+          <t>Vientiane, Laos</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -7958,29 +7958,29 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Nanchang</t>
+          <t>Vientiane</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Laos</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>LA</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>KHN</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Yerevan, Armenia</t>
+          <t>Nanchang, China</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -7990,29 +7990,29 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Yerevan</t>
+          <t>Nanchang</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="inlineStr">
         <is>
-          <t>JOG</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Yogyakarta, Indonesia</t>
+          <t>Yerevan, Armenia</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -8022,29 +8022,29 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Yogyakarta</t>
+          <t>Yerevan</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>AM</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="inlineStr">
         <is>
-          <t>CGY</t>
+          <t>JOG</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Cagayan de Oro, Philippines</t>
+          <t>Yogyakarta, Indonesia</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -8054,29 +8054,29 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Cagayan de Oro</t>
+          <t>Yogyakarta</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="inlineStr">
         <is>
-          <t>COK</t>
+          <t>CGY</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Kochi, India</t>
+          <t>Cagayan de Oro, Philippines</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -8086,29 +8086,29 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Cagayan de Oro</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>PH</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="inlineStr">
         <is>
-          <t>DPS</t>
+          <t>COK</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Denpasar, Indonesia</t>
+          <t>Kochi, India</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -8118,29 +8118,29 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Denpasar</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="inlineStr">
         <is>
-          <t>CNN</t>
+          <t>DPS</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Kannur, India</t>
+          <t>Denpasar, Indonesia</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -8150,29 +8150,29 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Kannur</t>
+          <t>Denpasar</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="inlineStr">
         <is>
-          <t>SZX</t>
+          <t>CNN</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Shenzhen, China</t>
+          <t>Kannur, India</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -8182,29 +8182,29 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Shenzhen</t>
+          <t>Kannur</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="inlineStr">
         <is>
-          <t>KWE</t>
+          <t>SZX</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Guiyang, China</t>
+          <t>Shenzhen, China</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -8214,7 +8214,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Guiyang</t>
+          <t>Shenzhen</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -8231,12 +8231,12 @@
     <row r="247">
       <c r="A247" s="1" t="inlineStr">
         <is>
-          <t>HGH</t>
+          <t>KWE</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Shaoxing, China</t>
+          <t>Guiyang, China</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Shaoxing</t>
+          <t>Guiyang</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -8263,12 +8263,12 @@
     <row r="248">
       <c r="A248" s="1" t="inlineStr">
         <is>
-          <t>CZX</t>
+          <t>HGH</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Changzhou, China</t>
+          <t>Shaoxing, China</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Changzhou</t>
+          <t>Shaoxing</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -8295,12 +8295,12 @@
     <row r="249">
       <c r="A249" s="1" t="inlineStr">
         <is>
-          <t>KMG</t>
+          <t>CZX</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Kunming, China</t>
+          <t>Changzhou, China</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Kunming</t>
+          <t>Changzhou</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -8327,12 +8327,12 @@
     <row r="250">
       <c r="A250" s="1" t="inlineStr">
         <is>
-          <t>CNX</t>
+          <t>KMG</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Chiang Mai, Thailand</t>
+          <t>Kunming, China</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -8342,29 +8342,29 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Chiang Mai</t>
+          <t>Kunming</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="inlineStr">
         <is>
-          <t>CGO</t>
+          <t>CNX</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Zhengzhou, China</t>
+          <t>Chiang Mai, Thailand</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -8374,29 +8374,29 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Zhengzhou</t>
+          <t>Chiang Mai</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>TH</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="inlineStr">
         <is>
-          <t>TYN</t>
+          <t>CGO</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Yangquan, China</t>
+          <t>Zhengzhou, China</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Yangquan</t>
+          <t>Zhengzhou</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -8423,12 +8423,12 @@
     <row r="253">
       <c r="A253" s="1" t="inlineStr">
         <is>
-          <t>CSX</t>
+          <t>TYN</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Changsha, China</t>
+          <t>Yangquan, China</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -8438,7 +8438,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Changsha</t>
+          <t>Yangquan</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -8455,12 +8455,12 @@
     <row r="254">
       <c r="A254" s="1" t="inlineStr">
         <is>
-          <t>DLC</t>
+          <t>CSX</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Dalian, China</t>
+          <t>Changsha, China</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -8470,7 +8470,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Dalian</t>
+          <t>Changsha</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -8487,12 +8487,12 @@
     <row r="255">
       <c r="A255" s="1" t="inlineStr">
         <is>
-          <t>BHY</t>
+          <t>DLC</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Beihai, China</t>
+          <t>Dalian, China</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Beihai</t>
+          <t>Dalian</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -8519,12 +8519,12 @@
     <row r="256">
       <c r="A256" s="1" t="inlineStr">
         <is>
-          <t>CKG</t>
+          <t>BHY</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Chongqing, China</t>
+          <t>Beihai, China</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Chongqing</t>
+          <t>Beihai</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -8551,12 +8551,12 @@
     <row r="257">
       <c r="A257" s="1" t="inlineStr">
         <is>
-          <t>XFN</t>
+          <t>CKG</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Xiangyang, China</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -8566,7 +8566,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Xiangyang</t>
+          <t>Chongqing</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -8583,12 +8583,12 @@
     <row r="258">
       <c r="A258" s="1" t="inlineStr">
         <is>
-          <t>DAD</t>
+          <t>XFN</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Da Nang, Vietnam</t>
+          <t>Xiangyang, China</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -8598,29 +8598,29 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Xiangyang</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>VN</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="inlineStr">
         <is>
-          <t>JXG</t>
+          <t>DAD</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Jiaxing, China</t>
+          <t>Da Nang, Vietnam</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -8630,29 +8630,29 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Jiaxing</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>VN</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="inlineStr">
         <is>
-          <t>CRK</t>
+          <t>JXG</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Tarlac City, Philippines</t>
+          <t>Jiaxing, China</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -8662,29 +8662,29 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Tarlac City</t>
+          <t>Jiaxing</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="inlineStr">
         <is>
-          <t>PBH</t>
+          <t>CRK</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Thimphu, Bhutan</t>
+          <t>Tarlac City, Philippines</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -8694,29 +8694,29 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Thimphu</t>
+          <t>Tarlac City</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Bhutan</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>PH</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="inlineStr">
         <is>
-          <t>XIY</t>
+          <t>PBH</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Baoji, China</t>
+          <t>Thimphu, Bhutan</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -8726,29 +8726,29 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Baoji</t>
+          <t>Thimphu</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Bhutan</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>BT</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="inlineStr">
         <is>
-          <t>NQZ</t>
+          <t>XIY</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Astana, Kazakhstan</t>
+          <t>Baoji, China</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -8758,29 +8758,29 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Baoji</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="inlineStr">
         <is>
-          <t>KCH</t>
+          <t>NQZ</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Kuching, Malaysia</t>
+          <t>Astana, Kazakhstan</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -8790,29 +8790,29 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Kuching</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>KZ</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="inlineStr">
         <is>
-          <t>AKX</t>
+          <t>KCH</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Aktobe, Kazakhstan</t>
+          <t>Kuching, Malaysia</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -8822,29 +8822,29 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Kuching</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>MY</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="1" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>AKX</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Tongren, China</t>
+          <t>Aktobe, Kazakhstan</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -8854,29 +8854,29 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Tongren</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>KZ</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Taizhou, China</t>
+          <t>Tongren, China</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -8886,7 +8886,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Taizhou</t>
+          <t>Tongren</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -8903,12 +8903,12 @@
     <row r="268">
       <c r="A268" s="1" t="inlineStr">
         <is>
-          <t>FRU</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Bishkek, Kyrgyzstan</t>
+          <t>Taizhou, China</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -8918,29 +8918,29 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Bishkek</t>
+          <t>Taizhou</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Kyrgyzstan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="inlineStr">
         <is>
-          <t>MLG</t>
+          <t>FRU</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Malang, Indonesia</t>
+          <t>Bishkek, Kyrgyzstan</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -8950,29 +8950,29 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Malang</t>
+          <t>Bishkek</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Kyrgyzstan</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>KG</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="inlineStr">
         <is>
-          <t>LHE</t>
+          <t>MLG</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Lahore, Pakistan</t>
+          <t>Malang, Indonesia</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -8982,29 +8982,29 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Lahore</t>
+          <t>Malang</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="inlineStr">
         <is>
-          <t>CTU</t>
+          <t>LHE</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Chengdu, China</t>
+          <t>Lahore, Pakistan</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -9014,29 +9014,29 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Chengdu</t>
+          <t>Lahore</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>PK</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="inlineStr">
         <is>
-          <t>AGR</t>
+          <t>CTU</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Agra, India</t>
+          <t>Chengdu, China</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -9046,29 +9046,29 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Agra</t>
+          <t>Chengdu</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="inlineStr">
         <is>
-          <t>CJB</t>
+          <t>AGR</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Coimbatore, India</t>
+          <t>Agra, India</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Coimbatore</t>
+          <t>Agra</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -9095,12 +9095,12 @@
     <row r="274">
       <c r="A274" s="1" t="inlineStr">
         <is>
-          <t>ACX</t>
+          <t>CJB</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Xingyi, China</t>
+          <t>Coimbatore, India</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -9110,61 +9110,61 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Xingyi</t>
+          <t>Coimbatore</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="1" t="inlineStr">
         <is>
-          <t>ABQ</t>
+          <t>ACX</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, United States</t>
+          <t>Xingyi, China</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Albuquerque, NM</t>
+          <t>Xingyi</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="1" t="inlineStr">
         <is>
-          <t>ANC</t>
+          <t>ABQ</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Anchorage, AK, United States</t>
+          <t>Albuquerque, NM, United States</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Anchorage, AK</t>
+          <t>Albuquerque, NM</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -9191,12 +9191,12 @@
     <row r="277">
       <c r="A277" s="1" t="inlineStr">
         <is>
-          <t>IAD</t>
+          <t>ANC</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Ashburn, VA, United States</t>
+          <t>Anchorage, AK, United States</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Ashburn, VA</t>
+          <t>Anchorage, AK</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -9223,12 +9223,12 @@
     <row r="278">
       <c r="A278" s="1" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>IAD</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Atlanta, GA, United States</t>
+          <t>Ashburn, VA, United States</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Ashburn, VA</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -9255,12 +9255,12 @@
     <row r="279">
       <c r="A279" s="1" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Austin, TX, United States</t>
+          <t>Atlanta, GA, United States</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -9287,12 +9287,12 @@
     <row r="280">
       <c r="A280" s="1" t="inlineStr">
         <is>
-          <t>BGR</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Bangor, ME, United States</t>
+          <t>Austin, TX, United States</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -9302,7 +9302,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Bangor, ME</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -9319,12 +9319,12 @@
     <row r="281">
       <c r="A281" s="1" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BGR</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Boston, MA, United States</t>
+          <t>Bangor, ME, United States</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Bangor, ME</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -9351,12 +9351,12 @@
     <row r="282">
       <c r="A282" s="1" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Buffalo, NY, United States</t>
+          <t>Boston, MA, United States</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Buffalo, NY</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -9383,12 +9383,12 @@
     <row r="283">
       <c r="A283" s="1" t="inlineStr">
         <is>
-          <t>YYC</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Calgary, AB, Canada</t>
+          <t>Buffalo, NY, United States</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -9398,29 +9398,29 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Calgary, AB</t>
+          <t>Buffalo, NY</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="1" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>YYC</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Charlotte, NC, United States</t>
+          <t>Calgary, AB, Canada</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -9430,29 +9430,29 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Charlotte, NC</t>
+          <t>Calgary, AB</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="1" t="inlineStr">
         <is>
-          <t>ORD</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Chicago, IL, United States</t>
+          <t>Charlotte, NC, United States</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -9462,7 +9462,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Charlotte, NC</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -9479,12 +9479,12 @@
     <row r="286">
       <c r="A286" s="1" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ORD</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Cleveland, OH, United States</t>
+          <t>Chicago, IL, United States</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -9494,7 +9494,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Cleveland, OH</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -9511,12 +9511,12 @@
     <row r="287">
       <c r="A287" s="1" t="inlineStr">
         <is>
-          <t>CMH</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Columbus, OH, United States</t>
+          <t>Cleveland, OH, United States</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Columbus, OH</t>
+          <t>Cleveland, OH</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -9543,12 +9543,12 @@
     <row r="288">
       <c r="A288" s="1" t="inlineStr">
         <is>
-          <t>DFW</t>
+          <t>CMH</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Dallas, TX, United States</t>
+          <t>Columbus, OH, United States</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -9558,7 +9558,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Dallas, TX</t>
+          <t>Columbus, OH</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -9575,12 +9575,12 @@
     <row r="289">
       <c r="A289" s="1" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DFW</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Denver, CO, United States</t>
+          <t>Dallas, TX, United States</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>Dallas, TX</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -9607,12 +9607,12 @@
     <row r="290">
       <c r="A290" s="1" t="inlineStr">
         <is>
-          <t>DTW</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Detroit, MI, United States</t>
+          <t>Denver, CO, United States</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Detroit, MI</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -9639,12 +9639,12 @@
     <row r="291">
       <c r="A291" s="1" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DTW</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Durham, NC, United States</t>
+          <t>Detroit, MI, United States</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -9654,7 +9654,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Durham, NC</t>
+          <t>Detroit, MI</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -9671,12 +9671,12 @@
     <row r="292">
       <c r="A292" s="1" t="inlineStr">
         <is>
-          <t>GDL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Guadalajara, Mexico</t>
+          <t>Durham, NC, United States</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -9686,29 +9686,29 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Durham, NC</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="1" t="inlineStr">
         <is>
-          <t>YHZ</t>
+          <t>GDL</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Halifax, Canada</t>
+          <t>Guadalajara, Mexico</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -9718,29 +9718,29 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Halifax</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>MX</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="inlineStr">
         <is>
-          <t>HNL</t>
+          <t>YHZ</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Honolulu, HI, United States</t>
+          <t>Halifax, Canada</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -9750,29 +9750,29 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Honolulu, HI</t>
+          <t>Halifax</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="inlineStr">
         <is>
-          <t>IAH</t>
+          <t>HNL</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Houston, TX, United States</t>
+          <t>Honolulu, HI, United States</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -9782,7 +9782,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Houston, TX</t>
+          <t>Honolulu, HI</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -9799,12 +9799,12 @@
     <row r="296">
       <c r="A296" s="1" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>IAH</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, United States</t>
+          <t>Houston, TX, United States</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Indianapolis, IN</t>
+          <t>Houston, TX</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -9831,12 +9831,12 @@
     <row r="297">
       <c r="A297" s="1" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, United States</t>
+          <t>Indianapolis, IN, United States</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -9846,7 +9846,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Jacksonville, FL</t>
+          <t>Indianapolis, IN</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -9863,12 +9863,12 @@
     <row r="298">
       <c r="A298" s="1" t="inlineStr">
         <is>
-          <t>MCI</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Kansas City, MO, United States</t>
+          <t>Jacksonville, FL, United States</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -9878,7 +9878,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Kansas City, MO</t>
+          <t>Jacksonville, FL</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -9895,12 +9895,12 @@
     <row r="299">
       <c r="A299" s="1" t="inlineStr">
         <is>
-          <t>KIN</t>
+          <t>MCI</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Kingston, Jamaica</t>
+          <t>Kansas City, MO, United States</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -9910,29 +9910,29 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Kingston</t>
+          <t>Kansas City, MO</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Jamaica</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>JM</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="1" t="inlineStr">
         <is>
-          <t>LAS</t>
+          <t>KIN</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, United States</t>
+          <t>Kingston, Jamaica</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -9942,29 +9942,29 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Las Vegas, NV</t>
+          <t>Kingston</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Jamaica</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JM</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="1" t="inlineStr">
         <is>
-          <t>LAX</t>
+          <t>LAS</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, United States</t>
+          <t>Las Vegas, NV, United States</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
+          <t>Las Vegas, NV</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -9991,12 +9991,12 @@
     <row r="302">
       <c r="A302" s="1" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>LAX</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Memphis, TN, United States</t>
+          <t>Los Angeles, CA, United States</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -10006,7 +10006,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Memphis, TN</t>
+          <t>Los Angeles, CA</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -10023,12 +10023,12 @@
     <row r="303">
       <c r="A303" s="1" t="inlineStr">
         <is>
-          <t>MEX</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Mexico City, Mexico</t>
+          <t>Memphis, TN, United States</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -10038,29 +10038,29 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Mexico City</t>
+          <t>Memphis, TN</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MEX</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Miami, FL, United States</t>
+          <t>Mexico City, Mexico</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -10070,29 +10070,29 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Miami, FL</t>
+          <t>Mexico City</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="inlineStr">
         <is>
-          <t>MSP</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, United States</t>
+          <t>Miami, FL, United States</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Minneapolis, MN</t>
+          <t>Miami, FL</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -10119,12 +10119,12 @@
     <row r="306">
       <c r="A306" s="1" t="inlineStr">
         <is>
-          <t>YUL</t>
+          <t>MSP</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Montréal, QC, Canada</t>
+          <t>Minneapolis, MN, United States</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -10134,29 +10134,29 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Montréal, QC</t>
+          <t>Minneapolis, MN</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="inlineStr">
         <is>
-          <t>BNA</t>
+          <t>YUL</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Nashville, United States</t>
+          <t>Montréal, QC, Canada</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -10166,29 +10166,29 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Nashville</t>
+          <t>Montréal, QC</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="inlineStr">
         <is>
-          <t>EWR</t>
+          <t>BNA</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Newark, NJ, United States</t>
+          <t>Nashville, United States</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -10198,7 +10198,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Newark, NJ</t>
+          <t>Nashville</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -10215,12 +10215,12 @@
     <row r="309">
       <c r="A309" s="1" t="inlineStr">
         <is>
-          <t>ORF</t>
+          <t>EWR</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Norfolk, VA, United States</t>
+          <t>Newark, NJ, United States</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Norfolk, VA</t>
+          <t>Newark, NJ</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -10247,12 +10247,12 @@
     <row r="310">
       <c r="A310" s="1" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>ORF</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, United States</t>
+          <t>Norfolk, VA, United States</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK</t>
+          <t>Norfolk, VA</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -10279,12 +10279,12 @@
     <row r="311">
       <c r="A311" s="1" t="inlineStr">
         <is>
-          <t>OMA</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Omaha, NE, United States</t>
+          <t>Oklahoma City, OK, United States</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -10294,7 +10294,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Omaha, NE</t>
+          <t>Oklahoma City, OK</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -10311,12 +10311,12 @@
     <row r="312">
       <c r="A312" s="1" t="inlineStr">
         <is>
-          <t>YOW</t>
+          <t>OMA</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Ottawa, Canada</t>
+          <t>Omaha, NE, United States</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -10326,29 +10326,29 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Ottawa</t>
+          <t>Omaha, NE</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="1" t="inlineStr">
         <is>
-          <t>PHL</t>
+          <t>YOW</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Philadelphia, United States</t>
+          <t>Ottawa, Canada</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -10358,29 +10358,29 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Ottawa</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="1" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>PHL</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, United States</t>
+          <t>Philadelphia, United States</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -10390,7 +10390,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Phoenix, AZ</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -10407,12 +10407,12 @@
     <row r="315">
       <c r="A315" s="1" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, United States</t>
+          <t>Phoenix, AZ, United States</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA</t>
+          <t>Phoenix, AZ</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -10439,12 +10439,12 @@
     <row r="316">
       <c r="A316" s="1" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Portland, OR, United States</t>
+          <t>Pittsburgh, PA, United States</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -10454,7 +10454,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Portland, OR</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -10471,12 +10471,12 @@
     <row r="317">
       <c r="A317" s="1" t="inlineStr">
         <is>
-          <t>QRO</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Queretaro, MX, Mexico</t>
+          <t>Portland, OR, United States</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -10486,29 +10486,29 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Queretaro, MX</t>
+          <t>Portland, OR</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="1" t="inlineStr">
         <is>
-          <t>RIC</t>
+          <t>QRO</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Richmond, VA, United States</t>
+          <t>Queretaro, MX, Mexico</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -10518,29 +10518,29 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Richmond, VA</t>
+          <t>Queretaro, MX</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="1" t="inlineStr">
         <is>
-          <t>SMF</t>
+          <t>RIC</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Sacramento, CA, United States</t>
+          <t>Richmond, VA, United States</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -10550,7 +10550,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Sacramento, CA</t>
+          <t>Richmond, VA</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -10567,12 +10567,12 @@
     <row r="320">
       <c r="A320" s="1" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>SMF</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, United States</t>
+          <t>Sacramento, CA, United States</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -10582,7 +10582,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT</t>
+          <t>Sacramento, CA</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -10599,12 +10599,12 @@
     <row r="321">
       <c r="A321" s="1" t="inlineStr">
         <is>
-          <t>SAT</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>San Antonio, TX, United States</t>
+          <t>Salt Lake City, UT, United States</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>San Antonio, TX</t>
+          <t>Salt Lake City, UT</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -10631,12 +10631,12 @@
     <row r="322">
       <c r="A322" s="1" t="inlineStr">
         <is>
-          <t>SAN</t>
+          <t>SAT</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>San Diego, CA, United States</t>
+          <t>San Antonio, TX, United States</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -10646,7 +10646,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>San Diego, CA</t>
+          <t>San Antonio, TX</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -10663,12 +10663,12 @@
     <row r="323">
       <c r="A323" s="1" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>SAN</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>San Francisco, CA, United States</t>
+          <t>San Diego, CA, United States</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -10678,7 +10678,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>San Diego, CA</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -10695,12 +10695,12 @@
     <row r="324">
       <c r="A324" s="1" t="inlineStr">
         <is>
-          <t>SJC</t>
+          <t>SFO</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>San Jose, CA, United States</t>
+          <t>San Francisco, CA, United States</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -10710,7 +10710,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -10727,12 +10727,12 @@
     <row r="325">
       <c r="A325" s="1" t="inlineStr">
         <is>
-          <t>YXE</t>
+          <t>SJC</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Saskatoon, SK, Canada</t>
+          <t>San Jose, CA, United States</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -10742,29 +10742,29 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Saskatoon, SK</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="1" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>YXE</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Seattle, WA, United States</t>
+          <t>Saskatoon, SK, Canada</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -10774,29 +10774,29 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Saskatoon, SK</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="1" t="inlineStr">
         <is>
-          <t>FSD</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, United States</t>
+          <t>Seattle, WA, United States</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -10806,7 +10806,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -10823,12 +10823,12 @@
     <row r="328">
       <c r="A328" s="1" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>FSD</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>St. Louis, MO, United States</t>
+          <t>Sioux Falls, SD, United States</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>St. Louis, MO</t>
+          <t>Sioux Falls, SD</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -10855,12 +10855,12 @@
     <row r="329">
       <c r="A329" s="1" t="inlineStr">
         <is>
-          <t>TLH</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, United States</t>
+          <t>St. Louis, MO, United States</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -10870,7 +10870,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Tallahassee, FL</t>
+          <t>St. Louis, MO</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -10887,12 +10887,12 @@
     <row r="330">
       <c r="A330" s="1" t="inlineStr">
         <is>
-          <t>TPA</t>
+          <t>TLH</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Tampa, FL, United States</t>
+          <t>Tallahassee, FL, United States</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -10902,7 +10902,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Tampa, FL</t>
+          <t>Tallahassee, FL</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -10919,12 +10919,12 @@
     <row r="331">
       <c r="A331" s="1" t="inlineStr">
         <is>
-          <t>YYZ</t>
+          <t>TPA</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Toronto, ON, Canada</t>
+          <t>Tampa, FL, United States</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -10934,29 +10934,29 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Toronto, ON</t>
+          <t>Tampa, FL</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="1" t="inlineStr">
         <is>
-          <t>YVR</t>
+          <t>YYZ</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Vancouver, BC, Canada</t>
+          <t>Toronto, ON, Canada</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -10966,7 +10966,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Vancouver, BC</t>
+          <t>Toronto, ON</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -10983,30 +10983,62 @@
     <row r="333">
       <c r="A333" s="1" t="inlineStr">
         <is>
+          <t>YVR</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Vancouver, BC, Canada</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Vancouver, BC</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="1" t="inlineStr">
+        <is>
           <t>YWG</t>
         </is>
       </c>
-      <c r="B333" t="inlineStr">
+      <c r="B334" t="inlineStr">
         <is>
           <t>Winnipeg, MB, Canada</t>
         </is>
       </c>
-      <c r="C333" t="inlineStr">
+      <c r="C334" t="inlineStr">
         <is>
           <t>North America</t>
         </is>
       </c>
-      <c r="D333" t="inlineStr">
+      <c r="D334" t="inlineStr">
         <is>
           <t>Winnipeg, MB</t>
         </is>
       </c>
-      <c r="E333" t="inlineStr">
+      <c r="E334" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="F333" t="inlineStr">
+      <c r="F334" t="inlineStr">
         <is>
           <t>CA</t>
         </is>

--- a/DC-Colos.xlsx
+++ b/DC-Colos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F334"/>
+  <dimension ref="A1:F335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9159,44 +9159,44 @@
     <row r="276">
       <c r="A276" s="1" t="inlineStr">
         <is>
-          <t>ABQ</t>
+          <t>BBI</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, United States</t>
+          <t>Bhubaneswar, India</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Albuquerque, NM</t>
+          <t>Bhubaneswar</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="inlineStr">
         <is>
-          <t>ANC</t>
+          <t>ABQ</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Anchorage, AK, United States</t>
+          <t>Albuquerque, NM, United States</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Anchorage, AK</t>
+          <t>Albuquerque, NM</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -9223,12 +9223,12 @@
     <row r="278">
       <c r="A278" s="1" t="inlineStr">
         <is>
-          <t>IAD</t>
+          <t>ANC</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Ashburn, VA, United States</t>
+          <t>Anchorage, AK, United States</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Ashburn, VA</t>
+          <t>Anchorage, AK</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -9255,12 +9255,12 @@
     <row r="279">
       <c r="A279" s="1" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>IAD</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Atlanta, GA, United States</t>
+          <t>Ashburn, VA, United States</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Ashburn, VA</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -9287,12 +9287,12 @@
     <row r="280">
       <c r="A280" s="1" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Austin, TX, United States</t>
+          <t>Atlanta, GA, United States</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -9302,7 +9302,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -9319,12 +9319,12 @@
     <row r="281">
       <c r="A281" s="1" t="inlineStr">
         <is>
-          <t>BGR</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Bangor, ME, United States</t>
+          <t>Austin, TX, United States</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Bangor, ME</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -9351,12 +9351,12 @@
     <row r="282">
       <c r="A282" s="1" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BGR</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Boston, MA, United States</t>
+          <t>Bangor, ME, United States</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Bangor, ME</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -9383,12 +9383,12 @@
     <row r="283">
       <c r="A283" s="1" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Buffalo, NY, United States</t>
+          <t>Boston, MA, United States</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -9398,7 +9398,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Buffalo, NY</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -9415,12 +9415,12 @@
     <row r="284">
       <c r="A284" s="1" t="inlineStr">
         <is>
-          <t>YYC</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Calgary, AB, Canada</t>
+          <t>Buffalo, NY, United States</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -9430,29 +9430,29 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Calgary, AB</t>
+          <t>Buffalo, NY</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="1" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>YYC</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Charlotte, NC, United States</t>
+          <t>Calgary, AB, Canada</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -9462,29 +9462,29 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Charlotte, NC</t>
+          <t>Calgary, AB</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="1" t="inlineStr">
         <is>
-          <t>ORD</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Chicago, IL, United States</t>
+          <t>Charlotte, NC, United States</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -9494,7 +9494,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Charlotte, NC</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -9511,12 +9511,12 @@
     <row r="287">
       <c r="A287" s="1" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ORD</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Cleveland, OH, United States</t>
+          <t>Chicago, IL, United States</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Cleveland, OH</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -9543,12 +9543,12 @@
     <row r="288">
       <c r="A288" s="1" t="inlineStr">
         <is>
-          <t>CMH</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Columbus, OH, United States</t>
+          <t>Cleveland, OH, United States</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -9558,7 +9558,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Columbus, OH</t>
+          <t>Cleveland, OH</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -9575,12 +9575,12 @@
     <row r="289">
       <c r="A289" s="1" t="inlineStr">
         <is>
-          <t>DFW</t>
+          <t>CMH</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Dallas, TX, United States</t>
+          <t>Columbus, OH, United States</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Dallas, TX</t>
+          <t>Columbus, OH</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -9607,12 +9607,12 @@
     <row r="290">
       <c r="A290" s="1" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DFW</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Denver, CO, United States</t>
+          <t>Dallas, TX, United States</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>Dallas, TX</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -9639,12 +9639,12 @@
     <row r="291">
       <c r="A291" s="1" t="inlineStr">
         <is>
-          <t>DTW</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Detroit, MI, United States</t>
+          <t>Denver, CO, United States</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -9654,7 +9654,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Detroit, MI</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -9671,12 +9671,12 @@
     <row r="292">
       <c r="A292" s="1" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DTW</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Durham, NC, United States</t>
+          <t>Detroit, MI, United States</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -9686,7 +9686,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Durham, NC</t>
+          <t>Detroit, MI</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -9703,12 +9703,12 @@
     <row r="293">
       <c r="A293" s="1" t="inlineStr">
         <is>
-          <t>GDL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Guadalajara, Mexico</t>
+          <t>Durham, NC, United States</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -9718,29 +9718,29 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Durham, NC</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="inlineStr">
         <is>
-          <t>YHZ</t>
+          <t>GDL</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Halifax, Canada</t>
+          <t>Guadalajara, Mexico</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -9750,29 +9750,29 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Halifax</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>MX</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="inlineStr">
         <is>
-          <t>HNL</t>
+          <t>YHZ</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Honolulu, HI, United States</t>
+          <t>Halifax, Canada</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -9782,29 +9782,29 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Honolulu, HI</t>
+          <t>Halifax</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="1" t="inlineStr">
         <is>
-          <t>IAH</t>
+          <t>HNL</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Houston, TX, United States</t>
+          <t>Honolulu, HI, United States</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Houston, TX</t>
+          <t>Honolulu, HI</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -9831,12 +9831,12 @@
     <row r="297">
       <c r="A297" s="1" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>IAH</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, United States</t>
+          <t>Houston, TX, United States</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -9846,7 +9846,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Indianapolis, IN</t>
+          <t>Houston, TX</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -9863,12 +9863,12 @@
     <row r="298">
       <c r="A298" s="1" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, United States</t>
+          <t>Indianapolis, IN, United States</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -9878,7 +9878,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Jacksonville, FL</t>
+          <t>Indianapolis, IN</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -9895,12 +9895,12 @@
     <row r="299">
       <c r="A299" s="1" t="inlineStr">
         <is>
-          <t>MCI</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Kansas City, MO, United States</t>
+          <t>Jacksonville, FL, United States</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -9910,7 +9910,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Kansas City, MO</t>
+          <t>Jacksonville, FL</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -9927,12 +9927,12 @@
     <row r="300">
       <c r="A300" s="1" t="inlineStr">
         <is>
-          <t>KIN</t>
+          <t>MCI</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Kingston, Jamaica</t>
+          <t>Kansas City, MO, United States</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -9942,29 +9942,29 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Kingston</t>
+          <t>Kansas City, MO</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Jamaica</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>JM</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="1" t="inlineStr">
         <is>
-          <t>LAS</t>
+          <t>KIN</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, United States</t>
+          <t>Kingston, Jamaica</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -9974,29 +9974,29 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Las Vegas, NV</t>
+          <t>Kingston</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Jamaica</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JM</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="inlineStr">
         <is>
-          <t>LAX</t>
+          <t>LAS</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, United States</t>
+          <t>Las Vegas, NV, United States</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -10006,7 +10006,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
+          <t>Las Vegas, NV</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -10023,12 +10023,12 @@
     <row r="303">
       <c r="A303" s="1" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>LAX</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Memphis, TN, United States</t>
+          <t>Los Angeles, CA, United States</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -10038,7 +10038,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Memphis, TN</t>
+          <t>Los Angeles, CA</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -10055,12 +10055,12 @@
     <row r="304">
       <c r="A304" s="1" t="inlineStr">
         <is>
-          <t>MEX</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Mexico City, Mexico</t>
+          <t>Memphis, TN, United States</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -10070,29 +10070,29 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Mexico City</t>
+          <t>Memphis, TN</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MEX</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Miami, FL, United States</t>
+          <t>Mexico City, Mexico</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -10102,29 +10102,29 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Miami, FL</t>
+          <t>Mexico City</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="1" t="inlineStr">
         <is>
-          <t>MSP</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, United States</t>
+          <t>Miami, FL, United States</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Minneapolis, MN</t>
+          <t>Miami, FL</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -10151,12 +10151,12 @@
     <row r="307">
       <c r="A307" s="1" t="inlineStr">
         <is>
-          <t>YUL</t>
+          <t>MSP</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Montréal, QC, Canada</t>
+          <t>Minneapolis, MN, United States</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -10166,29 +10166,29 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Montréal, QC</t>
+          <t>Minneapolis, MN</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="inlineStr">
         <is>
-          <t>BNA</t>
+          <t>YUL</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Nashville, United States</t>
+          <t>Montréal, QC, Canada</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -10198,29 +10198,29 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Nashville</t>
+          <t>Montréal, QC</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="inlineStr">
         <is>
-          <t>EWR</t>
+          <t>BNA</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Newark, NJ, United States</t>
+          <t>Nashville, United States</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Newark, NJ</t>
+          <t>Nashville</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -10247,12 +10247,12 @@
     <row r="310">
       <c r="A310" s="1" t="inlineStr">
         <is>
-          <t>ORF</t>
+          <t>EWR</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Norfolk, VA, United States</t>
+          <t>Newark, NJ, United States</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Norfolk, VA</t>
+          <t>Newark, NJ</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -10279,12 +10279,12 @@
     <row r="311">
       <c r="A311" s="1" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>ORF</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, United States</t>
+          <t>Norfolk, VA, United States</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -10294,7 +10294,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK</t>
+          <t>Norfolk, VA</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -10311,12 +10311,12 @@
     <row r="312">
       <c r="A312" s="1" t="inlineStr">
         <is>
-          <t>OMA</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Omaha, NE, United States</t>
+          <t>Oklahoma City, OK, United States</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Omaha, NE</t>
+          <t>Oklahoma City, OK</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -10343,12 +10343,12 @@
     <row r="313">
       <c r="A313" s="1" t="inlineStr">
         <is>
-          <t>YOW</t>
+          <t>OMA</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Ottawa, Canada</t>
+          <t>Omaha, NE, United States</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -10358,29 +10358,29 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Ottawa</t>
+          <t>Omaha, NE</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="1" t="inlineStr">
         <is>
-          <t>PHL</t>
+          <t>YOW</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Philadelphia, United States</t>
+          <t>Ottawa, Canada</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -10390,29 +10390,29 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Ottawa</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="1" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>PHL</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, United States</t>
+          <t>Philadelphia, United States</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Phoenix, AZ</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -10439,12 +10439,12 @@
     <row r="316">
       <c r="A316" s="1" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, United States</t>
+          <t>Phoenix, AZ, United States</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -10454,7 +10454,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA</t>
+          <t>Phoenix, AZ</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -10471,12 +10471,12 @@
     <row r="317">
       <c r="A317" s="1" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Portland, OR, United States</t>
+          <t>Pittsburgh, PA, United States</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Portland, OR</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -10503,12 +10503,12 @@
     <row r="318">
       <c r="A318" s="1" t="inlineStr">
         <is>
-          <t>QRO</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Queretaro, MX, Mexico</t>
+          <t>Portland, OR, United States</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -10518,29 +10518,29 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Queretaro, MX</t>
+          <t>Portland, OR</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="1" t="inlineStr">
         <is>
-          <t>RIC</t>
+          <t>QRO</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Richmond, VA, United States</t>
+          <t>Queretaro, MX, Mexico</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -10550,29 +10550,29 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Richmond, VA</t>
+          <t>Queretaro, MX</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="1" t="inlineStr">
         <is>
-          <t>SMF</t>
+          <t>RIC</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Sacramento, CA, United States</t>
+          <t>Richmond, VA, United States</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -10582,7 +10582,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Sacramento, CA</t>
+          <t>Richmond, VA</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -10599,12 +10599,12 @@
     <row r="321">
       <c r="A321" s="1" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>SMF</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, United States</t>
+          <t>Sacramento, CA, United States</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT</t>
+          <t>Sacramento, CA</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -10631,12 +10631,12 @@
     <row r="322">
       <c r="A322" s="1" t="inlineStr">
         <is>
-          <t>SAT</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>San Antonio, TX, United States</t>
+          <t>Salt Lake City, UT, United States</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -10646,7 +10646,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>San Antonio, TX</t>
+          <t>Salt Lake City, UT</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -10663,12 +10663,12 @@
     <row r="323">
       <c r="A323" s="1" t="inlineStr">
         <is>
-          <t>SAN</t>
+          <t>SAT</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>San Diego, CA, United States</t>
+          <t>San Antonio, TX, United States</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -10678,7 +10678,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>San Diego, CA</t>
+          <t>San Antonio, TX</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -10695,12 +10695,12 @@
     <row r="324">
       <c r="A324" s="1" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>SAN</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>San Francisco, CA, United States</t>
+          <t>San Diego, CA, United States</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -10710,7 +10710,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>San Diego, CA</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -10727,12 +10727,12 @@
     <row r="325">
       <c r="A325" s="1" t="inlineStr">
         <is>
-          <t>SJC</t>
+          <t>SFO</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>San Jose, CA, United States</t>
+          <t>San Francisco, CA, United States</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -10759,12 +10759,12 @@
     <row r="326">
       <c r="A326" s="1" t="inlineStr">
         <is>
-          <t>YXE</t>
+          <t>SJC</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Saskatoon, SK, Canada</t>
+          <t>San Jose, CA, United States</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -10774,29 +10774,29 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Saskatoon, SK</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="1" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>YXE</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Seattle, WA, United States</t>
+          <t>Saskatoon, SK, Canada</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -10806,29 +10806,29 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Saskatoon, SK</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="inlineStr">
         <is>
-          <t>FSD</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, United States</t>
+          <t>Seattle, WA, United States</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -10855,12 +10855,12 @@
     <row r="329">
       <c r="A329" s="1" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>FSD</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>St. Louis, MO, United States</t>
+          <t>Sioux Falls, SD, United States</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -10870,7 +10870,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>St. Louis, MO</t>
+          <t>Sioux Falls, SD</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -10887,12 +10887,12 @@
     <row r="330">
       <c r="A330" s="1" t="inlineStr">
         <is>
-          <t>TLH</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, United States</t>
+          <t>St. Louis, MO, United States</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -10902,7 +10902,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Tallahassee, FL</t>
+          <t>St. Louis, MO</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -10919,12 +10919,12 @@
     <row r="331">
       <c r="A331" s="1" t="inlineStr">
         <is>
-          <t>TPA</t>
+          <t>TLH</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Tampa, FL, United States</t>
+          <t>Tallahassee, FL, United States</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Tampa, FL</t>
+          <t>Tallahassee, FL</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -10951,12 +10951,12 @@
     <row r="332">
       <c r="A332" s="1" t="inlineStr">
         <is>
-          <t>YYZ</t>
+          <t>TPA</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Toronto, ON, Canada</t>
+          <t>Tampa, FL, United States</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -10966,29 +10966,29 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Toronto, ON</t>
+          <t>Tampa, FL</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="1" t="inlineStr">
         <is>
-          <t>YVR</t>
+          <t>YYZ</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Vancouver, BC, Canada</t>
+          <t>Toronto, ON, Canada</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -10998,7 +10998,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Vancouver, BC</t>
+          <t>Toronto, ON</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -11015,30 +11015,62 @@
     <row r="334">
       <c r="A334" s="1" t="inlineStr">
         <is>
+          <t>YVR</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Vancouver, BC, Canada</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Vancouver, BC</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="1" t="inlineStr">
+        <is>
           <t>YWG</t>
         </is>
       </c>
-      <c r="B334" t="inlineStr">
+      <c r="B335" t="inlineStr">
         <is>
           <t>Winnipeg, MB, Canada</t>
         </is>
       </c>
-      <c r="C334" t="inlineStr">
+      <c r="C335" t="inlineStr">
         <is>
           <t>North America</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr">
+      <c r="D335" t="inlineStr">
         <is>
           <t>Winnipeg, MB</t>
         </is>
       </c>
-      <c r="E334" t="inlineStr">
+      <c r="E335" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="F334" t="inlineStr">
+      <c r="F335" t="inlineStr">
         <is>
           <t>CA</t>
         </is>

--- a/DC-Colos.xlsx
+++ b/DC-Colos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F335"/>
+  <dimension ref="A1:F336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9191,44 +9191,44 @@
     <row r="277">
       <c r="A277" s="1" t="inlineStr">
         <is>
-          <t>ABQ</t>
+          <t>LYA</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, United States</t>
+          <t>Luoyang, China</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Albuquerque, NM</t>
+          <t>Luoyang</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="1" t="inlineStr">
         <is>
-          <t>ANC</t>
+          <t>ABQ</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Anchorage, AK, United States</t>
+          <t>Albuquerque, NM, United States</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Anchorage, AK</t>
+          <t>Albuquerque, NM</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -9255,12 +9255,12 @@
     <row r="279">
       <c r="A279" s="1" t="inlineStr">
         <is>
-          <t>IAD</t>
+          <t>ANC</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Ashburn, VA, United States</t>
+          <t>Anchorage, AK, United States</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Ashburn, VA</t>
+          <t>Anchorage, AK</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -9287,12 +9287,12 @@
     <row r="280">
       <c r="A280" s="1" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>IAD</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Atlanta, GA, United States</t>
+          <t>Ashburn, VA, United States</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -9302,7 +9302,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Ashburn, VA</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -9319,12 +9319,12 @@
     <row r="281">
       <c r="A281" s="1" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Austin, TX, United States</t>
+          <t>Atlanta, GA, United States</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -9351,12 +9351,12 @@
     <row r="282">
       <c r="A282" s="1" t="inlineStr">
         <is>
-          <t>BGR</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Bangor, ME, United States</t>
+          <t>Austin, TX, United States</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Bangor, ME</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -9383,12 +9383,12 @@
     <row r="283">
       <c r="A283" s="1" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BGR</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Boston, MA, United States</t>
+          <t>Bangor, ME, United States</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -9398,7 +9398,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Bangor, ME</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -9415,12 +9415,12 @@
     <row r="284">
       <c r="A284" s="1" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Buffalo, NY, United States</t>
+          <t>Boston, MA, United States</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -9430,7 +9430,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Buffalo, NY</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -9447,12 +9447,12 @@
     <row r="285">
       <c r="A285" s="1" t="inlineStr">
         <is>
-          <t>YYC</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Calgary, AB, Canada</t>
+          <t>Buffalo, NY, United States</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -9462,29 +9462,29 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Calgary, AB</t>
+          <t>Buffalo, NY</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="1" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>YYC</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Charlotte, NC, United States</t>
+          <t>Calgary, AB, Canada</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -9494,29 +9494,29 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Charlotte, NC</t>
+          <t>Calgary, AB</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="1" t="inlineStr">
         <is>
-          <t>ORD</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Chicago, IL, United States</t>
+          <t>Charlotte, NC, United States</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Charlotte, NC</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -9543,12 +9543,12 @@
     <row r="288">
       <c r="A288" s="1" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ORD</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Cleveland, OH, United States</t>
+          <t>Chicago, IL, United States</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -9558,7 +9558,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Cleveland, OH</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -9575,12 +9575,12 @@
     <row r="289">
       <c r="A289" s="1" t="inlineStr">
         <is>
-          <t>CMH</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Columbus, OH, United States</t>
+          <t>Cleveland, OH, United States</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Columbus, OH</t>
+          <t>Cleveland, OH</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -9607,12 +9607,12 @@
     <row r="290">
       <c r="A290" s="1" t="inlineStr">
         <is>
-          <t>DFW</t>
+          <t>CMH</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Dallas, TX, United States</t>
+          <t>Columbus, OH, United States</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Dallas, TX</t>
+          <t>Columbus, OH</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -9639,12 +9639,12 @@
     <row r="291">
       <c r="A291" s="1" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DFW</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Denver, CO, United States</t>
+          <t>Dallas, TX, United States</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -9654,7 +9654,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>Dallas, TX</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -9671,12 +9671,12 @@
     <row r="292">
       <c r="A292" s="1" t="inlineStr">
         <is>
-          <t>DTW</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Detroit, MI, United States</t>
+          <t>Denver, CO, United States</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -9686,7 +9686,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Detroit, MI</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -9703,12 +9703,12 @@
     <row r="293">
       <c r="A293" s="1" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DTW</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Durham, NC, United States</t>
+          <t>Detroit, MI, United States</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Durham, NC</t>
+          <t>Detroit, MI</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -9735,12 +9735,12 @@
     <row r="294">
       <c r="A294" s="1" t="inlineStr">
         <is>
-          <t>GDL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Guadalajara, Mexico</t>
+          <t>Durham, NC, United States</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -9750,29 +9750,29 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Durham, NC</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="inlineStr">
         <is>
-          <t>YHZ</t>
+          <t>GDL</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Halifax, Canada</t>
+          <t>Guadalajara, Mexico</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -9782,29 +9782,29 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Halifax</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>MX</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="1" t="inlineStr">
         <is>
-          <t>HNL</t>
+          <t>YHZ</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Honolulu, HI, United States</t>
+          <t>Halifax, Canada</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -9814,29 +9814,29 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Honolulu, HI</t>
+          <t>Halifax</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="inlineStr">
         <is>
-          <t>IAH</t>
+          <t>HNL</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Houston, TX, United States</t>
+          <t>Honolulu, HI, United States</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -9846,7 +9846,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Houston, TX</t>
+          <t>Honolulu, HI</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -9863,12 +9863,12 @@
     <row r="298">
       <c r="A298" s="1" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>IAH</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, United States</t>
+          <t>Houston, TX, United States</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -9878,7 +9878,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Indianapolis, IN</t>
+          <t>Houston, TX</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -9895,12 +9895,12 @@
     <row r="299">
       <c r="A299" s="1" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, United States</t>
+          <t>Indianapolis, IN, United States</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -9910,7 +9910,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Jacksonville, FL</t>
+          <t>Indianapolis, IN</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -9927,12 +9927,12 @@
     <row r="300">
       <c r="A300" s="1" t="inlineStr">
         <is>
-          <t>MCI</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Kansas City, MO, United States</t>
+          <t>Jacksonville, FL, United States</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Kansas City, MO</t>
+          <t>Jacksonville, FL</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -9959,12 +9959,12 @@
     <row r="301">
       <c r="A301" s="1" t="inlineStr">
         <is>
-          <t>KIN</t>
+          <t>MCI</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Kingston, Jamaica</t>
+          <t>Kansas City, MO, United States</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -9974,29 +9974,29 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Kingston</t>
+          <t>Kansas City, MO</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Jamaica</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>JM</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="inlineStr">
         <is>
-          <t>LAS</t>
+          <t>KIN</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, United States</t>
+          <t>Kingston, Jamaica</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -10006,29 +10006,29 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Las Vegas, NV</t>
+          <t>Kingston</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Jamaica</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JM</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="inlineStr">
         <is>
-          <t>LAX</t>
+          <t>LAS</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, United States</t>
+          <t>Las Vegas, NV, United States</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -10038,7 +10038,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
+          <t>Las Vegas, NV</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -10055,12 +10055,12 @@
     <row r="304">
       <c r="A304" s="1" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>LAX</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Memphis, TN, United States</t>
+          <t>Los Angeles, CA, United States</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -10070,7 +10070,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Memphis, TN</t>
+          <t>Los Angeles, CA</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -10087,12 +10087,12 @@
     <row r="305">
       <c r="A305" s="1" t="inlineStr">
         <is>
-          <t>MEX</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Mexico City, Mexico</t>
+          <t>Memphis, TN, United States</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -10102,29 +10102,29 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Mexico City</t>
+          <t>Memphis, TN</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="1" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MEX</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Miami, FL, United States</t>
+          <t>Mexico City, Mexico</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -10134,29 +10134,29 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Miami, FL</t>
+          <t>Mexico City</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="inlineStr">
         <is>
-          <t>MSP</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, United States</t>
+          <t>Miami, FL, United States</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Minneapolis, MN</t>
+          <t>Miami, FL</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -10183,12 +10183,12 @@
     <row r="308">
       <c r="A308" s="1" t="inlineStr">
         <is>
-          <t>YUL</t>
+          <t>MSP</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Montréal, QC, Canada</t>
+          <t>Minneapolis, MN, United States</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -10198,29 +10198,29 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Montréal, QC</t>
+          <t>Minneapolis, MN</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="inlineStr">
         <is>
-          <t>BNA</t>
+          <t>YUL</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Nashville, United States</t>
+          <t>Montréal, QC, Canada</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -10230,29 +10230,29 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Nashville</t>
+          <t>Montréal, QC</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="1" t="inlineStr">
         <is>
-          <t>EWR</t>
+          <t>BNA</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Newark, NJ, United States</t>
+          <t>Nashville, United States</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Newark, NJ</t>
+          <t>Nashville</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -10279,12 +10279,12 @@
     <row r="311">
       <c r="A311" s="1" t="inlineStr">
         <is>
-          <t>ORF</t>
+          <t>EWR</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Norfolk, VA, United States</t>
+          <t>Newark, NJ, United States</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -10294,7 +10294,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Norfolk, VA</t>
+          <t>Newark, NJ</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -10311,12 +10311,12 @@
     <row r="312">
       <c r="A312" s="1" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>ORF</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, United States</t>
+          <t>Norfolk, VA, United States</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK</t>
+          <t>Norfolk, VA</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -10343,12 +10343,12 @@
     <row r="313">
       <c r="A313" s="1" t="inlineStr">
         <is>
-          <t>OMA</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Omaha, NE, United States</t>
+          <t>Oklahoma City, OK, United States</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Omaha, NE</t>
+          <t>Oklahoma City, OK</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -10375,12 +10375,12 @@
     <row r="314">
       <c r="A314" s="1" t="inlineStr">
         <is>
-          <t>YOW</t>
+          <t>OMA</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Ottawa, Canada</t>
+          <t>Omaha, NE, United States</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -10390,29 +10390,29 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Ottawa</t>
+          <t>Omaha, NE</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="1" t="inlineStr">
         <is>
-          <t>PHL</t>
+          <t>YOW</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Philadelphia, United States</t>
+          <t>Ottawa, Canada</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -10422,29 +10422,29 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Ottawa</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="1" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>PHL</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, United States</t>
+          <t>Philadelphia, United States</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -10454,7 +10454,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Phoenix, AZ</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -10471,12 +10471,12 @@
     <row r="317">
       <c r="A317" s="1" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, United States</t>
+          <t>Phoenix, AZ, United States</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA</t>
+          <t>Phoenix, AZ</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -10503,12 +10503,12 @@
     <row r="318">
       <c r="A318" s="1" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Portland, OR, United States</t>
+          <t>Pittsburgh, PA, United States</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -10518,7 +10518,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Portland, OR</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -10535,12 +10535,12 @@
     <row r="319">
       <c r="A319" s="1" t="inlineStr">
         <is>
-          <t>QRO</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Queretaro, MX, Mexico</t>
+          <t>Portland, OR, United States</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -10550,29 +10550,29 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Queretaro, MX</t>
+          <t>Portland, OR</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="1" t="inlineStr">
         <is>
-          <t>RIC</t>
+          <t>QRO</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Richmond, VA, United States</t>
+          <t>Queretaro, MX, Mexico</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -10582,29 +10582,29 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Richmond, VA</t>
+          <t>Queretaro, MX</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="inlineStr">
         <is>
-          <t>SMF</t>
+          <t>RIC</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Sacramento, CA, United States</t>
+          <t>Richmond, VA, United States</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Sacramento, CA</t>
+          <t>Richmond, VA</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -10631,12 +10631,12 @@
     <row r="322">
       <c r="A322" s="1" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>SMF</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, United States</t>
+          <t>Sacramento, CA, United States</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -10646,7 +10646,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT</t>
+          <t>Sacramento, CA</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -10663,12 +10663,12 @@
     <row r="323">
       <c r="A323" s="1" t="inlineStr">
         <is>
-          <t>SAT</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>San Antonio, TX, United States</t>
+          <t>Salt Lake City, UT, United States</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -10678,7 +10678,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>San Antonio, TX</t>
+          <t>Salt Lake City, UT</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -10695,12 +10695,12 @@
     <row r="324">
       <c r="A324" s="1" t="inlineStr">
         <is>
-          <t>SAN</t>
+          <t>SAT</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>San Diego, CA, United States</t>
+          <t>San Antonio, TX, United States</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -10710,7 +10710,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>San Diego, CA</t>
+          <t>San Antonio, TX</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -10727,12 +10727,12 @@
     <row r="325">
       <c r="A325" s="1" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>SAN</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>San Francisco, CA, United States</t>
+          <t>San Diego, CA, United States</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>San Diego, CA</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -10759,12 +10759,12 @@
     <row r="326">
       <c r="A326" s="1" t="inlineStr">
         <is>
-          <t>SJC</t>
+          <t>SFO</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>San Jose, CA, United States</t>
+          <t>San Francisco, CA, United States</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -10774,7 +10774,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -10791,12 +10791,12 @@
     <row r="327">
       <c r="A327" s="1" t="inlineStr">
         <is>
-          <t>YXE</t>
+          <t>SJC</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Saskatoon, SK, Canada</t>
+          <t>San Jose, CA, United States</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -10806,29 +10806,29 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Saskatoon, SK</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>YXE</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Seattle, WA, United States</t>
+          <t>Saskatoon, SK, Canada</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -10838,29 +10838,29 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Saskatoon, SK</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="inlineStr">
         <is>
-          <t>FSD</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, United States</t>
+          <t>Seattle, WA, United States</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -10870,7 +10870,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -10887,12 +10887,12 @@
     <row r="330">
       <c r="A330" s="1" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>FSD</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>St. Louis, MO, United States</t>
+          <t>Sioux Falls, SD, United States</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -10902,7 +10902,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>St. Louis, MO</t>
+          <t>Sioux Falls, SD</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -10919,12 +10919,12 @@
     <row r="331">
       <c r="A331" s="1" t="inlineStr">
         <is>
-          <t>TLH</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, United States</t>
+          <t>St. Louis, MO, United States</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Tallahassee, FL</t>
+          <t>St. Louis, MO</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -10951,12 +10951,12 @@
     <row r="332">
       <c r="A332" s="1" t="inlineStr">
         <is>
-          <t>TPA</t>
+          <t>TLH</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Tampa, FL, United States</t>
+          <t>Tallahassee, FL, United States</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -10966,7 +10966,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Tampa, FL</t>
+          <t>Tallahassee, FL</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -10983,12 +10983,12 @@
     <row r="333">
       <c r="A333" s="1" t="inlineStr">
         <is>
-          <t>YYZ</t>
+          <t>TPA</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Toronto, ON, Canada</t>
+          <t>Tampa, FL, United States</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -10998,29 +10998,29 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Toronto, ON</t>
+          <t>Tampa, FL</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="1" t="inlineStr">
         <is>
-          <t>YVR</t>
+          <t>YYZ</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Vancouver, BC, Canada</t>
+          <t>Toronto, ON, Canada</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Vancouver, BC</t>
+          <t>Toronto, ON</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -11047,30 +11047,62 @@
     <row r="335">
       <c r="A335" s="1" t="inlineStr">
         <is>
+          <t>YVR</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Vancouver, BC, Canada</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Vancouver, BC</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="1" t="inlineStr">
+        <is>
           <t>YWG</t>
         </is>
       </c>
-      <c r="B335" t="inlineStr">
+      <c r="B336" t="inlineStr">
         <is>
           <t>Winnipeg, MB, Canada</t>
         </is>
       </c>
-      <c r="C335" t="inlineStr">
+      <c r="C336" t="inlineStr">
         <is>
           <t>North America</t>
         </is>
       </c>
-      <c r="D335" t="inlineStr">
+      <c r="D336" t="inlineStr">
         <is>
           <t>Winnipeg, MB</t>
         </is>
       </c>
-      <c r="E335" t="inlineStr">
+      <c r="E336" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="F335" t="inlineStr">
+      <c r="F336" t="inlineStr">
         <is>
           <t>CA</t>
         </is>

--- a/DC-Colos.xlsx
+++ b/DC-Colos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F336"/>
+  <dimension ref="A1:F337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2283,44 +2283,44 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>AMM</t>
+          <t>LJU</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Amman, Jordan</t>
+          <t>Ljubljana, Slovenia</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Middle East</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Amman</t>
+          <t>Ljubljana</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>JO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>LLK</t>
+          <t>AMM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Astara, Azerbaijan</t>
+          <t>Amman, Jordan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2330,29 +2330,29 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Astara</t>
+          <t>Amman</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Azerbaijan</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>JO</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>BGW</t>
+          <t>LLK</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Baghdad, Iraq</t>
+          <t>Astara, Azerbaijan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2362,29 +2362,29 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Baghdad</t>
+          <t>Astara</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Azerbaijan</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>IQ</t>
+          <t>AZ</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>GYD</t>
+          <t>BGW</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Baku, Azerbaijan</t>
+          <t>Baghdad, Iraq</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2394,29 +2394,29 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Baku</t>
+          <t>Baghdad</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Azerbaijan</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>IQ</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>BSR</t>
+          <t>GYD</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Basra, Iraq</t>
+          <t>Baku, Azerbaijan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2426,29 +2426,29 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Basra</t>
+          <t>Baku</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Azerbaijan</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>IQ</t>
+          <t>AZ</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>BEY</t>
+          <t>BSR</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Beirut, Lebanon</t>
+          <t>Basra, Iraq</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2458,29 +2458,29 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Beirut</t>
+          <t>Basra</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>IQ</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>DMM</t>
+          <t>BEY</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Dammam, Saudi Arabia</t>
+          <t>Beirut, Lebanon</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2490,29 +2490,29 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Dammam</t>
+          <t>Beirut</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>LB</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>DOH</t>
+          <t>DMM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Doha, Qatar</t>
+          <t>Dammam, Saudi Arabia</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2522,29 +2522,29 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Doha</t>
+          <t>Dammam</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>SA</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>DXB</t>
+          <t>DOH</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Dubai, United Arab Emirates</t>
+          <t>Doha, Qatar</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2554,29 +2554,29 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Doha</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>QA</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>EBL</t>
+          <t>DXB</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Erbil, Iraq</t>
+          <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2586,29 +2586,29 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Erbil</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>IQ</t>
+          <t>AE</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>HFA</t>
+          <t>EBL</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Haifa, Israel</t>
+          <t>Erbil, Iraq</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2618,29 +2618,29 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Haifa</t>
+          <t>Erbil</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>IQ</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>JED</t>
+          <t>HFA</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Jeddah, Saudi Arabia</t>
+          <t>Haifa, Israel</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2650,29 +2650,29 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Jeddah</t>
+          <t>Haifa</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>IL</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>KWI</t>
+          <t>JED</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Kuwait City, Kuwait</t>
+          <t>Jeddah, Saudi Arabia</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2682,29 +2682,29 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Kuwait City</t>
+          <t>Jeddah</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>KW</t>
+          <t>SA</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>BAH</t>
+          <t>KWI</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Manama, Bahrain</t>
+          <t>Kuwait City, Kuwait</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2714,29 +2714,29 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Manama</t>
+          <t>Kuwait City</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bahrain</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>BH</t>
+          <t>KW</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>MCT</t>
+          <t>BAH</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Muscat, Oman</t>
+          <t>Manama, Bahrain</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2746,29 +2746,29 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Muscat</t>
+          <t>Manama</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>Bahrain</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>OM</t>
+          <t>BH</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>NJF</t>
+          <t>MCT</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Najaf, Iraq</t>
+          <t>Muscat, Oman</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2778,29 +2778,29 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Najaf</t>
+          <t>Muscat</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Oman</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>IQ</t>
+          <t>OM</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>XNH</t>
+          <t>NJF</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Nasiriyah, Iraq</t>
+          <t>Najaf, Iraq</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Nasiriyah</t>
+          <t>Najaf</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2827,12 +2827,12 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>ZDM</t>
+          <t>XNH</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ramallah</t>
+          <t>Nasiriyah, Iraq</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2840,19 +2840,31 @@
           <t>Middle East</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Nasiriyah</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Iraq</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>IQ</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>RUH</t>
+          <t>ZDM</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Riyadh, Saudi Arabia</t>
+          <t>Ramallah</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2860,31 +2872,19 @@
           <t>Middle East</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Riyadh</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Saudi Arabia</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>ISU</t>
+          <t>RUH</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Sulaymaniyah, Iraq</t>
+          <t>Riyadh, Saudi Arabia</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2894,29 +2894,29 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Sulaymaniyah</t>
+          <t>Riyadh</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>IQ</t>
+          <t>SA</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>TLV</t>
+          <t>ISU</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Tel Aviv, Israel</t>
+          <t>Sulaymaniyah, Iraq</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2926,61 +2926,61 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Tel Aviv</t>
+          <t>Sulaymaniyah</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>IQ</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>ADL</t>
+          <t>TLV</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Adelaide, SA, Australia</t>
+          <t>Tel Aviv, Israel</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Oceania</t>
+          <t>Middle East</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Adelaide, SA</t>
+          <t>Tel Aviv</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>IL</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>AKL</t>
+          <t>ADL</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Auckland, New Zealand</t>
+          <t>Adelaide, SA, Australia</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2990,29 +2990,29 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Adelaide, SA</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>AU</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>BNE</t>
+          <t>AKL</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Brisbane, QLD, Australia</t>
+          <t>Auckland, New Zealand</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3022,29 +3022,29 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Brisbane, QLD</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>NZ</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>CBR</t>
+          <t>BNE</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Canberra, ACT, Australia</t>
+          <t>Brisbane, QLD, Australia</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Canberra, ACT</t>
+          <t>Brisbane, QLD</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3071,12 +3071,12 @@
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>CBR</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Christchurch, New Zealand</t>
+          <t>Canberra, ACT, Australia</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3086,29 +3086,29 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Christchurch</t>
+          <t>Canberra, ACT</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>AU</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>GUM</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Hagatna, Guam</t>
+          <t>Christchurch, New Zealand</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3118,29 +3118,29 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Hagatna</t>
+          <t>Christchurch</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Guam</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>GU</t>
+          <t>NZ</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>MEL</t>
+          <t>GUM</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Melbourne, VIC, Australia</t>
+          <t>Hagatna, Guam</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3150,29 +3150,29 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Melbourne, VIC</t>
+          <t>Hagatna</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Guam</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>GU</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>NOU</t>
+          <t>MEL</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Noumea, New Caledonia</t>
+          <t>Melbourne, VIC, Australia</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3182,29 +3182,29 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Noumea</t>
+          <t>Melbourne, VIC</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>New Caledonia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>AU</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>PER</t>
+          <t>NOU</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Perth, WA, Australia</t>
+          <t>Noumea, New Caledonia</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3214,29 +3214,29 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Perth, WA</t>
+          <t>Noumea</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>New Caledonia</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>NC</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>SYD</t>
+          <t>PER</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Sydney, NSW, Australia</t>
+          <t>Perth, WA, Australia</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Sydney, NSW</t>
+          <t>Perth, WA</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3263,12 +3263,12 @@
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>PPT</t>
+          <t>SYD</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Tahiti, French Polynesia</t>
+          <t>Sydney, NSW, Australia</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3278,29 +3278,29 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Tahiti</t>
+          <t>Sydney, NSW</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>French Polynesia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>AU</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>SUV</t>
+          <t>PPT</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Suva, Fiji</t>
+          <t>Tahiti, French Polynesia</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3310,29 +3310,29 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Suva</t>
+          <t>Tahiti</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Fiji</t>
+          <t>French Polynesia</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>FJ</t>
+          <t>PF</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>HBA</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Hobart, Australia</t>
+          <t>Suva, Fiji</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3342,29 +3342,29 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Hobart</t>
+          <t>Suva</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Fiji</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>FJ</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>WLG</t>
+          <t>HBA</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Wellington, New Zealand</t>
+          <t>Hobart, Australia</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3374,61 +3374,61 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Wellington</t>
+          <t>Hobart</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>AU</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>QWJ</t>
+          <t>WLG</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Americana, Brazil</t>
+          <t>Wellington, New Zealand</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Latin America &amp; the Caribbean</t>
+          <t>Oceania</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Americana</t>
+          <t>Wellington</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>NZ</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>QWJ</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Arica, Chile</t>
+          <t>Americana, Brazil</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3438,29 +3438,29 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Arica</t>
+          <t>Americana</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>ASU</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Asunción, Paraguay</t>
+          <t>Arica, Chile</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3470,29 +3470,29 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Asunción</t>
+          <t>Arica</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>PY</t>
+          <t>CL</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>ASU</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Belém, Brazil</t>
+          <t>Asunción, Paraguay</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3502,29 +3502,29 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Belém</t>
+          <t>Asunción</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>PY</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>CNF</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Belo Horizonte, Brazil</t>
+          <t>Belém, Brazil</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Belo Horizonte</t>
+          <t>Belém</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -3551,12 +3551,12 @@
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>BNU</t>
+          <t>CNF</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Blumenau, Brazil</t>
+          <t>Belo Horizonte, Brazil</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Blumenau</t>
+          <t>Belo Horizonte</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3583,12 +3583,12 @@
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>BOG</t>
+          <t>BNU</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Bogota, Colombia</t>
+          <t>Blumenau, Brazil</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3598,29 +3598,29 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Bogota</t>
+          <t>Blumenau</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>BSB</t>
+          <t>BOG</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Brasilia, Brazil</t>
+          <t>Bogota, Colombia</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3630,29 +3630,29 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Brasilia</t>
+          <t>Bogota</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CO</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>EZE</t>
+          <t>BSB</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Buenos Aires, Argentina</t>
+          <t>Brasilia, Brazil</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3662,29 +3662,29 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Brasilia</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>CFC</t>
+          <t>EZE</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Cacador, Brazil</t>
+          <t>Buenos Aires, Argentina</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3694,29 +3694,29 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Cacador</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>AR</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>VCP</t>
+          <t>CFC</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Campinas, Brazil</t>
+          <t>Cacador, Brazil</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Campinas</t>
+          <t>Cacador</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -3743,12 +3743,12 @@
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>VCP</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Córdoba, Argentina</t>
+          <t>Campinas, Brazil</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3758,29 +3758,29 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Campinas</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>CWB</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Curitiba, Brazil</t>
+          <t>Córdoba, Argentina</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3790,29 +3790,29 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Curitiba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>AR</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>FLN</t>
+          <t>CWB</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Florianopolis, Brazil</t>
+          <t>Curitiba, Brazil</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Florianopolis</t>
+          <t>Curitiba</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -3839,12 +3839,12 @@
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>FOR</t>
+          <t>FLN</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Fortaleza, Brazil</t>
+          <t>Florianopolis, Brazil</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Florianopolis</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -3871,12 +3871,12 @@
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>GEO</t>
+          <t>FOR</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Georgetown, Guyana</t>
+          <t>Fortaleza, Brazil</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3886,29 +3886,29 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Georgetown</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>GY</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>GYN</t>
+          <t>GEO</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Goiania, Brazil</t>
+          <t>Georgetown, Guyana</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3918,29 +3918,29 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Goiania</t>
+          <t>Georgetown</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>GY</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>GUA</t>
+          <t>GYN</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Guatemala City, Guatemala</t>
+          <t>Goiania, Brazil</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3950,29 +3950,29 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Guatemala City</t>
+          <t>Goiania</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Guatemala</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>GYE</t>
+          <t>GUA</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Guayaquil, Ecuador</t>
+          <t>Guatemala City, Guatemala</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3982,29 +3982,29 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Guayaquil</t>
+          <t>Guatemala City</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Guatemala</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>GT</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>JOI</t>
+          <t>GYE</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Joinville, Brazil</t>
+          <t>Guayaquil, Ecuador</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4014,29 +4014,29 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Joinville</t>
+          <t>Guayaquil</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>EC</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>JDO</t>
+          <t>JOI</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Juazeiro do Norte, Brazil</t>
+          <t>Joinville, Brazil</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Juazeiro do Norte</t>
+          <t>Joinville</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4063,12 +4063,12 @@
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>JDO</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Lima, Peru</t>
+          <t>Juazeiro do Norte, Brazil</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4078,29 +4078,29 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Lima</t>
+          <t>Juazeiro do Norte</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>MAO</t>
+          <t>LIM</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Manaus, Brazil</t>
+          <t>Lima, Peru</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4110,29 +4110,29 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Manaus</t>
+          <t>Lima</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>PE</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>MDE</t>
+          <t>MAO</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Medellín, Colombia</t>
+          <t>Manaus, Brazil</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4142,29 +4142,29 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Manaus</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>NQN</t>
+          <t>MDE</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Neuquen, Argentina</t>
+          <t>Medellín, Colombia</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4174,29 +4174,29 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Neuquen</t>
+          <t>Medellín</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CO</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>PTY</t>
+          <t>NQN</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Panama City, Panama</t>
+          <t>Neuquen, Argentina</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4206,29 +4206,29 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Panama City</t>
+          <t>Neuquen</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>AR</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>PBM</t>
+          <t>PTY</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Paramaribo, Suriname</t>
+          <t>Panama City, Panama</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4238,29 +4238,29 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Paramaribo</t>
+          <t>Panama City</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Suriname</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>PA</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>PBM</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Porto Alegre, Brazil</t>
+          <t>Paramaribo, Suriname</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4270,29 +4270,29 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Porto Alegre</t>
+          <t>Paramaribo</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Suriname</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>SR</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>UIO</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Quito, Ecuador</t>
+          <t>Porto Alegre, Brazil</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4302,29 +4302,29 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Quito</t>
+          <t>Porto Alegre</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>REC</t>
+          <t>UIO</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Recife, Brazil</t>
+          <t>Quito, Ecuador</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4334,29 +4334,29 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Recife</t>
+          <t>Quito</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>EC</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>RAO</t>
+          <t>REC</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Ribeirao Preto, Brazil</t>
+          <t>Recife, Brazil</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Ribeirao Preto</t>
+          <t>Recife</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -4383,12 +4383,12 @@
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>GIG</t>
+          <t>RAO</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Rio de Janeiro, Brazil</t>
+          <t>Ribeirao Preto, Brazil</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Rio de Janeiro</t>
+          <t>Ribeirao Preto</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -4415,12 +4415,12 @@
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>SJO</t>
+          <t>GIG</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>San José, Costa Rica</t>
+          <t>Rio de Janeiro, Brazil</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4430,29 +4430,29 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>San José</t>
+          <t>Rio de Janeiro</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Costa Rica</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>SCL</t>
+          <t>SJO</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Santiago, Chile</t>
+          <t>San José, Costa Rica</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4462,29 +4462,29 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>San José</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Costa Rica</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>CR</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>SDQ</t>
+          <t>SCL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Santo Domingo, Dominican Republic</t>
+          <t>Santiago, Chile</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4494,29 +4494,29 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Santo Domingo</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>CL</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>SJP</t>
+          <t>SDQ</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>São José do Rio Preto, Brazil</t>
+          <t>Santo Domingo, Dominican Republic</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4526,29 +4526,29 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>São José do Rio Preto</t>
+          <t>Santo Domingo</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>DO</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>SJP</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>São José dos Campos, Brazil</t>
+          <t>São José do Rio Preto, Brazil</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>São José dos Campos</t>
+          <t>São José do Rio Preto</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -4575,12 +4575,12 @@
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>GRU</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>São Paulo, Brazil</t>
+          <t>São José dos Campos, Brazil</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>São José dos Campos</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -4607,12 +4607,12 @@
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>SOD</t>
+          <t>GRU</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Sorocaba, Brazil</t>
+          <t>São Paulo, Brazil</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Sorocaba</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -4639,12 +4639,12 @@
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>TGU</t>
+          <t>SOD</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Tegucigalpa, Honduras</t>
+          <t>Sorocaba, Brazil</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4654,29 +4654,29 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Tegucigalpa</t>
+          <t>Sorocaba</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Honduras</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>HN</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>TGU</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Timbo, Brazil</t>
+          <t>Tegucigalpa, Honduras</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4686,29 +4686,29 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Timbo</t>
+          <t>Tegucigalpa</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Honduras</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>HN</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>UDI</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Uberlandia, Brazil</t>
+          <t>Timbo, Brazil</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Uberlandia</t>
+          <t>Timbo</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -4735,12 +4735,12 @@
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>VIX</t>
+          <t>UDI</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Vitoria, Brazil</t>
+          <t>Uberlandia, Brazil</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Vitoria</t>
+          <t>Uberlandia</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -4767,12 +4767,12 @@
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>CAW</t>
+          <t>VIX</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Campos dos Goytacazes, Brazil</t>
+          <t>Vitoria, Brazil</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Campos dos Goytacazes</t>
+          <t>Vitoria</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -4799,12 +4799,12 @@
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>XAP</t>
+          <t>CAW</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Chapeco, Brazil</t>
+          <t>Campos dos Goytacazes, Brazil</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Chapeco</t>
+          <t>Campos dos Goytacazes</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -4831,12 +4831,12 @@
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>BGI</t>
+          <t>XAP</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Bridgetown, Barbados</t>
+          <t>Chapeco, Brazil</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4846,29 +4846,29 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Bridgetown</t>
+          <t>Chapeco</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Barbados</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>GND</t>
+          <t>BGI</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>St. George's, Grenada</t>
+          <t>Bridgetown, Barbados</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4878,29 +4878,29 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>St. George's</t>
+          <t>Bridgetown</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Grenada</t>
+          <t>Barbados</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>BB</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>STI</t>
+          <t>GND</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Santiago de los Caballeros, Dominican Republic</t>
+          <t>St. George's, Grenada</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4910,29 +4910,29 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Santiago de los Caballeros</t>
+          <t>St. George's</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Grenada</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>GD</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>LPB</t>
+          <t>STI</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>La Paz, Bolivia</t>
+          <t>Santiago de los Caballeros, Dominican Republic</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4942,29 +4942,29 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Santiago de los Caballeros</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>DO</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>SJU</t>
+          <t>LPB</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>San Juan, Puerto Rico</t>
+          <t>La Paz, Bolivia</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4974,29 +4974,29 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>San Juan</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Puerto Rico</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>BO</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>BAQ</t>
+          <t>SJU</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Barranquilla, Colombia</t>
+          <t>San Juan, Puerto Rico</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5006,29 +5006,29 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>San Juan</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Puerto Rico</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>PR</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>PMW</t>
+          <t>BAQ</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Palmas, Brazil</t>
+          <t>Barranquilla, Colombia</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5038,29 +5038,29 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Palmas</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CO</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>ARU</t>
+          <t>PMW</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Aracatuba, Brazil</t>
+          <t>Palmas, Brazil</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Aracatuba</t>
+          <t>Palmas</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -5087,12 +5087,12 @@
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>POS</t>
+          <t>ARU</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Port of Spain, Trinidad and Tobago</t>
+          <t>Aracatuba, Brazil</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5102,25 +5102,29 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Port of Spain</t>
+          <t>Aracatuba</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Trinidad and Tobago</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr"/>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>POS</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Salvador, Brazil</t>
+          <t>Port of Spain, Trinidad and Tobago</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5130,29 +5134,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Salvador</t>
+          <t>Port of Spain</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>BR</t>
-        </is>
-      </c>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Cuiaba, Brazil</t>
+          <t>Salvador, Brazil</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Cuiaba</t>
+          <t>Salvador</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -5179,12 +5179,12 @@
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>CLO</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Cali, Colombia</t>
+          <t>Cuiaba, Brazil</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5194,29 +5194,29 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Cuiaba</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>CLO</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>San Pedro Sula, Honduras</t>
+          <t>Cali, Colombia</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5226,29 +5226,29 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>San Pedro Sula</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Honduras</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>HN</t>
+          <t>CO</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>CCP</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Concepción, Chile</t>
+          <t>San Pedro Sula, Honduras</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5258,61 +5258,61 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>San Pedro Sula</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Honduras</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>HN</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>CCP</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Accra, Ghana</t>
+          <t>Concepción, Chile</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Latin America &amp; the Caribbean</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Accra</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>GH</t>
+          <t>CL</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>ALG</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Algiers, Algeria</t>
+          <t>Accra, Ghana</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5322,29 +5322,29 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Algiers</t>
+          <t>Accra</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>DZ</t>
+          <t>GH</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>AAE</t>
+          <t>ALG</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Annaba, Algeria</t>
+          <t>Algiers, Algeria</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5354,7 +5354,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Annaba</t>
+          <t>Algiers</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -5371,12 +5371,12 @@
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>TNR</t>
+          <t>AAE</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Antananarivo, Madagascar</t>
+          <t>Annaba, Algeria</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5386,29 +5386,29 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Antananarivo</t>
+          <t>Annaba</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>DZ</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>CPT</t>
+          <t>TNR</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Cape Town, South Africa</t>
+          <t>Antananarivo, Madagascar</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5418,29 +5418,29 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Cape Town</t>
+          <t>Antananarivo</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>MG</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>DKR</t>
+          <t>CPT</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Dakar, Senegal</t>
+          <t>Cape Town, South Africa</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5450,29 +5450,29 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Dakar</t>
+          <t>Cape Town</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>SN</t>
+          <t>ZA</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>DKR</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Dar es Salaam, Tanzania</t>
+          <t>Dakar, Senegal</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5482,29 +5482,29 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Dar es Salaam</t>
+          <t>Dakar</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>TZ</t>
+          <t>SN</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>JIB</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Djibouti, Djibouti</t>
+          <t>Dar es Salaam, Tanzania</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5514,29 +5514,29 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Djibouti</t>
+          <t>Dar es Salaam</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Djibouti</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>DJ</t>
+          <t>TZ</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>DUR</t>
+          <t>JIB</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Durban, South Africa</t>
+          <t>Djibouti, Djibouti</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5546,29 +5546,29 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Durban</t>
+          <t>Djibouti</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Djibouti</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>DJ</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>GBE</t>
+          <t>DUR</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Gaborone, Botswana</t>
+          <t>Durban, South Africa</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5578,29 +5578,29 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Gaborone</t>
+          <t>Durban</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>BW</t>
+          <t>ZA</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>HRE</t>
+          <t>GBE</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Harare, Zimbabwe</t>
+          <t>Gaborone, Botswana</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5610,29 +5610,29 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Harare</t>
+          <t>Gaborone</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>ZW</t>
+          <t>BW</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Johannesburg, South Africa</t>
+          <t>Harare, Zimbabwe</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5642,29 +5642,29 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Johannesburg</t>
+          <t>Harare</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>ZW</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>KGL</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Kigali, Rwanda</t>
+          <t>Johannesburg, South Africa</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -5674,29 +5674,29 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Kigali</t>
+          <t>Johannesburg</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>ZA</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>LOS</t>
+          <t>KGL</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Lagos, Nigeria</t>
+          <t>Kigali, Rwanda</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -5706,29 +5706,29 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Lagos</t>
+          <t>Kigali</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>NG</t>
+          <t>RW</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>LOS</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Luanda, Angola</t>
+          <t>Lagos, Nigeria</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -5738,29 +5738,29 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Luanda</t>
+          <t>Lagos</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>AO</t>
+          <t>NG</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>MPM</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Maputo, Mozambique</t>
+          <t>Luanda, Angola</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5770,29 +5770,29 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Maputo</t>
+          <t>Luanda</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>MZ</t>
+          <t>AO</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>MPM</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Mombasa, Kenya</t>
+          <t>Maputo, Mozambique</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5802,29 +5802,29 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Mombasa</t>
+          <t>Maputo</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>KE</t>
+          <t>MZ</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Nairobi, Kenya</t>
+          <t>Mombasa, Kenya</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Nairobi</t>
+          <t>Mombasa</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -5851,12 +5851,12 @@
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>ORN</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Oran, Algeria</t>
+          <t>Nairobi, Kenya</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5866,29 +5866,29 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Oran</t>
+          <t>Nairobi</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>DZ</t>
+          <t>KE</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>OUA</t>
+          <t>ORN</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Ouagadougou, Burkina Faso</t>
+          <t>Oran, Algeria</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5898,29 +5898,29 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Ouagadougou</t>
+          <t>Oran</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Burkina Faso</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>BF</t>
+          <t>DZ</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>MRU</t>
+          <t>OUA</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Port Louis, Mauritius</t>
+          <t>Ouagadougou, Burkina Faso</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5930,29 +5930,29 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Port Louis</t>
+          <t>Ouagadougou</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Mauritius</t>
+          <t>Burkina Faso</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>BF</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>TUN</t>
+          <t>MRU</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Tunis, Tunisia</t>
+          <t>Port Louis, Mauritius</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5962,29 +5962,29 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Tunis</t>
+          <t>Port Louis</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Mauritius</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>MU</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>FIH</t>
+          <t>TUN</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Kinshasa, DR Congo</t>
+          <t>Tunis, Tunisia</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5994,25 +5994,29 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Kinshasa</t>
+          <t>Tunis</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>DR Congo</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr"/>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t>CAI</t>
+          <t>FIH</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Cairo, Egypt</t>
+          <t>Kinshasa, DR Congo</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6022,29 +6026,25 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Cairo</t>
+          <t>Kinshasa</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
+          <t>DR Congo</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t>WDH</t>
+          <t>CAI</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Windhoek, Namibia</t>
+          <t>Cairo, Egypt</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6054,29 +6054,29 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Windhoek</t>
+          <t>Cairo</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>EG</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t>ASK</t>
+          <t>WDH</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Yamoussoukro, Ivory Coast</t>
+          <t>Windhoek, Namibia</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6086,25 +6086,29 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Yamoussoukro</t>
+          <t>Windhoek</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr"/>
+          <t>Namibia</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t>ABJ</t>
+          <t>ASK</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Abidjan, Ivory Coast</t>
+          <t>Yamoussoukro, Ivory Coast</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6114,7 +6118,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Abidjan</t>
+          <t>Yamoussoukro</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -6127,12 +6131,12 @@
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>ABJ</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Kampala, Uganda</t>
+          <t>Abidjan, Ivory Coast</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6142,29 +6146,25 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Kampala</t>
+          <t>Abidjan</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Uganda</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
+          <t>Ivory Coast</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>RUN</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Saint-Denis, Réunion</t>
+          <t>Kampala, Uganda</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6174,25 +6174,29 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Saint-Denis</t>
+          <t>Kampala</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Réunion</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr"/>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t>LUN</t>
+          <t>RUN</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Lusaka, Zambia</t>
+          <t>Saint-Denis, Réunion</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6202,29 +6206,25 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Lusaka</t>
+          <t>Saint-Denis</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Zambia</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>ZM</t>
-        </is>
-      </c>
+          <t>Réunion</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t>ADD</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Addis Ababa, Ethiopia</t>
+          <t>Lusaka, Zambia</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6234,29 +6234,29 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Addis Ababa</t>
+          <t>Lusaka</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>ET</t>
+          <t>ZM</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t>LLW</t>
+          <t>ADD</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Lilongwe, Malawi</t>
+          <t>Addis Ababa, Ethiopia</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6266,29 +6266,29 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Lilongwe</t>
+          <t>Addis Ababa</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Malawi</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>MW</t>
+          <t>ET</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t>CZL</t>
+          <t>LLW</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Constantine, Algeria</t>
+          <t>Lilongwe, Malawi</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6298,61 +6298,61 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Constantine</t>
+          <t>Lilongwe</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>DZ</t>
+          <t>MW</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>CZL</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Ahmedabad, India</t>
+          <t>Constantine, Algeria</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>Constantine</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>DZ</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Almaty, Kazakhstan</t>
+          <t>Ahmedabad, India</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6362,29 +6362,29 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Almaty</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>BLR</t>
+          <t>ALA</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Bangalore, India</t>
+          <t>Almaty, Kazakhstan</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6394,29 +6394,29 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Almaty</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>KZ</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>BKK</t>
+          <t>BLR</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Bangkok, Thailand</t>
+          <t>Bangalore, India</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6426,29 +6426,29 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>BWN</t>
+          <t>BKK</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Bandar Seri Begawan, Brunei</t>
+          <t>Bangkok, Thailand</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6458,29 +6458,29 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Bandar Seri Begawan</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Brunei</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>BN</t>
+          <t>TH</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>BWN</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Cebu, Philippines</t>
+          <t>Bandar Seri Begawan, Brunei</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6490,29 +6490,29 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Cebu</t>
+          <t>Bandar Seri Begawan</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Brunei</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>BN</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>IXC</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Chandigarh, India</t>
+          <t>Cebu, Philippines</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6522,29 +6522,29 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Chandigarh</t>
+          <t>Cebu</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>PH</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>CGD</t>
+          <t>IXC</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Changde, China</t>
+          <t>Chandigarh, India</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6554,29 +6554,29 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Changde</t>
+          <t>Chandigarh</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>CGD</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Chennai, India</t>
+          <t>Changde, China</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -6586,29 +6586,29 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Changde</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t>CGP</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Chittagong, Bangladesh</t>
+          <t>Chennai, India</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -6618,29 +6618,29 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Chittagong</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>BD</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t>CMB</t>
+          <t>CGP</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Colombo, Sri Lanka</t>
+          <t>Chittagong, Bangladesh</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -6650,29 +6650,29 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Colombo</t>
+          <t>Chittagong</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>LK</t>
+          <t>BD</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>CMB</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Dhaka, Bangladesh</t>
+          <t>Colombo, Sri Lanka</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -6682,29 +6682,29 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>Colombo</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>Sri Lanka</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>BD</t>
+          <t>LK</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>FUO</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Foshan, China</t>
+          <t>Dhaka, Bangladesh</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -6714,29 +6714,29 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Foshan</t>
+          <t>Dhaka</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>BD</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>FUK</t>
+          <t>FUO</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Fukuoka, Japan</t>
+          <t>Foshan, China</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -6746,29 +6746,29 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Fukuoka</t>
+          <t>Foshan</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>FOC</t>
+          <t>FUK</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Fuzhou, China</t>
+          <t>Fukuoka, Japan</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -6778,29 +6778,29 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Fuzhou</t>
+          <t>Fukuoka</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>JP</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>FOC</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Guangzhou, China</t>
+          <t>Fuzhou, China</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Guangzhou</t>
+          <t>Fuzhou</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -6827,12 +6827,12 @@
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t>HAK</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Chengmai, China</t>
+          <t>Guangzhou, China</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Chengmai</t>
+          <t>Guangzhou</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -6859,12 +6859,12 @@
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
         <is>
-          <t>HAN</t>
+          <t>HAK</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Hanoi, Vietnam</t>
+          <t>Chengmai, China</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -6874,29 +6874,29 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Hanoi</t>
+          <t>Chengmai</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>VN</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
         <is>
-          <t>SJW</t>
+          <t>HAN</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Shijiazhuang, China</t>
+          <t>Hanoi, Vietnam</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -6906,29 +6906,29 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Shijiazhuang</t>
+          <t>Hanoi</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>VN</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t>SGN</t>
+          <t>SJW</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City, Vietnam</t>
+          <t>Shijiazhuang, China</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6938,29 +6938,29 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Shijiazhuang</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>VN</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="inlineStr">
         <is>
-          <t>HKG</t>
+          <t>SGN</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Ho Chi Minh City, Vietnam</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6968,19 +6968,31 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
-      <c r="E206" t="inlineStr"/>
-      <c r="F206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Ho Chi Minh City</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>VN</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
         <is>
-          <t>HYD</t>
+          <t>HKG</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Hyderabad, India</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -6988,31 +7000,19 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>Hyderabad</t>
-        </is>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="1" t="inlineStr">
         <is>
-          <t>ISB</t>
+          <t>HYD</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Islamabad, Pakistan</t>
+          <t>Hyderabad, India</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7022,29 +7022,29 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Islamabad</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="inlineStr">
         <is>
-          <t>CGK</t>
+          <t>ISB</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Jakarta, Indonesia</t>
+          <t>Islamabad, Pakistan</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7054,29 +7054,29 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Jakarta</t>
+          <t>Islamabad</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>PK</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="inlineStr">
         <is>
-          <t>TNA</t>
+          <t>CGK</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Zibo, China</t>
+          <t>Jakarta, Indonesia</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7086,29 +7086,29 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Zibo</t>
+          <t>Jakarta</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
         <is>
-          <t>JHB</t>
+          <t>TNA</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Johor Bahru, Malaysia</t>
+          <t>Zibo, China</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -7118,29 +7118,29 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Johor Bahru</t>
+          <t>Zibo</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
         <is>
-          <t>KNU</t>
+          <t>JHB</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Kanpur, India</t>
+          <t>Johor Bahru, Malaysia</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -7150,29 +7150,29 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Kanpur</t>
+          <t>Johor Bahru</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>MY</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="inlineStr">
         <is>
-          <t>KHH</t>
+          <t>KNU</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Kaohsiung City, Taiwan</t>
+          <t>Kanpur, India</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -7182,29 +7182,29 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Kaohsiung City</t>
+          <t>Kanpur</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="inlineStr">
         <is>
-          <t>KHI</t>
+          <t>KHH</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Karachi, Pakistan</t>
+          <t>Kaohsiung City, Taiwan</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -7214,29 +7214,29 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Karachi</t>
+          <t>Kaohsiung City</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>TW</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="inlineStr">
         <is>
-          <t>KTM</t>
+          <t>KHI</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Kathmandu, Nepal</t>
+          <t>Karachi, Pakistan</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -7246,29 +7246,29 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Kathmandu</t>
+          <t>Karachi</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>PK</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="inlineStr">
         <is>
-          <t>CCU</t>
+          <t>KTM</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Kolkata, India</t>
+          <t>Kathmandu, Nepal</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -7278,29 +7278,29 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Kathmandu</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NP</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
         <is>
-          <t>KJA</t>
+          <t>CCU</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Krasnoyarsk, Russia</t>
+          <t>Kolkata, India</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -7310,29 +7310,29 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Krasnoyarsk</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>RU</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="inlineStr">
         <is>
-          <t>KUL</t>
+          <t>KJA</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Kuala Lumpur, Malaysia</t>
+          <t>Krasnoyarsk, Russia</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -7342,29 +7342,29 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Krasnoyarsk</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>RU</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="inlineStr">
         <is>
-          <t>PKX</t>
+          <t>KUL</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Langfang, China</t>
+          <t>Kuala Lumpur, Malaysia</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -7374,29 +7374,29 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Langfang</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MY</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
         <is>
-          <t>MFM</t>
+          <t>PKX</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Macau</t>
+          <t>Langfang, China</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -7404,19 +7404,31 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
-      <c r="E220" t="inlineStr"/>
-      <c r="F220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Langfang</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="inlineStr">
         <is>
-          <t>MLE</t>
+          <t>MFM</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Male, Maldives</t>
+          <t>Macau</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -7424,31 +7436,19 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>Maldives</t>
-        </is>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>MV</t>
-        </is>
-      </c>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="1" t="inlineStr">
         <is>
-          <t>MNL</t>
+          <t>MLE</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Manila, Philippines</t>
+          <t>Male, Maldives</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -7458,29 +7458,29 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Manila</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Maldives</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>MV</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="inlineStr">
         <is>
-          <t>BOM</t>
+          <t>MNL</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Mumbai, India</t>
+          <t>Manila, Philippines</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -7490,29 +7490,29 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Manila</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>PH</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="inlineStr">
         <is>
-          <t>NAG</t>
+          <t>BOM</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Nagpur, India</t>
+          <t>Mumbai, India</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Nagpur</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -7539,12 +7539,12 @@
     <row r="225">
       <c r="A225" s="1" t="inlineStr">
         <is>
-          <t>OKA</t>
+          <t>NAG</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Naha, Japan</t>
+          <t>Nagpur, India</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -7554,29 +7554,29 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Naha</t>
+          <t>Nagpur</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="inlineStr">
         <is>
-          <t>DEL</t>
+          <t>OKA</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>New Delhi, India</t>
+          <t>Naha, Japan</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -7586,29 +7586,29 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>Naha</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>JP</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="inlineStr">
         <is>
-          <t>KIX</t>
+          <t>DEL</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Osaka, Japan</t>
+          <t>New Delhi, India</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -7618,29 +7618,29 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Osaka</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="inlineStr">
         <is>
-          <t>PAT</t>
+          <t>KIX</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Patna, India</t>
+          <t>Osaka, Japan</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -7650,29 +7650,29 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Patna</t>
+          <t>Osaka</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>JP</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="inlineStr">
         <is>
-          <t>PNH</t>
+          <t>PAT</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Phnom Penh, Cambodia</t>
+          <t>Patna, India</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -7682,29 +7682,29 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Phnom Penh</t>
+          <t>Patna</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Cambodia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>KH</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="inlineStr">
         <is>
-          <t>TAO</t>
+          <t>PNH</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Qingdao, China</t>
+          <t>Phnom Penh, Cambodia</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -7714,29 +7714,29 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Qingdao</t>
+          <t>Phnom Penh</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>KH</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="inlineStr">
         <is>
-          <t>ICN</t>
+          <t>TAO</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Seoul, South Korea</t>
+          <t>Qingdao, China</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -7746,29 +7746,29 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Seoul</t>
+          <t>Qingdao</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="inlineStr">
         <is>
-          <t>SHA</t>
+          <t>ICN</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Seoul, South Korea</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -7778,29 +7778,29 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Shanghai</t>
+          <t>Seoul</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>KR</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="inlineStr">
         <is>
-          <t>SIN</t>
+          <t>SHA</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Singapore, Singapore</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -7810,29 +7810,29 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="inlineStr">
         <is>
-          <t>URT</t>
+          <t>SIN</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Surat Thani, Thailand</t>
+          <t>Singapore, Singapore</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -7842,29 +7842,29 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Surat Thani</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>SG</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="inlineStr">
         <is>
-          <t>TPE</t>
+          <t>URT</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Taipei</t>
+          <t>Surat Thani, Thailand</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -7872,19 +7872,31 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
-      <c r="E235" t="inlineStr"/>
-      <c r="F235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Surat Thani</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="inlineStr">
         <is>
-          <t>NRT</t>
+          <t>TPE</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Tokyo, Japan</t>
+          <t>Taipei</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -7892,31 +7904,19 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>Tokyo</t>
-        </is>
-      </c>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
+      <c r="D236" t="inlineStr"/>
+      <c r="E236" t="inlineStr"/>
+      <c r="F236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="1" t="inlineStr">
         <is>
-          <t>ULN</t>
+          <t>NRT</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Ulaanbaatar, Mongolia</t>
+          <t>Tokyo, Japan</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -7926,29 +7926,29 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Ulaanbaatar</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Mongolia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>MN</t>
+          <t>JP</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="inlineStr">
         <is>
-          <t>VTE</t>
+          <t>ULN</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Vientiane, Laos</t>
+          <t>Ulaanbaatar, Mongolia</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -7958,29 +7958,29 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Vientiane</t>
+          <t>Ulaanbaatar</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Laos</t>
+          <t>Mongolia</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>MN</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="inlineStr">
         <is>
-          <t>KHN</t>
+          <t>VTE</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Nanchang, China</t>
+          <t>Vientiane, Laos</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -7990,29 +7990,29 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Nanchang</t>
+          <t>Vientiane</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Laos</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>LA</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>KHN</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Yerevan, Armenia</t>
+          <t>Nanchang, China</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -8022,29 +8022,29 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Yerevan</t>
+          <t>Nanchang</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="inlineStr">
         <is>
-          <t>JOG</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Yogyakarta, Indonesia</t>
+          <t>Yerevan, Armenia</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -8054,29 +8054,29 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Yogyakarta</t>
+          <t>Yerevan</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>AM</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="inlineStr">
         <is>
-          <t>CGY</t>
+          <t>JOG</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Cagayan de Oro, Philippines</t>
+          <t>Yogyakarta, Indonesia</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -8086,29 +8086,29 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Cagayan de Oro</t>
+          <t>Yogyakarta</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="inlineStr">
         <is>
-          <t>COK</t>
+          <t>CGY</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Kochi, India</t>
+          <t>Cagayan de Oro, Philippines</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -8118,29 +8118,29 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Cagayan de Oro</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>PH</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="inlineStr">
         <is>
-          <t>DPS</t>
+          <t>COK</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Denpasar, Indonesia</t>
+          <t>Kochi, India</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -8150,29 +8150,29 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Denpasar</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="inlineStr">
         <is>
-          <t>CNN</t>
+          <t>DPS</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Kannur, India</t>
+          <t>Denpasar, Indonesia</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -8182,29 +8182,29 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Kannur</t>
+          <t>Denpasar</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="inlineStr">
         <is>
-          <t>SZX</t>
+          <t>CNN</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Shenzhen, China</t>
+          <t>Kannur, India</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -8214,29 +8214,29 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Shenzhen</t>
+          <t>Kannur</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="inlineStr">
         <is>
-          <t>KWE</t>
+          <t>SZX</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Guiyang, China</t>
+          <t>Shenzhen, China</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Guiyang</t>
+          <t>Shenzhen</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -8263,12 +8263,12 @@
     <row r="248">
       <c r="A248" s="1" t="inlineStr">
         <is>
-          <t>HGH</t>
+          <t>KWE</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Shaoxing, China</t>
+          <t>Guiyang, China</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Shaoxing</t>
+          <t>Guiyang</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -8295,12 +8295,12 @@
     <row r="249">
       <c r="A249" s="1" t="inlineStr">
         <is>
-          <t>CZX</t>
+          <t>HGH</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Changzhou, China</t>
+          <t>Shaoxing, China</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Changzhou</t>
+          <t>Shaoxing</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -8327,12 +8327,12 @@
     <row r="250">
       <c r="A250" s="1" t="inlineStr">
         <is>
-          <t>KMG</t>
+          <t>CZX</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Kunming, China</t>
+          <t>Changzhou, China</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -8342,7 +8342,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Kunming</t>
+          <t>Changzhou</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -8359,12 +8359,12 @@
     <row r="251">
       <c r="A251" s="1" t="inlineStr">
         <is>
-          <t>CNX</t>
+          <t>KMG</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Chiang Mai, Thailand</t>
+          <t>Kunming, China</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -8374,29 +8374,29 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Chiang Mai</t>
+          <t>Kunming</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="inlineStr">
         <is>
-          <t>CGO</t>
+          <t>CNX</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Zhengzhou, China</t>
+          <t>Chiang Mai, Thailand</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -8406,29 +8406,29 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Zhengzhou</t>
+          <t>Chiang Mai</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>TH</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="inlineStr">
         <is>
-          <t>TYN</t>
+          <t>CGO</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Yangquan, China</t>
+          <t>Zhengzhou, China</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -8438,7 +8438,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Yangquan</t>
+          <t>Zhengzhou</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -8455,12 +8455,12 @@
     <row r="254">
       <c r="A254" s="1" t="inlineStr">
         <is>
-          <t>CSX</t>
+          <t>TYN</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Changsha, China</t>
+          <t>Yangquan, China</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -8470,7 +8470,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Changsha</t>
+          <t>Yangquan</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -8487,12 +8487,12 @@
     <row r="255">
       <c r="A255" s="1" t="inlineStr">
         <is>
-          <t>DLC</t>
+          <t>CSX</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Dalian, China</t>
+          <t>Changsha, China</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Dalian</t>
+          <t>Changsha</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -8519,12 +8519,12 @@
     <row r="256">
       <c r="A256" s="1" t="inlineStr">
         <is>
-          <t>BHY</t>
+          <t>DLC</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Beihai, China</t>
+          <t>Dalian, China</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Beihai</t>
+          <t>Dalian</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -8551,12 +8551,12 @@
     <row r="257">
       <c r="A257" s="1" t="inlineStr">
         <is>
-          <t>CKG</t>
+          <t>BHY</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Chongqing, China</t>
+          <t>Beihai, China</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -8566,7 +8566,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Chongqing</t>
+          <t>Beihai</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -8583,12 +8583,12 @@
     <row r="258">
       <c r="A258" s="1" t="inlineStr">
         <is>
-          <t>XFN</t>
+          <t>CKG</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Xiangyang, China</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Xiangyang</t>
+          <t>Chongqing</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -8615,12 +8615,12 @@
     <row r="259">
       <c r="A259" s="1" t="inlineStr">
         <is>
-          <t>DAD</t>
+          <t>XFN</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Da Nang, Vietnam</t>
+          <t>Xiangyang, China</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -8630,29 +8630,29 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Xiangyang</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>VN</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="inlineStr">
         <is>
-          <t>JXG</t>
+          <t>DAD</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Jiaxing, China</t>
+          <t>Da Nang, Vietnam</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -8662,29 +8662,29 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Jiaxing</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>VN</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="inlineStr">
         <is>
-          <t>CRK</t>
+          <t>JXG</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Tarlac City, Philippines</t>
+          <t>Jiaxing, China</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -8694,29 +8694,29 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Tarlac City</t>
+          <t>Jiaxing</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="inlineStr">
         <is>
-          <t>PBH</t>
+          <t>CRK</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Thimphu, Bhutan</t>
+          <t>Tarlac City, Philippines</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -8726,29 +8726,29 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Thimphu</t>
+          <t>Tarlac City</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Bhutan</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>PH</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="inlineStr">
         <is>
-          <t>XIY</t>
+          <t>PBH</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Baoji, China</t>
+          <t>Thimphu, Bhutan</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -8758,29 +8758,29 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Baoji</t>
+          <t>Thimphu</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Bhutan</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>BT</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="inlineStr">
         <is>
-          <t>NQZ</t>
+          <t>XIY</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Astana, Kazakhstan</t>
+          <t>Baoji, China</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -8790,29 +8790,29 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Baoji</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="inlineStr">
         <is>
-          <t>KCH</t>
+          <t>NQZ</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Kuching, Malaysia</t>
+          <t>Astana, Kazakhstan</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -8822,29 +8822,29 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Kuching</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>KZ</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="1" t="inlineStr">
         <is>
-          <t>AKX</t>
+          <t>KCH</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Aktobe, Kazakhstan</t>
+          <t>Kuching, Malaysia</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -8854,29 +8854,29 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Kuching</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>MY</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>AKX</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Tongren, China</t>
+          <t>Aktobe, Kazakhstan</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -8886,29 +8886,29 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Tongren</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>KZ</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Taizhou, China</t>
+          <t>Tongren, China</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -8918,7 +8918,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Taizhou</t>
+          <t>Tongren</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -8935,12 +8935,12 @@
     <row r="269">
       <c r="A269" s="1" t="inlineStr">
         <is>
-          <t>FRU</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Bishkek, Kyrgyzstan</t>
+          <t>Taizhou, China</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -8950,29 +8950,29 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Bishkek</t>
+          <t>Taizhou</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Kyrgyzstan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="inlineStr">
         <is>
-          <t>MLG</t>
+          <t>FRU</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Malang, Indonesia</t>
+          <t>Bishkek, Kyrgyzstan</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -8982,29 +8982,29 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Malang</t>
+          <t>Bishkek</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Kyrgyzstan</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>KG</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="inlineStr">
         <is>
-          <t>LHE</t>
+          <t>MLG</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Lahore, Pakistan</t>
+          <t>Malang, Indonesia</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -9014,29 +9014,29 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Lahore</t>
+          <t>Malang</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="inlineStr">
         <is>
-          <t>CTU</t>
+          <t>LHE</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Chengdu, China</t>
+          <t>Lahore, Pakistan</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -9046,29 +9046,29 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Chengdu</t>
+          <t>Lahore</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>PK</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="inlineStr">
         <is>
-          <t>AGR</t>
+          <t>CTU</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Agra, India</t>
+          <t>Chengdu, China</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -9078,29 +9078,29 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Agra</t>
+          <t>Chengdu</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="inlineStr">
         <is>
-          <t>CJB</t>
+          <t>AGR</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Coimbatore, India</t>
+          <t>Agra, India</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Coimbatore</t>
+          <t>Agra</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -9127,12 +9127,12 @@
     <row r="275">
       <c r="A275" s="1" t="inlineStr">
         <is>
-          <t>ACX</t>
+          <t>CJB</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Xingyi, China</t>
+          <t>Coimbatore, India</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -9142,29 +9142,29 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Xingyi</t>
+          <t>Coimbatore</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="1" t="inlineStr">
         <is>
-          <t>BBI</t>
+          <t>ACX</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Bhubaneswar, India</t>
+          <t>Xingyi, China</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -9174,29 +9174,29 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Bhubaneswar</t>
+          <t>Xingyi</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="inlineStr">
         <is>
-          <t>LYA</t>
+          <t>BBI</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Luoyang, China</t>
+          <t>Bhubaneswar, India</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -9206,61 +9206,61 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Luoyang</t>
+          <t>Bhubaneswar</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="1" t="inlineStr">
         <is>
-          <t>ABQ</t>
+          <t>LYA</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, United States</t>
+          <t>Luoyang, China</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Albuquerque, NM</t>
+          <t>Luoyang</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="1" t="inlineStr">
         <is>
-          <t>ANC</t>
+          <t>ABQ</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Anchorage, AK, United States</t>
+          <t>Albuquerque, NM, United States</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Anchorage, AK</t>
+          <t>Albuquerque, NM</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -9287,12 +9287,12 @@
     <row r="280">
       <c r="A280" s="1" t="inlineStr">
         <is>
-          <t>IAD</t>
+          <t>ANC</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Ashburn, VA, United States</t>
+          <t>Anchorage, AK, United States</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -9302,7 +9302,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Ashburn, VA</t>
+          <t>Anchorage, AK</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -9319,12 +9319,12 @@
     <row r="281">
       <c r="A281" s="1" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>IAD</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Atlanta, GA, United States</t>
+          <t>Ashburn, VA, United States</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Ashburn, VA</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -9351,12 +9351,12 @@
     <row r="282">
       <c r="A282" s="1" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Austin, TX, United States</t>
+          <t>Atlanta, GA, United States</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -9383,12 +9383,12 @@
     <row r="283">
       <c r="A283" s="1" t="inlineStr">
         <is>
-          <t>BGR</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Bangor, ME, United States</t>
+          <t>Austin, TX, United States</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -9398,7 +9398,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Bangor, ME</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -9415,12 +9415,12 @@
     <row r="284">
       <c r="A284" s="1" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BGR</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Boston, MA, United States</t>
+          <t>Bangor, ME, United States</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -9430,7 +9430,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Bangor, ME</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -9447,12 +9447,12 @@
     <row r="285">
       <c r="A285" s="1" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Buffalo, NY, United States</t>
+          <t>Boston, MA, United States</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -9462,7 +9462,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Buffalo, NY</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -9479,12 +9479,12 @@
     <row r="286">
       <c r="A286" s="1" t="inlineStr">
         <is>
-          <t>YYC</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Calgary, AB, Canada</t>
+          <t>Buffalo, NY, United States</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -9494,29 +9494,29 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Calgary, AB</t>
+          <t>Buffalo, NY</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="1" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>YYC</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Charlotte, NC, United States</t>
+          <t>Calgary, AB, Canada</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -9526,29 +9526,29 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Charlotte, NC</t>
+          <t>Calgary, AB</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="inlineStr">
         <is>
-          <t>ORD</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Chicago, IL, United States</t>
+          <t>Charlotte, NC, United States</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -9558,7 +9558,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Charlotte, NC</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -9575,12 +9575,12 @@
     <row r="289">
       <c r="A289" s="1" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ORD</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Cleveland, OH, United States</t>
+          <t>Chicago, IL, United States</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Cleveland, OH</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -9607,12 +9607,12 @@
     <row r="290">
       <c r="A290" s="1" t="inlineStr">
         <is>
-          <t>CMH</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Columbus, OH, United States</t>
+          <t>Cleveland, OH, United States</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Columbus, OH</t>
+          <t>Cleveland, OH</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -9639,12 +9639,12 @@
     <row r="291">
       <c r="A291" s="1" t="inlineStr">
         <is>
-          <t>DFW</t>
+          <t>CMH</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Dallas, TX, United States</t>
+          <t>Columbus, OH, United States</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -9654,7 +9654,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Dallas, TX</t>
+          <t>Columbus, OH</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -9671,12 +9671,12 @@
     <row r="292">
       <c r="A292" s="1" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DFW</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Denver, CO, United States</t>
+          <t>Dallas, TX, United States</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -9686,7 +9686,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>Dallas, TX</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -9703,12 +9703,12 @@
     <row r="293">
       <c r="A293" s="1" t="inlineStr">
         <is>
-          <t>DTW</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Detroit, MI, United States</t>
+          <t>Denver, CO, United States</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Detroit, MI</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -9735,12 +9735,12 @@
     <row r="294">
       <c r="A294" s="1" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DTW</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Durham, NC, United States</t>
+          <t>Detroit, MI, United States</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -9750,7 +9750,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Durham, NC</t>
+          <t>Detroit, MI</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -9767,12 +9767,12 @@
     <row r="295">
       <c r="A295" s="1" t="inlineStr">
         <is>
-          <t>GDL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Guadalajara, Mexico</t>
+          <t>Durham, NC, United States</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -9782,29 +9782,29 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Durham, NC</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="1" t="inlineStr">
         <is>
-          <t>YHZ</t>
+          <t>GDL</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Halifax, Canada</t>
+          <t>Guadalajara, Mexico</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -9814,29 +9814,29 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Halifax</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>MX</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="inlineStr">
         <is>
-          <t>HNL</t>
+          <t>YHZ</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Honolulu, HI, United States</t>
+          <t>Halifax, Canada</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -9846,29 +9846,29 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Honolulu, HI</t>
+          <t>Halifax</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="inlineStr">
         <is>
-          <t>IAH</t>
+          <t>HNL</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Houston, TX, United States</t>
+          <t>Honolulu, HI, United States</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -9878,7 +9878,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Houston, TX</t>
+          <t>Honolulu, HI</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -9895,12 +9895,12 @@
     <row r="299">
       <c r="A299" s="1" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>IAH</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, United States</t>
+          <t>Houston, TX, United States</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -9910,7 +9910,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Indianapolis, IN</t>
+          <t>Houston, TX</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -9927,12 +9927,12 @@
     <row r="300">
       <c r="A300" s="1" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, United States</t>
+          <t>Indianapolis, IN, United States</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Jacksonville, FL</t>
+          <t>Indianapolis, IN</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -9959,12 +9959,12 @@
     <row r="301">
       <c r="A301" s="1" t="inlineStr">
         <is>
-          <t>MCI</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Kansas City, MO, United States</t>
+          <t>Jacksonville, FL, United States</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Kansas City, MO</t>
+          <t>Jacksonville, FL</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -9991,12 +9991,12 @@
     <row r="302">
       <c r="A302" s="1" t="inlineStr">
         <is>
-          <t>KIN</t>
+          <t>MCI</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Kingston, Jamaica</t>
+          <t>Kansas City, MO, United States</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -10006,29 +10006,29 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Kingston</t>
+          <t>Kansas City, MO</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Jamaica</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>JM</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="inlineStr">
         <is>
-          <t>LAS</t>
+          <t>KIN</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, United States</t>
+          <t>Kingston, Jamaica</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -10038,29 +10038,29 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Las Vegas, NV</t>
+          <t>Kingston</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Jamaica</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JM</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="inlineStr">
         <is>
-          <t>LAX</t>
+          <t>LAS</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, United States</t>
+          <t>Las Vegas, NV, United States</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -10070,7 +10070,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
+          <t>Las Vegas, NV</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -10087,12 +10087,12 @@
     <row r="305">
       <c r="A305" s="1" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>LAX</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Memphis, TN, United States</t>
+          <t>Los Angeles, CA, United States</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Memphis, TN</t>
+          <t>Los Angeles, CA</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -10119,12 +10119,12 @@
     <row r="306">
       <c r="A306" s="1" t="inlineStr">
         <is>
-          <t>MEX</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Mexico City, Mexico</t>
+          <t>Memphis, TN, United States</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -10134,29 +10134,29 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Mexico City</t>
+          <t>Memphis, TN</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MEX</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Miami, FL, United States</t>
+          <t>Mexico City, Mexico</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -10166,29 +10166,29 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Miami, FL</t>
+          <t>Mexico City</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="inlineStr">
         <is>
-          <t>MSP</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, United States</t>
+          <t>Miami, FL, United States</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -10198,7 +10198,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Minneapolis, MN</t>
+          <t>Miami, FL</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -10215,12 +10215,12 @@
     <row r="309">
       <c r="A309" s="1" t="inlineStr">
         <is>
-          <t>YUL</t>
+          <t>MSP</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Montréal, QC, Canada</t>
+          <t>Minneapolis, MN, United States</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -10230,29 +10230,29 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Montréal, QC</t>
+          <t>Minneapolis, MN</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="1" t="inlineStr">
         <is>
-          <t>BNA</t>
+          <t>YUL</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Nashville, United States</t>
+          <t>Montréal, QC, Canada</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -10262,29 +10262,29 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Nashville</t>
+          <t>Montréal, QC</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="inlineStr">
         <is>
-          <t>EWR</t>
+          <t>BNA</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Newark, NJ, United States</t>
+          <t>Nashville, United States</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -10294,7 +10294,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Newark, NJ</t>
+          <t>Nashville</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -10311,12 +10311,12 @@
     <row r="312">
       <c r="A312" s="1" t="inlineStr">
         <is>
-          <t>ORF</t>
+          <t>EWR</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Norfolk, VA, United States</t>
+          <t>Newark, NJ, United States</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Norfolk, VA</t>
+          <t>Newark, NJ</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -10343,12 +10343,12 @@
     <row r="313">
       <c r="A313" s="1" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>ORF</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, United States</t>
+          <t>Norfolk, VA, United States</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK</t>
+          <t>Norfolk, VA</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -10375,12 +10375,12 @@
     <row r="314">
       <c r="A314" s="1" t="inlineStr">
         <is>
-          <t>OMA</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Omaha, NE, United States</t>
+          <t>Oklahoma City, OK, United States</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -10390,7 +10390,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Omaha, NE</t>
+          <t>Oklahoma City, OK</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -10407,12 +10407,12 @@
     <row r="315">
       <c r="A315" s="1" t="inlineStr">
         <is>
-          <t>YOW</t>
+          <t>OMA</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Ottawa, Canada</t>
+          <t>Omaha, NE, United States</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -10422,29 +10422,29 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Ottawa</t>
+          <t>Omaha, NE</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="1" t="inlineStr">
         <is>
-          <t>PHL</t>
+          <t>YOW</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Philadelphia, United States</t>
+          <t>Ottawa, Canada</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -10454,29 +10454,29 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Ottawa</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="1" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>PHL</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, United States</t>
+          <t>Philadelphia, United States</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Phoenix, AZ</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -10503,12 +10503,12 @@
     <row r="318">
       <c r="A318" s="1" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, United States</t>
+          <t>Phoenix, AZ, United States</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -10518,7 +10518,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA</t>
+          <t>Phoenix, AZ</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -10535,12 +10535,12 @@
     <row r="319">
       <c r="A319" s="1" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Portland, OR, United States</t>
+          <t>Pittsburgh, PA, United States</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -10550,7 +10550,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Portland, OR</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -10567,12 +10567,12 @@
     <row r="320">
       <c r="A320" s="1" t="inlineStr">
         <is>
-          <t>QRO</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Queretaro, MX, Mexico</t>
+          <t>Portland, OR, United States</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -10582,29 +10582,29 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Queretaro, MX</t>
+          <t>Portland, OR</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="inlineStr">
         <is>
-          <t>RIC</t>
+          <t>QRO</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Richmond, VA, United States</t>
+          <t>Queretaro, MX, Mexico</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -10614,29 +10614,29 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Richmond, VA</t>
+          <t>Queretaro, MX</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="inlineStr">
         <is>
-          <t>SMF</t>
+          <t>RIC</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Sacramento, CA, United States</t>
+          <t>Richmond, VA, United States</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -10646,7 +10646,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Sacramento, CA</t>
+          <t>Richmond, VA</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -10663,12 +10663,12 @@
     <row r="323">
       <c r="A323" s="1" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>SMF</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, United States</t>
+          <t>Sacramento, CA, United States</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -10678,7 +10678,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT</t>
+          <t>Sacramento, CA</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -10695,12 +10695,12 @@
     <row r="324">
       <c r="A324" s="1" t="inlineStr">
         <is>
-          <t>SAT</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>San Antonio, TX, United States</t>
+          <t>Salt Lake City, UT, United States</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -10710,7 +10710,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>San Antonio, TX</t>
+          <t>Salt Lake City, UT</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -10727,12 +10727,12 @@
     <row r="325">
       <c r="A325" s="1" t="inlineStr">
         <is>
-          <t>SAN</t>
+          <t>SAT</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>San Diego, CA, United States</t>
+          <t>San Antonio, TX, United States</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>San Diego, CA</t>
+          <t>San Antonio, TX</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -10759,12 +10759,12 @@
     <row r="326">
       <c r="A326" s="1" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>SAN</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>San Francisco, CA, United States</t>
+          <t>San Diego, CA, United States</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -10774,7 +10774,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>San Diego, CA</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -10791,12 +10791,12 @@
     <row r="327">
       <c r="A327" s="1" t="inlineStr">
         <is>
-          <t>SJC</t>
+          <t>SFO</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>San Jose, CA, United States</t>
+          <t>San Francisco, CA, United States</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -10806,7 +10806,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -10823,12 +10823,12 @@
     <row r="328">
       <c r="A328" s="1" t="inlineStr">
         <is>
-          <t>YXE</t>
+          <t>SJC</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Saskatoon, SK, Canada</t>
+          <t>San Jose, CA, United States</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -10838,29 +10838,29 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Saskatoon, SK</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>YXE</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Seattle, WA, United States</t>
+          <t>Saskatoon, SK, Canada</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -10870,29 +10870,29 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Saskatoon, SK</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="inlineStr">
         <is>
-          <t>FSD</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, United States</t>
+          <t>Seattle, WA, United States</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -10902,7 +10902,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -10919,12 +10919,12 @@
     <row r="331">
       <c r="A331" s="1" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>FSD</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>St. Louis, MO, United States</t>
+          <t>Sioux Falls, SD, United States</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>St. Louis, MO</t>
+          <t>Sioux Falls, SD</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -10951,12 +10951,12 @@
     <row r="332">
       <c r="A332" s="1" t="inlineStr">
         <is>
-          <t>TLH</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, United States</t>
+          <t>St. Louis, MO, United States</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -10966,7 +10966,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Tallahassee, FL</t>
+          <t>St. Louis, MO</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -10983,12 +10983,12 @@
     <row r="333">
       <c r="A333" s="1" t="inlineStr">
         <is>
-          <t>TPA</t>
+          <t>TLH</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Tampa, FL, United States</t>
+          <t>Tallahassee, FL, United States</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -10998,7 +10998,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Tampa, FL</t>
+          <t>Tallahassee, FL</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -11015,12 +11015,12 @@
     <row r="334">
       <c r="A334" s="1" t="inlineStr">
         <is>
-          <t>YYZ</t>
+          <t>TPA</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Toronto, ON, Canada</t>
+          <t>Tampa, FL, United States</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -11030,29 +11030,29 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Toronto, ON</t>
+          <t>Tampa, FL</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="inlineStr">
         <is>
-          <t>YVR</t>
+          <t>YYZ</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Vancouver, BC, Canada</t>
+          <t>Toronto, ON, Canada</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -11062,7 +11062,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Vancouver, BC</t>
+          <t>Toronto, ON</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -11079,30 +11079,62 @@
     <row r="336">
       <c r="A336" s="1" t="inlineStr">
         <is>
+          <t>YVR</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Vancouver, BC, Canada</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Vancouver, BC</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="1" t="inlineStr">
+        <is>
           <t>YWG</t>
         </is>
       </c>
-      <c r="B336" t="inlineStr">
+      <c r="B337" t="inlineStr">
         <is>
           <t>Winnipeg, MB, Canada</t>
         </is>
       </c>
-      <c r="C336" t="inlineStr">
+      <c r="C337" t="inlineStr">
         <is>
           <t>North America</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr">
+      <c r="D337" t="inlineStr">
         <is>
           <t>Winnipeg, MB</t>
         </is>
       </c>
-      <c r="E336" t="inlineStr">
+      <c r="E337" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="F336" t="inlineStr">
+      <c r="F337" t="inlineStr">
         <is>
           <t>CA</t>
         </is>

--- a/DC-Colos.xlsx
+++ b/DC-Colos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F337"/>
+  <dimension ref="A1:F338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9255,44 +9255,44 @@
     <row r="279">
       <c r="A279" s="1" t="inlineStr">
         <is>
-          <t>ABQ</t>
+          <t>PNQ</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, United States</t>
+          <t>Pune, India</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Albuquerque, NM</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="1" t="inlineStr">
         <is>
-          <t>ANC</t>
+          <t>ABQ</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Anchorage, AK, United States</t>
+          <t>Albuquerque, NM, United States</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -9302,7 +9302,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Anchorage, AK</t>
+          <t>Albuquerque, NM</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -9319,12 +9319,12 @@
     <row r="281">
       <c r="A281" s="1" t="inlineStr">
         <is>
-          <t>IAD</t>
+          <t>ANC</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Ashburn, VA, United States</t>
+          <t>Anchorage, AK, United States</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Ashburn, VA</t>
+          <t>Anchorage, AK</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -9351,12 +9351,12 @@
     <row r="282">
       <c r="A282" s="1" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>IAD</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Atlanta, GA, United States</t>
+          <t>Ashburn, VA, United States</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Ashburn, VA</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -9383,12 +9383,12 @@
     <row r="283">
       <c r="A283" s="1" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Austin, TX, United States</t>
+          <t>Atlanta, GA, United States</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -9398,7 +9398,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -9415,12 +9415,12 @@
     <row r="284">
       <c r="A284" s="1" t="inlineStr">
         <is>
-          <t>BGR</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Bangor, ME, United States</t>
+          <t>Austin, TX, United States</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -9430,7 +9430,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Bangor, ME</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -9447,12 +9447,12 @@
     <row r="285">
       <c r="A285" s="1" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BGR</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Boston, MA, United States</t>
+          <t>Bangor, ME, United States</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -9462,7 +9462,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Bangor, ME</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -9479,12 +9479,12 @@
     <row r="286">
       <c r="A286" s="1" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Buffalo, NY, United States</t>
+          <t>Boston, MA, United States</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -9494,7 +9494,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Buffalo, NY</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -9511,12 +9511,12 @@
     <row r="287">
       <c r="A287" s="1" t="inlineStr">
         <is>
-          <t>YYC</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Calgary, AB, Canada</t>
+          <t>Buffalo, NY, United States</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -9526,29 +9526,29 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Calgary, AB</t>
+          <t>Buffalo, NY</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>YYC</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Charlotte, NC, United States</t>
+          <t>Calgary, AB, Canada</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -9558,29 +9558,29 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Charlotte, NC</t>
+          <t>Calgary, AB</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="inlineStr">
         <is>
-          <t>ORD</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Chicago, IL, United States</t>
+          <t>Charlotte, NC, United States</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Charlotte, NC</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -9607,12 +9607,12 @@
     <row r="290">
       <c r="A290" s="1" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ORD</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Cleveland, OH, United States</t>
+          <t>Chicago, IL, United States</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Cleveland, OH</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -9639,12 +9639,12 @@
     <row r="291">
       <c r="A291" s="1" t="inlineStr">
         <is>
-          <t>CMH</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Columbus, OH, United States</t>
+          <t>Cleveland, OH, United States</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -9654,7 +9654,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Columbus, OH</t>
+          <t>Cleveland, OH</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -9671,12 +9671,12 @@
     <row r="292">
       <c r="A292" s="1" t="inlineStr">
         <is>
-          <t>DFW</t>
+          <t>CMH</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Dallas, TX, United States</t>
+          <t>Columbus, OH, United States</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -9686,7 +9686,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Dallas, TX</t>
+          <t>Columbus, OH</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -9703,12 +9703,12 @@
     <row r="293">
       <c r="A293" s="1" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DFW</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Denver, CO, United States</t>
+          <t>Dallas, TX, United States</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>Dallas, TX</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -9735,12 +9735,12 @@
     <row r="294">
       <c r="A294" s="1" t="inlineStr">
         <is>
-          <t>DTW</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Detroit, MI, United States</t>
+          <t>Denver, CO, United States</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -9750,7 +9750,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Detroit, MI</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -9767,12 +9767,12 @@
     <row r="295">
       <c r="A295" s="1" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DTW</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Durham, NC, United States</t>
+          <t>Detroit, MI, United States</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -9782,7 +9782,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Durham, NC</t>
+          <t>Detroit, MI</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -9799,12 +9799,12 @@
     <row r="296">
       <c r="A296" s="1" t="inlineStr">
         <is>
-          <t>GDL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Guadalajara, Mexico</t>
+          <t>Durham, NC, United States</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -9814,29 +9814,29 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Durham, NC</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="inlineStr">
         <is>
-          <t>YHZ</t>
+          <t>GDL</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Halifax, Canada</t>
+          <t>Guadalajara, Mexico</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -9846,29 +9846,29 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Halifax</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>MX</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="inlineStr">
         <is>
-          <t>HNL</t>
+          <t>YHZ</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Honolulu, HI, United States</t>
+          <t>Halifax, Canada</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -9878,29 +9878,29 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Honolulu, HI</t>
+          <t>Halifax</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="1" t="inlineStr">
         <is>
-          <t>IAH</t>
+          <t>HNL</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Houston, TX, United States</t>
+          <t>Honolulu, HI, United States</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -9910,7 +9910,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Houston, TX</t>
+          <t>Honolulu, HI</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -9927,12 +9927,12 @@
     <row r="300">
       <c r="A300" s="1" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>IAH</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, United States</t>
+          <t>Houston, TX, United States</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Indianapolis, IN</t>
+          <t>Houston, TX</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -9959,12 +9959,12 @@
     <row r="301">
       <c r="A301" s="1" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, United States</t>
+          <t>Indianapolis, IN, United States</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Jacksonville, FL</t>
+          <t>Indianapolis, IN</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -9991,12 +9991,12 @@
     <row r="302">
       <c r="A302" s="1" t="inlineStr">
         <is>
-          <t>MCI</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Kansas City, MO, United States</t>
+          <t>Jacksonville, FL, United States</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -10006,7 +10006,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Kansas City, MO</t>
+          <t>Jacksonville, FL</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -10023,12 +10023,12 @@
     <row r="303">
       <c r="A303" s="1" t="inlineStr">
         <is>
-          <t>KIN</t>
+          <t>MCI</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Kingston, Jamaica</t>
+          <t>Kansas City, MO, United States</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -10038,29 +10038,29 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Kingston</t>
+          <t>Kansas City, MO</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Jamaica</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>JM</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="inlineStr">
         <is>
-          <t>LAS</t>
+          <t>KIN</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, United States</t>
+          <t>Kingston, Jamaica</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -10070,29 +10070,29 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Las Vegas, NV</t>
+          <t>Kingston</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Jamaica</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JM</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="inlineStr">
         <is>
-          <t>LAX</t>
+          <t>LAS</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, United States</t>
+          <t>Las Vegas, NV, United States</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
+          <t>Las Vegas, NV</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -10119,12 +10119,12 @@
     <row r="306">
       <c r="A306" s="1" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>LAX</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Memphis, TN, United States</t>
+          <t>Los Angeles, CA, United States</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Memphis, TN</t>
+          <t>Los Angeles, CA</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -10151,12 +10151,12 @@
     <row r="307">
       <c r="A307" s="1" t="inlineStr">
         <is>
-          <t>MEX</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Mexico City, Mexico</t>
+          <t>Memphis, TN, United States</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -10166,29 +10166,29 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Mexico City</t>
+          <t>Memphis, TN</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MEX</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Miami, FL, United States</t>
+          <t>Mexico City, Mexico</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -10198,29 +10198,29 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Miami, FL</t>
+          <t>Mexico City</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="inlineStr">
         <is>
-          <t>MSP</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, United States</t>
+          <t>Miami, FL, United States</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Minneapolis, MN</t>
+          <t>Miami, FL</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -10247,12 +10247,12 @@
     <row r="310">
       <c r="A310" s="1" t="inlineStr">
         <is>
-          <t>YUL</t>
+          <t>MSP</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Montréal, QC, Canada</t>
+          <t>Minneapolis, MN, United States</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -10262,29 +10262,29 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Montréal, QC</t>
+          <t>Minneapolis, MN</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="inlineStr">
         <is>
-          <t>BNA</t>
+          <t>YUL</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Nashville, United States</t>
+          <t>Montréal, QC, Canada</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -10294,29 +10294,29 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Nashville</t>
+          <t>Montréal, QC</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="1" t="inlineStr">
         <is>
-          <t>EWR</t>
+          <t>BNA</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Newark, NJ, United States</t>
+          <t>Nashville, United States</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Newark, NJ</t>
+          <t>Nashville</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -10343,12 +10343,12 @@
     <row r="313">
       <c r="A313" s="1" t="inlineStr">
         <is>
-          <t>ORF</t>
+          <t>EWR</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Norfolk, VA, United States</t>
+          <t>Newark, NJ, United States</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Norfolk, VA</t>
+          <t>Newark, NJ</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -10375,12 +10375,12 @@
     <row r="314">
       <c r="A314" s="1" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>ORF</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, United States</t>
+          <t>Norfolk, VA, United States</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -10390,7 +10390,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK</t>
+          <t>Norfolk, VA</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -10407,12 +10407,12 @@
     <row r="315">
       <c r="A315" s="1" t="inlineStr">
         <is>
-          <t>OMA</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Omaha, NE, United States</t>
+          <t>Oklahoma City, OK, United States</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Omaha, NE</t>
+          <t>Oklahoma City, OK</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -10439,12 +10439,12 @@
     <row r="316">
       <c r="A316" s="1" t="inlineStr">
         <is>
-          <t>YOW</t>
+          <t>OMA</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Ottawa, Canada</t>
+          <t>Omaha, NE, United States</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -10454,29 +10454,29 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Ottawa</t>
+          <t>Omaha, NE</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="1" t="inlineStr">
         <is>
-          <t>PHL</t>
+          <t>YOW</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Philadelphia, United States</t>
+          <t>Ottawa, Canada</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -10486,29 +10486,29 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Ottawa</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="1" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>PHL</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, United States</t>
+          <t>Philadelphia, United States</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -10518,7 +10518,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Phoenix, AZ</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -10535,12 +10535,12 @@
     <row r="319">
       <c r="A319" s="1" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, United States</t>
+          <t>Phoenix, AZ, United States</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -10550,7 +10550,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA</t>
+          <t>Phoenix, AZ</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -10567,12 +10567,12 @@
     <row r="320">
       <c r="A320" s="1" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Portland, OR, United States</t>
+          <t>Pittsburgh, PA, United States</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -10582,7 +10582,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Portland, OR</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -10599,12 +10599,12 @@
     <row r="321">
       <c r="A321" s="1" t="inlineStr">
         <is>
-          <t>QRO</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Queretaro, MX, Mexico</t>
+          <t>Portland, OR, United States</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -10614,29 +10614,29 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Queretaro, MX</t>
+          <t>Portland, OR</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="inlineStr">
         <is>
-          <t>RIC</t>
+          <t>QRO</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Richmond, VA, United States</t>
+          <t>Queretaro, MX, Mexico</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -10646,29 +10646,29 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Richmond, VA</t>
+          <t>Queretaro, MX</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="1" t="inlineStr">
         <is>
-          <t>SMF</t>
+          <t>RIC</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Sacramento, CA, United States</t>
+          <t>Richmond, VA, United States</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -10678,7 +10678,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Sacramento, CA</t>
+          <t>Richmond, VA</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -10695,12 +10695,12 @@
     <row r="324">
       <c r="A324" s="1" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>SMF</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, United States</t>
+          <t>Sacramento, CA, United States</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -10710,7 +10710,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT</t>
+          <t>Sacramento, CA</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -10727,12 +10727,12 @@
     <row r="325">
       <c r="A325" s="1" t="inlineStr">
         <is>
-          <t>SAT</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>San Antonio, TX, United States</t>
+          <t>Salt Lake City, UT, United States</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>San Antonio, TX</t>
+          <t>Salt Lake City, UT</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -10759,12 +10759,12 @@
     <row r="326">
       <c r="A326" s="1" t="inlineStr">
         <is>
-          <t>SAN</t>
+          <t>SAT</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>San Diego, CA, United States</t>
+          <t>San Antonio, TX, United States</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -10774,7 +10774,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>San Diego, CA</t>
+          <t>San Antonio, TX</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -10791,12 +10791,12 @@
     <row r="327">
       <c r="A327" s="1" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>SAN</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>San Francisco, CA, United States</t>
+          <t>San Diego, CA, United States</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -10806,7 +10806,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>San Diego, CA</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -10823,12 +10823,12 @@
     <row r="328">
       <c r="A328" s="1" t="inlineStr">
         <is>
-          <t>SJC</t>
+          <t>SFO</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>San Jose, CA, United States</t>
+          <t>San Francisco, CA, United States</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -10855,12 +10855,12 @@
     <row r="329">
       <c r="A329" s="1" t="inlineStr">
         <is>
-          <t>YXE</t>
+          <t>SJC</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Saskatoon, SK, Canada</t>
+          <t>San Jose, CA, United States</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -10870,29 +10870,29 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Saskatoon, SK</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>YXE</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Seattle, WA, United States</t>
+          <t>Saskatoon, SK, Canada</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -10902,29 +10902,29 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Saskatoon, SK</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="1" t="inlineStr">
         <is>
-          <t>FSD</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, United States</t>
+          <t>Seattle, WA, United States</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -10951,12 +10951,12 @@
     <row r="332">
       <c r="A332" s="1" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>FSD</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>St. Louis, MO, United States</t>
+          <t>Sioux Falls, SD, United States</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -10966,7 +10966,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>St. Louis, MO</t>
+          <t>Sioux Falls, SD</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -10983,12 +10983,12 @@
     <row r="333">
       <c r="A333" s="1" t="inlineStr">
         <is>
-          <t>TLH</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, United States</t>
+          <t>St. Louis, MO, United States</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -10998,7 +10998,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Tallahassee, FL</t>
+          <t>St. Louis, MO</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -11015,12 +11015,12 @@
     <row r="334">
       <c r="A334" s="1" t="inlineStr">
         <is>
-          <t>TPA</t>
+          <t>TLH</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Tampa, FL, United States</t>
+          <t>Tallahassee, FL, United States</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Tampa, FL</t>
+          <t>Tallahassee, FL</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -11047,12 +11047,12 @@
     <row r="335">
       <c r="A335" s="1" t="inlineStr">
         <is>
-          <t>YYZ</t>
+          <t>TPA</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Toronto, ON, Canada</t>
+          <t>Tampa, FL, United States</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -11062,29 +11062,29 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Toronto, ON</t>
+          <t>Tampa, FL</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="inlineStr">
         <is>
-          <t>YVR</t>
+          <t>YYZ</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Vancouver, BC, Canada</t>
+          <t>Toronto, ON, Canada</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -11094,7 +11094,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Vancouver, BC</t>
+          <t>Toronto, ON</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -11111,30 +11111,62 @@
     <row r="337">
       <c r="A337" s="1" t="inlineStr">
         <is>
+          <t>YVR</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Vancouver, BC, Canada</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Vancouver, BC</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="inlineStr">
+        <is>
           <t>YWG</t>
         </is>
       </c>
-      <c r="B337" t="inlineStr">
+      <c r="B338" t="inlineStr">
         <is>
           <t>Winnipeg, MB, Canada</t>
         </is>
       </c>
-      <c r="C337" t="inlineStr">
+      <c r="C338" t="inlineStr">
         <is>
           <t>North America</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr">
+      <c r="D338" t="inlineStr">
         <is>
           <t>Winnipeg, MB</t>
         </is>
       </c>
-      <c r="E337" t="inlineStr">
+      <c r="E338" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="F337" t="inlineStr">
+      <c r="F338" t="inlineStr">
         <is>
           <t>CA</t>
         </is>

--- a/DC-Colos.xlsx
+++ b/DC-Colos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F338"/>
+  <dimension ref="A1:F337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5275,44 +5275,44 @@
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>CCP</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Concepción, Chile</t>
+          <t>Accra, Ghana</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Latin America &amp; the Caribbean</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Accra</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>GH</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>ALG</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Accra, Ghana</t>
+          <t>Algiers, Algeria</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5322,29 +5322,29 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Accra</t>
+          <t>Algiers</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>GH</t>
+          <t>DZ</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>ALG</t>
+          <t>AAE</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Algiers, Algeria</t>
+          <t>Annaba, Algeria</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5354,7 +5354,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Algiers</t>
+          <t>Annaba</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -5371,12 +5371,12 @@
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>AAE</t>
+          <t>TNR</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Annaba, Algeria</t>
+          <t>Antananarivo, Madagascar</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5386,29 +5386,29 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Annaba</t>
+          <t>Antananarivo</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>DZ</t>
+          <t>MG</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>TNR</t>
+          <t>CPT</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Antananarivo, Madagascar</t>
+          <t>Cape Town, South Africa</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5418,29 +5418,29 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Antananarivo</t>
+          <t>Cape Town</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>ZA</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>CPT</t>
+          <t>DKR</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Cape Town, South Africa</t>
+          <t>Dakar, Senegal</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5450,29 +5450,29 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Cape Town</t>
+          <t>Dakar</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>SN</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>DKR</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Dakar, Senegal</t>
+          <t>Dar es Salaam, Tanzania</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5482,29 +5482,29 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Dakar</t>
+          <t>Dar es Salaam</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>SN</t>
+          <t>TZ</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>JIB</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Dar es Salaam, Tanzania</t>
+          <t>Djibouti, Djibouti</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5514,29 +5514,29 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Dar es Salaam</t>
+          <t>Djibouti</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Djibouti</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>TZ</t>
+          <t>DJ</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>JIB</t>
+          <t>DUR</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Djibouti, Djibouti</t>
+          <t>Durban, South Africa</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5546,29 +5546,29 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Djibouti</t>
+          <t>Durban</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Djibouti</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>DJ</t>
+          <t>ZA</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>DUR</t>
+          <t>GBE</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Durban, South Africa</t>
+          <t>Gaborone, Botswana</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5578,29 +5578,29 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Durban</t>
+          <t>Gaborone</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>BW</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>GBE</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Gaborone, Botswana</t>
+          <t>Harare, Zimbabwe</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5610,29 +5610,29 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Gaborone</t>
+          <t>Harare</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>BW</t>
+          <t>ZW</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>HRE</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Harare, Zimbabwe</t>
+          <t>Johannesburg, South Africa</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5642,29 +5642,29 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Harare</t>
+          <t>Johannesburg</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>ZW</t>
+          <t>ZA</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>KGL</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Johannesburg, South Africa</t>
+          <t>Kigali, Rwanda</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -5674,29 +5674,29 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Johannesburg</t>
+          <t>Kigali</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>RW</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>KGL</t>
+          <t>LOS</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Kigali, Rwanda</t>
+          <t>Lagos, Nigeria</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -5706,29 +5706,29 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Kigali</t>
+          <t>Lagos</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>NG</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>LOS</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Lagos, Nigeria</t>
+          <t>Luanda, Angola</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -5738,29 +5738,29 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Lagos</t>
+          <t>Luanda</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>NG</t>
+          <t>AO</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>MPM</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Luanda, Angola</t>
+          <t>Maputo, Mozambique</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5770,29 +5770,29 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Luanda</t>
+          <t>Maputo</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>AO</t>
+          <t>MZ</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>MPM</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Maputo, Mozambique</t>
+          <t>Mombasa, Kenya</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5802,29 +5802,29 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Maputo</t>
+          <t>Mombasa</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>MZ</t>
+          <t>KE</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Mombasa, Kenya</t>
+          <t>Nairobi, Kenya</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Mombasa</t>
+          <t>Nairobi</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -5851,12 +5851,12 @@
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>ORN</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Nairobi, Kenya</t>
+          <t>Oran, Algeria</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5866,29 +5866,29 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Nairobi</t>
+          <t>Oran</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>KE</t>
+          <t>DZ</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>ORN</t>
+          <t>OUA</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Oran, Algeria</t>
+          <t>Ouagadougou, Burkina Faso</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5898,29 +5898,29 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Oran</t>
+          <t>Ouagadougou</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Burkina Faso</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>DZ</t>
+          <t>BF</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>OUA</t>
+          <t>MRU</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Ouagadougou, Burkina Faso</t>
+          <t>Port Louis, Mauritius</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5930,29 +5930,29 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Ouagadougou</t>
+          <t>Port Louis</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Burkina Faso</t>
+          <t>Mauritius</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>BF</t>
+          <t>MU</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>MRU</t>
+          <t>TUN</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Port Louis, Mauritius</t>
+          <t>Tunis, Tunisia</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5962,29 +5962,29 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Port Louis</t>
+          <t>Tunis</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Mauritius</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TN</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>TUN</t>
+          <t>FIH</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Tunis, Tunisia</t>
+          <t>Kinshasa, DR Congo</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5994,29 +5994,25 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Tunis</t>
+          <t>Kinshasa</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Tunisia</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>TN</t>
-        </is>
-      </c>
+          <t>DR Congo</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t>FIH</t>
+          <t>CAI</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Kinshasa, DR Congo</t>
+          <t>Cairo, Egypt</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6026,25 +6022,29 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Kinshasa</t>
+          <t>Cairo</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>DR Congo</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr"/>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t>CAI</t>
+          <t>WDH</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Cairo, Egypt</t>
+          <t>Windhoek, Namibia</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6054,29 +6054,29 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Cairo</t>
+          <t>Windhoek</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t>WDH</t>
+          <t>ASK</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Windhoek, Namibia</t>
+          <t>Yamoussoukro, Ivory Coast</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6086,29 +6086,25 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Windhoek</t>
+          <t>Yamoussoukro</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Namibia</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+          <t>Ivory Coast</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t>ASK</t>
+          <t>ABJ</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Yamoussoukro, Ivory Coast</t>
+          <t>Abidjan, Ivory Coast</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6118,7 +6114,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Yamoussoukro</t>
+          <t>Abidjan</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -6131,12 +6127,12 @@
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t>ABJ</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Abidjan, Ivory Coast</t>
+          <t>Kampala, Uganda</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6146,25 +6142,29 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Abidjan</t>
+          <t>Kampala</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr"/>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>RUN</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Kampala, Uganda</t>
+          <t>Saint-Denis, Réunion</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6174,29 +6174,25 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Kampala</t>
+          <t>Saint-Denis</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Uganda</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
+          <t>Réunion</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t>RUN</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Saint-Denis, Réunion</t>
+          <t>Lusaka, Zambia</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6206,25 +6202,29 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Saint-Denis</t>
+          <t>Lusaka</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Réunion</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr"/>
+          <t>Zambia</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>ZM</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t>LUN</t>
+          <t>ADD</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Lusaka, Zambia</t>
+          <t>Addis Ababa, Ethiopia</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6234,29 +6234,29 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Lusaka</t>
+          <t>Addis Ababa</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>ZM</t>
+          <t>ET</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t>ADD</t>
+          <t>LLW</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Addis Ababa, Ethiopia</t>
+          <t>Lilongwe, Malawi</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6266,29 +6266,29 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Addis Ababa</t>
+          <t>Lilongwe</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>ET</t>
+          <t>MW</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t>LLW</t>
+          <t>CZL</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Lilongwe, Malawi</t>
+          <t>Constantine, Algeria</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6298,61 +6298,61 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Lilongwe</t>
+          <t>Constantine</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Malawi</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>MW</t>
+          <t>DZ</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t>CZL</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Constantine, Algeria</t>
+          <t>Ahmedabad, India</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Constantine</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>DZ</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>ALA</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Ahmedabad, India</t>
+          <t>Almaty, Kazakhstan</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6362,29 +6362,29 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>Almaty</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>KZ</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>BLR</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Almaty, Kazakhstan</t>
+          <t>Bangalore, India</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6394,29 +6394,29 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Almaty</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>BLR</t>
+          <t>BKK</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Bangalore, India</t>
+          <t>Bangkok, Thailand</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6426,29 +6426,29 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>TH</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>BKK</t>
+          <t>BWN</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Bangkok, Thailand</t>
+          <t>Bandar Seri Begawan, Brunei</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6458,29 +6458,29 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Bandar Seri Begawan</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Brunei</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>BN</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>BWN</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Bandar Seri Begawan, Brunei</t>
+          <t>Cebu, Philippines</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6490,29 +6490,29 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Bandar Seri Begawan</t>
+          <t>Cebu</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Brunei</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>BN</t>
+          <t>PH</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>IXC</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Cebu, Philippines</t>
+          <t>Chandigarh, India</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6522,29 +6522,29 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Cebu</t>
+          <t>Chandigarh</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>IXC</t>
+          <t>CGD</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Chandigarh, India</t>
+          <t>Changde, China</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6554,29 +6554,29 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Chandigarh</t>
+          <t>Changde</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>CGD</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Changde, China</t>
+          <t>Chennai, India</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -6586,29 +6586,29 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Changde</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>CGP</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Chennai, India</t>
+          <t>Chittagong, Bangladesh</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -6618,29 +6618,29 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Chittagong</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>BD</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t>CGP</t>
+          <t>CMB</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Chittagong, Bangladesh</t>
+          <t>Colombo, Sri Lanka</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -6650,29 +6650,29 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Chittagong</t>
+          <t>Colombo</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>Sri Lanka</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>BD</t>
+          <t>LK</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>CMB</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Colombo, Sri Lanka</t>
+          <t>Dhaka, Bangladesh</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -6682,29 +6682,29 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Colombo</t>
+          <t>Dhaka</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>LK</t>
+          <t>BD</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>FUO</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Dhaka, Bangladesh</t>
+          <t>Foshan, China</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -6714,29 +6714,29 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>Foshan</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>BD</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>FUO</t>
+          <t>FUK</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Foshan, China</t>
+          <t>Fukuoka, Japan</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -6746,29 +6746,29 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Foshan</t>
+          <t>Fukuoka</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>JP</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>FUK</t>
+          <t>FOC</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Fukuoka, Japan</t>
+          <t>Fuzhou, China</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -6778,29 +6778,29 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Fukuoka</t>
+          <t>Fuzhou</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t>FOC</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Fuzhou, China</t>
+          <t>Guangzhou, China</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Fuzhou</t>
+          <t>Guangzhou</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -6827,12 +6827,12 @@
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>HAK</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Guangzhou, China</t>
+          <t>Chengmai, China</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Guangzhou</t>
+          <t>Chengmai</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -6859,12 +6859,12 @@
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
         <is>
-          <t>HAK</t>
+          <t>HAN</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Chengmai, China</t>
+          <t>Hanoi, Vietnam</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -6874,29 +6874,29 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Chengmai</t>
+          <t>Hanoi</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>VN</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
         <is>
-          <t>HAN</t>
+          <t>SJW</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Hanoi, Vietnam</t>
+          <t>Shijiazhuang, China</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -6906,29 +6906,29 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Hanoi</t>
+          <t>Shijiazhuang</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>VN</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t>SJW</t>
+          <t>SGN</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Shijiazhuang, China</t>
+          <t>Ho Chi Minh City, Vietnam</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6938,29 +6938,29 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Shijiazhuang</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>VN</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="inlineStr">
         <is>
-          <t>SGN</t>
+          <t>HKG</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City, Vietnam</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6968,31 +6968,19 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>Ho Chi Minh City</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>Vietnam</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>VN</t>
-        </is>
-      </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
         <is>
-          <t>HKG</t>
+          <t>HYD</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Hyderabad, India</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -7000,19 +6988,31 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
-      <c r="E207" t="inlineStr"/>
-      <c r="F207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="inlineStr">
         <is>
-          <t>HYD</t>
+          <t>ISB</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Hyderabad, India</t>
+          <t>Islamabad, Pakistan</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7022,29 +7022,29 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Islamabad</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>PK</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="inlineStr">
         <is>
-          <t>ISB</t>
+          <t>CGK</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Islamabad, Pakistan</t>
+          <t>Jakarta, Indonesia</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7054,29 +7054,29 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Islamabad</t>
+          <t>Jakarta</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="inlineStr">
         <is>
-          <t>CGK</t>
+          <t>TNA</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Jakarta, Indonesia</t>
+          <t>Zibo, China</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7086,29 +7086,29 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Jakarta</t>
+          <t>Zibo</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
         <is>
-          <t>TNA</t>
+          <t>JHB</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Zibo, China</t>
+          <t>Johor Bahru, Malaysia</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -7118,29 +7118,29 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Zibo</t>
+          <t>Johor Bahru</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MY</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
         <is>
-          <t>JHB</t>
+          <t>KNU</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Johor Bahru, Malaysia</t>
+          <t>Kanpur, India</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -7150,29 +7150,29 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Johor Bahru</t>
+          <t>Kanpur</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="inlineStr">
         <is>
-          <t>KNU</t>
+          <t>KHH</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Kanpur, India</t>
+          <t>Kaohsiung City, Taiwan</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -7182,29 +7182,29 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Kanpur</t>
+          <t>Kaohsiung City</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>TW</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="inlineStr">
         <is>
-          <t>KHH</t>
+          <t>KHI</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Kaohsiung City, Taiwan</t>
+          <t>Karachi, Pakistan</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -7214,29 +7214,29 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Kaohsiung City</t>
+          <t>Karachi</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>PK</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="inlineStr">
         <is>
-          <t>KHI</t>
+          <t>KTM</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Karachi, Pakistan</t>
+          <t>Kathmandu, Nepal</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -7246,29 +7246,29 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Karachi</t>
+          <t>Kathmandu</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>NP</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="inlineStr">
         <is>
-          <t>KTM</t>
+          <t>CCU</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Kathmandu, Nepal</t>
+          <t>Kolkata, India</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -7278,29 +7278,29 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Kathmandu</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
         <is>
-          <t>CCU</t>
+          <t>KJA</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Kolkata, India</t>
+          <t>Krasnoyarsk, Russia</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -7310,29 +7310,29 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Krasnoyarsk</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>RU</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="inlineStr">
         <is>
-          <t>KJA</t>
+          <t>KUL</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Krasnoyarsk, Russia</t>
+          <t>Kuala Lumpur, Malaysia</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -7342,29 +7342,29 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Krasnoyarsk</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>RU</t>
+          <t>MY</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="inlineStr">
         <is>
-          <t>KUL</t>
+          <t>PKX</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Kuala Lumpur, Malaysia</t>
+          <t>Langfang, China</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -7374,29 +7374,29 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Langfang</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
         <is>
-          <t>PKX</t>
+          <t>MFM</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Langfang, China</t>
+          <t>Macau</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -7404,31 +7404,19 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>Langfang</t>
-        </is>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="1" t="inlineStr">
         <is>
-          <t>MFM</t>
+          <t>MLE</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Macau</t>
+          <t>Male, Maldives</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -7436,19 +7424,31 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
-      <c r="E221" t="inlineStr"/>
-      <c r="F221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Maldives</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>MV</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="inlineStr">
         <is>
-          <t>MLE</t>
+          <t>MNL</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Male, Maldives</t>
+          <t>Manila, Philippines</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -7458,29 +7458,29 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Manila</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Maldives</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>MV</t>
+          <t>PH</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="inlineStr">
         <is>
-          <t>MNL</t>
+          <t>BOM</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Manila, Philippines</t>
+          <t>Mumbai, India</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -7490,29 +7490,29 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Manila</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="inlineStr">
         <is>
-          <t>BOM</t>
+          <t>NAG</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Mumbai, India</t>
+          <t>Nagpur, India</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Nagpur</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -7539,12 +7539,12 @@
     <row r="225">
       <c r="A225" s="1" t="inlineStr">
         <is>
-          <t>NAG</t>
+          <t>OKA</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Nagpur, India</t>
+          <t>Naha, Japan</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -7554,29 +7554,29 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Nagpur</t>
+          <t>Naha</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>JP</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="inlineStr">
         <is>
-          <t>OKA</t>
+          <t>DEL</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Naha, Japan</t>
+          <t>New Delhi, India</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -7586,29 +7586,29 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Naha</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="inlineStr">
         <is>
-          <t>DEL</t>
+          <t>KIX</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>New Delhi, India</t>
+          <t>Osaka, Japan</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -7618,29 +7618,29 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>Osaka</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>JP</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="inlineStr">
         <is>
-          <t>KIX</t>
+          <t>PAT</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Osaka, Japan</t>
+          <t>Patna, India</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -7650,29 +7650,29 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Osaka</t>
+          <t>Patna</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="inlineStr">
         <is>
-          <t>PAT</t>
+          <t>PNH</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Patna, India</t>
+          <t>Phnom Penh, Cambodia</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -7682,29 +7682,29 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Patna</t>
+          <t>Phnom Penh</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>KH</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="inlineStr">
         <is>
-          <t>PNH</t>
+          <t>TAO</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Phnom Penh, Cambodia</t>
+          <t>Qingdao, China</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -7714,29 +7714,29 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Phnom Penh</t>
+          <t>Qingdao</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Cambodia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>KH</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="inlineStr">
         <is>
-          <t>TAO</t>
+          <t>ICN</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Qingdao, China</t>
+          <t>Seoul, South Korea</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -7746,29 +7746,29 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Qingdao</t>
+          <t>Seoul</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>KR</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="inlineStr">
         <is>
-          <t>ICN</t>
+          <t>SHA</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Seoul, South Korea</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -7778,29 +7778,29 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Seoul</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="inlineStr">
         <is>
-          <t>SHA</t>
+          <t>SIN</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Singapore, Singapore</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -7810,29 +7810,29 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Shanghai</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>SG</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="inlineStr">
         <is>
-          <t>SIN</t>
+          <t>URT</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Singapore, Singapore</t>
+          <t>Surat Thani, Thailand</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -7842,29 +7842,29 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Surat Thani</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>TH</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="inlineStr">
         <is>
-          <t>URT</t>
+          <t>TPE</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Surat Thani, Thailand</t>
+          <t>Taipei</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -7872,31 +7872,19 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>Surat Thani</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>Thailand</t>
-        </is>
-      </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>TH</t>
-        </is>
-      </c>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="1" t="inlineStr">
         <is>
-          <t>TPE</t>
+          <t>NRT</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Taipei</t>
+          <t>Tokyo, Japan</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -7904,19 +7892,31 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
-      <c r="E236" t="inlineStr"/>
-      <c r="F236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="inlineStr">
         <is>
-          <t>NRT</t>
+          <t>ULN</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Tokyo, Japan</t>
+          <t>Ulaanbaatar, Mongolia</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -7926,29 +7926,29 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Ulaanbaatar</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Mongolia</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>MN</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="inlineStr">
         <is>
-          <t>ULN</t>
+          <t>VTE</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Ulaanbaatar, Mongolia</t>
+          <t>Vientiane, Laos</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -7958,29 +7958,29 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Ulaanbaatar</t>
+          <t>Vientiane</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Mongolia</t>
+          <t>Laos</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>MN</t>
+          <t>LA</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="inlineStr">
         <is>
-          <t>VTE</t>
+          <t>KHN</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Vientiane, Laos</t>
+          <t>Nanchang, China</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -7990,29 +7990,29 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Vientiane</t>
+          <t>Nanchang</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Laos</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="inlineStr">
         <is>
-          <t>KHN</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Nanchang, China</t>
+          <t>Yerevan, Armenia</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -8022,29 +8022,29 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Nanchang</t>
+          <t>Yerevan</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>AM</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>JOG</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Yerevan, Armenia</t>
+          <t>Yogyakarta, Indonesia</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -8054,29 +8054,29 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Yerevan</t>
+          <t>Yogyakarta</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="inlineStr">
         <is>
-          <t>JOG</t>
+          <t>CGY</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Yogyakarta, Indonesia</t>
+          <t>Cagayan de Oro, Philippines</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -8086,29 +8086,29 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Yogyakarta</t>
+          <t>Cagayan de Oro</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>PH</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="inlineStr">
         <is>
-          <t>CGY</t>
+          <t>COK</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Cagayan de Oro, Philippines</t>
+          <t>Kochi, India</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -8118,29 +8118,29 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Cagayan de Oro</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="inlineStr">
         <is>
-          <t>COK</t>
+          <t>DPS</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Kochi, India</t>
+          <t>Denpasar, Indonesia</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -8150,29 +8150,29 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Denpasar</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="inlineStr">
         <is>
-          <t>DPS</t>
+          <t>CNN</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Denpasar, Indonesia</t>
+          <t>Kannur, India</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -8182,29 +8182,29 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Denpasar</t>
+          <t>Kannur</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="inlineStr">
         <is>
-          <t>CNN</t>
+          <t>SZX</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Kannur, India</t>
+          <t>Shenzhen, China</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -8214,29 +8214,29 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Kannur</t>
+          <t>Shenzhen</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="inlineStr">
         <is>
-          <t>SZX</t>
+          <t>KWE</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Shenzhen, China</t>
+          <t>Guiyang, China</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Shenzhen</t>
+          <t>Guiyang</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -8263,12 +8263,12 @@
     <row r="248">
       <c r="A248" s="1" t="inlineStr">
         <is>
-          <t>KWE</t>
+          <t>HGH</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Guiyang, China</t>
+          <t>Shaoxing, China</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Guiyang</t>
+          <t>Shaoxing</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -8295,12 +8295,12 @@
     <row r="249">
       <c r="A249" s="1" t="inlineStr">
         <is>
-          <t>HGH</t>
+          <t>CZX</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Shaoxing, China</t>
+          <t>Changzhou, China</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Shaoxing</t>
+          <t>Changzhou</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -8327,12 +8327,12 @@
     <row r="250">
       <c r="A250" s="1" t="inlineStr">
         <is>
-          <t>CZX</t>
+          <t>KMG</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Changzhou, China</t>
+          <t>Kunming, China</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -8342,7 +8342,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Changzhou</t>
+          <t>Kunming</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -8359,12 +8359,12 @@
     <row r="251">
       <c r="A251" s="1" t="inlineStr">
         <is>
-          <t>KMG</t>
+          <t>CNX</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Kunming, China</t>
+          <t>Chiang Mai, Thailand</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -8374,29 +8374,29 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Kunming</t>
+          <t>Chiang Mai</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>TH</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="inlineStr">
         <is>
-          <t>CNX</t>
+          <t>CGO</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Chiang Mai, Thailand</t>
+          <t>Zhengzhou, China</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -8406,29 +8406,29 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Chiang Mai</t>
+          <t>Zhengzhou</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="inlineStr">
         <is>
-          <t>CGO</t>
+          <t>TYN</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Zhengzhou, China</t>
+          <t>Yangquan, China</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -8438,7 +8438,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Zhengzhou</t>
+          <t>Yangquan</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -8455,12 +8455,12 @@
     <row r="254">
       <c r="A254" s="1" t="inlineStr">
         <is>
-          <t>TYN</t>
+          <t>CSX</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Yangquan, China</t>
+          <t>Changsha, China</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -8470,7 +8470,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Yangquan</t>
+          <t>Changsha</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -8487,12 +8487,12 @@
     <row r="255">
       <c r="A255" s="1" t="inlineStr">
         <is>
-          <t>CSX</t>
+          <t>DLC</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Changsha, China</t>
+          <t>Dalian, China</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Changsha</t>
+          <t>Dalian</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -8519,12 +8519,12 @@
     <row r="256">
       <c r="A256" s="1" t="inlineStr">
         <is>
-          <t>DLC</t>
+          <t>BHY</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Dalian, China</t>
+          <t>Beihai, China</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Dalian</t>
+          <t>Beihai</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -8551,12 +8551,12 @@
     <row r="257">
       <c r="A257" s="1" t="inlineStr">
         <is>
-          <t>BHY</t>
+          <t>CKG</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Beihai, China</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -8566,7 +8566,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Beihai</t>
+          <t>Chongqing</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -8583,12 +8583,12 @@
     <row r="258">
       <c r="A258" s="1" t="inlineStr">
         <is>
-          <t>CKG</t>
+          <t>XFN</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Chongqing, China</t>
+          <t>Xiangyang, China</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Chongqing</t>
+          <t>Xiangyang</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -8615,12 +8615,12 @@
     <row r="259">
       <c r="A259" s="1" t="inlineStr">
         <is>
-          <t>XFN</t>
+          <t>DAD</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Xiangyang, China</t>
+          <t>Da Nang, Vietnam</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -8630,29 +8630,29 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Xiangyang</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>VN</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="inlineStr">
         <is>
-          <t>DAD</t>
+          <t>JXG</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Da Nang, Vietnam</t>
+          <t>Jiaxing, China</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -8662,29 +8662,29 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Jiaxing</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>VN</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="inlineStr">
         <is>
-          <t>JXG</t>
+          <t>CRK</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Jiaxing, China</t>
+          <t>Tarlac City, Philippines</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -8694,29 +8694,29 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Jiaxing</t>
+          <t>Tarlac City</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>PH</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="inlineStr">
         <is>
-          <t>CRK</t>
+          <t>PBH</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Tarlac City, Philippines</t>
+          <t>Thimphu, Bhutan</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -8726,29 +8726,29 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Tarlac City</t>
+          <t>Thimphu</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Bhutan</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>BT</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="inlineStr">
         <is>
-          <t>PBH</t>
+          <t>XIY</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Thimphu, Bhutan</t>
+          <t>Baoji, China</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -8758,29 +8758,29 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Thimphu</t>
+          <t>Baoji</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Bhutan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="inlineStr">
         <is>
-          <t>XIY</t>
+          <t>NQZ</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Baoji, China</t>
+          <t>Astana, Kazakhstan</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -8790,29 +8790,29 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Baoji</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>KZ</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="inlineStr">
         <is>
-          <t>NQZ</t>
+          <t>KCH</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Astana, Kazakhstan</t>
+          <t>Kuching, Malaysia</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -8822,29 +8822,29 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Kuching</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>MY</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="1" t="inlineStr">
         <is>
-          <t>KCH</t>
+          <t>AKX</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Kuching, Malaysia</t>
+          <t>Aktobe, Kazakhstan</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -8854,29 +8854,29 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Kuching</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>KZ</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="inlineStr">
         <is>
-          <t>AKX</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Aktobe, Kazakhstan</t>
+          <t>Tongren, China</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -8886,29 +8886,29 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Tongren</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Tongren, China</t>
+          <t>Taizhou, China</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -8918,7 +8918,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Tongren</t>
+          <t>Taizhou</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -8935,12 +8935,12 @@
     <row r="269">
       <c r="A269" s="1" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>FRU</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Taizhou, China</t>
+          <t>Bishkek, Kyrgyzstan</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -8950,29 +8950,29 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Taizhou</t>
+          <t>Bishkek</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kyrgyzstan</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>KG</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="inlineStr">
         <is>
-          <t>FRU</t>
+          <t>MLG</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Bishkek, Kyrgyzstan</t>
+          <t>Malang, Indonesia</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -8982,29 +8982,29 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Bishkek</t>
+          <t>Malang</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Kyrgyzstan</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="inlineStr">
         <is>
-          <t>MLG</t>
+          <t>LHE</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Malang, Indonesia</t>
+          <t>Lahore, Pakistan</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -9014,29 +9014,29 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Malang</t>
+          <t>Lahore</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>PK</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="inlineStr">
         <is>
-          <t>LHE</t>
+          <t>CTU</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Lahore, Pakistan</t>
+          <t>Chengdu, China</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -9046,29 +9046,29 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Lahore</t>
+          <t>Chengdu</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="inlineStr">
         <is>
-          <t>CTU</t>
+          <t>AGR</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Chengdu, China</t>
+          <t>Agra, India</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -9078,29 +9078,29 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Chengdu</t>
+          <t>Agra</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="inlineStr">
         <is>
-          <t>AGR</t>
+          <t>CJB</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Agra, India</t>
+          <t>Coimbatore, India</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Agra</t>
+          <t>Coimbatore</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -9127,12 +9127,12 @@
     <row r="275">
       <c r="A275" s="1" t="inlineStr">
         <is>
-          <t>CJB</t>
+          <t>ACX</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Coimbatore, India</t>
+          <t>Xingyi, China</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -9142,29 +9142,29 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Coimbatore</t>
+          <t>Xingyi</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="1" t="inlineStr">
         <is>
-          <t>ACX</t>
+          <t>BBI</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Xingyi, China</t>
+          <t>Bhubaneswar, India</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -9174,29 +9174,29 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Xingyi</t>
+          <t>Bhubaneswar</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="inlineStr">
         <is>
-          <t>BBI</t>
+          <t>LYA</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Bhubaneswar, India</t>
+          <t>Luoyang, China</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -9206,29 +9206,29 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Bhubaneswar</t>
+          <t>Luoyang</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="1" t="inlineStr">
         <is>
-          <t>LYA</t>
+          <t>PNQ</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Luoyang, China</t>
+          <t>Pune, India</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -9238,61 +9238,61 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Luoyang</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="1" t="inlineStr">
         <is>
-          <t>PNQ</t>
+          <t>ABQ</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Pune, India</t>
+          <t>Albuquerque, NM, United States</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Albuquerque, NM</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="1" t="inlineStr">
         <is>
-          <t>ABQ</t>
+          <t>ANC</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, United States</t>
+          <t>Anchorage, AK, United States</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -9302,7 +9302,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Albuquerque, NM</t>
+          <t>Anchorage, AK</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -9319,12 +9319,12 @@
     <row r="281">
       <c r="A281" s="1" t="inlineStr">
         <is>
-          <t>ANC</t>
+          <t>IAD</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Anchorage, AK, United States</t>
+          <t>Ashburn, VA, United States</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Anchorage, AK</t>
+          <t>Ashburn, VA</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -9351,12 +9351,12 @@
     <row r="282">
       <c r="A282" s="1" t="inlineStr">
         <is>
-          <t>IAD</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Ashburn, VA, United States</t>
+          <t>Atlanta, GA, United States</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Ashburn, VA</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -9383,12 +9383,12 @@
     <row r="283">
       <c r="A283" s="1" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Atlanta, GA, United States</t>
+          <t>Austin, TX, United States</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -9398,7 +9398,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -9415,12 +9415,12 @@
     <row r="284">
       <c r="A284" s="1" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>BGR</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Austin, TX, United States</t>
+          <t>Bangor, ME, United States</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -9430,7 +9430,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Bangor, ME</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -9447,12 +9447,12 @@
     <row r="285">
       <c r="A285" s="1" t="inlineStr">
         <is>
-          <t>BGR</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Bangor, ME, United States</t>
+          <t>Boston, MA, United States</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -9462,7 +9462,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Bangor, ME</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -9479,12 +9479,12 @@
     <row r="286">
       <c r="A286" s="1" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Boston, MA, United States</t>
+          <t>Buffalo, NY, United States</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -9494,7 +9494,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Buffalo, NY</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -9511,12 +9511,12 @@
     <row r="287">
       <c r="A287" s="1" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>YYC</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Buffalo, NY, United States</t>
+          <t>Calgary, AB, Canada</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -9526,29 +9526,29 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Buffalo, NY</t>
+          <t>Calgary, AB</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="inlineStr">
         <is>
-          <t>YYC</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Calgary, AB, Canada</t>
+          <t>Charlotte, NC, United States</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -9558,29 +9558,29 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Calgary, AB</t>
+          <t>Charlotte, NC</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>ORD</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Charlotte, NC, United States</t>
+          <t>Chicago, IL, United States</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Charlotte, NC</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -9607,12 +9607,12 @@
     <row r="290">
       <c r="A290" s="1" t="inlineStr">
         <is>
-          <t>ORD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Chicago, IL, United States</t>
+          <t>Cleveland, OH, United States</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Cleveland, OH</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -9639,12 +9639,12 @@
     <row r="291">
       <c r="A291" s="1" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CMH</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Cleveland, OH, United States</t>
+          <t>Columbus, OH, United States</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -9654,7 +9654,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Cleveland, OH</t>
+          <t>Columbus, OH</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -9671,12 +9671,12 @@
     <row r="292">
       <c r="A292" s="1" t="inlineStr">
         <is>
-          <t>CMH</t>
+          <t>DFW</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Columbus, OH, United States</t>
+          <t>Dallas, TX, United States</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -9686,7 +9686,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Columbus, OH</t>
+          <t>Dallas, TX</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -9703,12 +9703,12 @@
     <row r="293">
       <c r="A293" s="1" t="inlineStr">
         <is>
-          <t>DFW</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Dallas, TX, United States</t>
+          <t>Denver, CO, United States</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Dallas, TX</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -9735,12 +9735,12 @@
     <row r="294">
       <c r="A294" s="1" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DTW</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Denver, CO, United States</t>
+          <t>Detroit, MI, United States</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -9750,7 +9750,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>Detroit, MI</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -9767,12 +9767,12 @@
     <row r="295">
       <c r="A295" s="1" t="inlineStr">
         <is>
-          <t>DTW</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Detroit, MI, United States</t>
+          <t>Durham, NC, United States</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -9782,7 +9782,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Detroit, MI</t>
+          <t>Durham, NC</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -9799,12 +9799,12 @@
     <row r="296">
       <c r="A296" s="1" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GDL</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Durham, NC, United States</t>
+          <t>Guadalajara, Mexico</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -9814,29 +9814,29 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Durham, NC</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="inlineStr">
         <is>
-          <t>GDL</t>
+          <t>YHZ</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Guadalajara, Mexico</t>
+          <t>Halifax, Canada</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -9846,29 +9846,29 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Halifax</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="inlineStr">
         <is>
-          <t>YHZ</t>
+          <t>HNL</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Halifax, Canada</t>
+          <t>Honolulu, HI, United States</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -9878,29 +9878,29 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Halifax</t>
+          <t>Honolulu, HI</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="1" t="inlineStr">
         <is>
-          <t>HNL</t>
+          <t>IAH</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Honolulu, HI, United States</t>
+          <t>Houston, TX, United States</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -9910,7 +9910,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Honolulu, HI</t>
+          <t>Houston, TX</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -9927,12 +9927,12 @@
     <row r="300">
       <c r="A300" s="1" t="inlineStr">
         <is>
-          <t>IAH</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Houston, TX, United States</t>
+          <t>Indianapolis, IN, United States</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Houston, TX</t>
+          <t>Indianapolis, IN</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -9959,12 +9959,12 @@
     <row r="301">
       <c r="A301" s="1" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, United States</t>
+          <t>Jacksonville, FL, United States</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Indianapolis, IN</t>
+          <t>Jacksonville, FL</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -9991,12 +9991,12 @@
     <row r="302">
       <c r="A302" s="1" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>MCI</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, United States</t>
+          <t>Kansas City, MO, United States</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -10006,7 +10006,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Jacksonville, FL</t>
+          <t>Kansas City, MO</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -10023,12 +10023,12 @@
     <row r="303">
       <c r="A303" s="1" t="inlineStr">
         <is>
-          <t>MCI</t>
+          <t>KIN</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Kansas City, MO, United States</t>
+          <t>Kingston, Jamaica</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -10038,29 +10038,29 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Kansas City, MO</t>
+          <t>Kingston</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Jamaica</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JM</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="inlineStr">
         <is>
-          <t>KIN</t>
+          <t>LAS</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Kingston, Jamaica</t>
+          <t>Las Vegas, NV, United States</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -10070,29 +10070,29 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Kingston</t>
+          <t>Las Vegas, NV</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Jamaica</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>JM</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="inlineStr">
         <is>
-          <t>LAS</t>
+          <t>LAX</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, United States</t>
+          <t>Los Angeles, CA, United States</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Las Vegas, NV</t>
+          <t>Los Angeles, CA</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -10119,12 +10119,12 @@
     <row r="306">
       <c r="A306" s="1" t="inlineStr">
         <is>
-          <t>LAX</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, United States</t>
+          <t>Memphis, TN, United States</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
+          <t>Memphis, TN</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -10151,12 +10151,12 @@
     <row r="307">
       <c r="A307" s="1" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MEX</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Memphis, TN, United States</t>
+          <t>Mexico City, Mexico</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -10166,29 +10166,29 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Memphis, TN</t>
+          <t>Mexico City</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="inlineStr">
         <is>
-          <t>MEX</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Mexico City, Mexico</t>
+          <t>Miami, FL, United States</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -10198,29 +10198,29 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Mexico City</t>
+          <t>Miami, FL</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MSP</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Miami, FL, United States</t>
+          <t>Minneapolis, MN, United States</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Miami, FL</t>
+          <t>Minneapolis, MN</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -10247,12 +10247,12 @@
     <row r="310">
       <c r="A310" s="1" t="inlineStr">
         <is>
-          <t>MSP</t>
+          <t>YUL</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, United States</t>
+          <t>Montréal, QC, Canada</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -10262,29 +10262,29 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Minneapolis, MN</t>
+          <t>Montréal, QC</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="inlineStr">
         <is>
-          <t>YUL</t>
+          <t>BNA</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Montréal, QC, Canada</t>
+          <t>Nashville, United States</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -10294,29 +10294,29 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Montréal, QC</t>
+          <t>Nashville</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="1" t="inlineStr">
         <is>
-          <t>BNA</t>
+          <t>EWR</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Nashville, United States</t>
+          <t>Newark, NJ, United States</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Nashville</t>
+          <t>Newark, NJ</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -10343,12 +10343,12 @@
     <row r="313">
       <c r="A313" s="1" t="inlineStr">
         <is>
-          <t>EWR</t>
+          <t>ORF</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Newark, NJ, United States</t>
+          <t>Norfolk, VA, United States</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Newark, NJ</t>
+          <t>Norfolk, VA</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -10375,12 +10375,12 @@
     <row r="314">
       <c r="A314" s="1" t="inlineStr">
         <is>
-          <t>ORF</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Norfolk, VA, United States</t>
+          <t>Oklahoma City, OK, United States</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -10390,7 +10390,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Norfolk, VA</t>
+          <t>Oklahoma City, OK</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -10407,12 +10407,12 @@
     <row r="315">
       <c r="A315" s="1" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>OMA</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, United States</t>
+          <t>Omaha, NE, United States</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK</t>
+          <t>Omaha, NE</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -10439,12 +10439,12 @@
     <row r="316">
       <c r="A316" s="1" t="inlineStr">
         <is>
-          <t>OMA</t>
+          <t>YOW</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Omaha, NE, United States</t>
+          <t>Ottawa, Canada</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -10454,29 +10454,29 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Omaha, NE</t>
+          <t>Ottawa</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="1" t="inlineStr">
         <is>
-          <t>YOW</t>
+          <t>PHL</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Ottawa, Canada</t>
+          <t>Philadelphia, United States</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -10486,29 +10486,29 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Ottawa</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="1" t="inlineStr">
         <is>
-          <t>PHL</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Philadelphia, United States</t>
+          <t>Phoenix, AZ, United States</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -10518,7 +10518,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Phoenix, AZ</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -10535,12 +10535,12 @@
     <row r="319">
       <c r="A319" s="1" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, United States</t>
+          <t>Pittsburgh, PA, United States</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -10550,7 +10550,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Phoenix, AZ</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -10567,12 +10567,12 @@
     <row r="320">
       <c r="A320" s="1" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, United States</t>
+          <t>Portland, OR, United States</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -10582,7 +10582,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA</t>
+          <t>Portland, OR</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -10599,12 +10599,12 @@
     <row r="321">
       <c r="A321" s="1" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>QRO</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Portland, OR, United States</t>
+          <t>Queretaro, MX, Mexico</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -10614,29 +10614,29 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Portland, OR</t>
+          <t>Queretaro, MX</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="inlineStr">
         <is>
-          <t>QRO</t>
+          <t>RIC</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Queretaro, MX, Mexico</t>
+          <t>Richmond, VA, United States</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -10646,29 +10646,29 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Queretaro, MX</t>
+          <t>Richmond, VA</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="1" t="inlineStr">
         <is>
-          <t>RIC</t>
+          <t>SMF</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Richmond, VA, United States</t>
+          <t>Sacramento, CA, United States</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -10678,7 +10678,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Richmond, VA</t>
+          <t>Sacramento, CA</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -10695,12 +10695,12 @@
     <row r="324">
       <c r="A324" s="1" t="inlineStr">
         <is>
-          <t>SMF</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Sacramento, CA, United States</t>
+          <t>Salt Lake City, UT, United States</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -10710,7 +10710,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Sacramento, CA</t>
+          <t>Salt Lake City, UT</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -10727,12 +10727,12 @@
     <row r="325">
       <c r="A325" s="1" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>SAT</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, United States</t>
+          <t>San Antonio, TX, United States</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT</t>
+          <t>San Antonio, TX</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -10759,12 +10759,12 @@
     <row r="326">
       <c r="A326" s="1" t="inlineStr">
         <is>
-          <t>SAT</t>
+          <t>SAN</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>San Antonio, TX, United States</t>
+          <t>San Diego, CA, United States</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -10774,7 +10774,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>San Antonio, TX</t>
+          <t>San Diego, CA</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -10791,12 +10791,12 @@
     <row r="327">
       <c r="A327" s="1" t="inlineStr">
         <is>
-          <t>SAN</t>
+          <t>SFO</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>San Diego, CA, United States</t>
+          <t>San Francisco, CA, United States</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -10806,7 +10806,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>San Diego, CA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -10823,12 +10823,12 @@
     <row r="328">
       <c r="A328" s="1" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>SJC</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>San Francisco, CA, United States</t>
+          <t>San Jose, CA, United States</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -10855,12 +10855,12 @@
     <row r="329">
       <c r="A329" s="1" t="inlineStr">
         <is>
-          <t>SJC</t>
+          <t>YXE</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>San Jose, CA, United States</t>
+          <t>Saskatoon, SK, Canada</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -10870,29 +10870,29 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>Saskatoon, SK</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="inlineStr">
         <is>
-          <t>YXE</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Saskatoon, SK, Canada</t>
+          <t>Seattle, WA, United States</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -10902,29 +10902,29 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Saskatoon, SK</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="1" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>FSD</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Seattle, WA, United States</t>
+          <t>Sioux Falls, SD, United States</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Sioux Falls, SD</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -10951,12 +10951,12 @@
     <row r="332">
       <c r="A332" s="1" t="inlineStr">
         <is>
-          <t>FSD</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, United States</t>
+          <t>St. Louis, MO, United States</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -10966,7 +10966,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD</t>
+          <t>St. Louis, MO</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -10983,12 +10983,12 @@
     <row r="333">
       <c r="A333" s="1" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>TLH</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>St. Louis, MO, United States</t>
+          <t>Tallahassee, FL, United States</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -10998,7 +10998,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>St. Louis, MO</t>
+          <t>Tallahassee, FL</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -11015,12 +11015,12 @@
     <row r="334">
       <c r="A334" s="1" t="inlineStr">
         <is>
-          <t>TLH</t>
+          <t>TPA</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, United States</t>
+          <t>Tampa, FL, United States</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Tallahassee, FL</t>
+          <t>Tampa, FL</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -11047,12 +11047,12 @@
     <row r="335">
       <c r="A335" s="1" t="inlineStr">
         <is>
-          <t>TPA</t>
+          <t>YYZ</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Tampa, FL, United States</t>
+          <t>Toronto, ON, Canada</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -11062,29 +11062,29 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Tampa, FL</t>
+          <t>Toronto, ON</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="inlineStr">
         <is>
-          <t>YYZ</t>
+          <t>YVR</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Toronto, ON, Canada</t>
+          <t>Vancouver, BC, Canada</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -11094,7 +11094,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Toronto, ON</t>
+          <t>Vancouver, BC</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -11111,12 +11111,12 @@
     <row r="337">
       <c r="A337" s="1" t="inlineStr">
         <is>
-          <t>YVR</t>
+          <t>YWG</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Vancouver, BC, Canada</t>
+          <t>Winnipeg, MB, Canada</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -11126,7 +11126,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Vancouver, BC</t>
+          <t>Winnipeg, MB</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -11135,38 +11135,6 @@
         </is>
       </c>
       <c r="F337" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" s="1" t="inlineStr">
-        <is>
-          <t>YWG</t>
-        </is>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>Winnipeg, MB, Canada</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>North America</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>Winnipeg, MB</t>
-        </is>
-      </c>
-      <c r="E338" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="F338" t="inlineStr">
         <is>
           <t>CA</t>
         </is>

--- a/DC-Colos.xlsx
+++ b/DC-Colos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F337"/>
+  <dimension ref="A1:F338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9255,44 +9255,44 @@
     <row r="279">
       <c r="A279" s="1" t="inlineStr">
         <is>
-          <t>ABQ</t>
+          <t>JRG</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, United States</t>
+          <t>Sambalpur, India</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Albuquerque, NM</t>
+          <t>Sambalpur</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="1" t="inlineStr">
         <is>
-          <t>ANC</t>
+          <t>ABQ</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Anchorage, AK, United States</t>
+          <t>Albuquerque, NM, United States</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -9302,7 +9302,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Anchorage, AK</t>
+          <t>Albuquerque, NM</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -9319,12 +9319,12 @@
     <row r="281">
       <c r="A281" s="1" t="inlineStr">
         <is>
-          <t>IAD</t>
+          <t>ANC</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Ashburn, VA, United States</t>
+          <t>Anchorage, AK, United States</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Ashburn, VA</t>
+          <t>Anchorage, AK</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -9351,12 +9351,12 @@
     <row r="282">
       <c r="A282" s="1" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>IAD</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Atlanta, GA, United States</t>
+          <t>Ashburn, VA, United States</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Ashburn, VA</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -9383,12 +9383,12 @@
     <row r="283">
       <c r="A283" s="1" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Austin, TX, United States</t>
+          <t>Atlanta, GA, United States</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -9398,7 +9398,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -9415,12 +9415,12 @@
     <row r="284">
       <c r="A284" s="1" t="inlineStr">
         <is>
-          <t>BGR</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Bangor, ME, United States</t>
+          <t>Austin, TX, United States</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -9430,7 +9430,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Bangor, ME</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -9447,12 +9447,12 @@
     <row r="285">
       <c r="A285" s="1" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BGR</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Boston, MA, United States</t>
+          <t>Bangor, ME, United States</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -9462,7 +9462,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Bangor, ME</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -9479,12 +9479,12 @@
     <row r="286">
       <c r="A286" s="1" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Buffalo, NY, United States</t>
+          <t>Boston, MA, United States</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -9494,7 +9494,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Buffalo, NY</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -9511,12 +9511,12 @@
     <row r="287">
       <c r="A287" s="1" t="inlineStr">
         <is>
-          <t>YYC</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Calgary, AB, Canada</t>
+          <t>Buffalo, NY, United States</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -9526,29 +9526,29 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Calgary, AB</t>
+          <t>Buffalo, NY</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>YYC</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Charlotte, NC, United States</t>
+          <t>Calgary, AB, Canada</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -9558,29 +9558,29 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Charlotte, NC</t>
+          <t>Calgary, AB</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="inlineStr">
         <is>
-          <t>ORD</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Chicago, IL, United States</t>
+          <t>Charlotte, NC, United States</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Charlotte, NC</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -9607,12 +9607,12 @@
     <row r="290">
       <c r="A290" s="1" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ORD</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Cleveland, OH, United States</t>
+          <t>Chicago, IL, United States</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Cleveland, OH</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -9639,12 +9639,12 @@
     <row r="291">
       <c r="A291" s="1" t="inlineStr">
         <is>
-          <t>CMH</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Columbus, OH, United States</t>
+          <t>Cleveland, OH, United States</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -9654,7 +9654,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Columbus, OH</t>
+          <t>Cleveland, OH</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -9671,12 +9671,12 @@
     <row r="292">
       <c r="A292" s="1" t="inlineStr">
         <is>
-          <t>DFW</t>
+          <t>CMH</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Dallas, TX, United States</t>
+          <t>Columbus, OH, United States</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -9686,7 +9686,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Dallas, TX</t>
+          <t>Columbus, OH</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -9703,12 +9703,12 @@
     <row r="293">
       <c r="A293" s="1" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DFW</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Denver, CO, United States</t>
+          <t>Dallas, TX, United States</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>Dallas, TX</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -9735,12 +9735,12 @@
     <row r="294">
       <c r="A294" s="1" t="inlineStr">
         <is>
-          <t>DTW</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Detroit, MI, United States</t>
+          <t>Denver, CO, United States</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -9750,7 +9750,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Detroit, MI</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -9767,12 +9767,12 @@
     <row r="295">
       <c r="A295" s="1" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DTW</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Durham, NC, United States</t>
+          <t>Detroit, MI, United States</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -9782,7 +9782,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Durham, NC</t>
+          <t>Detroit, MI</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -9799,12 +9799,12 @@
     <row r="296">
       <c r="A296" s="1" t="inlineStr">
         <is>
-          <t>GDL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Guadalajara, Mexico</t>
+          <t>Durham, NC, United States</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -9814,29 +9814,29 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Durham, NC</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="inlineStr">
         <is>
-          <t>YHZ</t>
+          <t>GDL</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Halifax, Canada</t>
+          <t>Guadalajara, Mexico</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -9846,29 +9846,29 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Halifax</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>MX</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="inlineStr">
         <is>
-          <t>HNL</t>
+          <t>YHZ</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Honolulu, HI, United States</t>
+          <t>Halifax, Canada</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -9878,29 +9878,29 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Honolulu, HI</t>
+          <t>Halifax</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="1" t="inlineStr">
         <is>
-          <t>IAH</t>
+          <t>HNL</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Houston, TX, United States</t>
+          <t>Honolulu, HI, United States</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -9910,7 +9910,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Houston, TX</t>
+          <t>Honolulu, HI</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -9927,12 +9927,12 @@
     <row r="300">
       <c r="A300" s="1" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>IAH</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, United States</t>
+          <t>Houston, TX, United States</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Indianapolis, IN</t>
+          <t>Houston, TX</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -9959,12 +9959,12 @@
     <row r="301">
       <c r="A301" s="1" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, United States</t>
+          <t>Indianapolis, IN, United States</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Jacksonville, FL</t>
+          <t>Indianapolis, IN</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -9991,12 +9991,12 @@
     <row r="302">
       <c r="A302" s="1" t="inlineStr">
         <is>
-          <t>MCI</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Kansas City, MO, United States</t>
+          <t>Jacksonville, FL, United States</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -10006,7 +10006,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Kansas City, MO</t>
+          <t>Jacksonville, FL</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -10023,12 +10023,12 @@
     <row r="303">
       <c r="A303" s="1" t="inlineStr">
         <is>
-          <t>KIN</t>
+          <t>MCI</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Kingston, Jamaica</t>
+          <t>Kansas City, MO, United States</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -10038,29 +10038,29 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Kingston</t>
+          <t>Kansas City, MO</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Jamaica</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>JM</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="inlineStr">
         <is>
-          <t>LAS</t>
+          <t>KIN</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, United States</t>
+          <t>Kingston, Jamaica</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -10070,29 +10070,29 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Las Vegas, NV</t>
+          <t>Kingston</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Jamaica</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JM</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="inlineStr">
         <is>
-          <t>LAX</t>
+          <t>LAS</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, United States</t>
+          <t>Las Vegas, NV, United States</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
+          <t>Las Vegas, NV</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -10119,12 +10119,12 @@
     <row r="306">
       <c r="A306" s="1" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>LAX</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Memphis, TN, United States</t>
+          <t>Los Angeles, CA, United States</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Memphis, TN</t>
+          <t>Los Angeles, CA</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -10151,12 +10151,12 @@
     <row r="307">
       <c r="A307" s="1" t="inlineStr">
         <is>
-          <t>MEX</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Mexico City, Mexico</t>
+          <t>Memphis, TN, United States</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -10166,29 +10166,29 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Mexico City</t>
+          <t>Memphis, TN</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MEX</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Miami, FL, United States</t>
+          <t>Mexico City, Mexico</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -10198,29 +10198,29 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Miami, FL</t>
+          <t>Mexico City</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="inlineStr">
         <is>
-          <t>MSP</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, United States</t>
+          <t>Miami, FL, United States</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Minneapolis, MN</t>
+          <t>Miami, FL</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -10247,12 +10247,12 @@
     <row r="310">
       <c r="A310" s="1" t="inlineStr">
         <is>
-          <t>YUL</t>
+          <t>MSP</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Montréal, QC, Canada</t>
+          <t>Minneapolis, MN, United States</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -10262,29 +10262,29 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Montréal, QC</t>
+          <t>Minneapolis, MN</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="inlineStr">
         <is>
-          <t>BNA</t>
+          <t>YUL</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Nashville, United States</t>
+          <t>Montréal, QC, Canada</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -10294,29 +10294,29 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Nashville</t>
+          <t>Montréal, QC</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="1" t="inlineStr">
         <is>
-          <t>EWR</t>
+          <t>BNA</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Newark, NJ, United States</t>
+          <t>Nashville, United States</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Newark, NJ</t>
+          <t>Nashville</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -10343,12 +10343,12 @@
     <row r="313">
       <c r="A313" s="1" t="inlineStr">
         <is>
-          <t>ORF</t>
+          <t>EWR</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Norfolk, VA, United States</t>
+          <t>Newark, NJ, United States</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Norfolk, VA</t>
+          <t>Newark, NJ</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -10375,12 +10375,12 @@
     <row r="314">
       <c r="A314" s="1" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>ORF</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, United States</t>
+          <t>Norfolk, VA, United States</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -10390,7 +10390,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK</t>
+          <t>Norfolk, VA</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -10407,12 +10407,12 @@
     <row r="315">
       <c r="A315" s="1" t="inlineStr">
         <is>
-          <t>OMA</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Omaha, NE, United States</t>
+          <t>Oklahoma City, OK, United States</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Omaha, NE</t>
+          <t>Oklahoma City, OK</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -10439,12 +10439,12 @@
     <row r="316">
       <c r="A316" s="1" t="inlineStr">
         <is>
-          <t>YOW</t>
+          <t>OMA</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Ottawa, Canada</t>
+          <t>Omaha, NE, United States</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -10454,29 +10454,29 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Ottawa</t>
+          <t>Omaha, NE</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="1" t="inlineStr">
         <is>
-          <t>PHL</t>
+          <t>YOW</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Philadelphia, United States</t>
+          <t>Ottawa, Canada</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -10486,29 +10486,29 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Ottawa</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="1" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>PHL</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, United States</t>
+          <t>Philadelphia, United States</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -10518,7 +10518,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Phoenix, AZ</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -10535,12 +10535,12 @@
     <row r="319">
       <c r="A319" s="1" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, United States</t>
+          <t>Phoenix, AZ, United States</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -10550,7 +10550,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA</t>
+          <t>Phoenix, AZ</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -10567,12 +10567,12 @@
     <row r="320">
       <c r="A320" s="1" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Portland, OR, United States</t>
+          <t>Pittsburgh, PA, United States</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -10582,7 +10582,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Portland, OR</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -10599,12 +10599,12 @@
     <row r="321">
       <c r="A321" s="1" t="inlineStr">
         <is>
-          <t>QRO</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Queretaro, MX, Mexico</t>
+          <t>Portland, OR, United States</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -10614,29 +10614,29 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Queretaro, MX</t>
+          <t>Portland, OR</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="inlineStr">
         <is>
-          <t>RIC</t>
+          <t>QRO</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Richmond, VA, United States</t>
+          <t>Queretaro, MX, Mexico</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -10646,29 +10646,29 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Richmond, VA</t>
+          <t>Queretaro, MX</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="1" t="inlineStr">
         <is>
-          <t>SMF</t>
+          <t>RIC</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Sacramento, CA, United States</t>
+          <t>Richmond, VA, United States</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -10678,7 +10678,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Sacramento, CA</t>
+          <t>Richmond, VA</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -10695,12 +10695,12 @@
     <row r="324">
       <c r="A324" s="1" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>SMF</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, United States</t>
+          <t>Sacramento, CA, United States</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -10710,7 +10710,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT</t>
+          <t>Sacramento, CA</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -10727,12 +10727,12 @@
     <row r="325">
       <c r="A325" s="1" t="inlineStr">
         <is>
-          <t>SAT</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>San Antonio, TX, United States</t>
+          <t>Salt Lake City, UT, United States</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>San Antonio, TX</t>
+          <t>Salt Lake City, UT</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -10759,12 +10759,12 @@
     <row r="326">
       <c r="A326" s="1" t="inlineStr">
         <is>
-          <t>SAN</t>
+          <t>SAT</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>San Diego, CA, United States</t>
+          <t>San Antonio, TX, United States</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -10774,7 +10774,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>San Diego, CA</t>
+          <t>San Antonio, TX</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -10791,12 +10791,12 @@
     <row r="327">
       <c r="A327" s="1" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>SAN</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>San Francisco, CA, United States</t>
+          <t>San Diego, CA, United States</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -10806,7 +10806,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>San Diego, CA</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -10823,12 +10823,12 @@
     <row r="328">
       <c r="A328" s="1" t="inlineStr">
         <is>
-          <t>SJC</t>
+          <t>SFO</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>San Jose, CA, United States</t>
+          <t>San Francisco, CA, United States</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -10855,12 +10855,12 @@
     <row r="329">
       <c r="A329" s="1" t="inlineStr">
         <is>
-          <t>YXE</t>
+          <t>SJC</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Saskatoon, SK, Canada</t>
+          <t>San Jose, CA, United States</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -10870,29 +10870,29 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Saskatoon, SK</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>YXE</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Seattle, WA, United States</t>
+          <t>Saskatoon, SK, Canada</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -10902,29 +10902,29 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Saskatoon, SK</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="1" t="inlineStr">
         <is>
-          <t>FSD</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, United States</t>
+          <t>Seattle, WA, United States</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -10951,12 +10951,12 @@
     <row r="332">
       <c r="A332" s="1" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>FSD</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>St. Louis, MO, United States</t>
+          <t>Sioux Falls, SD, United States</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -10966,7 +10966,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>St. Louis, MO</t>
+          <t>Sioux Falls, SD</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -10983,12 +10983,12 @@
     <row r="333">
       <c r="A333" s="1" t="inlineStr">
         <is>
-          <t>TLH</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, United States</t>
+          <t>St. Louis, MO, United States</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -10998,7 +10998,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Tallahassee, FL</t>
+          <t>St. Louis, MO</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -11015,12 +11015,12 @@
     <row r="334">
       <c r="A334" s="1" t="inlineStr">
         <is>
-          <t>TPA</t>
+          <t>TLH</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Tampa, FL, United States</t>
+          <t>Tallahassee, FL, United States</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Tampa, FL</t>
+          <t>Tallahassee, FL</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -11047,12 +11047,12 @@
     <row r="335">
       <c r="A335" s="1" t="inlineStr">
         <is>
-          <t>YYZ</t>
+          <t>TPA</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Toronto, ON, Canada</t>
+          <t>Tampa, FL, United States</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -11062,29 +11062,29 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Toronto, ON</t>
+          <t>Tampa, FL</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="inlineStr">
         <is>
-          <t>YVR</t>
+          <t>YYZ</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Vancouver, BC, Canada</t>
+          <t>Toronto, ON, Canada</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -11094,7 +11094,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Vancouver, BC</t>
+          <t>Toronto, ON</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -11111,30 +11111,62 @@
     <row r="337">
       <c r="A337" s="1" t="inlineStr">
         <is>
+          <t>YVR</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Vancouver, BC, Canada</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Vancouver, BC</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="inlineStr">
+        <is>
           <t>YWG</t>
         </is>
       </c>
-      <c r="B337" t="inlineStr">
+      <c r="B338" t="inlineStr">
         <is>
           <t>Winnipeg, MB, Canada</t>
         </is>
       </c>
-      <c r="C337" t="inlineStr">
+      <c r="C338" t="inlineStr">
         <is>
           <t>North America</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr">
+      <c r="D338" t="inlineStr">
         <is>
           <t>Winnipeg, MB</t>
         </is>
       </c>
-      <c r="E337" t="inlineStr">
+      <c r="E338" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="F337" t="inlineStr">
+      <c r="F338" t="inlineStr">
         <is>
           <t>CA</t>
         </is>

--- a/DC-Colos.xlsx
+++ b/DC-Colos.xlsx
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Valletta, Malta</t>
+          <t>Santa Venera, Malta</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Valletta</t>
+          <t>Santa Venera</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Bogota, Colombia</t>
+          <t>Bogotá, Colombia</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Bogota</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Cacador, Brazil</t>
+          <t>Caçador, Brazil</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Cacador</t>
+          <t>Caçador</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Goiania, Brazil</t>
+          <t>Goiânia, Brazil</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Goiania</t>
+          <t>Goiânia</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Neuquen, Argentina</t>
+          <t>Neuquén, Argentina</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Neuquen</t>
+          <t>Neuquén</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Timbo, Brazil</t>
+          <t>Timbó, Brazil</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Timbo</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Uberlandia, Brazil</t>
+          <t>Uberlândia, Brazil</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Uberlandia</t>
+          <t>Uberlândia</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Dar es Salaam, Tanzania</t>
+          <t>Dar Es Salaam, Tanzania</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Dar es Salaam</t>
+          <t>Dar Es Salaam</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Djibouti, Djibouti</t>
+          <t>Djibouti City, Djibouti</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Djibouti</t>
+          <t>Djibouti City</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Chengmai, China</t>
+          <t>Haikou, China</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Chengmai</t>
+          <t>Haikou</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Shijiazhuang, China</t>
+          <t>Hengshui, China</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -6906,7 +6906,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Shijiazhuang</t>
+          <t>Hengshui</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Zibo, China</t>
+          <t>Jinan, China</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Zibo</t>
+          <t>Jinan</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Male, Maldives</t>
+          <t>Malé, Maldives</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Malé</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -7980,7 +7980,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Nanchang, China</t>
+          <t>Xinyu, China</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Nanchang</t>
+          <t>Xinyu</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">

--- a/DC-Colos.xlsx
+++ b/DC-Colos.xlsx
@@ -3583,12 +3583,12 @@
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>BNU</t>
+          <t>BOG</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Blumenau, Brazil</t>
+          <t>Bogotá, Colombia</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3598,29 +3598,29 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Blumenau</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CO</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>BOG</t>
+          <t>BSB</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Bogotá, Colombia</t>
+          <t>Brasilia, Brazil</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3630,29 +3630,29 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Brasilia</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>BSB</t>
+          <t>EZE</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Brasilia, Brazil</t>
+          <t>Buenos Aires, Argentina</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3662,29 +3662,29 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Brasilia</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>AR</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>EZE</t>
+          <t>CFC</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Buenos Aires, Argentina</t>
+          <t>Caçador, Brazil</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3694,29 +3694,29 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Caçador</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>CFC</t>
+          <t>VCP</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Caçador, Brazil</t>
+          <t>Campinas, Brazil</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Caçador</t>
+          <t>Campinas</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -3743,12 +3743,12 @@
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>VCP</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Campinas, Brazil</t>
+          <t>Córdoba, Argentina</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3758,29 +3758,29 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Campinas</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>AR</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>CWB</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Córdoba, Argentina</t>
+          <t>Curitiba, Brazil</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3790,29 +3790,29 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Curitiba</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>CWB</t>
+          <t>FLN</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Curitiba, Brazil</t>
+          <t>Florianopolis, Brazil</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Curitiba</t>
+          <t>Florianopolis</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -3839,12 +3839,12 @@
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>FLN</t>
+          <t>FOR</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Florianopolis, Brazil</t>
+          <t>Fortaleza, Brazil</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Florianopolis</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -3871,12 +3871,12 @@
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>FOR</t>
+          <t>GEO</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Fortaleza, Brazil</t>
+          <t>Georgetown, Guyana</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3886,29 +3886,29 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Georgetown</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>GY</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>GEO</t>
+          <t>GYN</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Georgetown, Guyana</t>
+          <t>Goiânia, Brazil</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3918,29 +3918,29 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Georgetown</t>
+          <t>Goiânia</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>GY</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>GYN</t>
+          <t>GUA</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Goiânia, Brazil</t>
+          <t>Guatemala City, Guatemala</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3950,29 +3950,29 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Goiânia</t>
+          <t>Guatemala City</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Guatemala</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>GT</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>GUA</t>
+          <t>GYE</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Guatemala City, Guatemala</t>
+          <t>Guayaquil, Ecuador</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3982,29 +3982,29 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Guatemala City</t>
+          <t>Guayaquil</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Guatemala</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>EC</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>GYE</t>
+          <t>JOI</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Guayaquil, Ecuador</t>
+          <t>Joinville, Brazil</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4014,29 +4014,29 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Guayaquil</t>
+          <t>Joinville</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>JOI</t>
+          <t>JDO</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Joinville, Brazil</t>
+          <t>Juazeiro do Norte, Brazil</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Joinville</t>
+          <t>Juazeiro do Norte</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4063,12 +4063,12 @@
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>JDO</t>
+          <t>LIM</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Juazeiro do Norte, Brazil</t>
+          <t>Lima, Peru</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4078,29 +4078,29 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Juazeiro do Norte</t>
+          <t>Lima</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>PE</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>MAO</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Lima, Peru</t>
+          <t>Manaus, Brazil</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4110,29 +4110,29 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Lima</t>
+          <t>Manaus</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>MAO</t>
+          <t>MDE</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Manaus, Brazil</t>
+          <t>Medellín, Colombia</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4142,29 +4142,29 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Manaus</t>
+          <t>Medellín</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CO</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>MDE</t>
+          <t>NQN</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Medellín, Colombia</t>
+          <t>Neuquén, Argentina</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4174,29 +4174,29 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Neuquén</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>AR</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>NQN</t>
+          <t>PTY</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Neuquén, Argentina</t>
+          <t>Panama City, Panama</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4206,29 +4206,29 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Neuquén</t>
+          <t>Panama City</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>PA</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>PTY</t>
+          <t>PBM</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Panama City, Panama</t>
+          <t>Paramaribo, Suriname</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4238,29 +4238,29 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Panama City</t>
+          <t>Paramaribo</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Suriname</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>SR</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>PBM</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Paramaribo, Suriname</t>
+          <t>Porto Alegre, Brazil</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4270,29 +4270,29 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Paramaribo</t>
+          <t>Porto Alegre</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Suriname</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>UIO</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Porto Alegre, Brazil</t>
+          <t>Quito, Ecuador</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4302,29 +4302,29 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Porto Alegre</t>
+          <t>Quito</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>EC</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>UIO</t>
+          <t>REC</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Quito, Ecuador</t>
+          <t>Recife, Brazil</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4334,29 +4334,29 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Quito</t>
+          <t>Recife</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>REC</t>
+          <t>RAO</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Recife, Brazil</t>
+          <t>Ribeirao Preto, Brazil</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Recife</t>
+          <t>Ribeirao Preto</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -4383,12 +4383,12 @@
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>RAO</t>
+          <t>GIG</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Ribeirao Preto, Brazil</t>
+          <t>Rio de Janeiro, Brazil</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Ribeirao Preto</t>
+          <t>Rio de Janeiro</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -4415,12 +4415,12 @@
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>GIG</t>
+          <t>SJO</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Rio de Janeiro, Brazil</t>
+          <t>San José, Costa Rica</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4430,29 +4430,29 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Rio de Janeiro</t>
+          <t>San José</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Costa Rica</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CR</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>SJO</t>
+          <t>SCL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>San José, Costa Rica</t>
+          <t>Santiago, Chile</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4462,29 +4462,29 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>San José</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Costa Rica</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>CL</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>SCL</t>
+          <t>SDQ</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Santiago, Chile</t>
+          <t>Santo Domingo, Dominican Republic</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4494,29 +4494,29 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Santo Domingo</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>DO</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>SDQ</t>
+          <t>SJP</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Santo Domingo, Dominican Republic</t>
+          <t>São José do Rio Preto, Brazil</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4526,29 +4526,29 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Santo Domingo</t>
+          <t>São José do Rio Preto</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>SJP</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>São José do Rio Preto, Brazil</t>
+          <t>São José dos Campos, Brazil</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>São José do Rio Preto</t>
+          <t>São José dos Campos</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -4575,12 +4575,12 @@
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>GRU</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>São José dos Campos, Brazil</t>
+          <t>São Paulo, Brazil</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>São José dos Campos</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -4607,12 +4607,12 @@
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>GRU</t>
+          <t>SOD</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>São Paulo, Brazil</t>
+          <t>Sorocaba, Brazil</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Sorocaba</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -4639,12 +4639,12 @@
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>SOD</t>
+          <t>TGU</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Sorocaba, Brazil</t>
+          <t>Tegucigalpa, Honduras</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4654,29 +4654,29 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Sorocaba</t>
+          <t>Tegucigalpa</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Honduras</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>HN</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>TGU</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Tegucigalpa, Honduras</t>
+          <t>Timbó, Brazil</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4686,29 +4686,29 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Tegucigalpa</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Honduras</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>HN</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>UDI</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Timbó, Brazil</t>
+          <t>Uberlândia, Brazil</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Uberlândia</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -4735,12 +4735,12 @@
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>UDI</t>
+          <t>VIX</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Uberlândia, Brazil</t>
+          <t>Vitoria, Brazil</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Uberlândia</t>
+          <t>Vitoria</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -4767,12 +4767,12 @@
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>VIX</t>
+          <t>CAW</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Vitoria, Brazil</t>
+          <t>Campos dos Goytacazes, Brazil</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Vitoria</t>
+          <t>Campos dos Goytacazes</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -4799,12 +4799,12 @@
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>CAW</t>
+          <t>XAP</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Campos dos Goytacazes, Brazil</t>
+          <t>Chapeco, Brazil</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Campos dos Goytacazes</t>
+          <t>Chapeco</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -4831,12 +4831,12 @@
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>XAP</t>
+          <t>BGI</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Chapeco, Brazil</t>
+          <t>Bridgetown, Barbados</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4846,29 +4846,29 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Chapeco</t>
+          <t>Bridgetown</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Barbados</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>BB</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>BGI</t>
+          <t>GND</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Bridgetown, Barbados</t>
+          <t>St. George's, Grenada</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4878,29 +4878,29 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Bridgetown</t>
+          <t>St. George's</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Barbados</t>
+          <t>Grenada</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>GD</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>GND</t>
+          <t>STI</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>St. George's, Grenada</t>
+          <t>Santiago de los Caballeros, Dominican Republic</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4910,29 +4910,29 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>St. George's</t>
+          <t>Santiago de los Caballeros</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Grenada</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>DO</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>STI</t>
+          <t>LPB</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Santiago de los Caballeros, Dominican Republic</t>
+          <t>La Paz, Bolivia</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4942,29 +4942,29 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Santiago de los Caballeros</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>BO</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>LPB</t>
+          <t>SJU</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>La Paz, Bolivia</t>
+          <t>San Juan, Puerto Rico</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4974,29 +4974,29 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>San Juan</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Puerto Rico</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>PR</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>SJU</t>
+          <t>BAQ</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>San Juan, Puerto Rico</t>
+          <t>Barranquilla, Colombia</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5006,29 +5006,29 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>San Juan</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Puerto Rico</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>CO</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>BAQ</t>
+          <t>PMW</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Barranquilla, Colombia</t>
+          <t>Palmas, Brazil</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5038,29 +5038,29 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Palmas</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>PMW</t>
+          <t>ARU</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Palmas, Brazil</t>
+          <t>Aracatuba, Brazil</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Palmas</t>
+          <t>Aracatuba</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -5087,12 +5087,12 @@
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>ARU</t>
+          <t>POS</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Aracatuba, Brazil</t>
+          <t>Port of Spain, Trinidad and Tobago</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5102,29 +5102,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Aracatuba</t>
+          <t>Port of Spain</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>BR</t>
-        </is>
-      </c>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>POS</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Port of Spain, Trinidad and Tobago</t>
+          <t>Salvador, Brazil</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5134,25 +5130,29 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Port of Spain</t>
+          <t>Salvador</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Trinidad and Tobago</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr"/>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Salvador, Brazil</t>
+          <t>Cuiaba, Brazil</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Salvador</t>
+          <t>Cuiaba</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -5179,12 +5179,12 @@
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>CLO</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Cuiaba, Brazil</t>
+          <t>Cali, Colombia</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5194,29 +5194,29 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Cuiaba</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CO</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>CLO</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Cali, Colombia</t>
+          <t>San Pedro Sula, Honduras</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5226,61 +5226,61 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>San Pedro Sula</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Honduras</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>HN</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>San Pedro Sula, Honduras</t>
+          <t>Accra, Ghana</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Latin America &amp; the Caribbean</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>San Pedro Sula</t>
+          <t>Accra</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Honduras</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>HN</t>
+          <t>GH</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>ALG</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Accra, Ghana</t>
+          <t>Algiers, Algeria</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5290,29 +5290,29 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Accra</t>
+          <t>Algiers</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>GH</t>
+          <t>DZ</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>ALG</t>
+          <t>AAE</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Algiers, Algeria</t>
+          <t>Annaba, Algeria</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Algiers</t>
+          <t>Annaba</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -5339,12 +5339,12 @@
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>AAE</t>
+          <t>TNR</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Annaba, Algeria</t>
+          <t>Antananarivo, Madagascar</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5354,29 +5354,29 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Annaba</t>
+          <t>Antananarivo</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>DZ</t>
+          <t>MG</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>TNR</t>
+          <t>CPT</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Antananarivo, Madagascar</t>
+          <t>Cape Town, South Africa</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5386,29 +5386,29 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Antananarivo</t>
+          <t>Cape Town</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>ZA</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>CPT</t>
+          <t>DKR</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Cape Town, South Africa</t>
+          <t>Dakar, Senegal</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5418,29 +5418,29 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Cape Town</t>
+          <t>Dakar</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>SN</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>DKR</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Dakar, Senegal</t>
+          <t>Dar Es Salaam, Tanzania</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5450,29 +5450,29 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Dakar</t>
+          <t>Dar Es Salaam</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>SN</t>
+          <t>TZ</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>JIB</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Dar Es Salaam, Tanzania</t>
+          <t>Djibouti City, Djibouti</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5482,29 +5482,29 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Dar Es Salaam</t>
+          <t>Djibouti City</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Djibouti</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>TZ</t>
+          <t>DJ</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>JIB</t>
+          <t>DUR</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Djibouti City, Djibouti</t>
+          <t>Durban, South Africa</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5514,29 +5514,29 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Djibouti City</t>
+          <t>Durban</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Djibouti</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>DJ</t>
+          <t>ZA</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>DUR</t>
+          <t>GBE</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Durban, South Africa</t>
+          <t>Gaborone, Botswana</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5546,29 +5546,29 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Durban</t>
+          <t>Gaborone</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>BW</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>GBE</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Gaborone, Botswana</t>
+          <t>Harare, Zimbabwe</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5578,29 +5578,29 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Gaborone</t>
+          <t>Harare</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>BW</t>
+          <t>ZW</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>HRE</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Harare, Zimbabwe</t>
+          <t>Johannesburg, South Africa</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5610,29 +5610,29 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Harare</t>
+          <t>Johannesburg</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>ZW</t>
+          <t>ZA</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>KGL</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Johannesburg, South Africa</t>
+          <t>Kigali, Rwanda</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5642,29 +5642,29 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Johannesburg</t>
+          <t>Kigali</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>RW</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>KGL</t>
+          <t>LOS</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Kigali, Rwanda</t>
+          <t>Lagos, Nigeria</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -5674,29 +5674,29 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Kigali</t>
+          <t>Lagos</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>NG</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>LOS</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Lagos, Nigeria</t>
+          <t>Luanda, Angola</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -5706,29 +5706,29 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Lagos</t>
+          <t>Luanda</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>NG</t>
+          <t>AO</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>MPM</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Luanda, Angola</t>
+          <t>Maputo, Mozambique</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -5738,29 +5738,29 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Luanda</t>
+          <t>Maputo</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>AO</t>
+          <t>MZ</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>MPM</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Maputo, Mozambique</t>
+          <t>Mombasa, Kenya</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5770,29 +5770,29 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Maputo</t>
+          <t>Mombasa</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>MZ</t>
+          <t>KE</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Mombasa, Kenya</t>
+          <t>Nairobi, Kenya</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Mombasa</t>
+          <t>Nairobi</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -5819,12 +5819,12 @@
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>ORN</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Nairobi, Kenya</t>
+          <t>Oran, Algeria</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5834,29 +5834,29 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Nairobi</t>
+          <t>Oran</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>KE</t>
+          <t>DZ</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>ORN</t>
+          <t>OUA</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Oran, Algeria</t>
+          <t>Ouagadougou, Burkina Faso</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5866,29 +5866,29 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Oran</t>
+          <t>Ouagadougou</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Burkina Faso</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>DZ</t>
+          <t>BF</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>OUA</t>
+          <t>MRU</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Ouagadougou, Burkina Faso</t>
+          <t>Port Louis, Mauritius</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5898,29 +5898,29 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Ouagadougou</t>
+          <t>Port Louis</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Burkina Faso</t>
+          <t>Mauritius</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>BF</t>
+          <t>MU</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>MRU</t>
+          <t>TUN</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Port Louis, Mauritius</t>
+          <t>Tunis, Tunisia</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5930,29 +5930,29 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Port Louis</t>
+          <t>Tunis</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Mauritius</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TN</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>TUN</t>
+          <t>FIH</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Tunis, Tunisia</t>
+          <t>Kinshasa, DR Congo</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5962,29 +5962,25 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Tunis</t>
+          <t>Kinshasa</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Tunisia</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>TN</t>
-        </is>
-      </c>
+          <t>DR Congo</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>FIH</t>
+          <t>CAI</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Kinshasa, DR Congo</t>
+          <t>Cairo, Egypt</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5994,25 +5990,29 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Kinshasa</t>
+          <t>Cairo</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>DR Congo</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr"/>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t>CAI</t>
+          <t>WDH</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Cairo, Egypt</t>
+          <t>Windhoek, Namibia</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6022,29 +6022,29 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Cairo</t>
+          <t>Windhoek</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t>WDH</t>
+          <t>ASK</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Windhoek, Namibia</t>
+          <t>Yamoussoukro, Ivory Coast</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6054,29 +6054,25 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Windhoek</t>
+          <t>Yamoussoukro</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Namibia</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+          <t>Ivory Coast</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t>ASK</t>
+          <t>ABJ</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Yamoussoukro, Ivory Coast</t>
+          <t>Abidjan, Ivory Coast</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6086,7 +6082,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Yamoussoukro</t>
+          <t>Abidjan</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -6099,12 +6095,12 @@
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t>ABJ</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Abidjan, Ivory Coast</t>
+          <t>Kampala, Uganda</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6114,25 +6110,29 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Abidjan</t>
+          <t>Kampala</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr"/>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>RUN</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Kampala, Uganda</t>
+          <t>Saint-Denis, Réunion</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6142,29 +6142,25 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Kampala</t>
+          <t>Saint-Denis</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Uganda</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
+          <t>Réunion</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>RUN</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Saint-Denis, Réunion</t>
+          <t>Lusaka, Zambia</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6174,25 +6170,29 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Saint-Denis</t>
+          <t>Lusaka</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Réunion</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr"/>
+          <t>Zambia</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>ZM</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t>LUN</t>
+          <t>ADD</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Lusaka, Zambia</t>
+          <t>Addis Ababa, Ethiopia</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6202,29 +6202,29 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Lusaka</t>
+          <t>Addis Ababa</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>ZM</t>
+          <t>ET</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t>ADD</t>
+          <t>LLW</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Addis Ababa, Ethiopia</t>
+          <t>Lilongwe, Malawi</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6234,29 +6234,29 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Addis Ababa</t>
+          <t>Lilongwe</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>ET</t>
+          <t>MW</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t>LLW</t>
+          <t>CZL</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Lilongwe, Malawi</t>
+          <t>Constantine, Algeria</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6266,61 +6266,61 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Lilongwe</t>
+          <t>Constantine</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Malawi</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>MW</t>
+          <t>DZ</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t>CZL</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Constantine, Algeria</t>
+          <t>Ahmedabad, India</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Constantine</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>DZ</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>ALA</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Ahmedabad, India</t>
+          <t>Almaty, Kazakhstan</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6330,29 +6330,29 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>Almaty</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>KZ</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>BLR</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Almaty, Kazakhstan</t>
+          <t>Bangalore, India</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6362,29 +6362,29 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Almaty</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>BLR</t>
+          <t>BKK</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Bangalore, India</t>
+          <t>Bangkok, Thailand</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6394,29 +6394,29 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>TH</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>BKK</t>
+          <t>BWN</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Bangkok, Thailand</t>
+          <t>Bandar Seri Begawan, Brunei</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6426,29 +6426,29 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Bandar Seri Begawan</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Brunei</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>BN</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>BWN</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Bandar Seri Begawan, Brunei</t>
+          <t>Cebu, Philippines</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6458,29 +6458,29 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Bandar Seri Begawan</t>
+          <t>Cebu</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Brunei</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>BN</t>
+          <t>PH</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>IXC</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Cebu, Philippines</t>
+          <t>Chandigarh, India</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6490,29 +6490,29 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Cebu</t>
+          <t>Chandigarh</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>IXC</t>
+          <t>CGD</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Chandigarh, India</t>
+          <t>Changde, China</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6522,29 +6522,29 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Chandigarh</t>
+          <t>Changde</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>CGD</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Changde, China</t>
+          <t>Chennai, India</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6554,29 +6554,29 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Changde</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>CGP</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Chennai, India</t>
+          <t>Chittagong, Bangladesh</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -6586,29 +6586,29 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Chittagong</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>BD</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t>CGP</t>
+          <t>CMB</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Chittagong, Bangladesh</t>
+          <t>Colombo, Sri Lanka</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -6618,29 +6618,29 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Chittagong</t>
+          <t>Colombo</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>Sri Lanka</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>BD</t>
+          <t>LK</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t>CMB</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Colombo, Sri Lanka</t>
+          <t>Dhaka, Bangladesh</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -6650,29 +6650,29 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Colombo</t>
+          <t>Dhaka</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>LK</t>
+          <t>BD</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>FUO</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Dhaka, Bangladesh</t>
+          <t>Foshan, China</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -6682,29 +6682,29 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>Foshan</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>BD</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>FUO</t>
+          <t>FUK</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Foshan, China</t>
+          <t>Fukuoka, Japan</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -6714,29 +6714,29 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Foshan</t>
+          <t>Fukuoka</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>JP</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>FUK</t>
+          <t>FOC</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Fukuoka, Japan</t>
+          <t>Fuzhou, China</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -6746,29 +6746,29 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Fukuoka</t>
+          <t>Fuzhou</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>FOC</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Fuzhou, China</t>
+          <t>Guangzhou, China</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Fuzhou</t>
+          <t>Guangzhou</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -6795,12 +6795,12 @@
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>HAK</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Guangzhou, China</t>
+          <t>Haikou, China</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Guangzhou</t>
+          <t>Haikou</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -6827,12 +6827,12 @@
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t>HAK</t>
+          <t>HAN</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Haikou, China</t>
+          <t>Hanoi, Vietnam</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -6842,29 +6842,29 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Haikou</t>
+          <t>Hanoi</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>VN</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
         <is>
-          <t>HAN</t>
+          <t>SJW</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Hanoi, Vietnam</t>
+          <t>Hengshui, China</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -6874,29 +6874,29 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Hanoi</t>
+          <t>Hengshui</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>VN</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
         <is>
-          <t>SJW</t>
+          <t>SGN</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Hengshui, China</t>
+          <t>Ho Chi Minh City, Vietnam</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -6906,29 +6906,29 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Hengshui</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>VN</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t>SGN</t>
+          <t>HKG</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City, Vietnam</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6936,31 +6936,19 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>Ho Chi Minh City</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>Vietnam</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>VN</t>
-        </is>
-      </c>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="1" t="inlineStr">
         <is>
-          <t>HKG</t>
+          <t>HYD</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Hyderabad, India</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6968,19 +6956,31 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
-      <c r="E206" t="inlineStr"/>
-      <c r="F206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
         <is>
-          <t>HYD</t>
+          <t>ISB</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Hyderabad, India</t>
+          <t>Islamabad, Pakistan</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -6990,29 +6990,29 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Islamabad</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>PK</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="inlineStr">
         <is>
-          <t>ISB</t>
+          <t>CGK</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Islamabad, Pakistan</t>
+          <t>Jakarta, Indonesia</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7022,29 +7022,29 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Islamabad</t>
+          <t>Jakarta</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="inlineStr">
         <is>
-          <t>CGK</t>
+          <t>TNA</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Jakarta, Indonesia</t>
+          <t>Jinan, China</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7054,29 +7054,29 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Jakarta</t>
+          <t>Jinan</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="inlineStr">
         <is>
-          <t>TNA</t>
+          <t>JHB</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Jinan, China</t>
+          <t>Johor Bahru, Malaysia</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7086,29 +7086,29 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Jinan</t>
+          <t>Johor Bahru</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MY</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
         <is>
-          <t>JHB</t>
+          <t>KNU</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Johor Bahru, Malaysia</t>
+          <t>Kanpur, India</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -7118,29 +7118,29 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Johor Bahru</t>
+          <t>Kanpur</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
         <is>
-          <t>KNU</t>
+          <t>KHH</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Kanpur, India</t>
+          <t>Kaohsiung City</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -7148,31 +7148,19 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>Kanpur</t>
-        </is>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="1" t="inlineStr">
         <is>
-          <t>KHH</t>
+          <t>KHI</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Kaohsiung City, Taiwan</t>
+          <t>Karachi, Pakistan</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -7182,29 +7170,29 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Kaohsiung City</t>
+          <t>Karachi</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>PK</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="inlineStr">
         <is>
-          <t>KHI</t>
+          <t>KTM</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Karachi, Pakistan</t>
+          <t>Kathmandu, Nepal</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -7214,29 +7202,29 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Karachi</t>
+          <t>Kathmandu</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>NP</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="inlineStr">
         <is>
-          <t>KTM</t>
+          <t>CCU</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Kathmandu, Nepal</t>
+          <t>Kolkata, India</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -7246,29 +7234,29 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Kathmandu</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="inlineStr">
         <is>
-          <t>CCU</t>
+          <t>KJA</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Kolkata, India</t>
+          <t>Krasnoyarsk, Russia</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -7278,29 +7266,29 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Krasnoyarsk</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>RU</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
         <is>
-          <t>KJA</t>
+          <t>KUL</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Krasnoyarsk, Russia</t>
+          <t>Kuala Lumpur, Malaysia</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -7310,29 +7298,29 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Krasnoyarsk</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>RU</t>
+          <t>MY</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="inlineStr">
         <is>
-          <t>KUL</t>
+          <t>PKX</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Kuala Lumpur, Malaysia</t>
+          <t>Langfang, China</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -7342,29 +7330,29 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Langfang</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="inlineStr">
         <is>
-          <t>PKX</t>
+          <t>MFM</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Langfang, China</t>
+          <t>Macau</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -7372,31 +7360,19 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>Langfang</t>
-        </is>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
         <is>
-          <t>MFM</t>
+          <t>MLE</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Macau</t>
+          <t>Malé, Maldives</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -7404,19 +7380,31 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
-      <c r="E220" t="inlineStr"/>
-      <c r="F220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Malé</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Maldives</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>MV</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="inlineStr">
         <is>
-          <t>MLE</t>
+          <t>MNL</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Malé, Maldives</t>
+          <t>Manila, Philippines</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -7426,29 +7414,29 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Malé</t>
+          <t>Manila</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Maldives</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>MV</t>
+          <t>PH</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="inlineStr">
         <is>
-          <t>MNL</t>
+          <t>BOM</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Manila, Philippines</t>
+          <t>Mumbai, India</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -7458,29 +7446,29 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Manila</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="inlineStr">
         <is>
-          <t>BOM</t>
+          <t>NAG</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Mumbai, India</t>
+          <t>Nagpur, India</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -7490,7 +7478,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Nagpur</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -7507,12 +7495,12 @@
     <row r="224">
       <c r="A224" s="1" t="inlineStr">
         <is>
-          <t>NAG</t>
+          <t>OKA</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Nagpur, India</t>
+          <t>Naha, Japan</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -7522,29 +7510,29 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Nagpur</t>
+          <t>Naha</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>JP</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="inlineStr">
         <is>
-          <t>OKA</t>
+          <t>DEL</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Naha, Japan</t>
+          <t>New Delhi, India</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -7554,29 +7542,29 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Naha</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="inlineStr">
         <is>
-          <t>DEL</t>
+          <t>KIX</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>New Delhi, India</t>
+          <t>Osaka, Japan</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -7586,29 +7574,29 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>Osaka</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>JP</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="inlineStr">
         <is>
-          <t>KIX</t>
+          <t>PAT</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Osaka, Japan</t>
+          <t>Patna, India</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -7618,29 +7606,29 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Osaka</t>
+          <t>Patna</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="inlineStr">
         <is>
-          <t>PAT</t>
+          <t>PNH</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Patna, India</t>
+          <t>Phnom Penh, Cambodia</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -7650,29 +7638,29 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Patna</t>
+          <t>Phnom Penh</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>KH</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="inlineStr">
         <is>
-          <t>PNH</t>
+          <t>TAO</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Phnom Penh, Cambodia</t>
+          <t>Qingdao, China</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -7682,29 +7670,29 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Phnom Penh</t>
+          <t>Qingdao</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Cambodia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>KH</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="inlineStr">
         <is>
-          <t>TAO</t>
+          <t>ICN</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Qingdao, China</t>
+          <t>Seoul, South Korea</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -7714,29 +7702,29 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Qingdao</t>
+          <t>Seoul</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>KR</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="inlineStr">
         <is>
-          <t>ICN</t>
+          <t>SHA</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Seoul, South Korea</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -7746,29 +7734,29 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Seoul</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="inlineStr">
         <is>
-          <t>SHA</t>
+          <t>SIN</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Singapore, Singapore</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -7778,29 +7766,29 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Shanghai</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>SG</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="inlineStr">
         <is>
-          <t>SIN</t>
+          <t>URT</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Singapore, Singapore</t>
+          <t>Surat Thani, Thailand</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -7810,29 +7798,29 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Surat Thani</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>TH</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="inlineStr">
         <is>
-          <t>URT</t>
+          <t>TPE</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Surat Thani, Thailand</t>
+          <t>Taipei</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -7840,31 +7828,19 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>Surat Thani</t>
-        </is>
-      </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>Thailand</t>
-        </is>
-      </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>TH</t>
-        </is>
-      </c>
+      <c r="D234" t="inlineStr"/>
+      <c r="E234" t="inlineStr"/>
+      <c r="F234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="1" t="inlineStr">
         <is>
-          <t>TPE</t>
+          <t>NRT</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Taipei</t>
+          <t>Tokyo, Japan</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -7872,19 +7848,31 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
-      <c r="E235" t="inlineStr"/>
-      <c r="F235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="inlineStr">
         <is>
-          <t>NRT</t>
+          <t>ULN</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Tokyo, Japan</t>
+          <t>Ulaanbaatar, Mongolia</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -7894,29 +7882,29 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Ulaanbaatar</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Mongolia</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>MN</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="inlineStr">
         <is>
-          <t>ULN</t>
+          <t>VTE</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Ulaanbaatar, Mongolia</t>
+          <t>Vientiane, Laos</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -7926,29 +7914,29 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Ulaanbaatar</t>
+          <t>Vientiane</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Mongolia</t>
+          <t>Laos</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>MN</t>
+          <t>LA</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="inlineStr">
         <is>
-          <t>VTE</t>
+          <t>KHN</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Vientiane, Laos</t>
+          <t>Xinyu, China</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -7958,29 +7946,29 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Vientiane</t>
+          <t>Xinyu</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Laos</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="inlineStr">
         <is>
-          <t>KHN</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Xinyu, China</t>
+          <t>Yerevan, Armenia</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -7990,29 +7978,29 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Xinyu</t>
+          <t>Yerevan</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>AM</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>JOG</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Yerevan, Armenia</t>
+          <t>Yogyakarta, Indonesia</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -8022,29 +8010,29 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Yerevan</t>
+          <t>Yogyakarta</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="inlineStr">
         <is>
-          <t>JOG</t>
+          <t>CGY</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Yogyakarta, Indonesia</t>
+          <t>Cagayan de Oro, Philippines</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -8054,29 +8042,29 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Yogyakarta</t>
+          <t>Cagayan de Oro</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>PH</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="inlineStr">
         <is>
-          <t>CGY</t>
+          <t>COK</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Cagayan de Oro, Philippines</t>
+          <t>Kochi, India</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -8086,29 +8074,29 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Cagayan de Oro</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="inlineStr">
         <is>
-          <t>COK</t>
+          <t>DPS</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Kochi, India</t>
+          <t>Denpasar, Indonesia</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -8118,29 +8106,29 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Denpasar</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="inlineStr">
         <is>
-          <t>DPS</t>
+          <t>CNN</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Denpasar, Indonesia</t>
+          <t>Kannur, India</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -8150,29 +8138,29 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Denpasar</t>
+          <t>Kannur</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="inlineStr">
         <is>
-          <t>CNN</t>
+          <t>SZX</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Kannur, India</t>
+          <t>Shenzhen, China</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -8182,29 +8170,29 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Kannur</t>
+          <t>Shenzhen</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="inlineStr">
         <is>
-          <t>SZX</t>
+          <t>KWE</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Shenzhen, China</t>
+          <t>Guiyang, China</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -8214,7 +8202,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Shenzhen</t>
+          <t>Guiyang</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -8231,12 +8219,12 @@
     <row r="247">
       <c r="A247" s="1" t="inlineStr">
         <is>
-          <t>KWE</t>
+          <t>HGH</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Guiyang, China</t>
+          <t>Shaoxing, China</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -8246,7 +8234,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Guiyang</t>
+          <t>Shaoxing</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -8263,12 +8251,12 @@
     <row r="248">
       <c r="A248" s="1" t="inlineStr">
         <is>
-          <t>HGH</t>
+          <t>CZX</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Shaoxing, China</t>
+          <t>Changzhou, China</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -8278,7 +8266,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Shaoxing</t>
+          <t>Changzhou</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -8295,12 +8283,12 @@
     <row r="249">
       <c r="A249" s="1" t="inlineStr">
         <is>
-          <t>CZX</t>
+          <t>KMG</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Changzhou, China</t>
+          <t>Kunming, China</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -8310,7 +8298,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Changzhou</t>
+          <t>Kunming</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -8327,12 +8315,12 @@
     <row r="250">
       <c r="A250" s="1" t="inlineStr">
         <is>
-          <t>KMG</t>
+          <t>CNX</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Kunming, China</t>
+          <t>Chiang Mai, Thailand</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -8342,29 +8330,29 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Kunming</t>
+          <t>Chiang Mai</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>TH</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="inlineStr">
         <is>
-          <t>CNX</t>
+          <t>CGO</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Chiang Mai, Thailand</t>
+          <t>Zhengzhou, China</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -8374,29 +8362,29 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Chiang Mai</t>
+          <t>Zhengzhou</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="inlineStr">
         <is>
-          <t>CGO</t>
+          <t>TYN</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Zhengzhou, China</t>
+          <t>Yangquan, China</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -8406,7 +8394,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Zhengzhou</t>
+          <t>Yangquan</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -8423,12 +8411,12 @@
     <row r="253">
       <c r="A253" s="1" t="inlineStr">
         <is>
-          <t>TYN</t>
+          <t>CSX</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Yangquan, China</t>
+          <t>Changsha, China</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -8438,7 +8426,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Yangquan</t>
+          <t>Changsha</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -8455,12 +8443,12 @@
     <row r="254">
       <c r="A254" s="1" t="inlineStr">
         <is>
-          <t>CSX</t>
+          <t>DLC</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Changsha, China</t>
+          <t>Dalian, China</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -8470,7 +8458,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Changsha</t>
+          <t>Dalian</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -8487,12 +8475,12 @@
     <row r="255">
       <c r="A255" s="1" t="inlineStr">
         <is>
-          <t>DLC</t>
+          <t>BHY</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Dalian, China</t>
+          <t>Beihai, China</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -8502,7 +8490,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Dalian</t>
+          <t>Beihai</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -8519,12 +8507,12 @@
     <row r="256">
       <c r="A256" s="1" t="inlineStr">
         <is>
-          <t>BHY</t>
+          <t>CKG</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Beihai, China</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -8534,7 +8522,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Beihai</t>
+          <t>Chongqing</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -8551,12 +8539,12 @@
     <row r="257">
       <c r="A257" s="1" t="inlineStr">
         <is>
-          <t>CKG</t>
+          <t>XFN</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Chongqing, China</t>
+          <t>Xiangyang, China</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -8566,7 +8554,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Chongqing</t>
+          <t>Xiangyang</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -8583,12 +8571,12 @@
     <row r="258">
       <c r="A258" s="1" t="inlineStr">
         <is>
-          <t>XFN</t>
+          <t>DAD</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Xiangyang, China</t>
+          <t>Da Nang, Vietnam</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -8598,29 +8586,29 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Xiangyang</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>VN</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="inlineStr">
         <is>
-          <t>DAD</t>
+          <t>JXG</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Da Nang, Vietnam</t>
+          <t>Jiaxing, China</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -8630,29 +8618,29 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Jiaxing</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>VN</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="inlineStr">
         <is>
-          <t>JXG</t>
+          <t>CRK</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Jiaxing, China</t>
+          <t>Tarlac City, Philippines</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -8662,29 +8650,29 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Jiaxing</t>
+          <t>Tarlac City</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>PH</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="inlineStr">
         <is>
-          <t>CRK</t>
+          <t>PBH</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Tarlac City, Philippines</t>
+          <t>Thimphu, Bhutan</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -8694,29 +8682,29 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Tarlac City</t>
+          <t>Thimphu</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Bhutan</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>BT</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="inlineStr">
         <is>
-          <t>PBH</t>
+          <t>XIY</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Thimphu, Bhutan</t>
+          <t>Baoji, China</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -8726,29 +8714,29 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Thimphu</t>
+          <t>Baoji</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Bhutan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="inlineStr">
         <is>
-          <t>XIY</t>
+          <t>NQZ</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Baoji, China</t>
+          <t>Astana, Kazakhstan</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -8758,29 +8746,29 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Baoji</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>KZ</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="inlineStr">
         <is>
-          <t>NQZ</t>
+          <t>KCH</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Astana, Kazakhstan</t>
+          <t>Kuching, Malaysia</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -8790,29 +8778,29 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Kuching</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>MY</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="inlineStr">
         <is>
-          <t>KCH</t>
+          <t>AKX</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Kuching, Malaysia</t>
+          <t>Aktobe, Kazakhstan</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -8822,29 +8810,29 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Kuching</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>KZ</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="1" t="inlineStr">
         <is>
-          <t>AKX</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Aktobe, Kazakhstan</t>
+          <t>Tongren, China</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -8854,29 +8842,29 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Tongren</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Tongren, China</t>
+          <t>Taizhou, China</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -8886,7 +8874,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Tongren</t>
+          <t>Taizhou</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -8903,12 +8891,12 @@
     <row r="268">
       <c r="A268" s="1" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>FRU</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Taizhou, China</t>
+          <t>Bishkek, Kyrgyzstan</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -8918,29 +8906,29 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Taizhou</t>
+          <t>Bishkek</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kyrgyzstan</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>KG</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="inlineStr">
         <is>
-          <t>FRU</t>
+          <t>MLG</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Bishkek, Kyrgyzstan</t>
+          <t>Malang, Indonesia</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -8950,29 +8938,29 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Bishkek</t>
+          <t>Malang</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Kyrgyzstan</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="inlineStr">
         <is>
-          <t>MLG</t>
+          <t>LHE</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Malang, Indonesia</t>
+          <t>Lahore, Pakistan</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -8982,29 +8970,29 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Malang</t>
+          <t>Lahore</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>PK</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="inlineStr">
         <is>
-          <t>LHE</t>
+          <t>CTU</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Lahore, Pakistan</t>
+          <t>Chengdu, China</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -9014,29 +9002,29 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Lahore</t>
+          <t>Chengdu</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="inlineStr">
         <is>
-          <t>CTU</t>
+          <t>AGR</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Chengdu, China</t>
+          <t>Agra, India</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -9046,29 +9034,29 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Chengdu</t>
+          <t>Agra</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="inlineStr">
         <is>
-          <t>AGR</t>
+          <t>CJB</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Agra, India</t>
+          <t>Coimbatore, India</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -9078,7 +9066,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Agra</t>
+          <t>Coimbatore</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -9095,12 +9083,12 @@
     <row r="274">
       <c r="A274" s="1" t="inlineStr">
         <is>
-          <t>CJB</t>
+          <t>ACX</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Coimbatore, India</t>
+          <t>Xingyi, China</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -9110,29 +9098,29 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Coimbatore</t>
+          <t>Xingyi</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="1" t="inlineStr">
         <is>
-          <t>ACX</t>
+          <t>BBI</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Xingyi, China</t>
+          <t>Bhubaneswar, India</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -9142,29 +9130,29 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Xingyi</t>
+          <t>Bhubaneswar</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="1" t="inlineStr">
         <is>
-          <t>BBI</t>
+          <t>LYA</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Bhubaneswar, India</t>
+          <t>Luoyang, China</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -9174,29 +9162,29 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Bhubaneswar</t>
+          <t>Luoyang</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="inlineStr">
         <is>
-          <t>LYA</t>
+          <t>PNQ</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Luoyang, China</t>
+          <t>Pune, India</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -9206,29 +9194,29 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Luoyang</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="1" t="inlineStr">
         <is>
-          <t>PNQ</t>
+          <t>JRG</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Pune, India</t>
+          <t>Sambalpur, India</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -9238,7 +9226,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Sambalpur</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -9255,44 +9243,44 @@
     <row r="279">
       <c r="A279" s="1" t="inlineStr">
         <is>
-          <t>JRG</t>
+          <t>ABQ</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Sambalpur, India</t>
+          <t>Albuquerque, NM, United States</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Sambalpur</t>
+          <t>Albuquerque, NM</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="1" t="inlineStr">
         <is>
-          <t>ABQ</t>
+          <t>ANC</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, United States</t>
+          <t>Anchorage, AK, United States</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -9302,7 +9290,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Albuquerque, NM</t>
+          <t>Anchorage, AK</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -9319,12 +9307,12 @@
     <row r="281">
       <c r="A281" s="1" t="inlineStr">
         <is>
-          <t>ANC</t>
+          <t>IAD</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Anchorage, AK, United States</t>
+          <t>Ashburn, VA, United States</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -9334,7 +9322,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Anchorage, AK</t>
+          <t>Ashburn, VA</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -9351,12 +9339,12 @@
     <row r="282">
       <c r="A282" s="1" t="inlineStr">
         <is>
-          <t>IAD</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Ashburn, VA, United States</t>
+          <t>Atlanta, GA, United States</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -9366,7 +9354,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Ashburn, VA</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -9383,12 +9371,12 @@
     <row r="283">
       <c r="A283" s="1" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Atlanta, GA, United States</t>
+          <t>Austin, TX, United States</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -9398,7 +9386,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -9415,12 +9403,12 @@
     <row r="284">
       <c r="A284" s="1" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>BGR</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Austin, TX, United States</t>
+          <t>Bangor, ME, United States</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -9430,7 +9418,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Bangor, ME</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -9447,12 +9435,12 @@
     <row r="285">
       <c r="A285" s="1" t="inlineStr">
         <is>
-          <t>BGR</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Bangor, ME, United States</t>
+          <t>Boston, MA, United States</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -9462,7 +9450,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Bangor, ME</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -9479,12 +9467,12 @@
     <row r="286">
       <c r="A286" s="1" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Boston, MA, United States</t>
+          <t>Buffalo, NY, United States</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -9494,7 +9482,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Buffalo, NY</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -9511,12 +9499,12 @@
     <row r="287">
       <c r="A287" s="1" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>YYC</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Buffalo, NY, United States</t>
+          <t>Calgary, AB, Canada</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -9526,29 +9514,29 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Buffalo, NY</t>
+          <t>Calgary, AB</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="inlineStr">
         <is>
-          <t>YYC</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Calgary, AB, Canada</t>
+          <t>Charlotte, NC, United States</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -9558,29 +9546,29 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Calgary, AB</t>
+          <t>Charlotte, NC</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>ORD</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Charlotte, NC, United States</t>
+          <t>Chicago, IL, United States</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -9590,7 +9578,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Charlotte, NC</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -9607,12 +9595,12 @@
     <row r="290">
       <c r="A290" s="1" t="inlineStr">
         <is>
-          <t>ORD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Chicago, IL, United States</t>
+          <t>Cleveland, OH, United States</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -9622,7 +9610,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Cleveland, OH</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -9639,12 +9627,12 @@
     <row r="291">
       <c r="A291" s="1" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CMH</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Cleveland, OH, United States</t>
+          <t>Columbus, OH, United States</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -9654,7 +9642,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Cleveland, OH</t>
+          <t>Columbus, OH</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -9671,12 +9659,12 @@
     <row r="292">
       <c r="A292" s="1" t="inlineStr">
         <is>
-          <t>CMH</t>
+          <t>DFW</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Columbus, OH, United States</t>
+          <t>Dallas, TX, United States</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -9686,7 +9674,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Columbus, OH</t>
+          <t>Dallas, TX</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -9703,12 +9691,12 @@
     <row r="293">
       <c r="A293" s="1" t="inlineStr">
         <is>
-          <t>DFW</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Dallas, TX, United States</t>
+          <t>Denver, CO, United States</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -9718,7 +9706,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Dallas, TX</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -9735,12 +9723,12 @@
     <row r="294">
       <c r="A294" s="1" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DTW</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Denver, CO, United States</t>
+          <t>Detroit, MI, United States</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -9750,7 +9738,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>Detroit, MI</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -9767,12 +9755,12 @@
     <row r="295">
       <c r="A295" s="1" t="inlineStr">
         <is>
-          <t>DTW</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Detroit, MI, United States</t>
+          <t>Durham, NC, United States</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -9782,7 +9770,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Detroit, MI</t>
+          <t>Durham, NC</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -9799,12 +9787,12 @@
     <row r="296">
       <c r="A296" s="1" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GDL</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Durham, NC, United States</t>
+          <t>Guadalajara, Mexico</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -9814,29 +9802,29 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Durham, NC</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="inlineStr">
         <is>
-          <t>GDL</t>
+          <t>YHZ</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Guadalajara, Mexico</t>
+          <t>Halifax, Canada</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -9846,29 +9834,29 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Halifax</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="inlineStr">
         <is>
-          <t>YHZ</t>
+          <t>HNL</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Halifax, Canada</t>
+          <t>Honolulu, HI, United States</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -9878,29 +9866,29 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Halifax</t>
+          <t>Honolulu, HI</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="1" t="inlineStr">
         <is>
-          <t>HNL</t>
+          <t>IAH</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Honolulu, HI, United States</t>
+          <t>Houston, TX, United States</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -9910,7 +9898,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Honolulu, HI</t>
+          <t>Houston, TX</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -9927,12 +9915,12 @@
     <row r="300">
       <c r="A300" s="1" t="inlineStr">
         <is>
-          <t>IAH</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Houston, TX, United States</t>
+          <t>Indianapolis, IN, United States</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -9942,7 +9930,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Houston, TX</t>
+          <t>Indianapolis, IN</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -9959,12 +9947,12 @@
     <row r="301">
       <c r="A301" s="1" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, United States</t>
+          <t>Jacksonville, FL, United States</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -9974,7 +9962,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Indianapolis, IN</t>
+          <t>Jacksonville, FL</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -9991,12 +9979,12 @@
     <row r="302">
       <c r="A302" s="1" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>MCI</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, United States</t>
+          <t>Kansas City, MO, United States</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -10006,7 +9994,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Jacksonville, FL</t>
+          <t>Kansas City, MO</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -10023,12 +10011,12 @@
     <row r="303">
       <c r="A303" s="1" t="inlineStr">
         <is>
-          <t>MCI</t>
+          <t>KIN</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Kansas City, MO, United States</t>
+          <t>Kingston, Jamaica</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -10038,29 +10026,29 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Kansas City, MO</t>
+          <t>Kingston</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Jamaica</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JM</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="inlineStr">
         <is>
-          <t>KIN</t>
+          <t>LAS</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Kingston, Jamaica</t>
+          <t>Las Vegas, NV, United States</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -10070,29 +10058,29 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Kingston</t>
+          <t>Las Vegas, NV</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Jamaica</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>JM</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="inlineStr">
         <is>
-          <t>LAS</t>
+          <t>LAX</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, United States</t>
+          <t>Los Angeles, CA, United States</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -10102,7 +10090,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Las Vegas, NV</t>
+          <t>Los Angeles, CA</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -10119,12 +10107,12 @@
     <row r="306">
       <c r="A306" s="1" t="inlineStr">
         <is>
-          <t>LAX</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, United States</t>
+          <t>Memphis, TN, United States</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -10134,7 +10122,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
+          <t>Memphis, TN</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -10151,12 +10139,12 @@
     <row r="307">
       <c r="A307" s="1" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MEX</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Memphis, TN, United States</t>
+          <t>Mexico City, Mexico</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -10166,29 +10154,29 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Memphis, TN</t>
+          <t>Mexico City</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="inlineStr">
         <is>
-          <t>MEX</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Mexico City, Mexico</t>
+          <t>Miami, FL, United States</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -10198,29 +10186,29 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Mexico City</t>
+          <t>Miami, FL</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MSP</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Miami, FL, United States</t>
+          <t>Minneapolis, MN, United States</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -10230,7 +10218,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Miami, FL</t>
+          <t>Minneapolis, MN</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -10247,12 +10235,12 @@
     <row r="310">
       <c r="A310" s="1" t="inlineStr">
         <is>
-          <t>MSP</t>
+          <t>YUL</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, United States</t>
+          <t>Montréal, QC, Canada</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -10262,29 +10250,29 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Minneapolis, MN</t>
+          <t>Montréal, QC</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="inlineStr">
         <is>
-          <t>YUL</t>
+          <t>BNA</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Montréal, QC, Canada</t>
+          <t>Nashville, United States</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -10294,29 +10282,29 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Montréal, QC</t>
+          <t>Nashville</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="1" t="inlineStr">
         <is>
-          <t>BNA</t>
+          <t>EWR</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Nashville, United States</t>
+          <t>Newark, NJ, United States</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -10326,7 +10314,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Nashville</t>
+          <t>Newark, NJ</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -10343,12 +10331,12 @@
     <row r="313">
       <c r="A313" s="1" t="inlineStr">
         <is>
-          <t>EWR</t>
+          <t>ORF</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Newark, NJ, United States</t>
+          <t>Norfolk, VA, United States</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -10358,7 +10346,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Newark, NJ</t>
+          <t>Norfolk, VA</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -10375,12 +10363,12 @@
     <row r="314">
       <c r="A314" s="1" t="inlineStr">
         <is>
-          <t>ORF</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Norfolk, VA, United States</t>
+          <t>Oklahoma City, OK, United States</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -10390,7 +10378,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Norfolk, VA</t>
+          <t>Oklahoma City, OK</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -10407,12 +10395,12 @@
     <row r="315">
       <c r="A315" s="1" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>OMA</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, United States</t>
+          <t>Omaha, NE, United States</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -10422,7 +10410,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK</t>
+          <t>Omaha, NE</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -10439,12 +10427,12 @@
     <row r="316">
       <c r="A316" s="1" t="inlineStr">
         <is>
-          <t>OMA</t>
+          <t>YOW</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Omaha, NE, United States</t>
+          <t>Ottawa, Canada</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -10454,29 +10442,29 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Omaha, NE</t>
+          <t>Ottawa</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="1" t="inlineStr">
         <is>
-          <t>YOW</t>
+          <t>PHL</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Ottawa, Canada</t>
+          <t>Philadelphia, United States</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -10486,29 +10474,29 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Ottawa</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="1" t="inlineStr">
         <is>
-          <t>PHL</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Philadelphia, United States</t>
+          <t>Phoenix, AZ, United States</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -10518,7 +10506,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Phoenix, AZ</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -10535,12 +10523,12 @@
     <row r="319">
       <c r="A319" s="1" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, United States</t>
+          <t>Pittsburgh, PA, United States</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -10550,7 +10538,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Phoenix, AZ</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -10567,12 +10555,12 @@
     <row r="320">
       <c r="A320" s="1" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, United States</t>
+          <t>Portland, OR, United States</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -10582,7 +10570,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA</t>
+          <t>Portland, OR</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -10599,12 +10587,12 @@
     <row r="321">
       <c r="A321" s="1" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>QRO</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Portland, OR, United States</t>
+          <t>Queretaro, MX, Mexico</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -10614,29 +10602,29 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Portland, OR</t>
+          <t>Queretaro, MX</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="inlineStr">
         <is>
-          <t>QRO</t>
+          <t>RIC</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Queretaro, MX, Mexico</t>
+          <t>Richmond, VA, United States</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -10646,29 +10634,29 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Queretaro, MX</t>
+          <t>Richmond, VA</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="1" t="inlineStr">
         <is>
-          <t>RIC</t>
+          <t>SMF</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Richmond, VA, United States</t>
+          <t>Sacramento, CA, United States</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -10678,7 +10666,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Richmond, VA</t>
+          <t>Sacramento, CA</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -10695,12 +10683,12 @@
     <row r="324">
       <c r="A324" s="1" t="inlineStr">
         <is>
-          <t>SMF</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Sacramento, CA, United States</t>
+          <t>Salt Lake City, UT, United States</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -10710,7 +10698,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Sacramento, CA</t>
+          <t>Salt Lake City, UT</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -10727,12 +10715,12 @@
     <row r="325">
       <c r="A325" s="1" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>SAT</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, United States</t>
+          <t>San Antonio, TX, United States</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -10742,7 +10730,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT</t>
+          <t>San Antonio, TX</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -10759,12 +10747,12 @@
     <row r="326">
       <c r="A326" s="1" t="inlineStr">
         <is>
-          <t>SAT</t>
+          <t>SAN</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>San Antonio, TX, United States</t>
+          <t>San Diego, CA, United States</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -10774,7 +10762,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>San Antonio, TX</t>
+          <t>San Diego, CA</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -10791,12 +10779,12 @@
     <row r="327">
       <c r="A327" s="1" t="inlineStr">
         <is>
-          <t>SAN</t>
+          <t>SFO</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>San Diego, CA, United States</t>
+          <t>San Francisco, CA, United States</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -10806,7 +10794,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>San Diego, CA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -10823,12 +10811,12 @@
     <row r="328">
       <c r="A328" s="1" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>SJC</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>San Francisco, CA, United States</t>
+          <t>San Jose, CA, United States</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -10838,7 +10826,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -10855,12 +10843,12 @@
     <row r="329">
       <c r="A329" s="1" t="inlineStr">
         <is>
-          <t>SJC</t>
+          <t>YXE</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>San Jose, CA, United States</t>
+          <t>Saskatoon, SK, Canada</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -10870,29 +10858,29 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>Saskatoon, SK</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="inlineStr">
         <is>
-          <t>YXE</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Saskatoon, SK, Canada</t>
+          <t>Seattle, WA, United States</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -10902,29 +10890,29 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Saskatoon, SK</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="1" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>FSD</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Seattle, WA, United States</t>
+          <t>Sioux Falls, SD, United States</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -10934,7 +10922,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Sioux Falls, SD</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -10951,12 +10939,12 @@
     <row r="332">
       <c r="A332" s="1" t="inlineStr">
         <is>
-          <t>FSD</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, United States</t>
+          <t>St. Louis, MO, United States</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -10966,7 +10954,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD</t>
+          <t>St. Louis, MO</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -10983,12 +10971,12 @@
     <row r="333">
       <c r="A333" s="1" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>TLH</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>St. Louis, MO, United States</t>
+          <t>Tallahassee, FL, United States</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -10998,7 +10986,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>St. Louis, MO</t>
+          <t>Tallahassee, FL</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -11015,12 +11003,12 @@
     <row r="334">
       <c r="A334" s="1" t="inlineStr">
         <is>
-          <t>TLH</t>
+          <t>TPA</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, United States</t>
+          <t>Tampa, FL, United States</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -11030,7 +11018,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Tallahassee, FL</t>
+          <t>Tampa, FL</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -11047,12 +11035,12 @@
     <row r="335">
       <c r="A335" s="1" t="inlineStr">
         <is>
-          <t>TPA</t>
+          <t>YYZ</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Tampa, FL, United States</t>
+          <t>Toronto, ON, Canada</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -11062,29 +11050,29 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Tampa, FL</t>
+          <t>Toronto, ON</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="inlineStr">
         <is>
-          <t>YYZ</t>
+          <t>YVR</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Toronto, ON, Canada</t>
+          <t>Vancouver, BC, Canada</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -11094,7 +11082,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Toronto, ON</t>
+          <t>Vancouver, BC</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -11111,12 +11099,12 @@
     <row r="337">
       <c r="A337" s="1" t="inlineStr">
         <is>
-          <t>YVR</t>
+          <t>YWG</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Vancouver, BC, Canada</t>
+          <t>Winnipeg, MB, Canada</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -11126,7 +11114,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Vancouver, BC</t>
+          <t>Winnipeg, MB</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -11143,12 +11131,12 @@
     <row r="338">
       <c r="A338" s="1" t="inlineStr">
         <is>
-          <t>YWG</t>
+          <t>CVG</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Winnipeg, MB, Canada</t>
+          <t>Cincinnati, United States</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -11158,17 +11146,17 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Winnipeg, MB</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>

--- a/DC-Colos.xlsx
+++ b/DC-Colos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F338"/>
+  <dimension ref="A1:F337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10427,12 +10427,12 @@
     <row r="316">
       <c r="A316" s="1" t="inlineStr">
         <is>
-          <t>YOW</t>
+          <t>PHL</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Ottawa, Canada</t>
+          <t>Philadelphia, United States</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -10442,29 +10442,29 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Ottawa</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="1" t="inlineStr">
         <is>
-          <t>PHL</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Philadelphia, United States</t>
+          <t>Phoenix, AZ, United States</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -10474,7 +10474,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Phoenix, AZ</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -10491,12 +10491,12 @@
     <row r="318">
       <c r="A318" s="1" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, United States</t>
+          <t>Pittsburgh, PA, United States</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -10506,7 +10506,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Phoenix, AZ</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -10523,12 +10523,12 @@
     <row r="319">
       <c r="A319" s="1" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, United States</t>
+          <t>Portland, OR, United States</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -10538,7 +10538,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA</t>
+          <t>Portland, OR</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -10555,12 +10555,12 @@
     <row r="320">
       <c r="A320" s="1" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>QRO</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Portland, OR, United States</t>
+          <t>Queretaro, MX, Mexico</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -10570,29 +10570,29 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Portland, OR</t>
+          <t>Queretaro, MX</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="inlineStr">
         <is>
-          <t>QRO</t>
+          <t>RIC</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Queretaro, MX, Mexico</t>
+          <t>Richmond, VA, United States</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -10602,29 +10602,29 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Queretaro, MX</t>
+          <t>Richmond, VA</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="inlineStr">
         <is>
-          <t>RIC</t>
+          <t>SMF</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Richmond, VA, United States</t>
+          <t>Sacramento, CA, United States</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -10634,7 +10634,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Richmond, VA</t>
+          <t>Sacramento, CA</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -10651,12 +10651,12 @@
     <row r="323">
       <c r="A323" s="1" t="inlineStr">
         <is>
-          <t>SMF</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Sacramento, CA, United States</t>
+          <t>Salt Lake City, UT, United States</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Sacramento, CA</t>
+          <t>Salt Lake City, UT</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -10683,12 +10683,12 @@
     <row r="324">
       <c r="A324" s="1" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>SAT</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, United States</t>
+          <t>San Antonio, TX, United States</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -10698,7 +10698,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT</t>
+          <t>San Antonio, TX</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -10715,12 +10715,12 @@
     <row r="325">
       <c r="A325" s="1" t="inlineStr">
         <is>
-          <t>SAT</t>
+          <t>SAN</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>San Antonio, TX, United States</t>
+          <t>San Diego, CA, United States</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -10730,7 +10730,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>San Antonio, TX</t>
+          <t>San Diego, CA</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -10747,12 +10747,12 @@
     <row r="326">
       <c r="A326" s="1" t="inlineStr">
         <is>
-          <t>SAN</t>
+          <t>SFO</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>San Diego, CA, United States</t>
+          <t>San Francisco, CA, United States</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>San Diego, CA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -10779,12 +10779,12 @@
     <row r="327">
       <c r="A327" s="1" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>SJC</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>San Francisco, CA, United States</t>
+          <t>San Jose, CA, United States</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -10811,12 +10811,12 @@
     <row r="328">
       <c r="A328" s="1" t="inlineStr">
         <is>
-          <t>SJC</t>
+          <t>YXE</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>San Jose, CA, United States</t>
+          <t>Saskatoon, SK, Canada</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -10826,29 +10826,29 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>Saskatoon, SK</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="inlineStr">
         <is>
-          <t>YXE</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Saskatoon, SK, Canada</t>
+          <t>Seattle, WA, United States</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -10858,29 +10858,29 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Saskatoon, SK</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>FSD</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Seattle, WA, United States</t>
+          <t>Sioux Falls, SD, United States</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -10890,7 +10890,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Sioux Falls, SD</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -10907,12 +10907,12 @@
     <row r="331">
       <c r="A331" s="1" t="inlineStr">
         <is>
-          <t>FSD</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, United States</t>
+          <t>St. Louis, MO, United States</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -10922,7 +10922,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD</t>
+          <t>St. Louis, MO</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -10939,12 +10939,12 @@
     <row r="332">
       <c r="A332" s="1" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>TLH</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>St. Louis, MO, United States</t>
+          <t>Tallahassee, FL, United States</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -10954,7 +10954,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>St. Louis, MO</t>
+          <t>Tallahassee, FL</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -10971,12 +10971,12 @@
     <row r="333">
       <c r="A333" s="1" t="inlineStr">
         <is>
-          <t>TLH</t>
+          <t>TPA</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, United States</t>
+          <t>Tampa, FL, United States</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -10986,7 +10986,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Tallahassee, FL</t>
+          <t>Tampa, FL</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -11003,12 +11003,12 @@
     <row r="334">
       <c r="A334" s="1" t="inlineStr">
         <is>
-          <t>TPA</t>
+          <t>YYZ</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Tampa, FL, United States</t>
+          <t>Toronto, ON, Canada</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -11018,29 +11018,29 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Tampa, FL</t>
+          <t>Toronto, ON</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="inlineStr">
         <is>
-          <t>YYZ</t>
+          <t>YVR</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Toronto, ON, Canada</t>
+          <t>Vancouver, BC, Canada</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -11050,7 +11050,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Toronto, ON</t>
+          <t>Vancouver, BC</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -11067,12 +11067,12 @@
     <row r="336">
       <c r="A336" s="1" t="inlineStr">
         <is>
-          <t>YVR</t>
+          <t>YWG</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Vancouver, BC, Canada</t>
+          <t>Winnipeg, MB, Canada</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Vancouver, BC</t>
+          <t>Winnipeg, MB</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -11099,12 +11099,12 @@
     <row r="337">
       <c r="A337" s="1" t="inlineStr">
         <is>
-          <t>YWG</t>
+          <t>CVG</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Winnipeg, MB, Canada</t>
+          <t>Cincinnati, United States</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -11114,47 +11114,15 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Winnipeg, MB</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" s="1" t="inlineStr">
-        <is>
-          <t>CVG</t>
-        </is>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>Cincinnati, United States</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>North America</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>Cincinnati</t>
-        </is>
-      </c>
-      <c r="E338" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="F338" t="inlineStr">
         <is>
           <t>US</t>
         </is>

--- a/DC-Colos.xlsx
+++ b/DC-Colos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F337"/>
+  <dimension ref="A1:F338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6283,44 +6283,44 @@
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>DLA</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Ahmedabad, India</t>
+          <t>Douala, Cameroon</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>Douala</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CM</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Almaty, Kazakhstan</t>
+          <t>Ahmedabad, India</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6330,29 +6330,29 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Almaty</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t>BLR</t>
+          <t>ALA</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Bangalore, India</t>
+          <t>Almaty, Kazakhstan</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6362,29 +6362,29 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Almaty</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>KZ</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>BKK</t>
+          <t>BLR</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Bangkok, Thailand</t>
+          <t>Bangalore, India</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6394,29 +6394,29 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>BWN</t>
+          <t>BKK</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Bandar Seri Begawan, Brunei</t>
+          <t>Bangkok, Thailand</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6426,29 +6426,29 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Bandar Seri Begawan</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Brunei</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>BN</t>
+          <t>TH</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>BWN</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Cebu, Philippines</t>
+          <t>Bandar Seri Begawan, Brunei</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6458,29 +6458,29 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Cebu</t>
+          <t>Bandar Seri Begawan</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Brunei</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>BN</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>IXC</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Chandigarh, India</t>
+          <t>Cebu, Philippines</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6490,29 +6490,29 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Chandigarh</t>
+          <t>Cebu</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>PH</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>CGD</t>
+          <t>IXC</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Changde, China</t>
+          <t>Chandigarh, India</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6522,29 +6522,29 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Changde</t>
+          <t>Chandigarh</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>CGD</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Chennai, India</t>
+          <t>Changde, China</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6554,29 +6554,29 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Changde</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>CGP</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Chittagong, Bangladesh</t>
+          <t>Chennai, India</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -6586,29 +6586,29 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Chittagong</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>BD</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t>CMB</t>
+          <t>CGP</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Colombo, Sri Lanka</t>
+          <t>Chittagong, Bangladesh</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -6618,29 +6618,29 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Colombo</t>
+          <t>Chittagong</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>LK</t>
+          <t>BD</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>CMB</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Dhaka, Bangladesh</t>
+          <t>Colombo, Sri Lanka</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -6650,29 +6650,29 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>Colombo</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>Sri Lanka</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>BD</t>
+          <t>LK</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>FUO</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Foshan, China</t>
+          <t>Dhaka, Bangladesh</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -6682,29 +6682,29 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Foshan</t>
+          <t>Dhaka</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>BD</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>FUK</t>
+          <t>FUO</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Fukuoka, Japan</t>
+          <t>Foshan, China</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -6714,29 +6714,29 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Fukuoka</t>
+          <t>Foshan</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>FOC</t>
+          <t>FUK</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Fuzhou, China</t>
+          <t>Fukuoka, Japan</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -6746,29 +6746,29 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Fuzhou</t>
+          <t>Fukuoka</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>JP</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>FOC</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Guangzhou, China</t>
+          <t>Fuzhou, China</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Guangzhou</t>
+          <t>Fuzhou</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -6795,12 +6795,12 @@
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t>HAK</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Haikou, China</t>
+          <t>Guangzhou, China</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Haikou</t>
+          <t>Guangzhou</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -6827,12 +6827,12 @@
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t>HAN</t>
+          <t>HAK</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Hanoi, Vietnam</t>
+          <t>Haikou, China</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -6842,29 +6842,29 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Hanoi</t>
+          <t>Haikou</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>VN</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
         <is>
-          <t>SJW</t>
+          <t>HAN</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Hengshui, China</t>
+          <t>Hanoi, Vietnam</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -6874,29 +6874,29 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Hengshui</t>
+          <t>Hanoi</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>VN</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
         <is>
-          <t>SGN</t>
+          <t>SJW</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City, Vietnam</t>
+          <t>Hengshui, China</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -6906,29 +6906,29 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Hengshui</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>VN</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t>HKG</t>
+          <t>SGN</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Ho Chi Minh City, Vietnam</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6936,19 +6936,31 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
-      <c r="E205" t="inlineStr"/>
-      <c r="F205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Ho Chi Minh City</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>VN</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="inlineStr">
         <is>
-          <t>HYD</t>
+          <t>HKG</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Hyderabad, India</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6956,31 +6968,19 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>Hyderabad</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
         <is>
-          <t>ISB</t>
+          <t>HYD</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Islamabad, Pakistan</t>
+          <t>Hyderabad, India</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -6990,29 +6990,29 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Islamabad</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="inlineStr">
         <is>
-          <t>CGK</t>
+          <t>ISB</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Jakarta, Indonesia</t>
+          <t>Islamabad, Pakistan</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7022,29 +7022,29 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Jakarta</t>
+          <t>Islamabad</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>PK</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="inlineStr">
         <is>
-          <t>TNA</t>
+          <t>CGK</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Jinan, China</t>
+          <t>Jakarta, Indonesia</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7054,29 +7054,29 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Jinan</t>
+          <t>Jakarta</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="inlineStr">
         <is>
-          <t>JHB</t>
+          <t>TNA</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Johor Bahru, Malaysia</t>
+          <t>Jinan, China</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7086,29 +7086,29 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Johor Bahru</t>
+          <t>Jinan</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
         <is>
-          <t>KNU</t>
+          <t>JHB</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Kanpur, India</t>
+          <t>Johor Bahru, Malaysia</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -7118,29 +7118,29 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Kanpur</t>
+          <t>Johor Bahru</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>MY</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
         <is>
-          <t>KHH</t>
+          <t>KNU</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Kaohsiung City</t>
+          <t>Kanpur, India</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -7148,19 +7148,31 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
-      <c r="E212" t="inlineStr"/>
-      <c r="F212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Kanpur</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="inlineStr">
         <is>
-          <t>KHI</t>
+          <t>KHH</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Karachi, Pakistan</t>
+          <t>Kaohsiung City</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -7168,31 +7180,19 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>Karachi</t>
-        </is>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>Pakistan</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="1" t="inlineStr">
         <is>
-          <t>KTM</t>
+          <t>KHI</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Kathmandu, Nepal</t>
+          <t>Karachi, Pakistan</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -7202,29 +7202,29 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Kathmandu</t>
+          <t>Karachi</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>PK</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="inlineStr">
         <is>
-          <t>CCU</t>
+          <t>KTM</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Kolkata, India</t>
+          <t>Kathmandu, Nepal</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -7234,29 +7234,29 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Kathmandu</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NP</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="inlineStr">
         <is>
-          <t>KJA</t>
+          <t>CCU</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Krasnoyarsk, Russia</t>
+          <t>Kolkata, India</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -7266,29 +7266,29 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Krasnoyarsk</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>RU</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
         <is>
-          <t>KUL</t>
+          <t>KJA</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Kuala Lumpur, Malaysia</t>
+          <t>Krasnoyarsk, Russia</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -7298,29 +7298,29 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Krasnoyarsk</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>RU</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="inlineStr">
         <is>
-          <t>PKX</t>
+          <t>KUL</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Langfang, China</t>
+          <t>Kuala Lumpur, Malaysia</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -7330,29 +7330,29 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Langfang</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MY</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="inlineStr">
         <is>
-          <t>MFM</t>
+          <t>PKX</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Macau</t>
+          <t>Langfang, China</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -7360,19 +7360,31 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
-      <c r="E219" t="inlineStr"/>
-      <c r="F219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Langfang</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
         <is>
-          <t>MLE</t>
+          <t>MFM</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Malé, Maldives</t>
+          <t>Macau</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -7380,31 +7392,19 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>Malé</t>
-        </is>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>Maldives</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>MV</t>
-        </is>
-      </c>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="1" t="inlineStr">
         <is>
-          <t>MNL</t>
+          <t>MLE</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Manila, Philippines</t>
+          <t>Malé, Maldives</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -7414,29 +7414,29 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Manila</t>
+          <t>Malé</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Maldives</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>MV</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="inlineStr">
         <is>
-          <t>BOM</t>
+          <t>MNL</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Mumbai, India</t>
+          <t>Manila, Philippines</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -7446,29 +7446,29 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Manila</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>PH</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="inlineStr">
         <is>
-          <t>NAG</t>
+          <t>BOM</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Nagpur, India</t>
+          <t>Mumbai, India</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Nagpur</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -7495,12 +7495,12 @@
     <row r="224">
       <c r="A224" s="1" t="inlineStr">
         <is>
-          <t>OKA</t>
+          <t>NAG</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Naha, Japan</t>
+          <t>Nagpur, India</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -7510,29 +7510,29 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Naha</t>
+          <t>Nagpur</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="inlineStr">
         <is>
-          <t>DEL</t>
+          <t>OKA</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>New Delhi, India</t>
+          <t>Naha, Japan</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -7542,29 +7542,29 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>Naha</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>JP</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="inlineStr">
         <is>
-          <t>KIX</t>
+          <t>DEL</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Osaka, Japan</t>
+          <t>New Delhi, India</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -7574,29 +7574,29 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Osaka</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="inlineStr">
         <is>
-          <t>PAT</t>
+          <t>KIX</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Patna, India</t>
+          <t>Osaka, Japan</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -7606,29 +7606,29 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Patna</t>
+          <t>Osaka</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>JP</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="inlineStr">
         <is>
-          <t>PNH</t>
+          <t>PAT</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Phnom Penh, Cambodia</t>
+          <t>Patna, India</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -7638,29 +7638,29 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Phnom Penh</t>
+          <t>Patna</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Cambodia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>KH</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="inlineStr">
         <is>
-          <t>TAO</t>
+          <t>PNH</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Qingdao, China</t>
+          <t>Phnom Penh, Cambodia</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -7670,29 +7670,29 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Qingdao</t>
+          <t>Phnom Penh</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>KH</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="inlineStr">
         <is>
-          <t>ICN</t>
+          <t>TAO</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Seoul, South Korea</t>
+          <t>Qingdao, China</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -7702,29 +7702,29 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Seoul</t>
+          <t>Qingdao</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="inlineStr">
         <is>
-          <t>SHA</t>
+          <t>ICN</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Seoul, South Korea</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -7734,29 +7734,29 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Shanghai</t>
+          <t>Seoul</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>KR</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="inlineStr">
         <is>
-          <t>SIN</t>
+          <t>SHA</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Singapore, Singapore</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -7766,29 +7766,29 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="inlineStr">
         <is>
-          <t>URT</t>
+          <t>SIN</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Surat Thani, Thailand</t>
+          <t>Singapore, Singapore</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -7798,29 +7798,29 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Surat Thani</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>SG</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="inlineStr">
         <is>
-          <t>TPE</t>
+          <t>URT</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Taipei</t>
+          <t>Surat Thani, Thailand</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -7828,19 +7828,31 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
-      <c r="E234" t="inlineStr"/>
-      <c r="F234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Surat Thani</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="inlineStr">
         <is>
-          <t>NRT</t>
+          <t>TPE</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Tokyo, Japan</t>
+          <t>Taipei</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -7848,31 +7860,19 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>Tokyo</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="1" t="inlineStr">
         <is>
-          <t>ULN</t>
+          <t>NRT</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Ulaanbaatar, Mongolia</t>
+          <t>Tokyo, Japan</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -7882,29 +7882,29 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Ulaanbaatar</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Mongolia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>MN</t>
+          <t>JP</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="inlineStr">
         <is>
-          <t>VTE</t>
+          <t>ULN</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Vientiane, Laos</t>
+          <t>Ulaanbaatar, Mongolia</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -7914,29 +7914,29 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Vientiane</t>
+          <t>Ulaanbaatar</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Laos</t>
+          <t>Mongolia</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>MN</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="inlineStr">
         <is>
-          <t>KHN</t>
+          <t>VTE</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Xinyu, China</t>
+          <t>Vientiane, Laos</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -7946,29 +7946,29 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Xinyu</t>
+          <t>Vientiane</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Laos</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>LA</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>KHN</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Yerevan, Armenia</t>
+          <t>Xinyu, China</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -7978,29 +7978,29 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Yerevan</t>
+          <t>Xinyu</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="inlineStr">
         <is>
-          <t>JOG</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Yogyakarta, Indonesia</t>
+          <t>Yerevan, Armenia</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -8010,29 +8010,29 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Yogyakarta</t>
+          <t>Yerevan</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>AM</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="inlineStr">
         <is>
-          <t>CGY</t>
+          <t>JOG</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Cagayan de Oro, Philippines</t>
+          <t>Yogyakarta, Indonesia</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -8042,29 +8042,29 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Cagayan de Oro</t>
+          <t>Yogyakarta</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="inlineStr">
         <is>
-          <t>COK</t>
+          <t>CGY</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Kochi, India</t>
+          <t>Cagayan de Oro, Philippines</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -8074,29 +8074,29 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Cagayan de Oro</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>PH</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="inlineStr">
         <is>
-          <t>DPS</t>
+          <t>COK</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Denpasar, Indonesia</t>
+          <t>Kochi, India</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -8106,29 +8106,29 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Denpasar</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="inlineStr">
         <is>
-          <t>CNN</t>
+          <t>DPS</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Kannur, India</t>
+          <t>Denpasar, Indonesia</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -8138,29 +8138,29 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Kannur</t>
+          <t>Denpasar</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="inlineStr">
         <is>
-          <t>SZX</t>
+          <t>CNN</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Shenzhen, China</t>
+          <t>Kannur, India</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -8170,29 +8170,29 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Shenzhen</t>
+          <t>Kannur</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="inlineStr">
         <is>
-          <t>KWE</t>
+          <t>SZX</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Guiyang, China</t>
+          <t>Shenzhen, China</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -8202,7 +8202,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Guiyang</t>
+          <t>Shenzhen</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -8219,12 +8219,12 @@
     <row r="247">
       <c r="A247" s="1" t="inlineStr">
         <is>
-          <t>HGH</t>
+          <t>KWE</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Shaoxing, China</t>
+          <t>Guiyang, China</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -8234,7 +8234,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Shaoxing</t>
+          <t>Guiyang</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -8251,12 +8251,12 @@
     <row r="248">
       <c r="A248" s="1" t="inlineStr">
         <is>
-          <t>CZX</t>
+          <t>HGH</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Changzhou, China</t>
+          <t>Shaoxing, China</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Changzhou</t>
+          <t>Shaoxing</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -8283,12 +8283,12 @@
     <row r="249">
       <c r="A249" s="1" t="inlineStr">
         <is>
-          <t>KMG</t>
+          <t>CZX</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Kunming, China</t>
+          <t>Changzhou, China</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Kunming</t>
+          <t>Changzhou</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -8315,12 +8315,12 @@
     <row r="250">
       <c r="A250" s="1" t="inlineStr">
         <is>
-          <t>CNX</t>
+          <t>KMG</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Chiang Mai, Thailand</t>
+          <t>Kunming, China</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -8330,29 +8330,29 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Chiang Mai</t>
+          <t>Kunming</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="inlineStr">
         <is>
-          <t>CGO</t>
+          <t>CNX</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Zhengzhou, China</t>
+          <t>Chiang Mai, Thailand</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -8362,29 +8362,29 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Zhengzhou</t>
+          <t>Chiang Mai</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>TH</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="inlineStr">
         <is>
-          <t>TYN</t>
+          <t>CGO</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Yangquan, China</t>
+          <t>Zhengzhou, China</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -8394,7 +8394,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Yangquan</t>
+          <t>Zhengzhou</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -8411,12 +8411,12 @@
     <row r="253">
       <c r="A253" s="1" t="inlineStr">
         <is>
-          <t>CSX</t>
+          <t>TYN</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Changsha, China</t>
+          <t>Yangquan, China</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Changsha</t>
+          <t>Yangquan</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -8443,12 +8443,12 @@
     <row r="254">
       <c r="A254" s="1" t="inlineStr">
         <is>
-          <t>DLC</t>
+          <t>CSX</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Dalian, China</t>
+          <t>Changsha, China</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Dalian</t>
+          <t>Changsha</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -8475,12 +8475,12 @@
     <row r="255">
       <c r="A255" s="1" t="inlineStr">
         <is>
-          <t>BHY</t>
+          <t>DLC</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Beihai, China</t>
+          <t>Dalian, China</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -8490,7 +8490,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Beihai</t>
+          <t>Dalian</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -8507,12 +8507,12 @@
     <row r="256">
       <c r="A256" s="1" t="inlineStr">
         <is>
-          <t>CKG</t>
+          <t>BHY</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Chongqing, China</t>
+          <t>Beihai, China</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -8522,7 +8522,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Chongqing</t>
+          <t>Beihai</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -8539,12 +8539,12 @@
     <row r="257">
       <c r="A257" s="1" t="inlineStr">
         <is>
-          <t>XFN</t>
+          <t>CKG</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Xiangyang, China</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Xiangyang</t>
+          <t>Chongqing</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -8571,12 +8571,12 @@
     <row r="258">
       <c r="A258" s="1" t="inlineStr">
         <is>
-          <t>DAD</t>
+          <t>XFN</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Da Nang, Vietnam</t>
+          <t>Xiangyang, China</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -8586,29 +8586,29 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Xiangyang</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>VN</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="inlineStr">
         <is>
-          <t>JXG</t>
+          <t>DAD</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Jiaxing, China</t>
+          <t>Da Nang, Vietnam</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -8618,29 +8618,29 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Jiaxing</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>VN</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="inlineStr">
         <is>
-          <t>CRK</t>
+          <t>JXG</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Tarlac City, Philippines</t>
+          <t>Jiaxing, China</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -8650,29 +8650,29 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Tarlac City</t>
+          <t>Jiaxing</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="inlineStr">
         <is>
-          <t>PBH</t>
+          <t>CRK</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Thimphu, Bhutan</t>
+          <t>Tarlac City, Philippines</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -8682,29 +8682,29 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Thimphu</t>
+          <t>Tarlac City</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Bhutan</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>PH</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="inlineStr">
         <is>
-          <t>XIY</t>
+          <t>PBH</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Baoji, China</t>
+          <t>Thimphu, Bhutan</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -8714,29 +8714,29 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Baoji</t>
+          <t>Thimphu</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Bhutan</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>BT</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="inlineStr">
         <is>
-          <t>NQZ</t>
+          <t>XIY</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Astana, Kazakhstan</t>
+          <t>Baoji, China</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -8746,29 +8746,29 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Baoji</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="inlineStr">
         <is>
-          <t>KCH</t>
+          <t>NQZ</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Kuching, Malaysia</t>
+          <t>Astana, Kazakhstan</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -8778,29 +8778,29 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Kuching</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>KZ</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="inlineStr">
         <is>
-          <t>AKX</t>
+          <t>KCH</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Aktobe, Kazakhstan</t>
+          <t>Kuching, Malaysia</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -8810,29 +8810,29 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Kuching</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>MY</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="1" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>AKX</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Tongren, China</t>
+          <t>Aktobe, Kazakhstan</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -8842,29 +8842,29 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Tongren</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>KZ</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Taizhou, China</t>
+          <t>Tongren, China</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Taizhou</t>
+          <t>Tongren</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -8891,12 +8891,12 @@
     <row r="268">
       <c r="A268" s="1" t="inlineStr">
         <is>
-          <t>FRU</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Bishkek, Kyrgyzstan</t>
+          <t>Taizhou, China</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -8906,29 +8906,29 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Bishkek</t>
+          <t>Taizhou</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Kyrgyzstan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="inlineStr">
         <is>
-          <t>MLG</t>
+          <t>FRU</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Malang, Indonesia</t>
+          <t>Bishkek, Kyrgyzstan</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -8938,29 +8938,29 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Malang</t>
+          <t>Bishkek</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Kyrgyzstan</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>KG</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="inlineStr">
         <is>
-          <t>LHE</t>
+          <t>MLG</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Lahore, Pakistan</t>
+          <t>Malang, Indonesia</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -8970,29 +8970,29 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Lahore</t>
+          <t>Malang</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="inlineStr">
         <is>
-          <t>CTU</t>
+          <t>LHE</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Chengdu, China</t>
+          <t>Lahore, Pakistan</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -9002,29 +9002,29 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Chengdu</t>
+          <t>Lahore</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>PK</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="inlineStr">
         <is>
-          <t>AGR</t>
+          <t>CTU</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Agra, India</t>
+          <t>Chengdu, China</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -9034,29 +9034,29 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Agra</t>
+          <t>Chengdu</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="inlineStr">
         <is>
-          <t>CJB</t>
+          <t>AGR</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Coimbatore, India</t>
+          <t>Agra, India</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Coimbatore</t>
+          <t>Agra</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -9083,12 +9083,12 @@
     <row r="274">
       <c r="A274" s="1" t="inlineStr">
         <is>
-          <t>ACX</t>
+          <t>CJB</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Xingyi, China</t>
+          <t>Coimbatore, India</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -9098,29 +9098,29 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Xingyi</t>
+          <t>Coimbatore</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="1" t="inlineStr">
         <is>
-          <t>BBI</t>
+          <t>ACX</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Bhubaneswar, India</t>
+          <t>Xingyi, China</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -9130,29 +9130,29 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Bhubaneswar</t>
+          <t>Xingyi</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="1" t="inlineStr">
         <is>
-          <t>LYA</t>
+          <t>BBI</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Luoyang, China</t>
+          <t>Bhubaneswar, India</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -9162,29 +9162,29 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Luoyang</t>
+          <t>Bhubaneswar</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="inlineStr">
         <is>
-          <t>PNQ</t>
+          <t>LYA</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Pune, India</t>
+          <t>Luoyang, China</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -9194,29 +9194,29 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Luoyang</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="1" t="inlineStr">
         <is>
-          <t>JRG</t>
+          <t>PNQ</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Sambalpur, India</t>
+          <t>Pune, India</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -9226,7 +9226,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Sambalpur</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -9243,44 +9243,44 @@
     <row r="279">
       <c r="A279" s="1" t="inlineStr">
         <is>
-          <t>ABQ</t>
+          <t>JRG</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, United States</t>
+          <t>Sambalpur, India</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Albuquerque, NM</t>
+          <t>Sambalpur</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="1" t="inlineStr">
         <is>
-          <t>ANC</t>
+          <t>ABQ</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Anchorage, AK, United States</t>
+          <t>Albuquerque, NM, United States</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -9290,7 +9290,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Anchorage, AK</t>
+          <t>Albuquerque, NM</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -9307,12 +9307,12 @@
     <row r="281">
       <c r="A281" s="1" t="inlineStr">
         <is>
-          <t>IAD</t>
+          <t>ANC</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Ashburn, VA, United States</t>
+          <t>Anchorage, AK, United States</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -9322,7 +9322,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Ashburn, VA</t>
+          <t>Anchorage, AK</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -9339,12 +9339,12 @@
     <row r="282">
       <c r="A282" s="1" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>IAD</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Atlanta, GA, United States</t>
+          <t>Ashburn, VA, United States</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Ashburn, VA</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -9371,12 +9371,12 @@
     <row r="283">
       <c r="A283" s="1" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Austin, TX, United States</t>
+          <t>Atlanta, GA, United States</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -9403,12 +9403,12 @@
     <row r="284">
       <c r="A284" s="1" t="inlineStr">
         <is>
-          <t>BGR</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Bangor, ME, United States</t>
+          <t>Austin, TX, United States</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -9418,7 +9418,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Bangor, ME</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -9435,12 +9435,12 @@
     <row r="285">
       <c r="A285" s="1" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BGR</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Boston, MA, United States</t>
+          <t>Bangor, ME, United States</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -9450,7 +9450,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Bangor, ME</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -9467,12 +9467,12 @@
     <row r="286">
       <c r="A286" s="1" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Buffalo, NY, United States</t>
+          <t>Boston, MA, United States</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -9482,7 +9482,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Buffalo, NY</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -9499,12 +9499,12 @@
     <row r="287">
       <c r="A287" s="1" t="inlineStr">
         <is>
-          <t>YYC</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Calgary, AB, Canada</t>
+          <t>Buffalo, NY, United States</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -9514,29 +9514,29 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Calgary, AB</t>
+          <t>Buffalo, NY</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>YYC</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Charlotte, NC, United States</t>
+          <t>Calgary, AB, Canada</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -9546,29 +9546,29 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Charlotte, NC</t>
+          <t>Calgary, AB</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="inlineStr">
         <is>
-          <t>ORD</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Chicago, IL, United States</t>
+          <t>Charlotte, NC, United States</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -9578,7 +9578,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Charlotte, NC</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -9595,12 +9595,12 @@
     <row r="290">
       <c r="A290" s="1" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ORD</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Cleveland, OH, United States</t>
+          <t>Chicago, IL, United States</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -9610,7 +9610,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Cleveland, OH</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -9627,12 +9627,12 @@
     <row r="291">
       <c r="A291" s="1" t="inlineStr">
         <is>
-          <t>CMH</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Columbus, OH, United States</t>
+          <t>Cleveland, OH, United States</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -9642,7 +9642,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Columbus, OH</t>
+          <t>Cleveland, OH</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -9659,12 +9659,12 @@
     <row r="292">
       <c r="A292" s="1" t="inlineStr">
         <is>
-          <t>DFW</t>
+          <t>CMH</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Dallas, TX, United States</t>
+          <t>Columbus, OH, United States</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Dallas, TX</t>
+          <t>Columbus, OH</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -9691,12 +9691,12 @@
     <row r="293">
       <c r="A293" s="1" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DFW</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Denver, CO, United States</t>
+          <t>Dallas, TX, United States</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -9706,7 +9706,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>Dallas, TX</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -9723,12 +9723,12 @@
     <row r="294">
       <c r="A294" s="1" t="inlineStr">
         <is>
-          <t>DTW</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Detroit, MI, United States</t>
+          <t>Denver, CO, United States</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -9738,7 +9738,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Detroit, MI</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -9755,12 +9755,12 @@
     <row r="295">
       <c r="A295" s="1" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>DTW</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Durham, NC, United States</t>
+          <t>Detroit, MI, United States</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -9770,7 +9770,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Durham, NC</t>
+          <t>Detroit, MI</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -9787,12 +9787,12 @@
     <row r="296">
       <c r="A296" s="1" t="inlineStr">
         <is>
-          <t>GDL</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Guadalajara, Mexico</t>
+          <t>Durham, NC, United States</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -9802,29 +9802,29 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Durham, NC</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="inlineStr">
         <is>
-          <t>YHZ</t>
+          <t>GDL</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Halifax, Canada</t>
+          <t>Guadalajara, Mexico</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -9834,29 +9834,29 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Halifax</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>MX</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="inlineStr">
         <is>
-          <t>HNL</t>
+          <t>YHZ</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Honolulu, HI, United States</t>
+          <t>Halifax, Canada</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -9866,29 +9866,29 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Honolulu, HI</t>
+          <t>Halifax</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="1" t="inlineStr">
         <is>
-          <t>IAH</t>
+          <t>HNL</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Houston, TX, United States</t>
+          <t>Honolulu, HI, United States</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -9898,7 +9898,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Houston, TX</t>
+          <t>Honolulu, HI</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -9915,12 +9915,12 @@
     <row r="300">
       <c r="A300" s="1" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>IAH</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, United States</t>
+          <t>Houston, TX, United States</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -9930,7 +9930,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Indianapolis, IN</t>
+          <t>Houston, TX</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -9947,12 +9947,12 @@
     <row r="301">
       <c r="A301" s="1" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, United States</t>
+          <t>Indianapolis, IN, United States</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -9962,7 +9962,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Jacksonville, FL</t>
+          <t>Indianapolis, IN</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -9979,12 +9979,12 @@
     <row r="302">
       <c r="A302" s="1" t="inlineStr">
         <is>
-          <t>MCI</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Kansas City, MO, United States</t>
+          <t>Jacksonville, FL, United States</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -9994,7 +9994,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Kansas City, MO</t>
+          <t>Jacksonville, FL</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -10011,12 +10011,12 @@
     <row r="303">
       <c r="A303" s="1" t="inlineStr">
         <is>
-          <t>KIN</t>
+          <t>MCI</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Kingston, Jamaica</t>
+          <t>Kansas City, MO, United States</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -10026,29 +10026,29 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Kingston</t>
+          <t>Kansas City, MO</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Jamaica</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>JM</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="inlineStr">
         <is>
-          <t>LAS</t>
+          <t>KIN</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, United States</t>
+          <t>Kingston, Jamaica</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -10058,29 +10058,29 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Las Vegas, NV</t>
+          <t>Kingston</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Jamaica</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JM</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="inlineStr">
         <is>
-          <t>LAX</t>
+          <t>LAS</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, United States</t>
+          <t>Las Vegas, NV, United States</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -10090,7 +10090,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
+          <t>Las Vegas, NV</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -10107,12 +10107,12 @@
     <row r="306">
       <c r="A306" s="1" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>LAX</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Memphis, TN, United States</t>
+          <t>Los Angeles, CA, United States</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -10122,7 +10122,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Memphis, TN</t>
+          <t>Los Angeles, CA</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -10139,12 +10139,12 @@
     <row r="307">
       <c r="A307" s="1" t="inlineStr">
         <is>
-          <t>MEX</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Mexico City, Mexico</t>
+          <t>Memphis, TN, United States</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -10154,29 +10154,29 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Mexico City</t>
+          <t>Memphis, TN</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MEX</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Miami, FL, United States</t>
+          <t>Mexico City, Mexico</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -10186,29 +10186,29 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Miami, FL</t>
+          <t>Mexico City</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="inlineStr">
         <is>
-          <t>MSP</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, United States</t>
+          <t>Miami, FL, United States</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -10218,7 +10218,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Minneapolis, MN</t>
+          <t>Miami, FL</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -10235,12 +10235,12 @@
     <row r="310">
       <c r="A310" s="1" t="inlineStr">
         <is>
-          <t>YUL</t>
+          <t>MSP</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Montréal, QC, Canada</t>
+          <t>Minneapolis, MN, United States</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -10250,29 +10250,29 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Montréal, QC</t>
+          <t>Minneapolis, MN</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="inlineStr">
         <is>
-          <t>BNA</t>
+          <t>YUL</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Nashville, United States</t>
+          <t>Montréal, QC, Canada</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -10282,29 +10282,29 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Nashville</t>
+          <t>Montréal, QC</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="1" t="inlineStr">
         <is>
-          <t>EWR</t>
+          <t>BNA</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Newark, NJ, United States</t>
+          <t>Nashville, United States</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -10314,7 +10314,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Newark, NJ</t>
+          <t>Nashville</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -10331,12 +10331,12 @@
     <row r="313">
       <c r="A313" s="1" t="inlineStr">
         <is>
-          <t>ORF</t>
+          <t>EWR</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Norfolk, VA, United States</t>
+          <t>Newark, NJ, United States</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -10346,7 +10346,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Norfolk, VA</t>
+          <t>Newark, NJ</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -10363,12 +10363,12 @@
     <row r="314">
       <c r="A314" s="1" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>ORF</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, United States</t>
+          <t>Norfolk, VA, United States</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK</t>
+          <t>Norfolk, VA</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -10395,12 +10395,12 @@
     <row r="315">
       <c r="A315" s="1" t="inlineStr">
         <is>
-          <t>OMA</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Omaha, NE, United States</t>
+          <t>Oklahoma City, OK, United States</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -10410,7 +10410,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Omaha, NE</t>
+          <t>Oklahoma City, OK</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -10427,12 +10427,12 @@
     <row r="316">
       <c r="A316" s="1" t="inlineStr">
         <is>
-          <t>PHL</t>
+          <t>OMA</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Philadelphia, United States</t>
+          <t>Omaha, NE, United States</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -10442,7 +10442,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Omaha, NE</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -10459,12 +10459,12 @@
     <row r="317">
       <c r="A317" s="1" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>PHL</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, United States</t>
+          <t>Philadelphia, United States</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -10474,7 +10474,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Phoenix, AZ</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -10491,12 +10491,12 @@
     <row r="318">
       <c r="A318" s="1" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, United States</t>
+          <t>Phoenix, AZ, United States</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -10506,7 +10506,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA</t>
+          <t>Phoenix, AZ</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -10523,12 +10523,12 @@
     <row r="319">
       <c r="A319" s="1" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Portland, OR, United States</t>
+          <t>Pittsburgh, PA, United States</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -10538,7 +10538,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Portland, OR</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -10555,12 +10555,12 @@
     <row r="320">
       <c r="A320" s="1" t="inlineStr">
         <is>
-          <t>QRO</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Queretaro, MX, Mexico</t>
+          <t>Portland, OR, United States</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -10570,29 +10570,29 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Queretaro, MX</t>
+          <t>Portland, OR</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="inlineStr">
         <is>
-          <t>RIC</t>
+          <t>QRO</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Richmond, VA, United States</t>
+          <t>Queretaro, MX, Mexico</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -10602,29 +10602,29 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Richmond, VA</t>
+          <t>Queretaro, MX</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="inlineStr">
         <is>
-          <t>SMF</t>
+          <t>RIC</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Sacramento, CA, United States</t>
+          <t>Richmond, VA, United States</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -10634,7 +10634,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Sacramento, CA</t>
+          <t>Richmond, VA</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -10651,12 +10651,12 @@
     <row r="323">
       <c r="A323" s="1" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>SMF</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, United States</t>
+          <t>Sacramento, CA, United States</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT</t>
+          <t>Sacramento, CA</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -10683,12 +10683,12 @@
     <row r="324">
       <c r="A324" s="1" t="inlineStr">
         <is>
-          <t>SAT</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>San Antonio, TX, United States</t>
+          <t>Salt Lake City, UT, United States</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -10698,7 +10698,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>San Antonio, TX</t>
+          <t>Salt Lake City, UT</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -10715,12 +10715,12 @@
     <row r="325">
       <c r="A325" s="1" t="inlineStr">
         <is>
-          <t>SAN</t>
+          <t>SAT</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>San Diego, CA, United States</t>
+          <t>San Antonio, TX, United States</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -10730,7 +10730,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>San Diego, CA</t>
+          <t>San Antonio, TX</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -10747,12 +10747,12 @@
     <row r="326">
       <c r="A326" s="1" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>SAN</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>San Francisco, CA, United States</t>
+          <t>San Diego, CA, United States</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>San Diego, CA</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -10779,12 +10779,12 @@
     <row r="327">
       <c r="A327" s="1" t="inlineStr">
         <is>
-          <t>SJC</t>
+          <t>SFO</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>San Jose, CA, United States</t>
+          <t>San Francisco, CA, United States</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -10811,12 +10811,12 @@
     <row r="328">
       <c r="A328" s="1" t="inlineStr">
         <is>
-          <t>YXE</t>
+          <t>SJC</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Saskatoon, SK, Canada</t>
+          <t>San Jose, CA, United States</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -10826,29 +10826,29 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Saskatoon, SK</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>YXE</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Seattle, WA, United States</t>
+          <t>Saskatoon, SK, Canada</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -10858,29 +10858,29 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Saskatoon, SK</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="inlineStr">
         <is>
-          <t>FSD</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, United States</t>
+          <t>Seattle, WA, United States</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -10890,7 +10890,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -10907,12 +10907,12 @@
     <row r="331">
       <c r="A331" s="1" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>FSD</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>St. Louis, MO, United States</t>
+          <t>Sioux Falls, SD, United States</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -10922,7 +10922,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>St. Louis, MO</t>
+          <t>Sioux Falls, SD</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -10939,12 +10939,12 @@
     <row r="332">
       <c r="A332" s="1" t="inlineStr">
         <is>
-          <t>TLH</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, United States</t>
+          <t>St. Louis, MO, United States</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -10954,7 +10954,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Tallahassee, FL</t>
+          <t>St. Louis, MO</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -10971,12 +10971,12 @@
     <row r="333">
       <c r="A333" s="1" t="inlineStr">
         <is>
-          <t>TPA</t>
+          <t>TLH</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Tampa, FL, United States</t>
+          <t>Tallahassee, FL, United States</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -10986,7 +10986,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Tampa, FL</t>
+          <t>Tallahassee, FL</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -11003,12 +11003,12 @@
     <row r="334">
       <c r="A334" s="1" t="inlineStr">
         <is>
-          <t>YYZ</t>
+          <t>TPA</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Toronto, ON, Canada</t>
+          <t>Tampa, FL, United States</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -11018,29 +11018,29 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Toronto, ON</t>
+          <t>Tampa, FL</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="inlineStr">
         <is>
-          <t>YVR</t>
+          <t>YYZ</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Vancouver, BC, Canada</t>
+          <t>Toronto, ON, Canada</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -11050,7 +11050,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Vancouver, BC</t>
+          <t>Toronto, ON</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -11067,12 +11067,12 @@
     <row r="336">
       <c r="A336" s="1" t="inlineStr">
         <is>
-          <t>YWG</t>
+          <t>YVR</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Winnipeg, MB, Canada</t>
+          <t>Vancouver, BC, Canada</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Winnipeg, MB</t>
+          <t>Vancouver, BC</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -11099,30 +11099,62 @@
     <row r="337">
       <c r="A337" s="1" t="inlineStr">
         <is>
+          <t>YWG</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Winnipeg, MB, Canada</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Winnipeg, MB</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="inlineStr">
+        <is>
           <t>CVG</t>
         </is>
       </c>
-      <c r="B337" t="inlineStr">
+      <c r="B338" t="inlineStr">
         <is>
           <t>Cincinnati, United States</t>
         </is>
       </c>
-      <c r="C337" t="inlineStr">
+      <c r="C338" t="inlineStr">
         <is>
           <t>North America</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr">
+      <c r="D338" t="inlineStr">
         <is>
           <t>Cincinnati</t>
         </is>
       </c>
-      <c r="E337" t="inlineStr">
+      <c r="E338" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="F337" t="inlineStr">
+      <c r="F338" t="inlineStr">
         <is>
           <t>US</t>
         </is>

--- a/DC-Colos.xlsx
+++ b/DC-Colos.xlsx
@@ -2315,44 +2315,44 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>AMM</t>
+          <t>NQZ</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Amman, Jordan</t>
+          <t>Astana, Kazakhstan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Middle East</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Amman</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>JO</t>
+          <t>KZ</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>LLK</t>
+          <t>AMM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Astara, Azerbaijan</t>
+          <t>Amman, Jordan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2362,29 +2362,29 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Astara</t>
+          <t>Amman</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Azerbaijan</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>JO</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>BGW</t>
+          <t>LLK</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Baghdad, Iraq</t>
+          <t>Astara, Azerbaijan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2394,29 +2394,29 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Baghdad</t>
+          <t>Astara</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Azerbaijan</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>IQ</t>
+          <t>AZ</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>GYD</t>
+          <t>BGW</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Baku, Azerbaijan</t>
+          <t>Baghdad, Iraq</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2426,29 +2426,29 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Baku</t>
+          <t>Baghdad</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Azerbaijan</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>IQ</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>BSR</t>
+          <t>GYD</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Basra, Iraq</t>
+          <t>Baku, Azerbaijan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2458,29 +2458,29 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Basra</t>
+          <t>Baku</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Azerbaijan</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>IQ</t>
+          <t>AZ</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>BEY</t>
+          <t>BSR</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Beirut, Lebanon</t>
+          <t>Basra, Iraq</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2490,29 +2490,29 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Beirut</t>
+          <t>Basra</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>IQ</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>DMM</t>
+          <t>BEY</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Dammam, Saudi Arabia</t>
+          <t>Beirut, Lebanon</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2522,29 +2522,29 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Dammam</t>
+          <t>Beirut</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>LB</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>DOH</t>
+          <t>DMM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Doha, Qatar</t>
+          <t>Dammam, Saudi Arabia</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2554,29 +2554,29 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Doha</t>
+          <t>Dammam</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>SA</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>DXB</t>
+          <t>DOH</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Dubai, United Arab Emirates</t>
+          <t>Doha, Qatar</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2586,29 +2586,29 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Doha</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>QA</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>EBL</t>
+          <t>DXB</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Erbil, Iraq</t>
+          <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2618,29 +2618,29 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Erbil</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>IQ</t>
+          <t>AE</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>HFA</t>
+          <t>EBL</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Haifa, Israel</t>
+          <t>Erbil, Iraq</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2650,29 +2650,29 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Haifa</t>
+          <t>Erbil</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>IQ</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>JED</t>
+          <t>HFA</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Jeddah, Saudi Arabia</t>
+          <t>Haifa, Israel</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2682,29 +2682,29 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Jeddah</t>
+          <t>Haifa</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>IL</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>KWI</t>
+          <t>JED</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Kuwait City, Kuwait</t>
+          <t>Jeddah, Saudi Arabia</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2714,29 +2714,29 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Kuwait City</t>
+          <t>Jeddah</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>KW</t>
+          <t>SA</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>BAH</t>
+          <t>KWI</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Manama, Bahrain</t>
+          <t>Kuwait City, Kuwait</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2746,29 +2746,29 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Manama</t>
+          <t>Kuwait City</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Bahrain</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>BH</t>
+          <t>KW</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>MCT</t>
+          <t>BAH</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Muscat, Oman</t>
+          <t>Manama, Bahrain</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2778,29 +2778,29 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Muscat</t>
+          <t>Manama</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>Bahrain</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>OM</t>
+          <t>BH</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>NJF</t>
+          <t>MCT</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Najaf, Iraq</t>
+          <t>Muscat, Oman</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2810,29 +2810,29 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Najaf</t>
+          <t>Muscat</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Oman</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>IQ</t>
+          <t>OM</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>XNH</t>
+          <t>NJF</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Nasiriyah, Iraq</t>
+          <t>Najaf, Iraq</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Nasiriyah</t>
+          <t>Najaf</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2859,12 +2859,12 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>ZDM</t>
+          <t>XNH</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ramallah</t>
+          <t>Nasiriyah, Iraq</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2872,19 +2872,31 @@
           <t>Middle East</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Nasiriyah</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Iraq</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>IQ</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>RUH</t>
+          <t>ZDM</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Riyadh, Saudi Arabia</t>
+          <t>Ramallah</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2892,31 +2904,19 @@
           <t>Middle East</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Riyadh</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Saudi Arabia</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>ISU</t>
+          <t>RUH</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Sulaymaniyah, Iraq</t>
+          <t>Riyadh, Saudi Arabia</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2926,29 +2926,29 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Sulaymaniyah</t>
+          <t>Riyadh</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>IQ</t>
+          <t>SA</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>TLV</t>
+          <t>ISU</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Tel Aviv, Israel</t>
+          <t>Sulaymaniyah, Iraq</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2958,61 +2958,61 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Tel Aviv</t>
+          <t>Sulaymaniyah</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>IQ</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>ADL</t>
+          <t>TLV</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Adelaide, SA, Australia</t>
+          <t>Tel Aviv, Israel</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Oceania</t>
+          <t>Middle East</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Adelaide, SA</t>
+          <t>Tel Aviv</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>IL</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>AKL</t>
+          <t>ADL</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Auckland, New Zealand</t>
+          <t>Adelaide, SA, Australia</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3022,29 +3022,29 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Adelaide, SA</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>AU</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>BNE</t>
+          <t>AKL</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Brisbane, QLD, Australia</t>
+          <t>Auckland, New Zealand</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3054,29 +3054,29 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Brisbane, QLD</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>NZ</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>CBR</t>
+          <t>BNE</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Canberra, ACT, Australia</t>
+          <t>Brisbane, QLD, Australia</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Canberra, ACT</t>
+          <t>Brisbane, QLD</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3103,12 +3103,12 @@
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>CBR</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Christchurch, New Zealand</t>
+          <t>Canberra, ACT, Australia</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3118,29 +3118,29 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Christchurch</t>
+          <t>Canberra, ACT</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>AU</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>GUM</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Hagatna, Guam</t>
+          <t>Christchurch, New Zealand</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3150,29 +3150,29 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Hagatna</t>
+          <t>Christchurch</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Guam</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>GU</t>
+          <t>NZ</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>MEL</t>
+          <t>GUM</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Melbourne, VIC, Australia</t>
+          <t>Hagatna, Guam</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3182,29 +3182,29 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Melbourne, VIC</t>
+          <t>Hagatna</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Guam</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>GU</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>NOU</t>
+          <t>MEL</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Noumea, New Caledonia</t>
+          <t>Melbourne, VIC, Australia</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3214,29 +3214,29 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Noumea</t>
+          <t>Melbourne, VIC</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>New Caledonia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>AU</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>PER</t>
+          <t>NOU</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Perth, WA, Australia</t>
+          <t>Noumea, New Caledonia</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3246,29 +3246,29 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Perth, WA</t>
+          <t>Noumea</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>New Caledonia</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>NC</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>SYD</t>
+          <t>PER</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Sydney, NSW, Australia</t>
+          <t>Perth, WA, Australia</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Sydney, NSW</t>
+          <t>Perth, WA</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3295,12 +3295,12 @@
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>PPT</t>
+          <t>SYD</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Tahiti, French Polynesia</t>
+          <t>Sydney, NSW, Australia</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3310,29 +3310,29 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Tahiti</t>
+          <t>Sydney, NSW</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>French Polynesia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>AU</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>SUV</t>
+          <t>PPT</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Suva, Fiji</t>
+          <t>Tahiti, French Polynesia</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3342,29 +3342,29 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Suva</t>
+          <t>Tahiti</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Fiji</t>
+          <t>French Polynesia</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>FJ</t>
+          <t>PF</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>HBA</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Hobart, Australia</t>
+          <t>Suva, Fiji</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3374,29 +3374,29 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Hobart</t>
+          <t>Suva</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Fiji</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>FJ</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>WLG</t>
+          <t>HBA</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Wellington, New Zealand</t>
+          <t>Hobart, Australia</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3406,61 +3406,61 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Wellington</t>
+          <t>Hobart</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>AU</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>QWJ</t>
+          <t>WLG</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Americana, Brazil</t>
+          <t>Wellington, New Zealand</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Latin America &amp; the Caribbean</t>
+          <t>Oceania</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Americana</t>
+          <t>Wellington</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>NZ</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>QWJ</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Arica, Chile</t>
+          <t>Americana, Brazil</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3470,29 +3470,29 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Arica</t>
+          <t>Americana</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>ASU</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Asunción, Paraguay</t>
+          <t>Arica, Chile</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3502,29 +3502,29 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Asunción</t>
+          <t>Arica</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>PY</t>
+          <t>CL</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>ASU</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Belém, Brazil</t>
+          <t>Asunción, Paraguay</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3534,29 +3534,29 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Belém</t>
+          <t>Asunción</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>PY</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>CNF</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Belo Horizonte, Brazil</t>
+          <t>Belém, Brazil</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Belo Horizonte</t>
+          <t>Belém</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3583,12 +3583,12 @@
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>BOG</t>
+          <t>CNF</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Bogotá, Colombia</t>
+          <t>Belo Horizonte, Brazil</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3598,29 +3598,29 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Belo Horizonte</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>BSB</t>
+          <t>BOG</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Brasilia, Brazil</t>
+          <t>Bogotá, Colombia</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3630,29 +3630,29 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Brasilia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CO</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>EZE</t>
+          <t>BSB</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Buenos Aires, Argentina</t>
+          <t>Brasilia, Brazil</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3662,29 +3662,29 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Brasilia</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>CFC</t>
+          <t>EZE</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Caçador, Brazil</t>
+          <t>Buenos Aires, Argentina</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3694,29 +3694,29 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Caçador</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>AR</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>VCP</t>
+          <t>CFC</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Campinas, Brazil</t>
+          <t>Caçador, Brazil</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Campinas</t>
+          <t>Caçador</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -3743,12 +3743,12 @@
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>VCP</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Córdoba, Argentina</t>
+          <t>Campinas, Brazil</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3758,29 +3758,29 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Campinas</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>CWB</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Curitiba, Brazil</t>
+          <t>Córdoba, Argentina</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3790,29 +3790,29 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Curitiba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>AR</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>FLN</t>
+          <t>CWB</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Florianopolis, Brazil</t>
+          <t>Curitiba, Brazil</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Florianopolis</t>
+          <t>Curitiba</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -3839,12 +3839,12 @@
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>FOR</t>
+          <t>FLN</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Fortaleza, Brazil</t>
+          <t>Florianopolis, Brazil</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Florianopolis</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -3871,12 +3871,12 @@
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>GEO</t>
+          <t>FOR</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Georgetown, Guyana</t>
+          <t>Fortaleza, Brazil</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3886,29 +3886,29 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Georgetown</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>GY</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>GYN</t>
+          <t>GEO</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Goiânia, Brazil</t>
+          <t>Georgetown, Guyana</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3918,29 +3918,29 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Goiânia</t>
+          <t>Georgetown</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>GY</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>GUA</t>
+          <t>GYN</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Guatemala City, Guatemala</t>
+          <t>Goiânia, Brazil</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3950,29 +3950,29 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Guatemala City</t>
+          <t>Goiânia</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Guatemala</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>GYE</t>
+          <t>GUA</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Guayaquil, Ecuador</t>
+          <t>Guatemala City, Guatemala</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3982,29 +3982,29 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Guayaquil</t>
+          <t>Guatemala City</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Guatemala</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>GT</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>JOI</t>
+          <t>GYE</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Joinville, Brazil</t>
+          <t>Guayaquil, Ecuador</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4014,29 +4014,29 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Joinville</t>
+          <t>Guayaquil</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>EC</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>JDO</t>
+          <t>JOI</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Juazeiro do Norte, Brazil</t>
+          <t>Joinville, Brazil</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Juazeiro do Norte</t>
+          <t>Joinville</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4063,12 +4063,12 @@
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>JDO</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Lima, Peru</t>
+          <t>Juazeiro do Norte, Brazil</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4078,29 +4078,29 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Lima</t>
+          <t>Juazeiro do Norte</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>MAO</t>
+          <t>LIM</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Manaus, Brazil</t>
+          <t>Lima, Peru</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4110,29 +4110,29 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Manaus</t>
+          <t>Lima</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>PE</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>MDE</t>
+          <t>MAO</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Medellín, Colombia</t>
+          <t>Manaus, Brazil</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4142,29 +4142,29 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Manaus</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>NQN</t>
+          <t>MDE</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Neuquén, Argentina</t>
+          <t>Medellín, Colombia</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4174,29 +4174,29 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Neuquén</t>
+          <t>Medellín</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CO</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>PTY</t>
+          <t>NQN</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Panama City, Panama</t>
+          <t>Neuquén, Argentina</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4206,29 +4206,29 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Panama City</t>
+          <t>Neuquén</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>AR</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>PBM</t>
+          <t>PTY</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Paramaribo, Suriname</t>
+          <t>Panama City, Panama</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4238,29 +4238,29 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Paramaribo</t>
+          <t>Panama City</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Suriname</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>PA</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>PBM</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Porto Alegre, Brazil</t>
+          <t>Paramaribo, Suriname</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4270,29 +4270,29 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Porto Alegre</t>
+          <t>Paramaribo</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Suriname</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>SR</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>UIO</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Quito, Ecuador</t>
+          <t>Porto Alegre, Brazil</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4302,29 +4302,29 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Quito</t>
+          <t>Porto Alegre</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>REC</t>
+          <t>UIO</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Recife, Brazil</t>
+          <t>Quito, Ecuador</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4334,29 +4334,29 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Recife</t>
+          <t>Quito</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>EC</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>RAO</t>
+          <t>REC</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Ribeirao Preto, Brazil</t>
+          <t>Recife, Brazil</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Ribeirao Preto</t>
+          <t>Recife</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -4383,12 +4383,12 @@
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>GIG</t>
+          <t>RAO</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Rio de Janeiro, Brazil</t>
+          <t>Ribeirao Preto, Brazil</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Rio de Janeiro</t>
+          <t>Ribeirao Preto</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -4415,12 +4415,12 @@
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>SJO</t>
+          <t>GIG</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>San José, Costa Rica</t>
+          <t>Rio de Janeiro, Brazil</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4430,29 +4430,29 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>San José</t>
+          <t>Rio de Janeiro</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Costa Rica</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>SCL</t>
+          <t>SJO</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Santiago, Chile</t>
+          <t>San José, Costa Rica</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4462,29 +4462,29 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>San José</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Costa Rica</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>CR</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>SDQ</t>
+          <t>SCL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Santo Domingo, Dominican Republic</t>
+          <t>Santiago, Chile</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4494,29 +4494,29 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Santo Domingo</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>CL</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>SJP</t>
+          <t>SDQ</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>São José do Rio Preto, Brazil</t>
+          <t>Santo Domingo, Dominican Republic</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4526,29 +4526,29 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>São José do Rio Preto</t>
+          <t>Santo Domingo</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>DO</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>SJP</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>São José dos Campos, Brazil</t>
+          <t>São José do Rio Preto, Brazil</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>São José dos Campos</t>
+          <t>São José do Rio Preto</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -4575,12 +4575,12 @@
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>GRU</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>São Paulo, Brazil</t>
+          <t>São José dos Campos, Brazil</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>São José dos Campos</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -4607,12 +4607,12 @@
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>SOD</t>
+          <t>GRU</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Sorocaba, Brazil</t>
+          <t>São Paulo, Brazil</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Sorocaba</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -4639,12 +4639,12 @@
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>TGU</t>
+          <t>SOD</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Tegucigalpa, Honduras</t>
+          <t>Sorocaba, Brazil</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4654,29 +4654,29 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Tegucigalpa</t>
+          <t>Sorocaba</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Honduras</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>HN</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>TGU</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Timbó, Brazil</t>
+          <t>Tegucigalpa, Honduras</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4686,29 +4686,29 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Tegucigalpa</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Honduras</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>HN</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>UDI</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Uberlândia, Brazil</t>
+          <t>Timbó, Brazil</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Uberlândia</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -4735,12 +4735,12 @@
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>VIX</t>
+          <t>UDI</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Vitoria, Brazil</t>
+          <t>Uberlândia, Brazil</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Vitoria</t>
+          <t>Uberlândia</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -4767,12 +4767,12 @@
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>CAW</t>
+          <t>VIX</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Campos dos Goytacazes, Brazil</t>
+          <t>Vitoria, Brazil</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Campos dos Goytacazes</t>
+          <t>Vitoria</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -4799,12 +4799,12 @@
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>XAP</t>
+          <t>CAW</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Chapeco, Brazil</t>
+          <t>Campos dos Goytacazes, Brazil</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Chapeco</t>
+          <t>Campos dos Goytacazes</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -4831,12 +4831,12 @@
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>BGI</t>
+          <t>XAP</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Bridgetown, Barbados</t>
+          <t>Chapeco, Brazil</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4846,29 +4846,29 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Bridgetown</t>
+          <t>Chapeco</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Barbados</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>GND</t>
+          <t>BGI</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>St. George's, Grenada</t>
+          <t>Bridgetown, Barbados</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4878,29 +4878,29 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>St. George's</t>
+          <t>Bridgetown</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Grenada</t>
+          <t>Barbados</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>BB</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>STI</t>
+          <t>GND</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Santiago de los Caballeros, Dominican Republic</t>
+          <t>St. George's, Grenada</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4910,29 +4910,29 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Santiago de los Caballeros</t>
+          <t>St. George's</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Grenada</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>GD</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>LPB</t>
+          <t>STI</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>La Paz, Bolivia</t>
+          <t>Santiago de los Caballeros, Dominican Republic</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4942,29 +4942,29 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Santiago de los Caballeros</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>DO</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>SJU</t>
+          <t>LPB</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>San Juan, Puerto Rico</t>
+          <t>La Paz, Bolivia</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4974,29 +4974,29 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>San Juan</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Puerto Rico</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>BO</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>BAQ</t>
+          <t>SJU</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Barranquilla, Colombia</t>
+          <t>San Juan, Puerto Rico</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5006,29 +5006,29 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>San Juan</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Puerto Rico</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>PR</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>PMW</t>
+          <t>BAQ</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Palmas, Brazil</t>
+          <t>Barranquilla, Colombia</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5038,29 +5038,29 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Palmas</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CO</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>ARU</t>
+          <t>PMW</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Aracatuba, Brazil</t>
+          <t>Palmas, Brazil</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Aracatuba</t>
+          <t>Palmas</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -5087,12 +5087,12 @@
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>POS</t>
+          <t>ARU</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Port of Spain, Trinidad and Tobago</t>
+          <t>Aracatuba, Brazil</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5102,25 +5102,29 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Port of Spain</t>
+          <t>Aracatuba</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Trinidad and Tobago</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr"/>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>POS</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Salvador, Brazil</t>
+          <t>Port of Spain, Trinidad and Tobago</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5130,29 +5134,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Salvador</t>
+          <t>Port of Spain</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>BR</t>
-        </is>
-      </c>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Cuiaba, Brazil</t>
+          <t>Salvador, Brazil</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Cuiaba</t>
+          <t>Salvador</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -5179,12 +5179,12 @@
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>CLO</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Cali, Colombia</t>
+          <t>Cuiaba, Brazil</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5194,29 +5194,29 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Cuiaba</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>CLO</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>San Pedro Sula, Honduras</t>
+          <t>Cali, Colombia</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5226,61 +5226,61 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>San Pedro Sula</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Honduras</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>HN</t>
+          <t>CO</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Accra, Ghana</t>
+          <t>San Pedro Sula, Honduras</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Latin America &amp; the Caribbean</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Accra</t>
+          <t>San Pedro Sula</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Honduras</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>GH</t>
+          <t>HN</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>ALG</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Algiers, Algeria</t>
+          <t>Accra, Ghana</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5290,29 +5290,29 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Algiers</t>
+          <t>Accra</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>DZ</t>
+          <t>GH</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>AAE</t>
+          <t>ALG</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Annaba, Algeria</t>
+          <t>Algiers, Algeria</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Annaba</t>
+          <t>Algiers</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -5339,12 +5339,12 @@
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>TNR</t>
+          <t>AAE</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Antananarivo, Madagascar</t>
+          <t>Annaba, Algeria</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5354,29 +5354,29 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Antananarivo</t>
+          <t>Annaba</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>DZ</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>CPT</t>
+          <t>TNR</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Cape Town, South Africa</t>
+          <t>Antananarivo, Madagascar</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5386,29 +5386,29 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Cape Town</t>
+          <t>Antananarivo</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>MG</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>DKR</t>
+          <t>CPT</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Dakar, Senegal</t>
+          <t>Cape Town, South Africa</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5418,29 +5418,29 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Dakar</t>
+          <t>Cape Town</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>SN</t>
+          <t>ZA</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>DKR</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Dar Es Salaam, Tanzania</t>
+          <t>Dakar, Senegal</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5450,29 +5450,29 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Dar Es Salaam</t>
+          <t>Dakar</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>TZ</t>
+          <t>SN</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>JIB</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Djibouti City, Djibouti</t>
+          <t>Dar Es Salaam, Tanzania</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5482,29 +5482,29 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Djibouti City</t>
+          <t>Dar Es Salaam</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Djibouti</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>DJ</t>
+          <t>TZ</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>DUR</t>
+          <t>JIB</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Durban, South Africa</t>
+          <t>Djibouti City, Djibouti</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5514,29 +5514,29 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Durban</t>
+          <t>Djibouti City</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Djibouti</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>DJ</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>GBE</t>
+          <t>DUR</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Gaborone, Botswana</t>
+          <t>Durban, South Africa</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5546,29 +5546,29 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Gaborone</t>
+          <t>Durban</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>BW</t>
+          <t>ZA</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>HRE</t>
+          <t>GBE</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Harare, Zimbabwe</t>
+          <t>Gaborone, Botswana</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5578,29 +5578,29 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Harare</t>
+          <t>Gaborone</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>ZW</t>
+          <t>BW</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Johannesburg, South Africa</t>
+          <t>Harare, Zimbabwe</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5610,29 +5610,29 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Johannesburg</t>
+          <t>Harare</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>ZW</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>KGL</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Kigali, Rwanda</t>
+          <t>Johannesburg, South Africa</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5642,29 +5642,29 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Kigali</t>
+          <t>Johannesburg</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>ZA</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>LOS</t>
+          <t>KGL</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Lagos, Nigeria</t>
+          <t>Kigali, Rwanda</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -5674,29 +5674,29 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Lagos</t>
+          <t>Kigali</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>NG</t>
+          <t>RW</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>LOS</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Luanda, Angola</t>
+          <t>Lagos, Nigeria</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -5706,29 +5706,29 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Luanda</t>
+          <t>Lagos</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>AO</t>
+          <t>NG</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>MPM</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Maputo, Mozambique</t>
+          <t>Luanda, Angola</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -5738,29 +5738,29 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Maputo</t>
+          <t>Luanda</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>MZ</t>
+          <t>AO</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>MPM</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Mombasa, Kenya</t>
+          <t>Maputo, Mozambique</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5770,29 +5770,29 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Mombasa</t>
+          <t>Maputo</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>KE</t>
+          <t>MZ</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Nairobi, Kenya</t>
+          <t>Mombasa, Kenya</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Nairobi</t>
+          <t>Mombasa</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -5819,12 +5819,12 @@
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>ORN</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Oran, Algeria</t>
+          <t>Nairobi, Kenya</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5834,29 +5834,29 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Oran</t>
+          <t>Nairobi</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>DZ</t>
+          <t>KE</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>OUA</t>
+          <t>ORN</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Ouagadougou, Burkina Faso</t>
+          <t>Oran, Algeria</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5866,29 +5866,29 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Ouagadougou</t>
+          <t>Oran</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Burkina Faso</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>BF</t>
+          <t>DZ</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>MRU</t>
+          <t>OUA</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Port Louis, Mauritius</t>
+          <t>Ouagadougou, Burkina Faso</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5898,29 +5898,29 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Port Louis</t>
+          <t>Ouagadougou</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Mauritius</t>
+          <t>Burkina Faso</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>BF</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>TUN</t>
+          <t>MRU</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Tunis, Tunisia</t>
+          <t>Port Louis, Mauritius</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5930,29 +5930,29 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Tunis</t>
+          <t>Port Louis</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Mauritius</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>MU</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>FIH</t>
+          <t>TUN</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Kinshasa, DR Congo</t>
+          <t>Tunis, Tunisia</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5962,25 +5962,29 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Kinshasa</t>
+          <t>Tunis</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>DR Congo</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr"/>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>CAI</t>
+          <t>FIH</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Cairo, Egypt</t>
+          <t>Kinshasa, DR Congo</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5990,29 +5994,25 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Cairo</t>
+          <t>Kinshasa</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
+          <t>DR Congo</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t>WDH</t>
+          <t>CAI</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Windhoek, Namibia</t>
+          <t>Cairo, Egypt</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6022,29 +6022,29 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Windhoek</t>
+          <t>Cairo</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>EG</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t>ASK</t>
+          <t>WDH</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Yamoussoukro, Ivory Coast</t>
+          <t>Windhoek, Namibia</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6054,25 +6054,29 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Yamoussoukro</t>
+          <t>Windhoek</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr"/>
+          <t>Namibia</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t>ABJ</t>
+          <t>ASK</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Abidjan, Ivory Coast</t>
+          <t>Yamoussoukro, Ivory Coast</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6082,7 +6086,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Abidjan</t>
+          <t>Yamoussoukro</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -6095,12 +6099,12 @@
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>ABJ</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Kampala, Uganda</t>
+          <t>Abidjan, Ivory Coast</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6110,29 +6114,25 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Kampala</t>
+          <t>Abidjan</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Uganda</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
+          <t>Ivory Coast</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t>RUN</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Saint-Denis, Réunion</t>
+          <t>Kampala, Uganda</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6142,25 +6142,29 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Saint-Denis</t>
+          <t>Kampala</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Réunion</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr"/>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>LUN</t>
+          <t>RUN</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Lusaka, Zambia</t>
+          <t>Saint-Denis, Réunion</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6170,29 +6174,25 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Lusaka</t>
+          <t>Saint-Denis</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Zambia</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>ZM</t>
-        </is>
-      </c>
+          <t>Réunion</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t>ADD</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Addis Ababa, Ethiopia</t>
+          <t>Lusaka, Zambia</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6202,29 +6202,29 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Addis Ababa</t>
+          <t>Lusaka</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>ET</t>
+          <t>ZM</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t>LLW</t>
+          <t>ADD</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Lilongwe, Malawi</t>
+          <t>Addis Ababa, Ethiopia</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6234,29 +6234,29 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Lilongwe</t>
+          <t>Addis Ababa</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Malawi</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>MW</t>
+          <t>ET</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t>CZL</t>
+          <t>LLW</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Constantine, Algeria</t>
+          <t>Lilongwe, Malawi</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6266,29 +6266,29 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Constantine</t>
+          <t>Lilongwe</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>DZ</t>
+          <t>MW</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t>DLA</t>
+          <t>CZL</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Douala, Cameroon</t>
+          <t>Constantine, Algeria</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6298,61 +6298,61 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Douala</t>
+          <t>Constantine</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>DZ</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>DLA</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Ahmedabad, India</t>
+          <t>Douala, Cameroon</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>Douala</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CM</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Almaty, Kazakhstan</t>
+          <t>Ahmedabad, India</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6362,29 +6362,29 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Almaty</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>BLR</t>
+          <t>ALA</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Bangalore, India</t>
+          <t>Almaty, Kazakhstan</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6394,29 +6394,29 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Almaty</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>KZ</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>BKK</t>
+          <t>BLR</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Bangkok, Thailand</t>
+          <t>Bangalore, India</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6426,29 +6426,29 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>BWN</t>
+          <t>BKK</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Bandar Seri Begawan, Brunei</t>
+          <t>Bangkok, Thailand</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6458,29 +6458,29 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Bandar Seri Begawan</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Brunei</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>BN</t>
+          <t>TH</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>BWN</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Cebu, Philippines</t>
+          <t>Bandar Seri Begawan, Brunei</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6490,29 +6490,29 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Cebu</t>
+          <t>Bandar Seri Begawan</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Brunei</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>BN</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>IXC</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Chandigarh, India</t>
+          <t>Cebu, Philippines</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6522,29 +6522,29 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Chandigarh</t>
+          <t>Cebu</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>PH</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>CGD</t>
+          <t>IXC</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Changde, China</t>
+          <t>Chandigarh, India</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6554,29 +6554,29 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Changde</t>
+          <t>Chandigarh</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>CGD</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Chennai, India</t>
+          <t>Changde, China</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -6586,29 +6586,29 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Changde</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t>CGP</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Chittagong, Bangladesh</t>
+          <t>Chennai, India</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -6618,29 +6618,29 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Chittagong</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>BD</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t>CMB</t>
+          <t>CGP</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Colombo, Sri Lanka</t>
+          <t>Chittagong, Bangladesh</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -6650,29 +6650,29 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Colombo</t>
+          <t>Chittagong</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>LK</t>
+          <t>BD</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>CMB</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Dhaka, Bangladesh</t>
+          <t>Colombo, Sri Lanka</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -6682,29 +6682,29 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>Colombo</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>Sri Lanka</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>BD</t>
+          <t>LK</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>FUO</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Foshan, China</t>
+          <t>Dhaka, Bangladesh</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -6714,29 +6714,29 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Foshan</t>
+          <t>Dhaka</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>BD</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>FUK</t>
+          <t>FUO</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Fukuoka, Japan</t>
+          <t>Foshan, China</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -6746,29 +6746,29 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Fukuoka</t>
+          <t>Foshan</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>FOC</t>
+          <t>FUK</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Fuzhou, China</t>
+          <t>Fukuoka, Japan</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -6778,29 +6778,29 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Fuzhou</t>
+          <t>Fukuoka</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>JP</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>FOC</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Guangzhou, China</t>
+          <t>Fuzhou, China</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Guangzhou</t>
+          <t>Fuzhou</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -6827,12 +6827,12 @@
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t>HAK</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Haikou, China</t>
+          <t>Guangzhou, China</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Haikou</t>
+          <t>Guangzhou</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -6859,12 +6859,12 @@
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
         <is>
-          <t>HAN</t>
+          <t>HAK</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Hanoi, Vietnam</t>
+          <t>Haikou, China</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -6874,29 +6874,29 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Hanoi</t>
+          <t>Haikou</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>VN</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
         <is>
-          <t>SJW</t>
+          <t>HAN</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Hengshui, China</t>
+          <t>Hanoi, Vietnam</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -6906,29 +6906,29 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Hengshui</t>
+          <t>Hanoi</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>VN</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t>SGN</t>
+          <t>SJW</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City, Vietnam</t>
+          <t>Hengshui, China</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6938,29 +6938,29 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Hengshui</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>VN</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="inlineStr">
         <is>
-          <t>HKG</t>
+          <t>SGN</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Ho Chi Minh City, Vietnam</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6968,19 +6968,31 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
-      <c r="E206" t="inlineStr"/>
-      <c r="F206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Ho Chi Minh City</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>VN</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
         <is>
-          <t>HYD</t>
+          <t>HKG</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Hyderabad, India</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -6988,31 +7000,19 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>Hyderabad</t>
-        </is>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="1" t="inlineStr">
         <is>
-          <t>ISB</t>
+          <t>HYD</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Islamabad, Pakistan</t>
+          <t>Hyderabad, India</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7022,29 +7022,29 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Islamabad</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="inlineStr">
         <is>
-          <t>CGK</t>
+          <t>ISB</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Jakarta, Indonesia</t>
+          <t>Islamabad, Pakistan</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7054,29 +7054,29 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Jakarta</t>
+          <t>Islamabad</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>PK</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="inlineStr">
         <is>
-          <t>TNA</t>
+          <t>CGK</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Jinan, China</t>
+          <t>Jakarta, Indonesia</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7086,29 +7086,29 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Jinan</t>
+          <t>Jakarta</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
         <is>
-          <t>JHB</t>
+          <t>TNA</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Johor Bahru, Malaysia</t>
+          <t>Jinan, China</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -7118,29 +7118,29 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Johor Bahru</t>
+          <t>Jinan</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
         <is>
-          <t>KNU</t>
+          <t>JHB</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Kanpur, India</t>
+          <t>Johor Bahru, Malaysia</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -7150,29 +7150,29 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Kanpur</t>
+          <t>Johor Bahru</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>MY</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="inlineStr">
         <is>
-          <t>KHH</t>
+          <t>KNU</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Kaohsiung City</t>
+          <t>Kanpur, India</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -7180,19 +7180,31 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
-      <c r="E213" t="inlineStr"/>
-      <c r="F213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Kanpur</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="inlineStr">
         <is>
-          <t>KHI</t>
+          <t>KHH</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Karachi, Pakistan</t>
+          <t>Kaohsiung City</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -7200,31 +7212,19 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>Karachi</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>Pakistan</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="1" t="inlineStr">
         <is>
-          <t>KTM</t>
+          <t>KHI</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Kathmandu, Nepal</t>
+          <t>Karachi, Pakistan</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -7234,29 +7234,29 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Kathmandu</t>
+          <t>Karachi</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>PK</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="inlineStr">
         <is>
-          <t>CCU</t>
+          <t>KTM</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Kolkata, India</t>
+          <t>Kathmandu, Nepal</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -7266,29 +7266,29 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Kathmandu</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NP</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
         <is>
-          <t>KJA</t>
+          <t>CCU</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Krasnoyarsk, Russia</t>
+          <t>Kolkata, India</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -7298,29 +7298,29 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Krasnoyarsk</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>RU</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="inlineStr">
         <is>
-          <t>KUL</t>
+          <t>KJA</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Kuala Lumpur, Malaysia</t>
+          <t>Krasnoyarsk, Russia</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -7330,29 +7330,29 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Krasnoyarsk</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>RU</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="inlineStr">
         <is>
-          <t>PKX</t>
+          <t>KUL</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Langfang, China</t>
+          <t>Kuala Lumpur, Malaysia</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -7362,29 +7362,29 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Langfang</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MY</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
         <is>
-          <t>MFM</t>
+          <t>PKX</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Macau</t>
+          <t>Langfang, China</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -7392,19 +7392,31 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
-      <c r="E220" t="inlineStr"/>
-      <c r="F220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Langfang</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="inlineStr">
         <is>
-          <t>MLE</t>
+          <t>MFM</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Malé, Maldives</t>
+          <t>Macau</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -7412,31 +7424,19 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>Malé</t>
-        </is>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>Maldives</t>
-        </is>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>MV</t>
-        </is>
-      </c>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="1" t="inlineStr">
         <is>
-          <t>MNL</t>
+          <t>MLE</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Manila, Philippines</t>
+          <t>Malé, Maldives</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -7446,29 +7446,29 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Manila</t>
+          <t>Malé</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Maldives</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>MV</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="inlineStr">
         <is>
-          <t>BOM</t>
+          <t>MNL</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Mumbai, India</t>
+          <t>Manila, Philippines</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -7478,29 +7478,29 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Manila</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>PH</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="inlineStr">
         <is>
-          <t>NAG</t>
+          <t>BOM</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Nagpur, India</t>
+          <t>Mumbai, India</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -7510,7 +7510,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Nagpur</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -7527,12 +7527,12 @@
     <row r="225">
       <c r="A225" s="1" t="inlineStr">
         <is>
-          <t>OKA</t>
+          <t>NAG</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Naha, Japan</t>
+          <t>Nagpur, India</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -7542,29 +7542,29 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Naha</t>
+          <t>Nagpur</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="inlineStr">
         <is>
-          <t>DEL</t>
+          <t>OKA</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>New Delhi, India</t>
+          <t>Naha, Japan</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -7574,29 +7574,29 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>Naha</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>JP</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="inlineStr">
         <is>
-          <t>KIX</t>
+          <t>DEL</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Osaka, Japan</t>
+          <t>New Delhi, India</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -7606,29 +7606,29 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Osaka</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="inlineStr">
         <is>
-          <t>PAT</t>
+          <t>KIX</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Patna, India</t>
+          <t>Osaka, Japan</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -7638,29 +7638,29 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Patna</t>
+          <t>Osaka</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>JP</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="inlineStr">
         <is>
-          <t>PNH</t>
+          <t>PAT</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Phnom Penh, Cambodia</t>
+          <t>Patna, India</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -7670,29 +7670,29 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Phnom Penh</t>
+          <t>Patna</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Cambodia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>KH</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="inlineStr">
         <is>
-          <t>TAO</t>
+          <t>PNH</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Qingdao, China</t>
+          <t>Phnom Penh, Cambodia</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -7702,29 +7702,29 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Qingdao</t>
+          <t>Phnom Penh</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>KH</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="inlineStr">
         <is>
-          <t>ICN</t>
+          <t>TAO</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Seoul, South Korea</t>
+          <t>Qingdao, China</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -7734,29 +7734,29 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Seoul</t>
+          <t>Qingdao</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="inlineStr">
         <is>
-          <t>SHA</t>
+          <t>ICN</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Seoul, South Korea</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -7766,29 +7766,29 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Shanghai</t>
+          <t>Seoul</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>KR</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="inlineStr">
         <is>
-          <t>SIN</t>
+          <t>SHA</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Singapore, Singapore</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -7798,29 +7798,29 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="inlineStr">
         <is>
-          <t>URT</t>
+          <t>SIN</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Surat Thani, Thailand</t>
+          <t>Singapore, Singapore</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -7830,29 +7830,29 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Surat Thani</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>SG</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="inlineStr">
         <is>
-          <t>TPE</t>
+          <t>URT</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Taipei</t>
+          <t>Surat Thani, Thailand</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -7860,19 +7860,31 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
-      <c r="E235" t="inlineStr"/>
-      <c r="F235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Surat Thani</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="inlineStr">
         <is>
-          <t>NRT</t>
+          <t>TPE</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Tokyo, Japan</t>
+          <t>Taipei</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -7880,31 +7892,19 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>Tokyo</t>
-        </is>
-      </c>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
+      <c r="D236" t="inlineStr"/>
+      <c r="E236" t="inlineStr"/>
+      <c r="F236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="1" t="inlineStr">
         <is>
-          <t>ULN</t>
+          <t>NRT</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Ulaanbaatar, Mongolia</t>
+          <t>Tokyo, Japan</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -7914,29 +7914,29 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Ulaanbaatar</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Mongolia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>MN</t>
+          <t>JP</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="inlineStr">
         <is>
-          <t>VTE</t>
+          <t>ULN</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Vientiane, Laos</t>
+          <t>Ulaanbaatar, Mongolia</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -7946,29 +7946,29 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Vientiane</t>
+          <t>Ulaanbaatar</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Laos</t>
+          <t>Mongolia</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>MN</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="inlineStr">
         <is>
-          <t>KHN</t>
+          <t>VTE</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Xinyu, China</t>
+          <t>Vientiane, Laos</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -7978,29 +7978,29 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Xinyu</t>
+          <t>Vientiane</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Laos</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>LA</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>KHN</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Yerevan, Armenia</t>
+          <t>Xinyu, China</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -8010,29 +8010,29 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Yerevan</t>
+          <t>Xinyu</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="inlineStr">
         <is>
-          <t>JOG</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Yogyakarta, Indonesia</t>
+          <t>Yerevan, Armenia</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -8042,29 +8042,29 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Yogyakarta</t>
+          <t>Yerevan</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>AM</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="inlineStr">
         <is>
-          <t>CGY</t>
+          <t>JOG</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Cagayan de Oro, Philippines</t>
+          <t>Yogyakarta, Indonesia</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -8074,29 +8074,29 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Cagayan de Oro</t>
+          <t>Yogyakarta</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="inlineStr">
         <is>
-          <t>COK</t>
+          <t>CGY</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Kochi, India</t>
+          <t>Cagayan de Oro, Philippines</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -8106,29 +8106,29 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Cagayan de Oro</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>PH</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="inlineStr">
         <is>
-          <t>DPS</t>
+          <t>COK</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Denpasar, Indonesia</t>
+          <t>Kochi, India</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -8138,29 +8138,29 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Denpasar</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="inlineStr">
         <is>
-          <t>CNN</t>
+          <t>DPS</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Kannur, India</t>
+          <t>Denpasar, Indonesia</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -8170,29 +8170,29 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Kannur</t>
+          <t>Denpasar</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="inlineStr">
         <is>
-          <t>SZX</t>
+          <t>CNN</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Shenzhen, China</t>
+          <t>Kannur, India</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -8202,29 +8202,29 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Shenzhen</t>
+          <t>Kannur</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="inlineStr">
         <is>
-          <t>KWE</t>
+          <t>SZX</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Guiyang, China</t>
+          <t>Shenzhen, China</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -8234,7 +8234,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Guiyang</t>
+          <t>Shenzhen</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -8251,12 +8251,12 @@
     <row r="248">
       <c r="A248" s="1" t="inlineStr">
         <is>
-          <t>HGH</t>
+          <t>KWE</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Shaoxing, China</t>
+          <t>Guiyang, China</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Shaoxing</t>
+          <t>Guiyang</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -8283,12 +8283,12 @@
     <row r="249">
       <c r="A249" s="1" t="inlineStr">
         <is>
-          <t>CZX</t>
+          <t>HGH</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Changzhou, China</t>
+          <t>Shaoxing, China</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Changzhou</t>
+          <t>Shaoxing</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -8315,12 +8315,12 @@
     <row r="250">
       <c r="A250" s="1" t="inlineStr">
         <is>
-          <t>KMG</t>
+          <t>CZX</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Kunming, China</t>
+          <t>Changzhou, China</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Kunming</t>
+          <t>Changzhou</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -8347,12 +8347,12 @@
     <row r="251">
       <c r="A251" s="1" t="inlineStr">
         <is>
-          <t>CNX</t>
+          <t>KMG</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Chiang Mai, Thailand</t>
+          <t>Kunming, China</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -8362,29 +8362,29 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Chiang Mai</t>
+          <t>Kunming</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="inlineStr">
         <is>
-          <t>CGO</t>
+          <t>CNX</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Zhengzhou, China</t>
+          <t>Chiang Mai, Thailand</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -8394,29 +8394,29 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Zhengzhou</t>
+          <t>Chiang Mai</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>TH</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="inlineStr">
         <is>
-          <t>TYN</t>
+          <t>CGO</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Yangquan, China</t>
+          <t>Zhengzhou, China</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Yangquan</t>
+          <t>Zhengzhou</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -8443,12 +8443,12 @@
     <row r="254">
       <c r="A254" s="1" t="inlineStr">
         <is>
-          <t>CSX</t>
+          <t>TYN</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Changsha, China</t>
+          <t>Yangquan, China</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Changsha</t>
+          <t>Yangquan</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -8475,12 +8475,12 @@
     <row r="255">
       <c r="A255" s="1" t="inlineStr">
         <is>
-          <t>DLC</t>
+          <t>CSX</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Dalian, China</t>
+          <t>Changsha, China</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -8490,7 +8490,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Dalian</t>
+          <t>Changsha</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -8507,12 +8507,12 @@
     <row r="256">
       <c r="A256" s="1" t="inlineStr">
         <is>
-          <t>BHY</t>
+          <t>DLC</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Beihai, China</t>
+          <t>Dalian, China</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -8522,7 +8522,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Beihai</t>
+          <t>Dalian</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -8539,12 +8539,12 @@
     <row r="257">
       <c r="A257" s="1" t="inlineStr">
         <is>
-          <t>CKG</t>
+          <t>BHY</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Chongqing, China</t>
+          <t>Beihai, China</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Chongqing</t>
+          <t>Beihai</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -8571,12 +8571,12 @@
     <row r="258">
       <c r="A258" s="1" t="inlineStr">
         <is>
-          <t>XFN</t>
+          <t>CKG</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Xiangyang, China</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Xiangyang</t>
+          <t>Chongqing</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -8603,12 +8603,12 @@
     <row r="259">
       <c r="A259" s="1" t="inlineStr">
         <is>
-          <t>DAD</t>
+          <t>XFN</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Da Nang, Vietnam</t>
+          <t>Xiangyang, China</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -8618,29 +8618,29 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Xiangyang</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>VN</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="inlineStr">
         <is>
-          <t>JXG</t>
+          <t>DAD</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Jiaxing, China</t>
+          <t>Da Nang, Vietnam</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -8650,29 +8650,29 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Jiaxing</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>VN</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="inlineStr">
         <is>
-          <t>CRK</t>
+          <t>JXG</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Tarlac City, Philippines</t>
+          <t>Jiaxing, China</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -8682,29 +8682,29 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Tarlac City</t>
+          <t>Jiaxing</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="inlineStr">
         <is>
-          <t>PBH</t>
+          <t>CRK</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Thimphu, Bhutan</t>
+          <t>Tarlac City, Philippines</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -8714,29 +8714,29 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Thimphu</t>
+          <t>Tarlac City</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Bhutan</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>PH</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="inlineStr">
         <is>
-          <t>XIY</t>
+          <t>PBH</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Baoji, China</t>
+          <t>Thimphu, Bhutan</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -8746,29 +8746,29 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Baoji</t>
+          <t>Thimphu</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Bhutan</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>BT</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="inlineStr">
         <is>
-          <t>NQZ</t>
+          <t>XIY</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Astana, Kazakhstan</t>
+          <t>Baoji, China</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -8778,17 +8778,17 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Baoji</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>CN</t>
         </is>
       </c>
     </row>

--- a/DC-Colos.xlsx
+++ b/DC-Colos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F338"/>
+  <dimension ref="A1:F337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2315,44 +2315,44 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>NQZ</t>
+          <t>AMM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Astana, Kazakhstan</t>
+          <t>Amman, Jordan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Middle East</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Amman</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>JO</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>AMM</t>
+          <t>LLK</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Amman, Jordan</t>
+          <t>Astara, Azerbaijan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2362,29 +2362,29 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Amman</t>
+          <t>Astara</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Azerbaijan</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>JO</t>
+          <t>AZ</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>LLK</t>
+          <t>BGW</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Astara, Azerbaijan</t>
+          <t>Baghdad, Iraq</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2394,29 +2394,29 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Astara</t>
+          <t>Baghdad</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Azerbaijan</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>IQ</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>BGW</t>
+          <t>GYD</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Baghdad, Iraq</t>
+          <t>Baku, Azerbaijan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2426,29 +2426,29 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Baghdad</t>
+          <t>Baku</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Azerbaijan</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>IQ</t>
+          <t>AZ</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>GYD</t>
+          <t>BSR</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Baku, Azerbaijan</t>
+          <t>Basra, Iraq</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2458,29 +2458,29 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Baku</t>
+          <t>Basra</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Azerbaijan</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>IQ</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>BSR</t>
+          <t>BEY</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Basra, Iraq</t>
+          <t>Beirut, Lebanon</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2490,29 +2490,29 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Basra</t>
+          <t>Beirut</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>IQ</t>
+          <t>LB</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>BEY</t>
+          <t>DMM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Beirut, Lebanon</t>
+          <t>Dammam, Saudi Arabia</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2522,29 +2522,29 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Beirut</t>
+          <t>Dammam</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>SA</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>DMM</t>
+          <t>DOH</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Dammam, Saudi Arabia</t>
+          <t>Doha, Qatar</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2554,29 +2554,29 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Dammam</t>
+          <t>Doha</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>QA</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>DOH</t>
+          <t>DXB</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Doha, Qatar</t>
+          <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2586,29 +2586,29 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Doha</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>AE</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>DXB</t>
+          <t>EBL</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Dubai, United Arab Emirates</t>
+          <t>Erbil, Iraq</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2618,29 +2618,29 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Erbil</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>IQ</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>EBL</t>
+          <t>HFA</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Erbil, Iraq</t>
+          <t>Haifa, Israel</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2650,29 +2650,29 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Erbil</t>
+          <t>Haifa</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>IQ</t>
+          <t>IL</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>HFA</t>
+          <t>JED</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Haifa, Israel</t>
+          <t>Jeddah, Saudi Arabia</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2682,29 +2682,29 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Haifa</t>
+          <t>Jeddah</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>SA</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>JED</t>
+          <t>KWI</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Jeddah, Saudi Arabia</t>
+          <t>Kuwait City, Kuwait</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2714,29 +2714,29 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Jeddah</t>
+          <t>Kuwait City</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>KW</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>KWI</t>
+          <t>BAH</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Kuwait City, Kuwait</t>
+          <t>Manama, Bahrain</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2746,29 +2746,29 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Kuwait City</t>
+          <t>Manama</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Bahrain</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>KW</t>
+          <t>BH</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>BAH</t>
+          <t>MCT</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Manama, Bahrain</t>
+          <t>Muscat, Oman</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2778,29 +2778,29 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Manama</t>
+          <t>Muscat</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Bahrain</t>
+          <t>Oman</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>BH</t>
+          <t>OM</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>MCT</t>
+          <t>NJF</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Muscat, Oman</t>
+          <t>Najaf, Iraq</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2810,29 +2810,29 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Muscat</t>
+          <t>Najaf</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>OM</t>
+          <t>IQ</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>NJF</t>
+          <t>XNH</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Najaf, Iraq</t>
+          <t>Nasiriyah, Iraq</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Najaf</t>
+          <t>Nasiriyah</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2859,12 +2859,12 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>XNH</t>
+          <t>ZDM</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Nasiriyah, Iraq</t>
+          <t>Ramallah</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2872,31 +2872,19 @@
           <t>Middle East</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Nasiriyah</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Iraq</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>IQ</t>
-        </is>
-      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>ZDM</t>
+          <t>RUH</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ramallah</t>
+          <t>Riyadh, Saudi Arabia</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2904,19 +2892,31 @@
           <t>Middle East</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>RUH</t>
+          <t>ISU</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Riyadh, Saudi Arabia</t>
+          <t>Sulaymaniyah, Iraq</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2926,29 +2926,29 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Riyadh</t>
+          <t>Sulaymaniyah</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>IQ</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>ISU</t>
+          <t>TLV</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Sulaymaniyah, Iraq</t>
+          <t>Tel Aviv, Israel</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2958,61 +2958,61 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Sulaymaniyah</t>
+          <t>Tel Aviv</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>IQ</t>
+          <t>IL</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>TLV</t>
+          <t>ADL</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Tel Aviv, Israel</t>
+          <t>Adelaide, SA, Australia</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Middle East</t>
+          <t>Oceania</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Tel Aviv</t>
+          <t>Adelaide, SA</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>AU</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>ADL</t>
+          <t>AKL</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Adelaide, SA, Australia</t>
+          <t>Auckland, New Zealand</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3022,29 +3022,29 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Adelaide, SA</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>NZ</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>AKL</t>
+          <t>BNE</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Auckland, New Zealand</t>
+          <t>Brisbane, QLD, Australia</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3054,29 +3054,29 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Brisbane, QLD</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>AU</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>BNE</t>
+          <t>CBR</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Brisbane, QLD, Australia</t>
+          <t>Canberra, ACT, Australia</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Brisbane, QLD</t>
+          <t>Canberra, ACT</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3103,12 +3103,12 @@
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>CBR</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Canberra, ACT, Australia</t>
+          <t>Christchurch, New Zealand</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3118,29 +3118,29 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Canberra, ACT</t>
+          <t>Christchurch</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>NZ</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>GUM</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Christchurch, New Zealand</t>
+          <t>Hagatna, Guam</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3150,29 +3150,29 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Christchurch</t>
+          <t>Hagatna</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Guam</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>GU</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>GUM</t>
+          <t>MEL</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Hagatna, Guam</t>
+          <t>Melbourne, VIC, Australia</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3182,29 +3182,29 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Hagatna</t>
+          <t>Melbourne, VIC</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Guam</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>GU</t>
+          <t>AU</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>MEL</t>
+          <t>NOU</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Melbourne, VIC, Australia</t>
+          <t>Noumea, New Caledonia</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3214,29 +3214,29 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Melbourne, VIC</t>
+          <t>Noumea</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>New Caledonia</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>NC</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>NOU</t>
+          <t>PER</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Noumea, New Caledonia</t>
+          <t>Perth, WA, Australia</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3246,29 +3246,29 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Noumea</t>
+          <t>Perth, WA</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>New Caledonia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>AU</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>PER</t>
+          <t>SYD</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Perth, WA, Australia</t>
+          <t>Sydney, NSW, Australia</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Perth, WA</t>
+          <t>Sydney, NSW</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3295,12 +3295,12 @@
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>SYD</t>
+          <t>PPT</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Sydney, NSW, Australia</t>
+          <t>Tahiti, French Polynesia</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3310,29 +3310,29 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Sydney, NSW</t>
+          <t>Tahiti</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>French Polynesia</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>PF</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>PPT</t>
+          <t>SUV</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Tahiti, French Polynesia</t>
+          <t>Suva, Fiji</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3342,29 +3342,29 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Tahiti</t>
+          <t>Suva</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>French Polynesia</t>
+          <t>Fiji</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>FJ</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>SUV</t>
+          <t>HBA</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Suva, Fiji</t>
+          <t>Hobart, Australia</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3374,29 +3374,29 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Suva</t>
+          <t>Hobart</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Fiji</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>FJ</t>
+          <t>AU</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>HBA</t>
+          <t>WLG</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Hobart, Australia</t>
+          <t>Wellington, New Zealand</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3406,61 +3406,61 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Hobart</t>
+          <t>Wellington</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>NZ</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>WLG</t>
+          <t>QWJ</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Wellington, New Zealand</t>
+          <t>Americana, Brazil</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Oceania</t>
+          <t>Latin America &amp; the Caribbean</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Wellington</t>
+          <t>Americana</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>QWJ</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Americana, Brazil</t>
+          <t>Arica, Chile</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3470,29 +3470,29 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Americana</t>
+          <t>Arica</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CL</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>ASU</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Arica, Chile</t>
+          <t>Asunción, Paraguay</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3502,29 +3502,29 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Arica</t>
+          <t>Asunción</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>PY</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>ASU</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Asunción, Paraguay</t>
+          <t>Belém, Brazil</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3534,29 +3534,29 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Asunción</t>
+          <t>Belém</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>PY</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>CNF</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Belém, Brazil</t>
+          <t>Belo Horizonte, Brazil</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Belém</t>
+          <t>Belo Horizonte</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3583,12 +3583,12 @@
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>CNF</t>
+          <t>BOG</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Belo Horizonte, Brazil</t>
+          <t>Bogotá, Colombia</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3598,29 +3598,29 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Belo Horizonte</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CO</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>BOG</t>
+          <t>BSB</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Bogotá, Colombia</t>
+          <t>Brasilia, Brazil</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3630,29 +3630,29 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Brasilia</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>BSB</t>
+          <t>EZE</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Brasilia, Brazil</t>
+          <t>Buenos Aires, Argentina</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3662,29 +3662,29 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Brasilia</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>AR</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>EZE</t>
+          <t>CFC</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Buenos Aires, Argentina</t>
+          <t>Caçador, Brazil</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3694,29 +3694,29 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Caçador</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>CFC</t>
+          <t>VCP</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Caçador, Brazil</t>
+          <t>Campinas, Brazil</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Caçador</t>
+          <t>Campinas</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -3743,12 +3743,12 @@
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>VCP</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Campinas, Brazil</t>
+          <t>Córdoba, Argentina</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3758,29 +3758,29 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Campinas</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>AR</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>CWB</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Córdoba, Argentina</t>
+          <t>Curitiba, Brazil</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3790,29 +3790,29 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Curitiba</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>CWB</t>
+          <t>FLN</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Curitiba, Brazil</t>
+          <t>Florianopolis, Brazil</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Curitiba</t>
+          <t>Florianopolis</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -3839,12 +3839,12 @@
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>FLN</t>
+          <t>FOR</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Florianopolis, Brazil</t>
+          <t>Fortaleza, Brazil</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Florianopolis</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -3871,12 +3871,12 @@
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>FOR</t>
+          <t>GEO</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Fortaleza, Brazil</t>
+          <t>Georgetown, Guyana</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3886,29 +3886,29 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Georgetown</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>GY</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>GEO</t>
+          <t>GYN</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Georgetown, Guyana</t>
+          <t>Goiânia, Brazil</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3918,29 +3918,29 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Georgetown</t>
+          <t>Goiânia</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>GY</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>GYN</t>
+          <t>GUA</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Goiânia, Brazil</t>
+          <t>Guatemala City, Guatemala</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3950,29 +3950,29 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Goiânia</t>
+          <t>Guatemala City</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Guatemala</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>GT</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>GUA</t>
+          <t>GYE</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Guatemala City, Guatemala</t>
+          <t>Guayaquil, Ecuador</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3982,29 +3982,29 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Guatemala City</t>
+          <t>Guayaquil</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Guatemala</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>EC</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>GYE</t>
+          <t>JOI</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Guayaquil, Ecuador</t>
+          <t>Joinville, Brazil</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4014,29 +4014,29 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Guayaquil</t>
+          <t>Joinville</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>JOI</t>
+          <t>JDO</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Joinville, Brazil</t>
+          <t>Juazeiro do Norte, Brazil</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Joinville</t>
+          <t>Juazeiro do Norte</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4063,12 +4063,12 @@
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>JDO</t>
+          <t>LIM</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Juazeiro do Norte, Brazil</t>
+          <t>Lima, Peru</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4078,29 +4078,29 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Juazeiro do Norte</t>
+          <t>Lima</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>PE</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>MAO</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Lima, Peru</t>
+          <t>Manaus, Brazil</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4110,29 +4110,29 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Lima</t>
+          <t>Manaus</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>MAO</t>
+          <t>MDE</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Manaus, Brazil</t>
+          <t>Medellín, Colombia</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4142,29 +4142,29 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Manaus</t>
+          <t>Medellín</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CO</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>MDE</t>
+          <t>NQN</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Medellín, Colombia</t>
+          <t>Neuquén, Argentina</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4174,29 +4174,29 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Neuquén</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>AR</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>NQN</t>
+          <t>PTY</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Neuquén, Argentina</t>
+          <t>Panama City, Panama</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4206,29 +4206,29 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Neuquén</t>
+          <t>Panama City</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>PA</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>PTY</t>
+          <t>PBM</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Panama City, Panama</t>
+          <t>Paramaribo, Suriname</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4238,29 +4238,29 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Panama City</t>
+          <t>Paramaribo</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Suriname</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>SR</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>PBM</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Paramaribo, Suriname</t>
+          <t>Porto Alegre, Brazil</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4270,29 +4270,29 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Paramaribo</t>
+          <t>Porto Alegre</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Suriname</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>UIO</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Porto Alegre, Brazil</t>
+          <t>Quito, Ecuador</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4302,29 +4302,29 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Porto Alegre</t>
+          <t>Quito</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>EC</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>UIO</t>
+          <t>REC</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Quito, Ecuador</t>
+          <t>Recife, Brazil</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4334,29 +4334,29 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Quito</t>
+          <t>Recife</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>REC</t>
+          <t>RAO</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Recife, Brazil</t>
+          <t>Ribeirao Preto, Brazil</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Recife</t>
+          <t>Ribeirao Preto</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -4383,12 +4383,12 @@
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>RAO</t>
+          <t>GIG</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Ribeirao Preto, Brazil</t>
+          <t>Rio de Janeiro, Brazil</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Ribeirao Preto</t>
+          <t>Rio de Janeiro</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -4415,12 +4415,12 @@
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>GIG</t>
+          <t>SJO</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Rio de Janeiro, Brazil</t>
+          <t>San José, Costa Rica</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4430,29 +4430,29 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Rio de Janeiro</t>
+          <t>San José</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Costa Rica</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CR</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>SJO</t>
+          <t>SCL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>San José, Costa Rica</t>
+          <t>Santiago, Chile</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4462,29 +4462,29 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>San José</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Costa Rica</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>CL</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>SCL</t>
+          <t>SDQ</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Santiago, Chile</t>
+          <t>Santo Domingo, Dominican Republic</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4494,29 +4494,29 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Santo Domingo</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>DO</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>SDQ</t>
+          <t>SJP</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Santo Domingo, Dominican Republic</t>
+          <t>São José do Rio Preto, Brazil</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4526,29 +4526,29 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Santo Domingo</t>
+          <t>São José do Rio Preto</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>SJP</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>São José do Rio Preto, Brazil</t>
+          <t>São José dos Campos, Brazil</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>São José do Rio Preto</t>
+          <t>São José dos Campos</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -4575,12 +4575,12 @@
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>GRU</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>São José dos Campos, Brazil</t>
+          <t>São Paulo, Brazil</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>São José dos Campos</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -4607,12 +4607,12 @@
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>GRU</t>
+          <t>SOD</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>São Paulo, Brazil</t>
+          <t>Sorocaba, Brazil</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Sorocaba</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -4639,12 +4639,12 @@
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>SOD</t>
+          <t>TGU</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Sorocaba, Brazil</t>
+          <t>Tegucigalpa, Honduras</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4654,29 +4654,29 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Sorocaba</t>
+          <t>Tegucigalpa</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Honduras</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>HN</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>TGU</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Tegucigalpa, Honduras</t>
+          <t>Timbó, Brazil</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4686,29 +4686,29 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Tegucigalpa</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Honduras</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>HN</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>UDI</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Timbó, Brazil</t>
+          <t>Uberlândia, Brazil</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Uberlândia</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -4735,12 +4735,12 @@
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>UDI</t>
+          <t>VIX</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Uberlândia, Brazil</t>
+          <t>Vitoria, Brazil</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Uberlândia</t>
+          <t>Vitoria</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -4767,12 +4767,12 @@
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>VIX</t>
+          <t>CAW</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Vitoria, Brazil</t>
+          <t>Campos dos Goytacazes, Brazil</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Vitoria</t>
+          <t>Campos dos Goytacazes</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -4799,12 +4799,12 @@
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>CAW</t>
+          <t>XAP</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Campos dos Goytacazes, Brazil</t>
+          <t>Chapeco, Brazil</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Campos dos Goytacazes</t>
+          <t>Chapeco</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -4831,12 +4831,12 @@
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>XAP</t>
+          <t>BGI</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Chapeco, Brazil</t>
+          <t>Bridgetown, Barbados</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4846,29 +4846,29 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Chapeco</t>
+          <t>Bridgetown</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Barbados</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>BB</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>BGI</t>
+          <t>GND</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Bridgetown, Barbados</t>
+          <t>St. George's, Grenada</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4878,29 +4878,29 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Bridgetown</t>
+          <t>St. George's</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Barbados</t>
+          <t>Grenada</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>GD</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>GND</t>
+          <t>STI</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>St. George's, Grenada</t>
+          <t>Santiago de los Caballeros, Dominican Republic</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4910,29 +4910,29 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>St. George's</t>
+          <t>Santiago de los Caballeros</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Grenada</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>DO</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>STI</t>
+          <t>LPB</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Santiago de los Caballeros, Dominican Republic</t>
+          <t>La Paz, Bolivia</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4942,29 +4942,29 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Santiago de los Caballeros</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>BO</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>LPB</t>
+          <t>SJU</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>La Paz, Bolivia</t>
+          <t>San Juan, Puerto Rico</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4974,29 +4974,29 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>San Juan</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Puerto Rico</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>PR</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>SJU</t>
+          <t>BAQ</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>San Juan, Puerto Rico</t>
+          <t>Barranquilla, Colombia</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5006,29 +5006,29 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>San Juan</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Puerto Rico</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>CO</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>BAQ</t>
+          <t>PMW</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Barranquilla, Colombia</t>
+          <t>Palmas, Brazil</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5038,29 +5038,29 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Palmas</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>PMW</t>
+          <t>ARU</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Palmas, Brazil</t>
+          <t>Aracatuba, Brazil</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Palmas</t>
+          <t>Aracatuba</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -5087,12 +5087,12 @@
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>ARU</t>
+          <t>POS</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Aracatuba, Brazil</t>
+          <t>Port of Spain, Trinidad and Tobago</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5102,29 +5102,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Aracatuba</t>
+          <t>Port of Spain</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>BR</t>
-        </is>
-      </c>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>POS</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Port of Spain, Trinidad and Tobago</t>
+          <t>Salvador, Brazil</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5134,25 +5130,29 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Port of Spain</t>
+          <t>Salvador</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Trinidad and Tobago</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr"/>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Salvador, Brazil</t>
+          <t>Cuiaba, Brazil</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Salvador</t>
+          <t>Cuiaba</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -5179,12 +5179,12 @@
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>CLO</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Cuiaba, Brazil</t>
+          <t>Cali, Colombia</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5194,29 +5194,29 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Cuiaba</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CO</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>CLO</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Cali, Colombia</t>
+          <t>San Pedro Sula, Honduras</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5226,61 +5226,61 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>San Pedro Sula</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Honduras</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>HN</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>San Pedro Sula, Honduras</t>
+          <t>Accra, Ghana</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Latin America &amp; the Caribbean</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>San Pedro Sula</t>
+          <t>Accra</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Honduras</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>HN</t>
+          <t>GH</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>ALG</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Accra, Ghana</t>
+          <t>Algiers, Algeria</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5290,29 +5290,29 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Accra</t>
+          <t>Algiers</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>GH</t>
+          <t>DZ</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>ALG</t>
+          <t>AAE</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Algiers, Algeria</t>
+          <t>Annaba, Algeria</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Algiers</t>
+          <t>Annaba</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -5339,12 +5339,12 @@
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>AAE</t>
+          <t>TNR</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Annaba, Algeria</t>
+          <t>Antananarivo, Madagascar</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5354,29 +5354,29 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Annaba</t>
+          <t>Antananarivo</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>DZ</t>
+          <t>MG</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>TNR</t>
+          <t>CPT</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Antananarivo, Madagascar</t>
+          <t>Cape Town, South Africa</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5386,29 +5386,29 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Antananarivo</t>
+          <t>Cape Town</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>ZA</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>CPT</t>
+          <t>DKR</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Cape Town, South Africa</t>
+          <t>Dakar, Senegal</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5418,29 +5418,29 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Cape Town</t>
+          <t>Dakar</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>SN</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>DKR</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Dakar, Senegal</t>
+          <t>Dar Es Salaam, Tanzania</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5450,29 +5450,29 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Dakar</t>
+          <t>Dar Es Salaam</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>SN</t>
+          <t>TZ</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>JIB</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Dar Es Salaam, Tanzania</t>
+          <t>Djibouti City, Djibouti</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5482,29 +5482,29 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Dar Es Salaam</t>
+          <t>Djibouti City</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Djibouti</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>TZ</t>
+          <t>DJ</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>JIB</t>
+          <t>DUR</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Djibouti City, Djibouti</t>
+          <t>Durban, South Africa</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5514,29 +5514,29 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Djibouti City</t>
+          <t>Durban</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Djibouti</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>DJ</t>
+          <t>ZA</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>DUR</t>
+          <t>GBE</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Durban, South Africa</t>
+          <t>Gaborone, Botswana</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5546,29 +5546,29 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Durban</t>
+          <t>Gaborone</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>BW</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>GBE</t>
+          <t>HRE</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Gaborone, Botswana</t>
+          <t>Harare, Zimbabwe</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5578,29 +5578,29 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Gaborone</t>
+          <t>Harare</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>BW</t>
+          <t>ZW</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>HRE</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Harare, Zimbabwe</t>
+          <t>Johannesburg, South Africa</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5610,29 +5610,29 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Harare</t>
+          <t>Johannesburg</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>ZW</t>
+          <t>ZA</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>KGL</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Johannesburg, South Africa</t>
+          <t>Kigali, Rwanda</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5642,29 +5642,29 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Johannesburg</t>
+          <t>Kigali</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>RW</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>KGL</t>
+          <t>LOS</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Kigali, Rwanda</t>
+          <t>Lagos, Nigeria</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -5674,29 +5674,29 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Kigali</t>
+          <t>Lagos</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>NG</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>LOS</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Lagos, Nigeria</t>
+          <t>Luanda, Angola</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -5706,29 +5706,29 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Lagos</t>
+          <t>Luanda</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>NG</t>
+          <t>AO</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>MPM</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Luanda, Angola</t>
+          <t>Maputo, Mozambique</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -5738,29 +5738,29 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Luanda</t>
+          <t>Maputo</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>AO</t>
+          <t>MZ</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>MPM</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Maputo, Mozambique</t>
+          <t>Mombasa, Kenya</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5770,29 +5770,29 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Maputo</t>
+          <t>Mombasa</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>MZ</t>
+          <t>KE</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Mombasa, Kenya</t>
+          <t>Nairobi, Kenya</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Mombasa</t>
+          <t>Nairobi</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -5819,12 +5819,12 @@
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>ORN</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Nairobi, Kenya</t>
+          <t>Oran, Algeria</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5834,29 +5834,29 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Nairobi</t>
+          <t>Oran</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>KE</t>
+          <t>DZ</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>ORN</t>
+          <t>OUA</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Oran, Algeria</t>
+          <t>Ouagadougou, Burkina Faso</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5866,29 +5866,29 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Oran</t>
+          <t>Ouagadougou</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Burkina Faso</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>DZ</t>
+          <t>BF</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>OUA</t>
+          <t>MRU</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Ouagadougou, Burkina Faso</t>
+          <t>Port Louis, Mauritius</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5898,29 +5898,29 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Ouagadougou</t>
+          <t>Port Louis</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Burkina Faso</t>
+          <t>Mauritius</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>BF</t>
+          <t>MU</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>MRU</t>
+          <t>TUN</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Port Louis, Mauritius</t>
+          <t>Tunis, Tunisia</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5930,29 +5930,29 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Port Louis</t>
+          <t>Tunis</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Mauritius</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TN</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>TUN</t>
+          <t>FIH</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Tunis, Tunisia</t>
+          <t>Kinshasa, DR Congo</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5962,29 +5962,25 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Tunis</t>
+          <t>Kinshasa</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Tunisia</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>TN</t>
-        </is>
-      </c>
+          <t>DR Congo</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>FIH</t>
+          <t>CAI</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Kinshasa, DR Congo</t>
+          <t>Cairo, Egypt</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5994,25 +5990,29 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Kinshasa</t>
+          <t>Cairo</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>DR Congo</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr"/>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t>CAI</t>
+          <t>WDH</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Cairo, Egypt</t>
+          <t>Windhoek, Namibia</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6022,29 +6022,29 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Cairo</t>
+          <t>Windhoek</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t>WDH</t>
+          <t>ASK</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Windhoek, Namibia</t>
+          <t>Yamoussoukro, Ivory Coast</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6054,29 +6054,25 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Windhoek</t>
+          <t>Yamoussoukro</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Namibia</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+          <t>Ivory Coast</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t>ASK</t>
+          <t>ABJ</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Yamoussoukro, Ivory Coast</t>
+          <t>Abidjan, Ivory Coast</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6086,7 +6082,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Yamoussoukro</t>
+          <t>Abidjan</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -6099,12 +6095,12 @@
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t>ABJ</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Abidjan, Ivory Coast</t>
+          <t>Kampala, Uganda</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6114,25 +6110,29 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Abidjan</t>
+          <t>Kampala</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr"/>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>RUN</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Kampala, Uganda</t>
+          <t>Saint-Denis, Réunion</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6142,29 +6142,25 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Kampala</t>
+          <t>Saint-Denis</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Uganda</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
+          <t>Réunion</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>RUN</t>
+          <t>LUN</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Saint-Denis, Réunion</t>
+          <t>Lusaka, Zambia</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6174,25 +6170,29 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Saint-Denis</t>
+          <t>Lusaka</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Réunion</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr"/>
+          <t>Zambia</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>ZM</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t>LUN</t>
+          <t>ADD</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Lusaka, Zambia</t>
+          <t>Addis Ababa, Ethiopia</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6202,29 +6202,29 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Lusaka</t>
+          <t>Addis Ababa</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>ZM</t>
+          <t>ET</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t>ADD</t>
+          <t>LLW</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Addis Ababa, Ethiopia</t>
+          <t>Lilongwe, Malawi</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6234,29 +6234,29 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Addis Ababa</t>
+          <t>Lilongwe</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>ET</t>
+          <t>MW</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t>LLW</t>
+          <t>CZL</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Lilongwe, Malawi</t>
+          <t>Constantine, Algeria</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6266,29 +6266,29 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Lilongwe</t>
+          <t>Constantine</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Malawi</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>MW</t>
+          <t>DZ</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t>CZL</t>
+          <t>DLA</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Constantine, Algeria</t>
+          <t>Douala, Cameroon</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6298,61 +6298,61 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Constantine</t>
+          <t>Douala</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>DZ</t>
+          <t>CM</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t>DLA</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Douala, Cameroon</t>
+          <t>Ahmedabad, India</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Douala</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>ALA</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Ahmedabad, India</t>
+          <t>Almaty, Kazakhstan</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6362,29 +6362,29 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>Almaty</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>KZ</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>BLR</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Almaty, Kazakhstan</t>
+          <t>Bangalore, India</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6394,29 +6394,29 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Almaty</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>BLR</t>
+          <t>BKK</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Bangalore, India</t>
+          <t>Bangkok, Thailand</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6426,29 +6426,29 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>TH</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>BKK</t>
+          <t>BWN</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Bangkok, Thailand</t>
+          <t>Bandar Seri Begawan, Brunei</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6458,29 +6458,29 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Bandar Seri Begawan</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Brunei</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>BN</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>BWN</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Bandar Seri Begawan, Brunei</t>
+          <t>Cebu, Philippines</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6490,29 +6490,29 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Bandar Seri Begawan</t>
+          <t>Cebu</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Brunei</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>BN</t>
+          <t>PH</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>IXC</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Cebu, Philippines</t>
+          <t>Chandigarh, India</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6522,29 +6522,29 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Cebu</t>
+          <t>Chandigarh</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>IXC</t>
+          <t>CGD</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Chandigarh, India</t>
+          <t>Changde, China</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6554,29 +6554,29 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Chandigarh</t>
+          <t>Changde</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>CGD</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Changde, China</t>
+          <t>Chennai, India</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -6586,29 +6586,29 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Changde</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>CGP</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Chennai, India</t>
+          <t>Chittagong, Bangladesh</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -6618,29 +6618,29 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Chittagong</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>BD</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t>CGP</t>
+          <t>CMB</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Chittagong, Bangladesh</t>
+          <t>Colombo, Sri Lanka</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -6650,29 +6650,29 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Chittagong</t>
+          <t>Colombo</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>Sri Lanka</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>BD</t>
+          <t>LK</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>CMB</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Colombo, Sri Lanka</t>
+          <t>Dhaka, Bangladesh</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -6682,29 +6682,29 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Colombo</t>
+          <t>Dhaka</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>LK</t>
+          <t>BD</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>FUO</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Dhaka, Bangladesh</t>
+          <t>Foshan, China</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -6714,29 +6714,29 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>Foshan</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>BD</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>FUO</t>
+          <t>FUK</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Foshan, China</t>
+          <t>Fukuoka, Japan</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -6746,29 +6746,29 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Foshan</t>
+          <t>Fukuoka</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>JP</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>FUK</t>
+          <t>FOC</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Fukuoka, Japan</t>
+          <t>Fuzhou, China</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -6778,29 +6778,29 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Fukuoka</t>
+          <t>Fuzhou</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t>FOC</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Fuzhou, China</t>
+          <t>Guangzhou, China</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Fuzhou</t>
+          <t>Guangzhou</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -6827,12 +6827,12 @@
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>HAK</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Guangzhou, China</t>
+          <t>Haikou, China</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Guangzhou</t>
+          <t>Haikou</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -6859,12 +6859,12 @@
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
         <is>
-          <t>HAK</t>
+          <t>HAN</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Haikou, China</t>
+          <t>Hanoi, Vietnam</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -6874,29 +6874,29 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Haikou</t>
+          <t>Hanoi</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>VN</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
         <is>
-          <t>HAN</t>
+          <t>SJW</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Hanoi, Vietnam</t>
+          <t>Hengshui, China</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -6906,29 +6906,29 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Hanoi</t>
+          <t>Hengshui</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>VN</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t>SJW</t>
+          <t>SGN</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Hengshui, China</t>
+          <t>Ho Chi Minh City, Vietnam</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6938,29 +6938,29 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Hengshui</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>VN</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="inlineStr">
         <is>
-          <t>SGN</t>
+          <t>HKG</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City, Vietnam</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6968,31 +6968,19 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>Ho Chi Minh City</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>Vietnam</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>VN</t>
-        </is>
-      </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
         <is>
-          <t>HKG</t>
+          <t>HYD</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Hyderabad, India</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -7000,19 +6988,31 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
-      <c r="E207" t="inlineStr"/>
-      <c r="F207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="inlineStr">
         <is>
-          <t>HYD</t>
+          <t>ISB</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Hyderabad, India</t>
+          <t>Islamabad, Pakistan</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7022,29 +7022,29 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Islamabad</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>PK</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="inlineStr">
         <is>
-          <t>ISB</t>
+          <t>CGK</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Islamabad, Pakistan</t>
+          <t>Jakarta, Indonesia</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7054,29 +7054,29 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Islamabad</t>
+          <t>Jakarta</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="inlineStr">
         <is>
-          <t>CGK</t>
+          <t>TNA</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Jakarta, Indonesia</t>
+          <t>Jinan, China</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7086,29 +7086,29 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Jakarta</t>
+          <t>Jinan</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
         <is>
-          <t>TNA</t>
+          <t>JHB</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Jinan, China</t>
+          <t>Johor Bahru, Malaysia</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -7118,29 +7118,29 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Jinan</t>
+          <t>Johor Bahru</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MY</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
         <is>
-          <t>JHB</t>
+          <t>KNU</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Johor Bahru, Malaysia</t>
+          <t>Kanpur, India</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -7150,29 +7150,29 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Johor Bahru</t>
+          <t>Kanpur</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="inlineStr">
         <is>
-          <t>KNU</t>
+          <t>KHH</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Kanpur, India</t>
+          <t>Kaohsiung City</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -7180,31 +7180,19 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>Kanpur</t>
-        </is>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="1" t="inlineStr">
         <is>
-          <t>KHH</t>
+          <t>KHI</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Kaohsiung City</t>
+          <t>Karachi, Pakistan</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -7212,19 +7200,31 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
-      <c r="E214" t="inlineStr"/>
-      <c r="F214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="inlineStr">
         <is>
-          <t>KHI</t>
+          <t>KTM</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Karachi, Pakistan</t>
+          <t>Kathmandu, Nepal</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -7234,29 +7234,29 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Karachi</t>
+          <t>Kathmandu</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>NP</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="inlineStr">
         <is>
-          <t>KTM</t>
+          <t>CCU</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Kathmandu, Nepal</t>
+          <t>Kolkata, India</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -7266,29 +7266,29 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Kathmandu</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
         <is>
-          <t>CCU</t>
+          <t>KJA</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Kolkata, India</t>
+          <t>Krasnoyarsk, Russia</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -7298,29 +7298,29 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Krasnoyarsk</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>RU</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="inlineStr">
         <is>
-          <t>KJA</t>
+          <t>KUL</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Krasnoyarsk, Russia</t>
+          <t>Kuala Lumpur, Malaysia</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -7330,29 +7330,29 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Krasnoyarsk</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>RU</t>
+          <t>MY</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="inlineStr">
         <is>
-          <t>KUL</t>
+          <t>PKX</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Kuala Lumpur, Malaysia</t>
+          <t>Langfang, China</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -7362,29 +7362,29 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Langfang</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
         <is>
-          <t>PKX</t>
+          <t>MFM</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Langfang, China</t>
+          <t>Macau</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -7392,31 +7392,19 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>Langfang</t>
-        </is>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="1" t="inlineStr">
         <is>
-          <t>MFM</t>
+          <t>MLE</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Macau</t>
+          <t>Malé, Maldives</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -7424,19 +7412,31 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
-      <c r="E221" t="inlineStr"/>
-      <c r="F221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Malé</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Maldives</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>MV</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="inlineStr">
         <is>
-          <t>MLE</t>
+          <t>MNL</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Malé, Maldives</t>
+          <t>Manila, Philippines</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -7446,29 +7446,29 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Malé</t>
+          <t>Manila</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Maldives</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>MV</t>
+          <t>PH</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="inlineStr">
         <is>
-          <t>MNL</t>
+          <t>BOM</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Manila, Philippines</t>
+          <t>Mumbai, India</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -7478,29 +7478,29 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Manila</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="inlineStr">
         <is>
-          <t>BOM</t>
+          <t>NAG</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Mumbai, India</t>
+          <t>Nagpur, India</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -7510,7 +7510,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Nagpur</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -7527,12 +7527,12 @@
     <row r="225">
       <c r="A225" s="1" t="inlineStr">
         <is>
-          <t>NAG</t>
+          <t>OKA</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Nagpur, India</t>
+          <t>Naha, Japan</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -7542,29 +7542,29 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Nagpur</t>
+          <t>Naha</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>JP</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="inlineStr">
         <is>
-          <t>OKA</t>
+          <t>DEL</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Naha, Japan</t>
+          <t>New Delhi, India</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -7574,29 +7574,29 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Naha</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="inlineStr">
         <is>
-          <t>DEL</t>
+          <t>KIX</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>New Delhi, India</t>
+          <t>Osaka, Japan</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -7606,29 +7606,29 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>Osaka</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>JP</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="inlineStr">
         <is>
-          <t>KIX</t>
+          <t>PAT</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Osaka, Japan</t>
+          <t>Patna, India</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -7638,29 +7638,29 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Osaka</t>
+          <t>Patna</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="inlineStr">
         <is>
-          <t>PAT</t>
+          <t>PNH</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Patna, India</t>
+          <t>Phnom Penh, Cambodia</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -7670,29 +7670,29 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Patna</t>
+          <t>Phnom Penh</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>KH</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="inlineStr">
         <is>
-          <t>PNH</t>
+          <t>TAO</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Phnom Penh, Cambodia</t>
+          <t>Qingdao, China</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -7702,29 +7702,29 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Phnom Penh</t>
+          <t>Qingdao</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Cambodia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>KH</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="inlineStr">
         <is>
-          <t>TAO</t>
+          <t>ICN</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Qingdao, China</t>
+          <t>Seoul, South Korea</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -7734,29 +7734,29 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Qingdao</t>
+          <t>Seoul</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>KR</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="inlineStr">
         <is>
-          <t>ICN</t>
+          <t>SHA</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Seoul, South Korea</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -7766,29 +7766,29 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Seoul</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="inlineStr">
         <is>
-          <t>SHA</t>
+          <t>SIN</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Singapore, Singapore</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -7798,29 +7798,29 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Shanghai</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>SG</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="inlineStr">
         <is>
-          <t>SIN</t>
+          <t>URT</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Singapore, Singapore</t>
+          <t>Surat Thani, Thailand</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -7830,29 +7830,29 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Surat Thani</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>TH</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="inlineStr">
         <is>
-          <t>URT</t>
+          <t>TPE</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Surat Thani, Thailand</t>
+          <t>Taipei</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -7860,31 +7860,19 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>Surat Thani</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>Thailand</t>
-        </is>
-      </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>TH</t>
-        </is>
-      </c>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="1" t="inlineStr">
         <is>
-          <t>TPE</t>
+          <t>NRT</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Taipei</t>
+          <t>Tokyo, Japan</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -7892,19 +7880,31 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
-      <c r="E236" t="inlineStr"/>
-      <c r="F236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="inlineStr">
         <is>
-          <t>NRT</t>
+          <t>ULN</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Tokyo, Japan</t>
+          <t>Ulaanbaatar, Mongolia</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -7914,29 +7914,29 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Ulaanbaatar</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Mongolia</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>MN</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="inlineStr">
         <is>
-          <t>ULN</t>
+          <t>VTE</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Ulaanbaatar, Mongolia</t>
+          <t>Vientiane, Laos</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -7946,29 +7946,29 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Ulaanbaatar</t>
+          <t>Vientiane</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Mongolia</t>
+          <t>Laos</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>MN</t>
+          <t>LA</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="inlineStr">
         <is>
-          <t>VTE</t>
+          <t>KHN</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Vientiane, Laos</t>
+          <t>Xinyu, China</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -7978,29 +7978,29 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Vientiane</t>
+          <t>Xinyu</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Laos</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="inlineStr">
         <is>
-          <t>KHN</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Xinyu, China</t>
+          <t>Yerevan, Armenia</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -8010,29 +8010,29 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Xinyu</t>
+          <t>Yerevan</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>AM</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>JOG</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Yerevan, Armenia</t>
+          <t>Yogyakarta, Indonesia</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -8042,29 +8042,29 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Yerevan</t>
+          <t>Yogyakarta</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="inlineStr">
         <is>
-          <t>JOG</t>
+          <t>CGY</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Yogyakarta, Indonesia</t>
+          <t>Cagayan de Oro, Philippines</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -8074,29 +8074,29 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Yogyakarta</t>
+          <t>Cagayan de Oro</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>PH</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="inlineStr">
         <is>
-          <t>CGY</t>
+          <t>COK</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Cagayan de Oro, Philippines</t>
+          <t>Kochi, India</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -8106,29 +8106,29 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Cagayan de Oro</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="inlineStr">
         <is>
-          <t>COK</t>
+          <t>DPS</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Kochi, India</t>
+          <t>Denpasar, Indonesia</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -8138,29 +8138,29 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Denpasar</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="inlineStr">
         <is>
-          <t>DPS</t>
+          <t>CNN</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Denpasar, Indonesia</t>
+          <t>Kannur, India</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -8170,29 +8170,29 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Denpasar</t>
+          <t>Kannur</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="inlineStr">
         <is>
-          <t>CNN</t>
+          <t>SZX</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Kannur, India</t>
+          <t>Shenzhen, China</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -8202,29 +8202,29 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Kannur</t>
+          <t>Shenzhen</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="inlineStr">
         <is>
-          <t>SZX</t>
+          <t>KWE</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Shenzhen, China</t>
+          <t>Guiyang, China</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -8234,7 +8234,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Shenzhen</t>
+          <t>Guiyang</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -8251,12 +8251,12 @@
     <row r="248">
       <c r="A248" s="1" t="inlineStr">
         <is>
-          <t>KWE</t>
+          <t>HGH</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Guiyang, China</t>
+          <t>Shaoxing, China</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Guiyang</t>
+          <t>Shaoxing</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -8283,12 +8283,12 @@
     <row r="249">
       <c r="A249" s="1" t="inlineStr">
         <is>
-          <t>HGH</t>
+          <t>CZX</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Shaoxing, China</t>
+          <t>Changzhou, China</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Shaoxing</t>
+          <t>Changzhou</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -8315,12 +8315,12 @@
     <row r="250">
       <c r="A250" s="1" t="inlineStr">
         <is>
-          <t>CZX</t>
+          <t>KMG</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Changzhou, China</t>
+          <t>Kunming, China</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Changzhou</t>
+          <t>Kunming</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -8347,12 +8347,12 @@
     <row r="251">
       <c r="A251" s="1" t="inlineStr">
         <is>
-          <t>KMG</t>
+          <t>CNX</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Kunming, China</t>
+          <t>Chiang Mai, Thailand</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -8362,29 +8362,29 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Kunming</t>
+          <t>Chiang Mai</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>TH</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="inlineStr">
         <is>
-          <t>CNX</t>
+          <t>CGO</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Chiang Mai, Thailand</t>
+          <t>Zhengzhou, China</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -8394,29 +8394,29 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Chiang Mai</t>
+          <t>Zhengzhou</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="inlineStr">
         <is>
-          <t>CGO</t>
+          <t>TYN</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Zhengzhou, China</t>
+          <t>Yangquan, China</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Zhengzhou</t>
+          <t>Yangquan</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -8443,12 +8443,12 @@
     <row r="254">
       <c r="A254" s="1" t="inlineStr">
         <is>
-          <t>TYN</t>
+          <t>CSX</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Yangquan, China</t>
+          <t>Changsha, China</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Yangquan</t>
+          <t>Changsha</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -8475,12 +8475,12 @@
     <row r="255">
       <c r="A255" s="1" t="inlineStr">
         <is>
-          <t>CSX</t>
+          <t>DLC</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Changsha, China</t>
+          <t>Dalian, China</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -8490,7 +8490,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Changsha</t>
+          <t>Dalian</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -8507,12 +8507,12 @@
     <row r="256">
       <c r="A256" s="1" t="inlineStr">
         <is>
-          <t>DLC</t>
+          <t>BHY</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Dalian, China</t>
+          <t>Beihai, China</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -8522,7 +8522,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Dalian</t>
+          <t>Beihai</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -8539,12 +8539,12 @@
     <row r="257">
       <c r="A257" s="1" t="inlineStr">
         <is>
-          <t>BHY</t>
+          <t>CKG</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Beihai, China</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Beihai</t>
+          <t>Chongqing</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -8571,12 +8571,12 @@
     <row r="258">
       <c r="A258" s="1" t="inlineStr">
         <is>
-          <t>CKG</t>
+          <t>XFN</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Chongqing, China</t>
+          <t>Xiangyang, China</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Chongqing</t>
+          <t>Xiangyang</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -8603,12 +8603,12 @@
     <row r="259">
       <c r="A259" s="1" t="inlineStr">
         <is>
-          <t>XFN</t>
+          <t>DAD</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Xiangyang, China</t>
+          <t>Da Nang, Vietnam</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -8618,29 +8618,29 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Xiangyang</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>VN</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="inlineStr">
         <is>
-          <t>DAD</t>
+          <t>JXG</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Da Nang, Vietnam</t>
+          <t>Jiaxing, China</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -8650,29 +8650,29 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Jiaxing</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>VN</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="inlineStr">
         <is>
-          <t>JXG</t>
+          <t>CRK</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Jiaxing, China</t>
+          <t>Tarlac City, Philippines</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -8682,29 +8682,29 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Jiaxing</t>
+          <t>Tarlac City</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>PH</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="inlineStr">
         <is>
-          <t>CRK</t>
+          <t>PBH</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Tarlac City, Philippines</t>
+          <t>Thimphu, Bhutan</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -8714,29 +8714,29 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Tarlac City</t>
+          <t>Thimphu</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Bhutan</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>BT</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="inlineStr">
         <is>
-          <t>PBH</t>
+          <t>XIY</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Thimphu, Bhutan</t>
+          <t>Baoji, China</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -8746,29 +8746,29 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Thimphu</t>
+          <t>Baoji</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Bhutan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="inlineStr">
         <is>
-          <t>XIY</t>
+          <t>KCH</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Baoji, China</t>
+          <t>Kuching, Malaysia</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -8778,29 +8778,29 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Baoji</t>
+          <t>Kuching</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MY</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="inlineStr">
         <is>
-          <t>KCH</t>
+          <t>AKX</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Kuching, Malaysia</t>
+          <t>Aktobe, Kazakhstan</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -8810,29 +8810,29 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Kuching</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>KZ</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="1" t="inlineStr">
         <is>
-          <t>AKX</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Aktobe, Kazakhstan</t>
+          <t>Tongren, China</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -8842,29 +8842,29 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Tongren</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Tongren, China</t>
+          <t>Taizhou, China</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Tongren</t>
+          <t>Taizhou</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -8891,12 +8891,12 @@
     <row r="268">
       <c r="A268" s="1" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>FRU</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Taizhou, China</t>
+          <t>Bishkek, Kyrgyzstan</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -8906,29 +8906,29 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Taizhou</t>
+          <t>Bishkek</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kyrgyzstan</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>KG</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="inlineStr">
         <is>
-          <t>FRU</t>
+          <t>MLG</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Bishkek, Kyrgyzstan</t>
+          <t>Malang, Indonesia</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -8938,29 +8938,29 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Bishkek</t>
+          <t>Malang</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Kyrgyzstan</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="inlineStr">
         <is>
-          <t>MLG</t>
+          <t>LHE</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Malang, Indonesia</t>
+          <t>Lahore, Pakistan</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -8970,29 +8970,29 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Malang</t>
+          <t>Lahore</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>PK</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="inlineStr">
         <is>
-          <t>LHE</t>
+          <t>CTU</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Lahore, Pakistan</t>
+          <t>Chengdu, China</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -9002,29 +9002,29 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Lahore</t>
+          <t>Chengdu</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="inlineStr">
         <is>
-          <t>CTU</t>
+          <t>AGR</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Chengdu, China</t>
+          <t>Agra, India</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -9034,29 +9034,29 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Chengdu</t>
+          <t>Agra</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="inlineStr">
         <is>
-          <t>AGR</t>
+          <t>CJB</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Agra, India</t>
+          <t>Coimbatore, India</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Agra</t>
+          <t>Coimbatore</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -9083,12 +9083,12 @@
     <row r="274">
       <c r="A274" s="1" t="inlineStr">
         <is>
-          <t>CJB</t>
+          <t>ACX</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Coimbatore, India</t>
+          <t>Xingyi, China</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -9098,29 +9098,29 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Coimbatore</t>
+          <t>Xingyi</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="1" t="inlineStr">
         <is>
-          <t>ACX</t>
+          <t>BBI</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Xingyi, China</t>
+          <t>Bhubaneswar, India</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -9130,29 +9130,29 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Xingyi</t>
+          <t>Bhubaneswar</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="1" t="inlineStr">
         <is>
-          <t>BBI</t>
+          <t>LYA</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Bhubaneswar, India</t>
+          <t>Luoyang, China</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -9162,29 +9162,29 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Bhubaneswar</t>
+          <t>Luoyang</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="inlineStr">
         <is>
-          <t>LYA</t>
+          <t>PNQ</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Luoyang, China</t>
+          <t>Pune, India</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -9194,29 +9194,29 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Luoyang</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="1" t="inlineStr">
         <is>
-          <t>PNQ</t>
+          <t>JRG</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Pune, India</t>
+          <t>Sambalpur, India</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -9226,7 +9226,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Sambalpur</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -9243,44 +9243,44 @@
     <row r="279">
       <c r="A279" s="1" t="inlineStr">
         <is>
-          <t>JRG</t>
+          <t>ABQ</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Sambalpur, India</t>
+          <t>Albuquerque, NM, United States</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Sambalpur</t>
+          <t>Albuquerque, NM</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="1" t="inlineStr">
         <is>
-          <t>ABQ</t>
+          <t>ANC</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, United States</t>
+          <t>Anchorage, AK, United States</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -9290,7 +9290,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Albuquerque, NM</t>
+          <t>Anchorage, AK</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -9307,12 +9307,12 @@
     <row r="281">
       <c r="A281" s="1" t="inlineStr">
         <is>
-          <t>ANC</t>
+          <t>IAD</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Anchorage, AK, United States</t>
+          <t>Ashburn, VA, United States</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -9322,7 +9322,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Anchorage, AK</t>
+          <t>Ashburn, VA</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -9339,12 +9339,12 @@
     <row r="282">
       <c r="A282" s="1" t="inlineStr">
         <is>
-          <t>IAD</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Ashburn, VA, United States</t>
+          <t>Atlanta, GA, United States</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Ashburn, VA</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -9371,12 +9371,12 @@
     <row r="283">
       <c r="A283" s="1" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Atlanta, GA, United States</t>
+          <t>Austin, TX, United States</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -9403,12 +9403,12 @@
     <row r="284">
       <c r="A284" s="1" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>BGR</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Austin, TX, United States</t>
+          <t>Bangor, ME, United States</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -9418,7 +9418,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Bangor, ME</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -9435,12 +9435,12 @@
     <row r="285">
       <c r="A285" s="1" t="inlineStr">
         <is>
-          <t>BGR</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Bangor, ME, United States</t>
+          <t>Boston, MA, United States</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -9450,7 +9450,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Bangor, ME</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -9467,12 +9467,12 @@
     <row r="286">
       <c r="A286" s="1" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Boston, MA, United States</t>
+          <t>Buffalo, NY, United States</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -9482,7 +9482,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Buffalo, NY</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -9499,12 +9499,12 @@
     <row r="287">
       <c r="A287" s="1" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>YYC</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Buffalo, NY, United States</t>
+          <t>Calgary, AB, Canada</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -9514,29 +9514,29 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Buffalo, NY</t>
+          <t>Calgary, AB</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="inlineStr">
         <is>
-          <t>YYC</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Calgary, AB, Canada</t>
+          <t>Charlotte, NC, United States</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -9546,29 +9546,29 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Calgary, AB</t>
+          <t>Charlotte, NC</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>ORD</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Charlotte, NC, United States</t>
+          <t>Chicago, IL, United States</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -9578,7 +9578,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Charlotte, NC</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -9595,12 +9595,12 @@
     <row r="290">
       <c r="A290" s="1" t="inlineStr">
         <is>
-          <t>ORD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Chicago, IL, United States</t>
+          <t>Cleveland, OH, United States</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -9610,7 +9610,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Cleveland, OH</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -9627,12 +9627,12 @@
     <row r="291">
       <c r="A291" s="1" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CMH</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Cleveland, OH, United States</t>
+          <t>Columbus, OH, United States</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -9642,7 +9642,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Cleveland, OH</t>
+          <t>Columbus, OH</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -9659,12 +9659,12 @@
     <row r="292">
       <c r="A292" s="1" t="inlineStr">
         <is>
-          <t>CMH</t>
+          <t>DFW</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Columbus, OH, United States</t>
+          <t>Dallas, TX, United States</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Columbus, OH</t>
+          <t>Dallas, TX</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -9691,12 +9691,12 @@
     <row r="293">
       <c r="A293" s="1" t="inlineStr">
         <is>
-          <t>DFW</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Dallas, TX, United States</t>
+          <t>Denver, CO, United States</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -9706,7 +9706,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Dallas, TX</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -9723,12 +9723,12 @@
     <row r="294">
       <c r="A294" s="1" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DTW</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Denver, CO, United States</t>
+          <t>Detroit, MI, United States</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -9738,7 +9738,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>Detroit, MI</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -9755,12 +9755,12 @@
     <row r="295">
       <c r="A295" s="1" t="inlineStr">
         <is>
-          <t>DTW</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Detroit, MI, United States</t>
+          <t>Durham, NC, United States</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -9770,7 +9770,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Detroit, MI</t>
+          <t>Durham, NC</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -9787,12 +9787,12 @@
     <row r="296">
       <c r="A296" s="1" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GDL</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Durham, NC, United States</t>
+          <t>Guadalajara, Mexico</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -9802,29 +9802,29 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Durham, NC</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="inlineStr">
         <is>
-          <t>GDL</t>
+          <t>YHZ</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Guadalajara, Mexico</t>
+          <t>Halifax, Canada</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -9834,29 +9834,29 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Halifax</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="inlineStr">
         <is>
-          <t>YHZ</t>
+          <t>HNL</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Halifax, Canada</t>
+          <t>Honolulu, HI, United States</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -9866,29 +9866,29 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Halifax</t>
+          <t>Honolulu, HI</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="1" t="inlineStr">
         <is>
-          <t>HNL</t>
+          <t>IAH</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Honolulu, HI, United States</t>
+          <t>Houston, TX, United States</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -9898,7 +9898,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Honolulu, HI</t>
+          <t>Houston, TX</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -9915,12 +9915,12 @@
     <row r="300">
       <c r="A300" s="1" t="inlineStr">
         <is>
-          <t>IAH</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Houston, TX, United States</t>
+          <t>Indianapolis, IN, United States</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -9930,7 +9930,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Houston, TX</t>
+          <t>Indianapolis, IN</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -9947,12 +9947,12 @@
     <row r="301">
       <c r="A301" s="1" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, United States</t>
+          <t>Jacksonville, FL, United States</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -9962,7 +9962,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Indianapolis, IN</t>
+          <t>Jacksonville, FL</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -9979,12 +9979,12 @@
     <row r="302">
       <c r="A302" s="1" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>MCI</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, United States</t>
+          <t>Kansas City, MO, United States</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -9994,7 +9994,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Jacksonville, FL</t>
+          <t>Kansas City, MO</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -10011,12 +10011,12 @@
     <row r="303">
       <c r="A303" s="1" t="inlineStr">
         <is>
-          <t>MCI</t>
+          <t>KIN</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Kansas City, MO, United States</t>
+          <t>Kingston, Jamaica</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -10026,29 +10026,29 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Kansas City, MO</t>
+          <t>Kingston</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Jamaica</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JM</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="inlineStr">
         <is>
-          <t>KIN</t>
+          <t>LAS</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Kingston, Jamaica</t>
+          <t>Las Vegas, NV, United States</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -10058,29 +10058,29 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Kingston</t>
+          <t>Las Vegas, NV</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Jamaica</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>JM</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="inlineStr">
         <is>
-          <t>LAS</t>
+          <t>LAX</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, United States</t>
+          <t>Los Angeles, CA, United States</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -10090,7 +10090,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Las Vegas, NV</t>
+          <t>Los Angeles, CA</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -10107,12 +10107,12 @@
     <row r="306">
       <c r="A306" s="1" t="inlineStr">
         <is>
-          <t>LAX</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, United States</t>
+          <t>Memphis, TN, United States</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -10122,7 +10122,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
+          <t>Memphis, TN</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -10139,12 +10139,12 @@
     <row r="307">
       <c r="A307" s="1" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MEX</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Memphis, TN, United States</t>
+          <t>Mexico City, Mexico</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -10154,29 +10154,29 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Memphis, TN</t>
+          <t>Mexico City</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="inlineStr">
         <is>
-          <t>MEX</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Mexico City, Mexico</t>
+          <t>Miami, FL, United States</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -10186,29 +10186,29 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Mexico City</t>
+          <t>Miami, FL</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MSP</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Miami, FL, United States</t>
+          <t>Minneapolis, MN, United States</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -10218,7 +10218,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Miami, FL</t>
+          <t>Minneapolis, MN</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -10235,12 +10235,12 @@
     <row r="310">
       <c r="A310" s="1" t="inlineStr">
         <is>
-          <t>MSP</t>
+          <t>YUL</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, United States</t>
+          <t>Montréal, QC, Canada</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -10250,29 +10250,29 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Minneapolis, MN</t>
+          <t>Montréal, QC</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="inlineStr">
         <is>
-          <t>YUL</t>
+          <t>BNA</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Montréal, QC, Canada</t>
+          <t>Nashville, United States</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -10282,29 +10282,29 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Montréal, QC</t>
+          <t>Nashville</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="1" t="inlineStr">
         <is>
-          <t>BNA</t>
+          <t>EWR</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Nashville, United States</t>
+          <t>Newark, NJ, United States</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -10314,7 +10314,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Nashville</t>
+          <t>Newark, NJ</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -10331,12 +10331,12 @@
     <row r="313">
       <c r="A313" s="1" t="inlineStr">
         <is>
-          <t>EWR</t>
+          <t>ORF</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Newark, NJ, United States</t>
+          <t>Norfolk, VA, United States</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -10346,7 +10346,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Newark, NJ</t>
+          <t>Norfolk, VA</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -10363,12 +10363,12 @@
     <row r="314">
       <c r="A314" s="1" t="inlineStr">
         <is>
-          <t>ORF</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Norfolk, VA, United States</t>
+          <t>Oklahoma City, OK, United States</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Norfolk, VA</t>
+          <t>Oklahoma City, OK</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -10395,12 +10395,12 @@
     <row r="315">
       <c r="A315" s="1" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>OMA</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, United States</t>
+          <t>Omaha, NE, United States</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -10410,7 +10410,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK</t>
+          <t>Omaha, NE</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -10427,12 +10427,12 @@
     <row r="316">
       <c r="A316" s="1" t="inlineStr">
         <is>
-          <t>OMA</t>
+          <t>PHL</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Omaha, NE, United States</t>
+          <t>Philadelphia, United States</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -10442,7 +10442,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Omaha, NE</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -10459,12 +10459,12 @@
     <row r="317">
       <c r="A317" s="1" t="inlineStr">
         <is>
-          <t>PHL</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Philadelphia, United States</t>
+          <t>Phoenix, AZ, United States</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -10474,7 +10474,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Phoenix, AZ</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -10491,12 +10491,12 @@
     <row r="318">
       <c r="A318" s="1" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, United States</t>
+          <t>Pittsburgh, PA, United States</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -10506,7 +10506,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Phoenix, AZ</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -10523,12 +10523,12 @@
     <row r="319">
       <c r="A319" s="1" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, United States</t>
+          <t>Portland, OR, United States</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -10538,7 +10538,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA</t>
+          <t>Portland, OR</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -10555,12 +10555,12 @@
     <row r="320">
       <c r="A320" s="1" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>QRO</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Portland, OR, United States</t>
+          <t>Queretaro, MX, Mexico</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -10570,29 +10570,29 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Portland, OR</t>
+          <t>Queretaro, MX</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="inlineStr">
         <is>
-          <t>QRO</t>
+          <t>RIC</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Queretaro, MX, Mexico</t>
+          <t>Richmond, VA, United States</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -10602,29 +10602,29 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Queretaro, MX</t>
+          <t>Richmond, VA</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="inlineStr">
         <is>
-          <t>RIC</t>
+          <t>SMF</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Richmond, VA, United States</t>
+          <t>Sacramento, CA, United States</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -10634,7 +10634,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Richmond, VA</t>
+          <t>Sacramento, CA</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -10651,12 +10651,12 @@
     <row r="323">
       <c r="A323" s="1" t="inlineStr">
         <is>
-          <t>SMF</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Sacramento, CA, United States</t>
+          <t>Salt Lake City, UT, United States</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Sacramento, CA</t>
+          <t>Salt Lake City, UT</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -10683,12 +10683,12 @@
     <row r="324">
       <c r="A324" s="1" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>SAT</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, United States</t>
+          <t>San Antonio, TX, United States</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -10698,7 +10698,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT</t>
+          <t>San Antonio, TX</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -10715,12 +10715,12 @@
     <row r="325">
       <c r="A325" s="1" t="inlineStr">
         <is>
-          <t>SAT</t>
+          <t>SAN</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>San Antonio, TX, United States</t>
+          <t>San Diego, CA, United States</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -10730,7 +10730,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>San Antonio, TX</t>
+          <t>San Diego, CA</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -10747,12 +10747,12 @@
     <row r="326">
       <c r="A326" s="1" t="inlineStr">
         <is>
-          <t>SAN</t>
+          <t>SFO</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>San Diego, CA, United States</t>
+          <t>San Francisco, CA, United States</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>San Diego, CA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -10779,12 +10779,12 @@
     <row r="327">
       <c r="A327" s="1" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>SJC</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>San Francisco, CA, United States</t>
+          <t>San Jose, CA, United States</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -10811,12 +10811,12 @@
     <row r="328">
       <c r="A328" s="1" t="inlineStr">
         <is>
-          <t>SJC</t>
+          <t>YXE</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>San Jose, CA, United States</t>
+          <t>Saskatoon, SK, Canada</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -10826,29 +10826,29 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>Saskatoon, SK</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="inlineStr">
         <is>
-          <t>YXE</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Saskatoon, SK, Canada</t>
+          <t>Seattle, WA, United States</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -10858,29 +10858,29 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Saskatoon, SK</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>FSD</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Seattle, WA, United States</t>
+          <t>Sioux Falls, SD, United States</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -10890,7 +10890,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Sioux Falls, SD</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -10907,12 +10907,12 @@
     <row r="331">
       <c r="A331" s="1" t="inlineStr">
         <is>
-          <t>FSD</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, United States</t>
+          <t>St. Louis, MO, United States</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -10922,7 +10922,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD</t>
+          <t>St. Louis, MO</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -10939,12 +10939,12 @@
     <row r="332">
       <c r="A332" s="1" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>TLH</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>St. Louis, MO, United States</t>
+          <t>Tallahassee, FL, United States</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -10954,7 +10954,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>St. Louis, MO</t>
+          <t>Tallahassee, FL</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -10971,12 +10971,12 @@
     <row r="333">
       <c r="A333" s="1" t="inlineStr">
         <is>
-          <t>TLH</t>
+          <t>TPA</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, United States</t>
+          <t>Tampa, FL, United States</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -10986,7 +10986,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Tallahassee, FL</t>
+          <t>Tampa, FL</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -11003,12 +11003,12 @@
     <row r="334">
       <c r="A334" s="1" t="inlineStr">
         <is>
-          <t>TPA</t>
+          <t>YYZ</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Tampa, FL, United States</t>
+          <t>Toronto, ON, Canada</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -11018,29 +11018,29 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Tampa, FL</t>
+          <t>Toronto, ON</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="inlineStr">
         <is>
-          <t>YYZ</t>
+          <t>YVR</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Toronto, ON, Canada</t>
+          <t>Vancouver, BC, Canada</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -11050,7 +11050,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Toronto, ON</t>
+          <t>Vancouver, BC</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -11067,12 +11067,12 @@
     <row r="336">
       <c r="A336" s="1" t="inlineStr">
         <is>
-          <t>YVR</t>
+          <t>YWG</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Vancouver, BC, Canada</t>
+          <t>Winnipeg, MB, Canada</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Vancouver, BC</t>
+          <t>Winnipeg, MB</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -11099,12 +11099,12 @@
     <row r="337">
       <c r="A337" s="1" t="inlineStr">
         <is>
-          <t>YWG</t>
+          <t>CVG</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Winnipeg, MB, Canada</t>
+          <t>Cincinnati, United States</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -11114,47 +11114,15 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Winnipeg, MB</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" s="1" t="inlineStr">
-        <is>
-          <t>CVG</t>
-        </is>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>Cincinnati, United States</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>North America</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>Cincinnati</t>
-        </is>
-      </c>
-      <c r="E338" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="F338" t="inlineStr">
         <is>
           <t>US</t>
         </is>
